--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>summerchristiee4</t>
+          <t>zimchi_meal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -476,49 +476,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-27 09:41:58</t>
+          <t>2026-08-29 11:45:09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@summerchristiee4</t>
+          <t>https://www.tiktok.com/@zimchi_meal</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zimchi_meal</t>
+          <t>tofanirina</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,108 +528,108 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-29 11:45:09</t>
+          <t>2026-09-12 19:42:02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zimchi_meal</t>
+          <t>https://www.tiktok.com/@tofanirina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>christinatmitsi</t>
+          <t>midlifehiddengems</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>250K-500K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-09 20:51:02</t>
+          <t>2026-09-04 22:30:55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@christinatmitsi</t>
+          <t>https://www.tiktok.com/@midlifehiddengems</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>midlifehiddengems</t>
+          <t>queennorxy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30:55</t>
+          <t>2026-08-31 11:31:09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@midlifehiddengems</t>
+          <t>https://www.tiktok.com/@queennorxy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>queennorxy</t>
+          <t>bilqeesajokeade</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -654,17 +654,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-31 11:31:09</t>
+          <t>2026-09-04 06:06:55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queennorxy</t>
+          <t>https://www.tiktok.com/@bilqeesajokeade</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>muhammadbilal_23</t>
+          <t>bam.bam5870</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -765,39 +765,39 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-02 11:44:03</t>
+          <t>2026-08-31 11:39:10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@muhammadbilal_23</t>
+          <t>https://www.tiktok.com/@bam.bam5870</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bam.bam5870</t>
+          <t>phil_becs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -807,39 +807,39 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-31 11:39:10</t>
+          <t>2026-08-31 11:42:09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bam.bam5870</t>
+          <t>https://www.tiktok.com/@phil_becs</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>phil_becs</t>
+          <t>kelliebelchamber</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -864,24 +864,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-31 11:42:09</t>
+          <t>2026-09-02 18:19:02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@phil_becs</t>
+          <t>https://www.tiktok.com/@kelliebelchamber</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kelliebelchamber</t>
+          <t>sh28___</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -891,39 +891,39 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>100K-250K</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-02 18:19:02</t>
+          <t>2026-08-31 11:57:09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kelliebelchamber</t>
+          <t>https://www.tiktok.com/@sh28___</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sh28___</t>
+          <t>cornelia.tik.tokshop</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -943,22 +943,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-31 11:57:09</t>
+          <t>2026-09-02 11:49:04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sh28___</t>
+          <t>https://www.tiktok.com/@cornelia.tik.tokshop</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1133,7 +1133,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cornelia.tik.tokshop</t>
+          <t>blondie19834</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1158,24 +1158,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-02 11:49:04</t>
+          <t>2026-09-01 09:33:03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cornelia.tik.tokshop</t>
+          <t>https://www.tiktok.com/@blondie19834</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kingdom.wins</t>
+          <t>amb3rin0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1200,24 +1200,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-02 18:11:02</t>
+          <t>2026-09-01 09:36:02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kingdom.wins</t>
+          <t>https://www.tiktok.com/@amb3rin0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>blondie19834</t>
+          <t>emma1503021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1242,34 +1242,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-01 09:33:03</t>
+          <t>2026-09-01 09:39:02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blondie19834</t>
+          <t>https://www.tiktok.com/@emma1503021</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>amb3rin0</t>
+          <t>lottieeve5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1284,34 +1284,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-01 09:36:02</t>
+          <t>2026-09-01 10:59:04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amb3rin0</t>
+          <t>https://www.tiktok.com/@lottieeve5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>emma1503021</t>
+          <t>hirahannan_official</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>250K-500K</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1326,29 +1326,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-01 09:39:02</t>
+          <t>2026-08-29 11:13:09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emma1503021</t>
+          <t>https://www.tiktok.com/@hirahannan_official</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>lottieeve5</t>
+          <t>kim.foster1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1368,49 +1368,49 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-01 10:59:04</t>
+          <t>2026-09-01 11:08:04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lottieeve5</t>
+          <t>https://www.tiktok.com/@kim.foster1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hirahannan_official</t>
+          <t>blondielovinglife</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>250K-500K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Moringa Capsules By</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-29 11:13:09</t>
+          <t>2026-09-01 11:35:02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1420,29 +1420,29 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hirahannan_official</t>
+          <t>https://www.tiktok.com/@blondielovinglife</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kim.foster1</t>
+          <t>tammyleek24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1452,34 +1452,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-01 11:08:04</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kim.foster1</t>
+          <t>https://www.tiktok.com/@tammyleek24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>blondielovinglife</t>
+          <t>leahswarbrick0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1494,34 +1494,34 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-09-01 11:35:03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blondielovinglife</t>
+          <t>https://www.tiktok.com/@leahswarbrick0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>domddo</t>
+          <t>wildwilkinsonsxx</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 11:26:03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@domddo</t>
+          <t>https://www.tiktok.com/@wildwilkinsonsxx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tammyleek24</t>
+          <t>ella.jaynefit</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1578,24 +1578,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tammyleek24</t>
+          <t>https://www.tiktok.com/@ella.jaynefit</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>leahswarbrick0</t>
+          <t>ambslouise99</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1610,34 +1610,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Moringa Capsules By</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:03</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@leahswarbrick0</t>
+          <t>https://www.tiktok.com/@ambslouise99</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>wildwilkinsonsxx</t>
+          <t>teheamyytehe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1662,24 +1662,24 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wildwilkinsonsxx</t>
+          <t>https://www.tiktok.com/@teheamyytehe</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ella.jaynefit</t>
+          <t>isloo7</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1704,24 +1704,24 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-09-02 18:18:02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ella.jaynefit</t>
+          <t>https://www.tiktok.com/@isloo7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ambslouise99</t>
+          <t>vonni349</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1741,29 +1741,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ambslouise99</t>
+          <t>https://www.tiktok.com/@vonni349</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>teheamyytehe</t>
+          <t>uncutwithice</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1788,24 +1788,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-09-12 12:02:03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teheamyytehe</t>
+          <t>https://www.tiktok.com/@uncutwithice</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>jazzzyjay360</t>
+          <t>sonix_luv</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1830,24 +1830,24 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:02</t>
+          <t>2026-09-01 10:35:21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jazzzyjay360</t>
+          <t>https://www.tiktok.com/@sonix_luv</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>isloo7</t>
+          <t>bellavidafacial</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1872,39 +1872,31 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-02 18:18:02</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@isloo7</t>
+          <t>https://www.tiktok.com/@bellavidafacial</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>vonni349</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>darkness10145</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1914,39 +1906,31 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-09-01 19:15:07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vonni349</t>
+          <t>https://www.tiktok.com/@darkness10145</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sonix_luv</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>courageous527</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1956,36 +1940,28 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-01 10:35:21</t>
+          <t>2026-09-11 19:24:33</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sonix_luv</t>
+          <t>https://www.tiktok.com/@courageous527</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bellavidafacial</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>50K-100K</t>
-        </is>
-      </c>
+          <t>dailygooods</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -1998,7 +1974,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-04 08:44:02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2008,55 +1984,55 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bellavidafacial</t>
+          <t>https://www.tiktok.com/@dailygooods</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>be__beauty1</t>
+          <t>dabrat1138</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-08 17:18:23</t>
+          <t>2026-09-10 01:03:04</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@be__beauty1</t>
+          <t>https://www.tiktok.com/@dabrat1138</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>akuapapabi364</t>
+          <t>craftyjo72</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2066,31 +2042,31 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-30 17:55:54</t>
+          <t>2026-09-08 10:27:04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akuapapabi364</t>
+          <t>https://www.tiktok.com/@craftyjo72</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>abenaduncan1</t>
+          <t>bellasbeauty07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2100,70 +2076,62 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-28 12:54:46</t>
+          <t>2026-09-08 10:16:05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abenaduncan1</t>
+          <t>https://www.tiktok.com/@bellasbeauty07</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>barbaraasiedu771</t>
+          <t>bisbis046</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-09 21:11:27</t>
+          <t>2026-09-03 09:57:56</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@barbaraasiedu771</t>
+          <t>https://www.tiktok.com/@bisbis046</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>banksofmay</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>annie.mahn</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2176,28 +2144,36 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-29 18:39:38</t>
+          <t>2026-08-30 18:11:22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@banksofmay</t>
+          <t>https://www.tiktok.com/@annie.mahn</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>annie.mahn</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
+          <t>banksofmay</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2210,36 +2186,28 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-30 18:11:22</t>
+          <t>2026-08-29 18:39:38</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@annie.mahn</t>
+          <t>https://www.tiktok.com/@banksofmay</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>amykirks.1</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>barbaraasiedu771</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2252,107 +2220,95 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-09-09 21:11:27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amykirks.1</t>
+          <t>https://www.tiktok.com/@barbaraasiedu771</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>anila_pk_uk</t>
+          <t>be__beauty1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-08 14:43:04</t>
+          <t>2026-09-08 17:18:23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@anila_pk_uk</t>
+          <t>https://www.tiktok.com/@be__beauty1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>amyhart2323</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>beauty_by_ash_attire</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-09-02 16:24:16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amyhart2323</t>
+          <t>https://www.tiktok.com/@beauty_by_ash_attire</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>akiatuconteh</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>beebee9537</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
@@ -2366,24 +2322,24 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-09 07:32:58</t>
+          <t>2026-08-30 13:59:25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akiatuconteh</t>
+          <t>https://www.tiktok.com/@beebee9537</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>erico2006</t>
+          <t>akiatuconteh</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2391,11 +2347,7 @@
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2408,24 +2360,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-01 22:26:53</t>
+          <t>2026-09-09 07:32:58</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@erico2006</t>
+          <t>https://www.tiktok.com/@akiatuconteh</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ennyluv76</t>
+          <t>abeehaamir24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2442,24 +2394,24 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-30 08:31:46</t>
+          <t>2026-08-30 10:05:16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ennyluv76</t>
+          <t>https://www.tiktok.com/@abeehaamir24</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>eni_folabi</t>
+          <t>akuapapabi364</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2476,28 +2428,36 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-09 11:38:46</t>
+          <t>2026-08-30 17:55:54</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eni_folabi</t>
+          <t>https://www.tiktok.com/@akuapapabi364</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>elizabetho001</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
+          <t>amykirks.1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2510,31 +2470,31 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-08 17:27:54</t>
+          <t>2026-09-01 11:26:03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elizabetho001</t>
+          <t>https://www.tiktok.com/@amykirks.1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>debrazerf</t>
+          <t>anila_pk_uk</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2544,24 +2504,24 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-27 19:29:33</t>
+          <t>2026-09-08 14:43:04</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@debrazerf</t>
+          <t>https://www.tiktok.com/@anila_pk_uk</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>deckynla</t>
+          <t>clare.w4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2578,24 +2538,24 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-09 11:52:15</t>
+          <t>2026-09-10 14:06:31</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@deckynla</t>
+          <t>https://www.tiktok.com/@clare.w4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>designer_suits</t>
+          <t>chlo._evans</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2603,44 +2563,56 @@
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-31 19:59:15</t>
+          <t>2026-08-31 11:52:47</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@designer_suits</t>
+          <t>https://www.tiktok.com/@chlo._evans</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>dlp7831</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
+          <t>clairegriff0</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2650,28 +2622,36 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-28 08:11:22</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dlp7831</t>
+          <t>https://www.tiktok.com/@clairegriff0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>david.adetokunbo2</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
+          <t>hannahtigg1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2684,31 +2664,31 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-26 22:15:55</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@david.adetokunbo2</t>
+          <t>https://www.tiktok.com/@hannahtigg1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>darkness10145</t>
+          <t>greenfields24</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2718,24 +2698,24 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-01 19:15:07</t>
+          <t>2026-09-08 10:27:05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@darkness10145</t>
+          <t>https://www.tiktok.com/@greenfields24</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>daliayasmin77</t>
+          <t>gl80.31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2752,24 +2732,24 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-27 22:31:42</t>
+          <t>2026-09-10 23:30:20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@daliayasmin77</t>
+          <t>https://www.tiktok.com/@gl80.31</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>dailygooods</t>
+          <t>helenbest0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2781,44 +2761,36 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:02</t>
+          <t>2026-08-31 06:52:19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailygooods</t>
+          <t>https://www.tiktok.com/@helenbest0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>clairegriff0</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>eni_folabi</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2828,24 +2800,24 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-09 11:38:46</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairegriff0</t>
+          <t>https://www.tiktok.com/@eni_folabi</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>claraeg01</t>
+          <t>ennyluv76</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2862,65 +2834,65 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-28 08:29:29</t>
+          <t>2026-08-30 08:31:46</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@claraeg01</t>
+          <t>https://www.tiktok.com/@ennyluv76</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>cocoleta7</t>
+          <t>finda9095</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-27 06:32:26</t>
+          <t>2026-09-01 13:23:27</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cocoleta7</t>
+          <t>https://www.tiktok.com/@finda9095</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>craftyjo72</t>
+          <t>elizabetho001</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2930,28 +2902,36 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:04</t>
+          <t>2026-09-08 17:27:54</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@craftyjo72</t>
+          <t>https://www.tiktok.com/@elizabetho001</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>beauty_by_ash_attire</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
+          <t>katiewanderlust</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -2959,36 +2939,36 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-02 16:24:16</t>
+          <t>2026-09-01 12:14:02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty_by_ash_attire</t>
+          <t>https://www.tiktok.com/@katiewanderlust</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>bellasbeauty07</t>
+          <t>k.tee146</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2998,92 +2978,92 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-08 10:16:05</t>
+          <t>2026-09-10 09:41:07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bellasbeauty07</t>
+          <t>https://www.tiktok.com/@k.tee146</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bisbis046</t>
+          <t>itsneema5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-03 09:57:56</t>
+          <t>2026-08-31 16:27:16</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bisbis046</t>
+          <t>https://www.tiktok.com/@itsneema5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>bilqeesajokeade</t>
+          <t>is.colonel</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-04 06:06:55</t>
+          <t>2026-09-05 23:55:02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bilqeesajokeade</t>
+          <t>https://www.tiktok.com/@is.colonel</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>chlo._evans</t>
+          <t>ijvpeanuts</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3093,39 +3073,39 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-31 11:52:47</t>
+          <t>2026-09-01 10:35:04</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chlo._evans</t>
+          <t>https://www.tiktok.com/@ijvpeanuts</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>beebee9537</t>
+          <t>kayyu247</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3142,65 +3122,65 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-30 13:59:25</t>
+          <t>2026-09-09 09:42:51</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beebee9537</t>
+          <t>https://www.tiktok.com/@kayyu247</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>abeehaamir24</t>
+          <t>kaymama31</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-30 10:05:16</t>
+          <t>2026-08-30 10:22:50</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abeehaamir24</t>
+          <t>https://www.tiktok.com/@kaymama31</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>healthyageinghq</t>
+          <t>kennybabe692</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3210,24 +3190,24 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:05</t>
+          <t>2026-09-10 11:43:02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@healthyageinghq</t>
+          <t>https://www.tiktok.com/@kennybabe692</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>iamgawjus</t>
+          <t>kofoworola2853</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3244,28 +3224,36 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-31 22:07:29</t>
+          <t>2026-09-11 10:52:59</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iamgawjus</t>
+          <t>https://www.tiktok.com/@kofoworola2853</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>hrahmancookings</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
+          <t>kiesha11matthews</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3278,24 +3266,24 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-08 19:45:29</t>
+          <t>2026-09-01 11:35:02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hrahmancookings</t>
+          <t>https://www.tiktok.com/@kiesha11matthews</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>homewithlauren_</t>
+          <t>laurenandsophiesjigglejo</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3312,31 +3300,31 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:03</t>
+          <t>2026-09-03 10:12:08</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@homewithlauren_</t>
+          <t>https://www.tiktok.com/@laurenandsophiesjigglejo</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>heyuser060</t>
+          <t>lady_dash07</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3346,24 +3334,24 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:20</t>
+          <t>2026-09-05 21:11:23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@heyuser060</t>
+          <t>https://www.tiktok.com/@lady_dash07</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>hannahtigg1</t>
+          <t>lifeofladyluna</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3373,7 +3361,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3388,24 +3376,24 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-01 11:26:02</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hannahtigg1</t>
+          <t>https://www.tiktok.com/@lifeofladyluna</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>hamidaahmed028</t>
+          <t>lifesabeach83</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3417,29 +3405,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-27 22:12:14</t>
+          <t>2026-09-01 16:37:08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hamidaahmed028</t>
+          <t>https://www.tiktok.com/@lifesabeach83</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>helenbest0</t>
+          <t>louisahusseymenopauseugc</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3456,24 +3444,24 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-31 06:52:19</t>
+          <t>2026-09-09 08:25:02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@helenbest0</t>
+          <t>https://www.tiktok.com/@louisahusseymenopauseugc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>famidak1</t>
+          <t>kay.h0</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3490,36 +3478,28 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-27 15:54:45</t>
+          <t>2026-09-09 04:27:35</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@famidak1</t>
+          <t>https://www.tiktok.com/@kay.h0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kiesha11matthews</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>lovemystarsign</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3527,101 +3507,117 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-09-01 18:46:55</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kiesha11matthews</t>
+          <t>https://www.tiktok.com/@lovemystarsign</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kay.h0</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
+          <t>lydiaburnettxx</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>25K-50K</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-09 04:27:35</t>
+          <t>2026-09-01 11:46:02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kay.h0</t>
+          <t>https://www.tiktok.com/@lydiaburnettxx</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kaymama31</t>
+          <t>macouly1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-30 10:22:50</t>
+          <t>2026-08-29 10:33:10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaymama31</t>
+          <t>https://www.tiktok.com/@macouly1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kayyu247</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
+          <t>mabes746</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3634,24 +3630,24 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-09 09:42:51</t>
+          <t>2026-09-01 11:35:04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kayyu247</t>
+          <t>https://www.tiktok.com/@mabes746</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>laurenandsophiesjigglejo</t>
+          <t>heyuser060</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3663,29 +3659,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:08</t>
+          <t>2026-09-01 17:21:20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@laurenandsophiesjigglejo</t>
+          <t>https://www.tiktok.com/@heyuser060</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>lexysluxurytravel</t>
+          <t>homewithlauren_</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3702,41 +3698,41 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-27 13:48:00</t>
+          <t>2026-09-03 10:12:03</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lexysluxurytravel</t>
+          <t>https://www.tiktok.com/@homewithlauren_</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>lady_dash07</t>
+          <t>hrahmancookings</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-05 21:11:23</t>
+          <t>2026-09-08 19:45:29</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3746,21 +3742,21 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lady_dash07</t>
+          <t>https://www.tiktok.com/@hrahmancookings</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>lady.p3600</t>
+          <t>healthyageinghq</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3770,24 +3766,24 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-26 15:34:27</t>
+          <t>2026-09-08 10:27:05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lady.p3600</t>
+          <t>https://www.tiktok.com/@healthyageinghq</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>louisahusseymenopauseugc</t>
+          <t>i.couldnt.give.a.fuckkkk</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3799,12 +3795,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-09 08:25:02</t>
+          <t>2026-09-12 11:58:47</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3814,14 +3810,14 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@louisahusseymenopauseugc</t>
+          <t>https://www.tiktok.com/@i.couldnt.give.a.fuckkkk</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>lovemystarsign</t>
+          <t>iamgawjus</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3833,29 +3829,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-01 18:46:55</t>
+          <t>2026-08-31 22:07:29</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lovemystarsign</t>
+          <t>https://www.tiktok.com/@iamgawjus</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>lydiaburnettxx</t>
+          <t>irrelevantlyliving</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3865,12 +3861,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3880,24 +3876,24 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-01 11:35:03</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lydiaburnettxx</t>
+          <t>https://www.tiktok.com/@irrelevantlyliving</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mabes746</t>
+          <t>erico2006</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3922,24 +3918,24 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:04</t>
+          <t>2026-09-01 22:26:53</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mabes746</t>
+          <t>https://www.tiktok.com/@erico2006</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>macouly1</t>
+          <t>fissysbakestudio</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3956,24 +3952,24 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-29 10:33:10</t>
+          <t>2026-08-31 21:21:04</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@macouly1</t>
+          <t>https://www.tiktok.com/@fissysbakestudio</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>maisiefinds0</t>
+          <t>elizabethj27</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3985,29 +3981,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-09-10 23:49:16</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maisiefinds0</t>
+          <t>https://www.tiktok.com/@elizabethj27</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>lifeofladyluna</t>
+          <t>designer_suits</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4015,11 +4011,7 @@
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4032,24 +4024,24 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-08-31 19:59:15</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeofladyluna</t>
+          <t>https://www.tiktok.com/@designer_suits</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>lifesabeach83</t>
+          <t>deckynla</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -4061,63 +4053,71 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-01 16:37:08</t>
+          <t>2026-09-09 11:52:15</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifesabeach83</t>
+          <t>https://www.tiktok.com/@deckynla</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mamarie146</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
+          <t>nathenjump</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-01 12:24:32</t>
+          <t>2026-09-01 14:09:02</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mamarie146</t>
+          <t>https://www.tiktok.com/@nathenjump</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mamacassyxo</t>
+          <t>nasirpatel690</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4134,24 +4134,24 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-27 16:05:15</t>
+          <t>2026-08-29 00:44:35</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mamacassyxo</t>
+          <t>https://www.tiktok.com/@nasirpatel690</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>martigergeraldine</t>
+          <t>mz.jada0</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4168,24 +4168,24 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-31 11:05:55</t>
+          <t>2026-09-07 21:15:37</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@martigergeraldine</t>
+          <t>https://www.tiktok.com/@mz.jada0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mandoki72</t>
+          <t>muhammadsha110</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4202,24 +4202,24 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-26 21:17:58</t>
+          <t>2026-09-11 15:36:47</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mandoki72</t>
+          <t>https://www.tiktok.com/@muhammadsha110</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>maxmeritbackup</t>
+          <t>moon19867</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4236,73 +4236,65 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-01 08:15:09</t>
+          <t>2026-09-11 19:21:54</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maxmeritbackup</t>
+          <t>https://www.tiktok.com/@moon19867</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>is.colonel</t>
+          <t>moon.x280</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-05 23:55:02</t>
+          <t>2026-09-01 18:11:41</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@is.colonel</t>
+          <t>https://www.tiktok.com/@moon.x280</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ijvpeanuts</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>monpakhi_202</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4312,24 +4304,24 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-01 10:35:04</t>
+          <t>2026-08-31 21:10:55</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ijvpeanuts</t>
+          <t>https://www.tiktok.com/@monpakhi_202</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>invalid58</t>
+          <t>maxmeritbackup</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4346,31 +4338,31 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-28 17:24:16</t>
+          <t>2026-09-01 08:15:09</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@invalid58</t>
+          <t>https://www.tiktok.com/@maxmeritbackup</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>jaofficial10</t>
+          <t>maisiefinds0</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4380,24 +4372,24 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-28 11:15:31</t>
+          <t>2026-09-04 08:44:04</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jaofficial10</t>
+          <t>https://www.tiktok.com/@maisiefinds0</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>itsneema5</t>
+          <t>martigergeraldine</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4414,39 +4406,31 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-31 16:27:16</t>
+          <t>2026-08-31 11:05:55</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsneema5</t>
+          <t>https://www.tiktok.com/@martigergeraldine</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>irrelevantlyliving</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>markh_8</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4456,36 +4440,28 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:03</t>
+          <t>2026-09-09 16:07:49</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@irrelevantlyliving</t>
+          <t>https://www.tiktok.com/@markh_8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>katiewanderlust</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>mamarie146</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -4493,36 +4469,36 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:02</t>
+          <t>2026-09-01 12:24:32</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katiewanderlust</t>
+          <t>https://www.tiktok.com/@mamarie146</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>fissysbakestudio</t>
+          <t>nutster58</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4532,36 +4508,36 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-31 21:21:04</t>
+          <t>2026-09-01 08:36:44</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fissysbakestudio</t>
+          <t>https://www.tiktok.com/@nutster58</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>greenfields24</t>
+          <t>nwabkhan760</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4571,53 +4547,53 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@greenfields24</t>
+          <t>https://www.tiktok.com/@nwabkhan760</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>finda9095</t>
+          <t>nellyedwin54</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-01 13:23:27</t>
+          <t>2026-08-30 13:16:24</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@finda9095</t>
+          <t>https://www.tiktok.com/@nellyedwin54</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>fffysigs0719</t>
+          <t>nikkigossal29</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4634,7 +4610,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-27 16:41:03</t>
+          <t>2026-08-30 17:46:28</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4644,48 +4620,48 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fffysigs0719</t>
+          <t>https://www.tiktok.com/@nikkigossal29</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>notlikeeveryday</t>
+          <t>remeradiance</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-09-04 19:49:19</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@notlikeeveryday</t>
+          <t>https://www.tiktok.com/@remeradiance</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>niknak190725</t>
+          <t>redbloodchurch1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4695,12 +4671,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4710,24 +4686,24 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:04</t>
+          <t>2026-08-29 15:02:18</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@niknak190725</t>
+          <t>https://www.tiktok.com/@redbloodchurch1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>nikkigossal29</t>
+          <t>saadia7166</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4744,24 +4720,24 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-30 17:46:28</t>
+          <t>2026-09-10 11:16:51</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nikkigossal29</t>
+          <t>https://www.tiktok.com/@saadia7166</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>nellyedwin54</t>
+          <t>rkh250496ad</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4778,36 +4754,28 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-30 13:16:24</t>
+          <t>2026-08-31 17:54:22</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nellyedwin54</t>
+          <t>https://www.tiktok.com/@rkh250496ad</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>nathenjump</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>samirakarim24</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4820,31 +4788,39 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-01 14:09:02</t>
+          <t>2026-09-11 11:10:48</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nathenjump</t>
+          <t>https://www.tiktok.com/@samirakarim24</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>nasirpatel690</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr"/>
+          <t>sarah565556</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4854,7 +4830,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-29 00:44:35</t>
+          <t>2026-09-01 12:03:02</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4864,21 +4840,21 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nasirpatel690</t>
+          <t>https://www.tiktok.com/@sarah565556</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>mz.jada0</t>
+          <t>seana_montgomery61</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4888,24 +4864,24 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-07 21:15:37</t>
+          <t>2026-09-03 10:12:09</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mz.jada0</t>
+          <t>https://www.tiktok.com/@seana_montgomery61</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>moon.x280</t>
+          <t>robbomsnvfv</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4922,24 +4898,24 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-01 18:11:41</t>
+          <t>2026-09-01 12:37:06</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moon.x280</t>
+          <t>https://www.tiktok.com/@robbomsnvfv</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>markh_8</t>
+          <t>ornellabeauty25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4956,31 +4932,39 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-09 16:07:49</t>
+          <t>2026-09-07 22:41:47</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@markh_8</t>
+          <t>https://www.tiktok.com/@ornellabeauty25</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>monpakhi_202</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
+          <t>olascornerpage</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4990,31 +4974,39 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-31 21:10:55</t>
+          <t>2026-09-12 21:52:02</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@monpakhi_202</t>
+          <t>https://www.tiktok.com/@olascornerpage</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>missberry.kayamatauk</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
+          <t>princess_wumi</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5024,7 +5016,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-26 13:15:36</t>
+          <t>2026-08-29 08:38:03</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5034,26 +5026,18 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@missberry.kayamatauk</t>
+          <t>https://www.tiktok.com/@princess_wumi</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>princess_wumi</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>oyetunji.sunday</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5066,24 +5050,24 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-29 08:38:03</t>
+          <t>2026-09-12 13:08:25</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princess_wumi</t>
+          <t>https://www.tiktok.com/@oyetunji.sunday</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ovwomani22</t>
+          <t>queen.of.boys42</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5100,24 +5084,24 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-28 18:04:58</t>
+          <t>2026-08-29 18:27:02</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ovwomani22</t>
+          <t>https://www.tiktok.com/@queen.of.boys42</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>pm37896</t>
+          <t>rabiaaman21</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5134,31 +5118,39 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-28 00:17:19</t>
+          <t>2026-09-01 14:27:46</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pm37896</t>
+          <t>https://www.tiktok.com/@rabiaaman21</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ornellabeauty25</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr"/>
+          <t>niknak190725</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5168,31 +5160,31 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-07 22:41:47</t>
+          <t>2026-09-01 12:14:04</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ornellabeauty25</t>
+          <t>https://www.tiktok.com/@niknak190725</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>nutster58</t>
+          <t>notlikeeveryday</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5202,7 +5194,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-01 08:36:44</t>
+          <t>2026-09-04 08:44:04</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5212,18 +5204,26 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nutster58</t>
+          <t>https://www.tiktok.com/@notlikeeveryday</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rkh250496ad</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr"/>
+          <t>skyviewbm</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D129" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5236,65 +5236,65 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-31 17:54:22</t>
+          <t>2026-08-30 16:29:14</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rkh250496ad</t>
+          <t>https://www.tiktok.com/@skyviewbm</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>remeradiance</t>
+          <t>sjahan83</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-04 19:49:19</t>
+          <t>2026-09-12 13:46:48</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@remeradiance</t>
+          <t>https://www.tiktok.com/@sjahan83</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>seana_montgomery61</t>
+          <t>shume.begum8</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5304,24 +5304,24 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:09</t>
+          <t>2026-09-01 20:33:17</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seana_montgomery61</t>
+          <t>https://www.tiktok.com/@shume.begum8</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>robbomsnvfv</t>
+          <t>shoni1984</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5333,29 +5333,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-01 12:37:06</t>
+          <t>2026-09-10 08:20:01</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@robbomsnvfv</t>
+          <t>https://www.tiktok.com/@shoni1984</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>sexybaby7657</t>
+          <t>sharansaleem</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5372,24 +5372,24 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-09 21:00:27</t>
+          <t>2026-08-29 11:45:48</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sexybaby7657</t>
+          <t>https://www.tiktok.com/@sharansaleem</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>shahzad.akram041</t>
+          <t>shezha17</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5401,78 +5401,70 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-03 04:27:22</t>
+          <t>2026-09-01 09:35:01</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shahzad.akram041</t>
+          <t>https://www.tiktok.com/@shezha17</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>shakirakhan296</t>
+          <t>shahzad.akram041</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-28 23:38:18</t>
+          <t>2026-09-03 04:27:22</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shakirakhan296</t>
+          <t>https://www.tiktok.com/@shahzad.akram041</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>sarah565556</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>sexybaby7657</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5482,24 +5474,24 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-09 21:00:27</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarah565556</t>
+          <t>https://www.tiktok.com/@sexybaby7657</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>sharansaleem</t>
+          <t>themamadee</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5516,31 +5508,27 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-29 11:45:48</t>
+          <t>2026-09-10 19:23:49</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sharansaleem</t>
+          <t>https://www.tiktok.com/@themamadee</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>princesslizy2010</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>tee_y.x</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
@@ -5554,75 +5542,75 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-26 20:03:55</t>
+          <t>2026-08-31 00:32:51</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princesslizy2010</t>
+          <t>https://www.tiktok.com/@tee_y.x</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>pubby1amob</t>
+          <t>sweetshez1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-27 18:28:59</t>
+          <t>2026-09-05 18:50:17</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pubby1amob</t>
+          <t>https://www.tiktok.com/@sweetshez1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>queen.of.boys42</t>
+          <t>thestoicphoenix</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-29 18:27:02</t>
+          <t>2026-09-01 12:03:16</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5632,14 +5620,14 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queen.of.boys42</t>
+          <t>https://www.tiktok.com/@thestoicphoenix</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>rabiaaman21</t>
+          <t>trending_gists_omoola</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5656,36 +5644,28 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:46</t>
+          <t>2026-08-30 21:32:52</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rabiaaman21</t>
+          <t>https://www.tiktok.com/@trending_gists_omoola</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>redbloodchurch1</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>syrashid</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5698,24 +5678,24 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-29 15:02:18</t>
+          <t>2026-09-11 12:35:39</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@redbloodchurch1</t>
+          <t>https://www.tiktok.com/@syrashid</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>primefindsuk_</t>
+          <t>spyingthedeals</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -5732,31 +5712,31 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-08 10:16:05</t>
+          <t>2026-09-08 10:27:03</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@primefindsuk_</t>
+          <t>https://www.tiktok.com/@spyingthedeals</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>nwabkhan760</t>
+          <t>ste.baby6</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5766,24 +5746,24 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:05</t>
+          <t>2026-09-09 16:28:17</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nwabkhan760</t>
+          <t>https://www.tiktok.com/@ste.baby6</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ste.baby6</t>
+          <t>user13457g</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5800,28 +5780,36 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-09-09 16:28:17</t>
+          <t>2026-09-10 08:04:29</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ste.baby6</t>
+          <t>https://www.tiktok.com/@user13457g</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>spyingthedeals</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
-      <c r="C146" t="inlineStr"/>
+          <t>ugcbyshristi</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D146" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -5834,100 +5822,92 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:03</t>
+          <t>2026-09-01 12:03:03</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@spyingthedeals</t>
+          <t>https://www.tiktok.com/@ugcbyshristi</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>skyviewbm</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>turelove730</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-30 16:29:14</t>
+          <t>2026-09-01 14:36:11</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@skyviewbm</t>
+          <t>https://www.tiktok.com/@turelove730</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>shurlar347</t>
+          <t>user2922793729949</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-27 14:53:08</t>
+          <t>2026-09-01 13:14:46</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shurlar347</t>
+          <t>https://www.tiktok.com/@user2922793729949</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>shezha17</t>
+          <t>user_steeze</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -5939,29 +5919,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-09-01 09:35:01</t>
+          <t>2026-08-30 17:59:09</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shezha17</t>
+          <t>https://www.tiktok.com/@user_steeze</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>shume.begum8</t>
+          <t>vera77524</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -5978,24 +5958,24 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-01 20:33:17</t>
+          <t>2026-09-09 07:38:35</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shume.begum8</t>
+          <t>https://www.tiktok.com/@vera77524</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>sharonhiggins46</t>
+          <t>user9199380</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -6012,58 +5992,58 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-28 20:19:57</t>
+          <t>2026-09-08 15:02:55</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sharonhiggins46</t>
+          <t>https://www.tiktok.com/@user9199380</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>sweetshez1</t>
+          <t>user7271293811175</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-05 18:50:17</t>
+          <t>2026-09-11 08:42:27</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sweetshez1</t>
+          <t>https://www.tiktok.com/@user7271293811175</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>tran.le455</t>
+          <t>vivianesoizeau</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -6080,7 +6060,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-28 14:45:25</t>
+          <t>2026-08-31 16:20:27</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6090,18 +6070,26 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tran.le455</t>
+          <t>https://www.tiktok.com/@vivianesoizeau</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>trendaura47</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr"/>
-      <c r="C154" t="inlineStr"/>
+          <t>veronpoks</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D154" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6114,58 +6102,58 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-09-09 09:29:07</t>
+          <t>2026-08-30 14:08:12</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@trendaura47</t>
+          <t>https://www.tiktok.com/@veronpoks</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>trending_gists_omoola</t>
+          <t>wolfie1830</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-30 21:32:52</t>
+          <t>2026-09-01 11:52:06</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@trending_gists_omoola</t>
+          <t>https://www.tiktok.com/@wolfie1830</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>turelove730</t>
+          <t>withlakisha</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -6177,12 +6165,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-09-01 14:36:11</t>
+          <t>2026-09-04 08:44:03</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6192,26 +6180,18 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@turelove730</t>
+          <t>https://www.tiktok.com/@withlakisha</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ugcbyshristi</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>xstormx33</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -6219,29 +6199,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-09-01 10:36:21</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ugcbyshristi</t>
+          <t>https://www.tiktok.com/@xstormx33</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>sukhdeepkaur343</t>
+          <t>yxsna_98</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -6258,7 +6238,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-08-27 15:52:29</t>
+          <t>2026-08-30 12:46:22</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -6268,18 +6248,26 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sukhdeepkaur343</t>
+          <t>https://www.tiktok.com/@yxsna_98</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tee_y.x</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr"/>
-      <c r="C159" t="inlineStr"/>
+          <t>zahidaparveen624</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D159" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6292,24 +6280,24 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-08-31 00:32:51</t>
+          <t>2026-09-11 13:42:26</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tee_y.x</t>
+          <t>https://www.tiktok.com/@zahidaparveen624</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>thestoicphoenix</t>
+          <t>zubairianaz15</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -6326,567 +6314,15 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:16</t>
+          <t>2026-09-05 22:51:12</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@thestoicphoenix</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>user2922793729949</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr"/>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-09-01 13:14:46</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user2922793729949</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>user26963863682186</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr"/>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-08-27 16:29:12</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user26963863682186</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>uky1090</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr"/>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-08-28 01:37:24</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uky1090</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>user4423713561101</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr"/>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-08-28 10:55:03</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user4423713561101</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>user_steeze</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr"/>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-08-30 17:59:09</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user_steeze</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>user4961074980381</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr"/>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:55:56</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user4961074980381</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>user596114145414</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-08-28 18:57:06</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user596114145414</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>user9199380</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr"/>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-09-08 15:02:55</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user9199380</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>vivianesoizeau</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr"/>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-08-31 16:20:27</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@vivianesoizeau</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>veronpoks</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-08-30 14:08:12</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@veronpoks</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>vera77524</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr"/>
-      <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-09-09 07:38:35</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@vera77524</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>withlakisha</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr"/>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-09-04 08:44:03</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@withlakisha</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>wolfie1830</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr"/>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-09-01 11:52:06</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@wolfie1830</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>xstormx33</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr"/>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-09-01 10:36:21</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@xstormx33</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>yxsna_98</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-08-30 12:46:22</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@yxsna_98</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>zubairianaz15</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr"/>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-09-05 22:51:12</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zubairianaz15</t>
         </is>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -1778,7 +1778,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,22 +461,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>zimchi_meal</t>
+          <t>simply_unboxed</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -486,17 +486,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-29 11:45:09</t>
+          <t>2026-09-16 07:50:03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zimchi_meal</t>
+          <t>https://www.tiktok.com/@simply_unboxed</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>midlifehiddengems</t>
+          <t>iboughtyousomething</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,12 +555,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -570,81 +570,81 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30:55</t>
+          <t>2026-09-14 06:52:02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@midlifehiddengems</t>
+          <t>https://www.tiktok.com/@iboughtyousomething</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>queennorxy</t>
+          <t>reviewedbysam</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-31 11:31:09</t>
+          <t>2026-09-14 06:50:09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queennorxy</t>
+          <t>https://www.tiktok.com/@reviewedbysam</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bilqeesajokeade</t>
+          <t>martzarmy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -654,29 +654,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-04 06:06:55</t>
+          <t>2026-09-16 09:42:04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bilqeesajokeade</t>
+          <t>https://www.tiktok.com/@martzarmy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fypdavesdeals</t>
+          <t>tiktokshopadvice</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -691,39 +691,39 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-31 11:31:10</t>
+          <t>2026-09-16 09:42:04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fypdavesdeals</t>
+          <t>https://www.tiktok.com/@tiktokshopadvice</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>clairlynda.x</t>
+          <t>rk_uk3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,76 +738,76 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-02 07:40:02</t>
+          <t>2026-09-14 05:38:02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairlynda.x</t>
+          <t>https://www.tiktok.com/@rk_uk3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bam.bam5870</t>
+          <t>angelinas.finds</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-31 11:39:10</t>
+          <t>2026-09-14 05:38:02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bam.bam5870</t>
+          <t>https://www.tiktok.com/@angelinas.finds</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>phil_becs</t>
+          <t>jenna_g_tiktok</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -822,39 +822,39 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-31 11:42:09</t>
+          <t>2026-09-17 15:30:26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@phil_becs</t>
+          <t>https://www.tiktok.com/@jenna_g_tiktok</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kelliebelchamber</t>
+          <t>ziab442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -864,39 +864,39 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-02 18:19:02</t>
+          <t>2026-09-14 05:38:02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kelliebelchamber</t>
+          <t>https://www.tiktok.com/@ziab442</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sh28___</t>
+          <t>inayapicks123</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -906,24 +906,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-31 11:57:09</t>
+          <t>2026-09-14 11:03:03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sh28___</t>
+          <t>https://www.tiktok.com/@inayapicks123</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cornelia.tik.tokshop</t>
+          <t>realabdu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -948,123 +948,123 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-02 11:49:04</t>
+          <t>2026-09-14 06:36:02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cornelia.tik.tokshop</t>
+          <t>https://www.tiktok.com/@realabdu</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hayleybumpbear</t>
+          <t>eminence4009</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[] Moringa 1000mg</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-31 12:12:09</t>
+          <t>2026-09-08 10:27:05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hayleybumpbear</t>
+          <t>https://www.tiktok.com/@eminence4009</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>amy.l094</t>
+          <t>manvsparkins0n</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>250K-500K</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[] Moringa 1000mg</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-31 12:07:10</t>
+          <t>2026-09-14 06:51:02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amy.l094</t>
+          <t>https://www.tiktok.com/@manvsparkins0n</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tonks1988</t>
+          <t>uncutwithice</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1074,39 +1074,31 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-31 12:11:09</t>
+          <t>2026-09-12 12:02:03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tonks1988</t>
+          <t>https://www.tiktok.com/@uncutwithice</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>eminence4009</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>bantzuk</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1116,7 +1108,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:05</t>
+          <t>2026-09-15 11:51:02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1126,26 +1118,18 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eminence4009</t>
+          <t>https://www.tiktok.com/@bantzuk</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>blondie19834</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>badmashi.007</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -1158,36 +1142,28 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-01 09:33:03</t>
+          <t>2026-09-14 18:24:25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blondie19834</t>
+          <t>https://www.tiktok.com/@badmashi.007</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>amb3rin0</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>ali.syed873</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -1200,39 +1176,31 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-01 09:36:02</t>
+          <t>2026-09-17 03:47:33</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amb3rin0</t>
+          <t>https://www.tiktok.com/@ali.syed873</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>emma1503021</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>alemap9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1242,36 +1210,28 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-01 09:39:02</t>
+          <t>2026-09-14 00:26:00</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emma1503021</t>
+          <t>https://www.tiktok.com/@alemap9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>lottieeve5</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£200-£500</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>a13dde</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -1284,39 +1244,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-01 10:59:04</t>
+          <t>2026-09-14 08:25:14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lottieeve5</t>
+          <t>https://www.tiktok.com/@a13dde</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hirahannan_official</t>
+          <t>akiatuconteh</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£200-£500</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>250K-500K</t>
-        </is>
-      </c>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1326,39 +1282,31 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-29 11:13:09</t>
+          <t>2026-09-09 07:32:58</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hirahannan_official</t>
+          <t>https://www.tiktok.com/@akiatuconteh</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kim.foster1</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>atokeade053</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1368,78 +1316,62 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-01 11:08:04</t>
+          <t>2026-09-14 20:29:27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kim.foster1</t>
+          <t>https://www.tiktok.com/@atokeade053</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>blondielovinglife</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>anita.wils</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Moringa Capsules By</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blondielovinglife</t>
+          <t>https://www.tiktok.com/@anita.wils</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tammyleek24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>£50-£100</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>angelaugochinyere</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -1452,78 +1384,62 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-16 22:04:31</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tammyleek24</t>
+          <t>https://www.tiktok.com/@angelaugochinyere</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>leahswarbrick0</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>allthingscutziee</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Moringa Capsules By</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:03</t>
+          <t>2026-09-15 11:51:03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@leahswarbrick0</t>
+          <t>https://www.tiktok.com/@allthingscutziee</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>wildwilkinsonsxx</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>beauty20208</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -1536,36 +1452,28 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-09-18 19:31:55</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wildwilkinsonsxx</t>
+          <t>https://www.tiktok.com/@beauty20208</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ella.jaynefit</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>barbaraasiedu771</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -1578,39 +1486,31 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-09-09 21:11:27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ella.jaynefit</t>
+          <t>https://www.tiktok.com/@barbaraasiedu771</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ambslouise99</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>deckynla</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1620,39 +1520,31 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-09 11:52:15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ambslouise99</t>
+          <t>https://www.tiktok.com/@deckynla</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>teheamyytehe</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>diane.docherty</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1662,39 +1554,31 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-09-15 09:50:59</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teheamyytehe</t>
+          <t>https://www.tiktok.com/@diane.docherty</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>isloo7</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>donsnewchapter</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1704,36 +1588,28 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-02 18:18:02</t>
+          <t>2026-09-16 09:45:02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@isloo7</t>
+          <t>https://www.tiktok.com/@donsnewchapter</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>vonni349</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>dollywithplaits73</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -1746,36 +1622,28 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:03</t>
+          <t>2026-09-16 16:47:28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vonni349</t>
+          <t>https://www.tiktok.com/@dollywithplaits73</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>uncutwithice</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>dulal.miah2471</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -1788,39 +1656,31 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-12 12:02:03</t>
+          <t>2026-09-14 07:26:09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uncutwithice</t>
+          <t>https://www.tiktok.com/@dulal.miah2471</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sonix_luv</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>dy7yobwohcu6</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1830,36 +1690,28 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-01 10:35:21</t>
+          <t>2026-09-18 21:30:44</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sonix_luv</t>
+          <t>https://www.tiktok.com/@dy7yobwohcu6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bellavidafacial</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>50K-100K</t>
-        </is>
-      </c>
+          <t>elizabethj27</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -1867,29 +1719,29 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-10 23:49:16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bellavidafacial</t>
+          <t>https://www.tiktok.com/@elizabethj27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>darkness10145</t>
+          <t>drantero_10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1901,36 +1753,36 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-01 19:15:07</t>
+          <t>2026-09-17 14:48:32</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@darkness10145</t>
+          <t>https://www.tiktok.com/@drantero_10</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>courageous527</t>
+          <t>chloeeflynnx</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1940,31 +1792,31 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-11 19:24:33</t>
+          <t>2026-09-16 11:07:02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courageous527</t>
+          <t>https://www.tiktok.com/@chloeeflynnx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dailygooods</t>
+          <t>chucky692</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1974,58 +1826,58 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:02</t>
+          <t>2026-09-15 07:29:48</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailygooods</t>
+          <t>https://www.tiktok.com/@chucky692</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dabrat1138</t>
+          <t>clairedipple66</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-10 01:03:04</t>
+          <t>2026-09-16 07:44:02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dabrat1138</t>
+          <t>https://www.tiktok.com/@clairedipple66</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>craftyjo72</t>
+          <t>be__beauty1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2037,22 +1889,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:04</t>
+          <t>2026-09-08 17:18:23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@craftyjo72</t>
+          <t>https://www.tiktok.com/@be__beauty1</t>
         </is>
       </c>
     </row>
@@ -2081,7 +1933,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2093,87 +1945,79 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bisbis046</t>
+          <t>bettyaddo398</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-03 09:57:56</t>
+          <t>2026-09-14 14:52:28</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bisbis046</t>
+          <t>https://www.tiktok.com/@bettyaddo398</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>annie.mahn</t>
+          <t>bex_lifeafter40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-30 18:11:22</t>
+          <t>2026-09-17 15:30:23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@annie.mahn</t>
+          <t>https://www.tiktok.com/@bex_lifeafter40</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>banksofmay</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>beemahempire</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2186,31 +2030,31 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-29 18:39:38</t>
+          <t>2026-09-15 11:52:03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@banksofmay</t>
+          <t>https://www.tiktok.com/@beemahempire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>barbaraasiedu771</t>
+          <t>haseeb.mum</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2220,7 +2064,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-09 21:11:27</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2230,82 +2074,82 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@barbaraasiedu771</t>
+          <t>https://www.tiktok.com/@haseeb.mum</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>be__beauty1</t>
+          <t>gl80.31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-08 17:18:23</t>
+          <t>2026-09-10 23:30:20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@be__beauty1</t>
+          <t>https://www.tiktok.com/@gl80.31</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>beauty_by_ash_attire</t>
+          <t>georgiafergg</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-02 16:24:16</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty_by_ash_attire</t>
+          <t>https://www.tiktok.com/@georgiafergg</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>beebee9537</t>
+          <t>gella4573</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2322,31 +2166,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-30 13:59:25</t>
+          <t>2026-09-16 07:50:13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beebee9537</t>
+          <t>https://www.tiktok.com/@gella4573</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>akiatuconteh</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>fernandasprivy</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
@@ -2360,24 +2200,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-09 07:32:58</t>
+          <t>2026-09-15 19:00:52</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akiatuconteh</t>
+          <t>https://www.tiktok.com/@fernandasprivy</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>abeehaamir24</t>
+          <t>hrahmancookings</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2394,31 +2234,31 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-30 10:05:16</t>
+          <t>2026-09-08 19:45:29</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abeehaamir24</t>
+          <t>https://www.tiktok.com/@hrahmancookings</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>akuapapabi364</t>
+          <t>i.couldnt.give.a.fuckkkk</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2428,36 +2268,28 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-30 17:55:54</t>
+          <t>2026-09-12 11:58:47</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akuapapabi364</t>
+          <t>https://www.tiktok.com/@i.couldnt.give.a.fuckkkk</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>amykirks.1</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>hchahal80</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2470,31 +2302,31 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:03</t>
+          <t>2026-09-15 20:35:21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amykirks.1</t>
+          <t>https://www.tiktok.com/@hchahal80</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>anila_pk_uk</t>
+          <t>is.colonel</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2504,115 +2336,99 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-08 14:43:04</t>
+          <t>2026-09-05 23:55:02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@anila_pk_uk</t>
+          <t>https://www.tiktok.com/@is.colonel</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>clare.w4</t>
+          <t>janetaliciac</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-10 14:06:31</t>
+          <t>2026-09-18 18:16:03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clare.w4</t>
+          <t>https://www.tiktok.com/@janetaliciac</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>chlo._evans</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>joandusabe</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-31 11:52:47</t>
+          <t>2026-09-19 08:31:29</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chlo._evans</t>
+          <t>https://www.tiktok.com/@joandusabe</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>clairegriff0</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>julietogu5</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2622,36 +2438,28 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-14 01:42:26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairegriff0</t>
+          <t>https://www.tiktok.com/@julietogu5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>hannahtigg1</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>jxnxxkxk</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2664,58 +2472,58 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-15 12:32:04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hannahtigg1</t>
+          <t>https://www.tiktok.com/@jxnxxkxk</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>greenfields24</t>
+          <t>k.tee146</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:05</t>
+          <t>2026-09-10 09:41:07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@greenfields24</t>
+          <t>https://www.tiktok.com/@k.tee146</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>gl80.31</t>
+          <t>iqrasumman19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2732,31 +2540,31 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-10 23:30:20</t>
+          <t>2026-09-19 22:51:02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gl80.31</t>
+          <t>https://www.tiktok.com/@iqrasumman19</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>helenbest0</t>
+          <t>hinas_beauty_buys</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2766,133 +2574,133 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-31 06:52:19</t>
+          <t>2026-09-18 09:46:05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@helenbest0</t>
+          <t>https://www.tiktok.com/@hinas_beauty_buys</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>eni_folabi</t>
+          <t>kay.h0</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-09 11:38:46</t>
+          <t>2026-09-09 04:27:35</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eni_folabi</t>
+          <t>https://www.tiktok.com/@kay.h0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ennyluv76</t>
+          <t>katseyelocer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-30 08:31:46</t>
+          <t>2026-09-15 22:58:52</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ennyluv76</t>
+          <t>https://www.tiktok.com/@katseyelocer</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>finda9095</t>
+          <t>kayyu247</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-01 13:23:27</t>
+          <t>2026-09-09 09:42:51</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@finda9095</t>
+          <t>https://www.tiktok.com/@kayyu247</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>elizabetho001</t>
+          <t>keeskloset</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2902,39 +2710,31 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-08 17:27:54</t>
+          <t>2026-09-16 09:57:04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elizabetho001</t>
+          <t>https://www.tiktok.com/@keeskloset</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>katiewanderlust</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>konaduroi</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2944,58 +2744,58 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:02</t>
+          <t>2026-09-15 03:00:44</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katiewanderlust</t>
+          <t>https://www.tiktok.com/@konaduroi</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>k.tee146</t>
+          <t>lady_dash07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-10 09:41:07</t>
+          <t>2026-09-05 21:11:23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@k.tee146</t>
+          <t>https://www.tiktok.com/@lady_dash07</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>itsneema5</t>
+          <t>kennybabe692</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -3012,31 +2812,31 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-31 16:27:16</t>
+          <t>2026-09-10 11:43:02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsneema5</t>
+          <t>https://www.tiktok.com/@kennybabe692</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>is.colonel</t>
+          <t>kofoworola2853</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3046,39 +2846,31 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-05 23:55:02</t>
+          <t>2026-09-11 10:52:59</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@is.colonel</t>
+          <t>https://www.tiktok.com/@kofoworola2853</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ijvpeanuts</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>elizabetho001</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3088,7 +2880,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-01 10:35:04</t>
+          <t>2026-09-08 17:27:54</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3098,82 +2890,82 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ijvpeanuts</t>
+          <t>https://www.tiktok.com/@elizabetho001</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kayyu247</t>
+          <t>emaanttshop</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-09 09:42:51</t>
+          <t>2026-09-15 21:32:02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kayyu247</t>
+          <t>https://www.tiktok.com/@emaanttshop</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kaymama31</t>
+          <t>eni_folabi</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-30 10:22:50</t>
+          <t>2026-09-09 11:38:46</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaymama31</t>
+          <t>https://www.tiktok.com/@eni_folabi</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kennybabe692</t>
+          <t>clare.w4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3190,24 +2982,24 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-10 11:43:02</t>
+          <t>2026-09-10 14:06:31</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kennybabe692</t>
+          <t>https://www.tiktok.com/@clare.w4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kofoworola2853</t>
+          <t>courageous527</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3224,36 +3016,28 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-11 10:52:59</t>
+          <t>2026-09-11 19:24:33</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kofoworola2853</t>
+          <t>https://www.tiktok.com/@courageous527</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kiesha11matthews</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>dabrat1138</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3266,31 +3050,31 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:02</t>
+          <t>2026-09-10 01:03:04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kiesha11matthews</t>
+          <t>https://www.tiktok.com/@dabrat1138</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>laurenandsophiesjigglejo</t>
+          <t>dailymusthaves20</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3300,100 +3084,92 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:08</t>
+          <t>2026-09-19 13:38:02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@laurenandsophiesjigglejo</t>
+          <t>https://www.tiktok.com/@dailymusthaves20</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>lady_dash07</t>
+          <t>bgee2345</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-05 21:11:23</t>
+          <t>2026-09-19 22:31:01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lady_dash07</t>
+          <t>https://www.tiktok.com/@bgee2345</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>lifeofladyluna</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>mlllifestyle</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-01 11:26:02</t>
+          <t>2026-09-18 09:46:03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeofladyluna</t>
+          <t>https://www.tiktok.com/@mlllifestyle</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>lifesabeach83</t>
+          <t>missyspranno12</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3405,104 +3181,104 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-01 16:37:08</t>
+          <t>2026-09-15 13:31:44</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifesabeach83</t>
+          <t>https://www.tiktok.com/@missyspranno12</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>louisahusseymenopauseugc</t>
+          <t>mehmoonaali238</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-09 08:25:02</t>
+          <t>2026-09-17 11:42:05</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@louisahusseymenopauseugc</t>
+          <t>https://www.tiktok.com/@mehmoonaali238</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kay.h0</t>
+          <t>markh_8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-09 04:27:35</t>
+          <t>2026-09-09 16:07:49</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kay.h0</t>
+          <t>https://www.tiktok.com/@markh_8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>lovemystarsign</t>
+          <t>lucia25070</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3512,66 +3288,58 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-01 18:46:55</t>
+          <t>2026-09-18 09:46:03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lovemystarsign</t>
+          <t>https://www.tiktok.com/@lucia25070</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>lydiaburnettxx</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>25K-50K</t>
-        </is>
-      </c>
+          <t>maish1002</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:02</t>
+          <t>2026-09-19 13:31:02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lydiaburnettxx</t>
+          <t>https://www.tiktok.com/@maish1002</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>macouly1</t>
+          <t>ladydonigbinosa</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3588,36 +3356,28 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-29 10:33:10</t>
+          <t>2026-09-14 07:25:08</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@macouly1</t>
+          <t>https://www.tiktok.com/@ladydonigbinosa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mabes746</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>ladyygold1</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3630,92 +3390,100 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:04</t>
+          <t>2026-09-16 09:45:05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mabes746</t>
+          <t>https://www.tiktok.com/@ladyygold1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>heyuser060</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
+          <t>olascornerpage</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:20</t>
+          <t>2026-09-12 21:52:02</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@heyuser060</t>
+          <t>https://www.tiktok.com/@olascornerpage</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>homewithlauren_</t>
+          <t>oluwatoyosiabayom</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:03</t>
+          <t>2026-09-14 17:04:02</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@homewithlauren_</t>
+          <t>https://www.tiktok.com/@oluwatoyosiabayom</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>hrahmancookings</t>
+          <t>omolade.abebi</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3732,31 +3500,31 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-08 19:45:29</t>
+          <t>2026-09-17 10:33:35</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hrahmancookings</t>
+          <t>https://www.tiktok.com/@omolade.abebi</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>healthyageinghq</t>
+          <t>monicalavern</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3766,7 +3534,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:05</t>
+          <t>2026-09-15 13:00:13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3776,21 +3544,21 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@healthyageinghq</t>
+          <t>https://www.tiktok.com/@monicalavern</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>i.couldnt.give.a.fuckkkk</t>
+          <t>mz.jada0</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3800,24 +3568,24 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-12 11:58:47</t>
+          <t>2026-09-07 21:15:37</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@i.couldnt.give.a.fuckkkk</t>
+          <t>https://www.tiktok.com/@mz.jada0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>iamgawjus</t>
+          <t>moon19867</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3834,39 +3602,31 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-31 22:07:29</t>
+          <t>2026-09-11 19:21:54</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iamgawjus</t>
+          <t>https://www.tiktok.com/@moon19867</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>irrelevantlyliving</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>muhammadsha110</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3876,36 +3636,28 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-01 11:35:03</t>
+          <t>2026-09-11 15:36:47</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@irrelevantlyliving</t>
+          <t>https://www.tiktok.com/@muhammadsha110</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>erico2006</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>mymojomindset</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3918,31 +3670,31 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-01 22:26:53</t>
+          <t>2026-09-15 10:29:05</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@erico2006</t>
+          <t>https://www.tiktok.com/@mymojomindset</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>fissysbakestudio</t>
+          <t>positiveproductsuk</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3952,24 +3704,24 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-31 21:21:04</t>
+          <t>2026-09-15 11:53:04</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fissysbakestudio</t>
+          <t>https://www.tiktok.com/@positiveproductsuk</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>elizabethj27</t>
+          <t>paultiktokshopuk</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3981,36 +3733,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-10 23:49:16</t>
+          <t>2026-09-15 10:29:04</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elizabethj27</t>
+          <t>https://www.tiktok.com/@paultiktokshopuk</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>designer_suits</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>padnerkupakuwana</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
@@ -4024,70 +3772,62 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-31 19:59:15</t>
+          <t>2026-09-13 02:02:06</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@designer_suits</t>
+          <t>https://www.tiktok.com/@padnerkupakuwana</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>deckynla</t>
+          <t>ranifarooq_3</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-09 11:52:15</t>
+          <t>2026-09-13 22:37:56</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@deckynla</t>
+          <t>https://www.tiktok.com/@ranifarooq_3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>nathenjump</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>queeen_0f_hearts</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4100,58 +3840,58 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-01 14:09:02</t>
+          <t>2026-09-13 23:51:38</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nathenjump</t>
+          <t>https://www.tiktok.com/@queeen_0f_hearts</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>nasirpatel690</t>
+          <t>rory.the.cocker</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-29 00:44:35</t>
+          <t>2026-09-18 18:13:02</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nasirpatel690</t>
+          <t>https://www.tiktok.com/@rory.the.cocker</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mz.jada0</t>
+          <t>rozana2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4168,24 +3908,24 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-07 21:15:37</t>
+          <t>2026-09-19 15:08:34</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mz.jada0</t>
+          <t>https://www.tiktok.com/@rozana2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>muhammadsha110</t>
+          <t>ruksi1607</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4202,24 +3942,24 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-11 15:36:47</t>
+          <t>2026-09-13 20:49:20</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@muhammadsha110</t>
+          <t>https://www.tiktok.com/@ruksi1607</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>moon19867</t>
+          <t>saadia7166</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4236,24 +3976,24 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:54</t>
+          <t>2026-09-10 11:16:51</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moon19867</t>
+          <t>https://www.tiktok.com/@saadia7166</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>moon.x280</t>
+          <t>sajarshed</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4265,29 +4005,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-01 18:11:41</t>
+          <t>2026-09-19 10:17:35</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moon.x280</t>
+          <t>https://www.tiktok.com/@sajarshed</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>monpakhi_202</t>
+          <t>samirakarim24</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4304,24 +4044,24 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-31 21:10:55</t>
+          <t>2026-09-11 11:10:48</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@monpakhi_202</t>
+          <t>https://www.tiktok.com/@samirakarim24</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>maxmeritbackup</t>
+          <t>ornellabeauty25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4338,31 +4078,31 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-01 08:15:09</t>
+          <t>2026-09-07 22:41:47</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maxmeritbackup</t>
+          <t>https://www.tiktok.com/@ornellabeauty25</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>maisiefinds0</t>
+          <t>oyetunji.sunday</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4372,24 +4112,24 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-09-12 13:08:25</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maisiefinds0</t>
+          <t>https://www.tiktok.com/@oyetunji.sunday</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>martigergeraldine</t>
+          <t>nanahdaramy</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4406,24 +4146,24 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-31 11:05:55</t>
+          <t>2026-09-14 00:12:20</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@martigergeraldine</t>
+          <t>https://www.tiktok.com/@nanahdaramy</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>markh_8</t>
+          <t>nancymm52</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4440,24 +4180,24 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-09 16:07:49</t>
+          <t>2026-09-18 07:04:23</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@markh_8</t>
+          <t>https://www.tiktok.com/@nancymm52</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>mamarie146</t>
+          <t>oladayomartins</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4474,31 +4214,31 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-01 12:24:32</t>
+          <t>2026-09-17 21:17:16</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mamarie146</t>
+          <t>https://www.tiktok.com/@oladayomartins</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>nutster58</t>
+          <t>shoni1984</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4508,31 +4248,31 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-01 08:36:44</t>
+          <t>2026-09-10 08:20:01</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nutster58</t>
+          <t>https://www.tiktok.com/@shoni1984</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>nwabkhan760</t>
+          <t>shazzbegum0</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4542,7 +4282,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:05</t>
+          <t>2026-09-15 11:58:02</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4552,14 +4292,14 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nwabkhan760</t>
+          <t>https://www.tiktok.com/@shazzbegum0</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>nellyedwin54</t>
+          <t>sexybaby7657</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4576,31 +4316,31 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-30 13:16:24</t>
+          <t>2026-09-09 21:00:27</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nellyedwin54</t>
+          <t>https://www.tiktok.com/@sexybaby7657</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>nikkigossal29</t>
+          <t>sehrish2015</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4610,83 +4350,75 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-30 17:46:28</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nikkigossal29</t>
+          <t>https://www.tiktok.com/@sehrish2015</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>remeradiance</t>
+          <t>sedi546</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-04 19:49:19</t>
+          <t>2026-09-13 15:46:07</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@remeradiance</t>
+          <t>https://www.tiktok.com/@sedi546</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>redbloodchurch1</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>sweetshez1</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-29 15:02:18</t>
+          <t>2026-09-05 18:50:17</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4696,14 +4428,14 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@redbloodchurch1</t>
+          <t>https://www.tiktok.com/@sweetshez1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>saadia7166</t>
+          <t>ste.baby6</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4720,24 +4452,24 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-10 11:16:51</t>
+          <t>2026-09-09 16:28:17</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saadia7166</t>
+          <t>https://www.tiktok.com/@ste.baby6</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>rkh250496ad</t>
+          <t>sjahan83</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4754,41 +4486,41 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-31 17:54:22</t>
+          <t>2026-09-12 13:46:48</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rkh250496ad</t>
+          <t>https://www.tiktok.com/@sjahan83</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>samirakarim24</t>
+          <t>thehomelylondon</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-11 11:10:48</t>
+          <t>2026-09-18 15:51:23</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4798,26 +4530,18 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samirakarim24</t>
+          <t>https://www.tiktok.com/@thehomelylondon</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>sarah565556</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>theartofprospering</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -4830,31 +4554,31 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:02</t>
+          <t>2026-09-15 11:53:04</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarah565556</t>
+          <t>https://www.tiktok.com/@theartofprospering</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>seana_montgomery61</t>
+          <t>syrashid</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4864,24 +4588,24 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-03 10:12:09</t>
+          <t>2026-09-11 12:35:39</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seana_montgomery61</t>
+          <t>https://www.tiktok.com/@syrashid</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>robbomsnvfv</t>
+          <t>themamadee</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4893,78 +4617,70 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-01 12:37:06</t>
+          <t>2026-09-10 19:23:49</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@robbomsnvfv</t>
+          <t>https://www.tiktok.com/@themamadee</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ornellabeauty25</t>
+          <t>tixtok148</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-07 22:41:47</t>
+          <t>2026-09-19 18:20:29</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ornellabeauty25</t>
+          <t>https://www.tiktok.com/@tixtok148</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>olascornerpage</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>tifetito02</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4974,36 +4690,28 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-12 21:52:02</t>
+          <t>2026-09-16 21:55:36</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@olascornerpage</t>
+          <t>https://www.tiktok.com/@tifetito02</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>princess_wumi</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>treeboyltd</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5016,99 +4724,99 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-29 08:38:03</t>
+          <t>2026-09-19 13:31:02</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princess_wumi</t>
+          <t>https://www.tiktok.com/@treeboyltd</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>oyetunji.sunday</t>
+          <t>su.k806</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-12 13:08:25</t>
+          <t>2026-09-17 20:34:02</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oyetunji.sunday</t>
+          <t>https://www.tiktok.com/@su.k806</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>queen.of.boys42</t>
+          <t>uksaleshop</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-29 18:27:02</t>
+          <t>2026-09-16 15:22:03</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queen.of.boys42</t>
+          <t>https://www.tiktok.com/@uksaleshop</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>rabiaaman21</t>
+          <t>unshoped</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5118,39 +4826,31 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:46</t>
+          <t>2026-09-16 09:42:04</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rabiaaman21</t>
+          <t>https://www.tiktok.com/@unshoped</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>niknak190725</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>user5251816210173</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5160,24 +4860,24 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-01 12:14:04</t>
+          <t>2026-09-15 20:13:06</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@niknak190725</t>
+          <t>https://www.tiktok.com/@user5251816210173</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>notlikeeveryday</t>
+          <t>user13457g</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5194,36 +4894,28 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-04 08:44:04</t>
+          <t>2026-09-10 08:04:29</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@notlikeeveryday</t>
+          <t>https://www.tiktok.com/@user13457g</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>skyviewbm</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>user8318338677754</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5236,58 +4928,58 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-30 16:29:14</t>
+          <t>2026-09-16 23:49:09</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@skyviewbm</t>
+          <t>https://www.tiktok.com/@user8318338677754</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>sjahan83</t>
+          <t>user9199380</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-12 13:46:48</t>
+          <t>2026-09-08 15:02:55</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sjahan83</t>
+          <t>https://www.tiktok.com/@user9199380</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>shume.begum8</t>
+          <t>vain119</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5304,24 +4996,24 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-01 20:33:17</t>
+          <t>2026-09-15 09:25:05</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shume.begum8</t>
+          <t>https://www.tiktok.com/@vain119</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>shoni1984</t>
+          <t>user7271293811175</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5338,24 +5030,24 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-10 08:20:01</t>
+          <t>2026-09-11 08:42:27</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shoni1984</t>
+          <t>https://www.tiktok.com/@user7271293811175</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>sharansaleem</t>
+          <t>vera77524</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5372,92 +5064,92 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-29 11:45:48</t>
+          <t>2026-09-09 07:38:35</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sharansaleem</t>
+          <t>https://www.tiktok.com/@vera77524</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>shezha17</t>
+          <t>vikingbeardshop</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-01 09:35:01</t>
+          <t>2026-09-19 13:38:02</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shezha17</t>
+          <t>https://www.tiktok.com/@vikingbeardshop</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>shahzad.akram041</t>
+          <t>yemishittuedemayibo</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-03 04:27:22</t>
+          <t>2026-09-19 00:15:14</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shahzad.akram041</t>
+          <t>https://www.tiktok.com/@yemishittuedemayibo</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>sexybaby7657</t>
+          <t>yemi.bello3</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5474,24 +5166,24 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-09 21:00:27</t>
+          <t>2026-09-17 07:22:35</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sexybaby7657</t>
+          <t>https://www.tiktok.com/@yemi.bello3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>themamadee</t>
+          <t>yourfindz0</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5508,24 +5200,24 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-10 19:23:49</t>
+          <t>2026-09-19 13:38:02</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@themamadee</t>
+          <t>https://www.tiktok.com/@yourfindz0</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>tee_y.x</t>
+          <t>yvonne21197</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5542,58 +5234,66 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-31 00:32:51</t>
+          <t>2026-09-16 22:41:43</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tee_y.x</t>
+          <t>https://www.tiktok.com/@yvonne21197</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>sweetshez1</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr"/>
+          <t>zahidaparveen624</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-09-05 18:50:17</t>
+          <t>2026-09-11 13:42:26</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sweetshez1</t>
+          <t>https://www.tiktok.com/@zahidaparveen624</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>thestoicphoenix</t>
+          <t>zubairianaz15</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5610,719 +5310,15 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-09-01 12:03:16</t>
+          <t>2026-09-05 22:51:12</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@thestoicphoenix</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>trending_gists_omoola</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-08-30 21:32:52</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@trending_gists_omoola</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>syrashid</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-09-11 12:35:39</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@syrashid</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>spyingthedeals</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-09-08 10:27:03</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@spyingthedeals</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>ste.baby6</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-09-09 16:28:17</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@ste.baby6</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>user13457g</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-09-10 08:04:29</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user13457g</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>ugcbyshristi</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-09-01 12:03:03</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@ugcbyshristi</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>turelove730</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-09-01 14:36:11</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@turelove730</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>user2922793729949</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-09-01 13:14:46</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user2922793729949</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>user_steeze</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-08-30 17:59:09</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user_steeze</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>vera77524</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-09-09 07:38:35</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@vera77524</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>user9199380</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-09-08 15:02:55</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user9199380</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>user7271293811175</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-09-11 08:42:27</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user7271293811175</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>vivianesoizeau</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-08-31 16:20:27</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@vivianesoizeau</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>veronpoks</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-08-30 14:08:12</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@veronpoks</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>wolfie1830</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr"/>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-09-01 11:52:06</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@wolfie1830</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>withlakisha</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-09-04 08:44:03</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@withlakisha</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>xstormx33</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr"/>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-09-01 10:36:21</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@xstormx33</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>yxsna_98</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr"/>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-08-30 12:46:22</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@yxsna_98</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>zahidaparveen624</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-09-11 13:42:26</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@zahidaparveen624</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>zubairianaz15</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr"/>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-09-05 22:51:12</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zubairianaz15</t>
         </is>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1091,10 +1091,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bantzuk</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>akiatuconteh</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
@@ -1108,24 +1112,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-15 11:51:02</t>
+          <t>2026-09-09 07:32:58</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bantzuk</t>
+          <t>https://www.tiktok.com/@akiatuconteh</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>badmashi.007</t>
+          <t>a13dde</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1142,24 +1146,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-14 18:24:25</t>
+          <t>2026-09-14 08:25:14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@badmashi.007</t>
+          <t>https://www.tiktok.com/@a13dde</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ali.syed873</t>
+          <t>atokeade053</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1176,24 +1180,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-17 03:47:33</t>
+          <t>2026-09-14 20:29:27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ali.syed873</t>
+          <t>https://www.tiktok.com/@atokeade053</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>alemap9</t>
+          <t>anita.wils</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1210,24 +1214,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-14 00:26:00</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@alemap9</t>
+          <t>https://www.tiktok.com/@anita.wils</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>a13dde</t>
+          <t>angelaugochinyere</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1244,35 +1248,31 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-14 08:25:14</t>
+          <t>2026-09-16 22:04:31</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@a13dde</t>
+          <t>https://www.tiktok.com/@angelaugochinyere</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>akiatuconteh</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>allthingscutziee</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1282,24 +1282,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-09 07:32:58</t>
+          <t>2026-09-15 11:51:03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akiatuconteh</t>
+          <t>https://www.tiktok.com/@allthingscutziee</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>atokeade053</t>
+          <t>alemap9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1316,24 +1316,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-14 20:29:27</t>
+          <t>2026-09-14 00:26:00</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@atokeade053</t>
+          <t>https://www.tiktok.com/@alemap9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>anita.wils</t>
+          <t>ali.syed873</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-17 03:47:33</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1360,14 +1360,14 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@anita.wils</t>
+          <t>https://www.tiktok.com/@ali.syed873</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>angelaugochinyere</t>
+          <t>barbaraasiedu771</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1384,31 +1384,31 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-16 22:04:31</t>
+          <t>2026-09-09 21:11:27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angelaugochinyere</t>
+          <t>https://www.tiktok.com/@barbaraasiedu771</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>allthingscutziee</t>
+          <t>badmashi.007</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1418,24 +1418,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-15 11:51:03</t>
+          <t>2026-09-14 18:24:25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@allthingscutziee</t>
+          <t>https://www.tiktok.com/@badmashi.007</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>beauty20208</t>
+          <t>courageous527</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1452,24 +1452,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-18 19:31:55</t>
+          <t>2026-09-11 19:24:33</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty20208</t>
+          <t>https://www.tiktok.com/@courageous527</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>barbaraasiedu771</t>
+          <t>dabrat1138</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-09 21:11:27</t>
+          <t>2026-09-10 01:03:04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@barbaraasiedu771</t>
+          <t>https://www.tiktok.com/@dabrat1138</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1537,14 +1537,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>diane.docherty</t>
+          <t>dailymusthaves20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1554,92 +1554,92 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-15 09:50:59</t>
+          <t>2026-09-19 13:38:02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@diane.docherty</t>
+          <t>https://www.tiktok.com/@dailymusthaves20</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>donsnewchapter</t>
+          <t>dollywithplaits73</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-16 09:45:02</t>
+          <t>2026-09-16 16:47:28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@donsnewchapter</t>
+          <t>https://www.tiktok.com/@dollywithplaits73</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dollywithplaits73</t>
+          <t>donsnewchapter</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-16 16:47:28</t>
+          <t>2026-09-16 09:45:02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dollywithplaits73</t>
+          <t>https://www.tiktok.com/@donsnewchapter</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dulal.miah2471</t>
+          <t>drantero_10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1656,24 +1656,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-14 07:26:09</t>
+          <t>2026-09-17 14:48:32</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dulal.miah2471</t>
+          <t>https://www.tiktok.com/@drantero_10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dy7yobwohcu6</t>
+          <t>diane.docherty</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1690,31 +1690,31 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-18 21:30:44</t>
+          <t>2026-09-15 09:50:59</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dy7yobwohcu6</t>
+          <t>https://www.tiktok.com/@diane.docherty</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>elizabethj27</t>
+          <t>bex_lifeafter40</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-10 23:49:16</t>
+          <t>2026-09-17 15:30:23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elizabethj27</t>
+          <t>https://www.tiktok.com/@bex_lifeafter40</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>drantero_10</t>
+          <t>bgee2345</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1758,17 +1758,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-17 14:48:32</t>
+          <t>2026-09-19 22:31:01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@drantero_10</t>
+          <t>https://www.tiktok.com/@bgee2345</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1809,7 +1809,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>chucky692</t>
+          <t>bantzuk</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1826,85 +1826,85 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-15 07:29:48</t>
+          <t>2026-09-15 11:51:02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chucky692</t>
+          <t>https://www.tiktok.com/@bantzuk</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>clairedipple66</t>
+          <t>beauty20208</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:02</t>
+          <t>2026-09-18 19:31:55</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairedipple66</t>
+          <t>https://www.tiktok.com/@beauty20208</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>be__beauty1</t>
+          <t>beemahempire</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-08 17:18:23</t>
+          <t>2026-09-15 11:52:03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@be__beauty1</t>
+          <t>https://www.tiktok.com/@beemahempire</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1945,75 +1945,75 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bettyaddo398</t>
+          <t>be__beauty1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-14 14:52:28</t>
+          <t>2026-09-08 17:18:23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bettyaddo398</t>
+          <t>https://www.tiktok.com/@be__beauty1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bex_lifeafter40</t>
+          <t>gella4573</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-17 15:30:23</t>
+          <t>2026-09-16 07:50:13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bex_lifeafter40</t>
+          <t>https://www.tiktok.com/@gella4573</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>beemahempire</t>
+          <t>fernandasprivy</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2030,31 +2030,31 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-15 11:52:03</t>
+          <t>2026-09-15 19:00:52</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beemahempire</t>
+          <t>https://www.tiktok.com/@fernandasprivy</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>haseeb.mum</t>
+          <t>eni_folabi</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2064,126 +2064,126 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-09 11:38:46</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@haseeb.mum</t>
+          <t>https://www.tiktok.com/@eni_folabi</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>gl80.31</t>
+          <t>emaanttshop</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-10 23:30:20</t>
+          <t>2026-09-15 21:32:02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gl80.31</t>
+          <t>https://www.tiktok.com/@emaanttshop</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>georgiafergg</t>
+          <t>elizabethj27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-10 23:49:16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@georgiafergg</t>
+          <t>https://www.tiktok.com/@elizabethj27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>gella4573</t>
+          <t>hinas_beauty_buys</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-16 07:50:13</t>
+          <t>2026-09-18 09:46:05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gella4573</t>
+          <t>https://www.tiktok.com/@hinas_beauty_buys</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>fernandasprivy</t>
+          <t>hchahal80</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2200,24 +2200,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-15 19:00:52</t>
+          <t>2026-09-15 20:35:21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fernandasprivy</t>
+          <t>https://www.tiktok.com/@hchahal80</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>hrahmancookings</t>
+          <t>georgiafergg</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2234,17 +2234,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-08 19:45:29</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hrahmancookings</t>
+          <t>https://www.tiktok.com/@georgiafergg</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2285,7 +2285,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>hchahal80</t>
+          <t>hrahmancookings</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2302,31 +2302,31 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-15 20:35:21</t>
+          <t>2026-09-08 19:45:29</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hchahal80</t>
+          <t>https://www.tiktok.com/@hrahmancookings</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>is.colonel</t>
+          <t>iqrasumman19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-05 23:55:02</t>
+          <t>2026-09-19 22:51:02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@is.colonel</t>
+          <t>https://www.tiktok.com/@iqrasumman19</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2455,14 +2455,14 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>jxnxxkxk</t>
+          <t>haseeb.mum</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-15 12:32:04</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2482,14 +2482,14 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jxnxxkxk</t>
+          <t>https://www.tiktok.com/@haseeb.mum</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>k.tee146</t>
+          <t>gl80.31</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2506,24 +2506,24 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-10 09:41:07</t>
+          <t>2026-09-10 23:30:20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@k.tee146</t>
+          <t>https://www.tiktok.com/@gl80.31</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>iqrasumman19</t>
+          <t>k.tee146</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2540,85 +2540,85 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-19 22:51:02</t>
+          <t>2026-09-10 09:41:07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iqrasumman19</t>
+          <t>https://www.tiktok.com/@k.tee146</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>hinas_beauty_buys</t>
+          <t>jxnxxkxk</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-18 09:46:05</t>
+          <t>2026-09-15 12:32:04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hinas_beauty_buys</t>
+          <t>https://www.tiktok.com/@jxnxxkxk</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kay.h0</t>
+          <t>kamo76710</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-09 04:27:35</t>
+          <t>2026-09-20 05:21:24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kay.h0</t>
+          <t>https://www.tiktok.com/@kamo76710</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2659,14 +2659,14 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kayyu247</t>
+          <t>keeskloset</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2676,31 +2676,31 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-09 09:42:51</t>
+          <t>2026-09-16 09:57:04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kayyu247</t>
+          <t>https://www.tiktok.com/@keeskloset</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>keeskloset</t>
+          <t>kennybabe692</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2710,92 +2710,92 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-16 09:57:04</t>
+          <t>2026-09-10 11:43:02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@keeskloset</t>
+          <t>https://www.tiktok.com/@kennybabe692</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>konaduroi</t>
+          <t>kay.h0</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-15 03:00:44</t>
+          <t>2026-09-09 04:27:35</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@konaduroi</t>
+          <t>https://www.tiktok.com/@kay.h0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>lady_dash07</t>
+          <t>kayyu247</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-05 21:11:23</t>
+          <t>2026-09-09 09:42:51</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lady_dash07</t>
+          <t>https://www.tiktok.com/@kayyu247</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kennybabe692</t>
+          <t>dulal.miah2471</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2812,24 +2812,24 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-10 11:43:02</t>
+          <t>2026-09-14 07:26:09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kennybabe692</t>
+          <t>https://www.tiktok.com/@dulal.miah2471</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kofoworola2853</t>
+          <t>dy7yobwohcu6</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-11 10:52:59</t>
+          <t>2026-09-18 21:30:44</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kofoworola2853</t>
+          <t>https://www.tiktok.com/@dy7yobwohcu6</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2897,68 +2897,68 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>emaanttshop</t>
+          <t>chucky692</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-15 21:32:02</t>
+          <t>2026-09-15 07:29:48</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emaanttshop</t>
+          <t>https://www.tiktok.com/@chucky692</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>eni_folabi</t>
+          <t>clairedipple66</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-09 11:38:46</t>
+          <t>2026-09-16 07:44:02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eni_folabi</t>
+          <t>https://www.tiktok.com/@clairedipple66</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -2999,41 +2999,41 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>courageous527</t>
+          <t>claudia.claudia970</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-11 19:24:33</t>
+          <t>2026-09-20 22:09:26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courageous527</t>
+          <t>https://www.tiktok.com/@claudia.claudia970</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>dabrat1138</t>
+          <t>bettyaddo398</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3050,31 +3050,31 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-10 01:03:04</t>
+          <t>2026-09-14 14:52:28</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dabrat1138</t>
+          <t>https://www.tiktok.com/@bettyaddo398</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>dailymusthaves20</t>
+          <t>missyspranno12</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3084,24 +3084,24 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-19 13:38:02</t>
+          <t>2026-09-15 13:31:44</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailymusthaves20</t>
+          <t>https://www.tiktok.com/@missyspranno12</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>bgee2345</t>
+          <t>mehmoonaali238</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3118,92 +3118,92 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-19 22:31:01</t>
+          <t>2026-09-17 11:42:05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bgee2345</t>
+          <t>https://www.tiktok.com/@mehmoonaali238</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>mlllifestyle</t>
+          <t>markh_8</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-18 09:46:03</t>
+          <t>2026-09-09 16:07:49</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mlllifestyle</t>
+          <t>https://www.tiktok.com/@markh_8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>missyspranno12</t>
+          <t>maish1002</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-15 13:31:44</t>
+          <t>2026-09-19 13:31:02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@missyspranno12</t>
+          <t>https://www.tiktok.com/@maish1002</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>mehmoonaali238</t>
+          <t>ladydonigbinosa</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3220,126 +3220,126 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-17 11:42:05</t>
+          <t>2026-09-14 07:25:08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mehmoonaali238</t>
+          <t>https://www.tiktok.com/@ladydonigbinosa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>markh_8</t>
+          <t>lucia25070</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-09 16:07:49</t>
+          <t>2026-09-18 09:46:03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@markh_8</t>
+          <t>https://www.tiktok.com/@lucia25070</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>lucia25070</t>
+          <t>kofoworola2853</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-18 09:46:03</t>
+          <t>2026-09-11 10:52:59</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lucia25070</t>
+          <t>https://www.tiktok.com/@kofoworola2853</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>maish1002</t>
+          <t>konaduroi</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-19 13:31:02</t>
+          <t>2026-09-15 03:00:44</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maish1002</t>
+          <t>https://www.tiktok.com/@konaduroi</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ladydonigbinosa</t>
+          <t>nrahi28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3356,41 +3356,41 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-14 07:25:08</t>
+          <t>2026-09-20 14:59:29</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ladydonigbinosa</t>
+          <t>https://www.tiktok.com/@nrahi28</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ladyygold1</t>
+          <t>oladayomartins</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-16 09:45:05</t>
+          <t>2026-09-17 21:17:16</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ladyygold1</t>
+          <t>https://www.tiktok.com/@oladayomartins</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3449,24 +3449,24 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>oluwatoyosiabayom</t>
+          <t>monicalavern</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-14 17:04:02</t>
+          <t>2026-09-15 13:00:13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3476,14 +3476,14 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwatoyosiabayom</t>
+          <t>https://www.tiktok.com/@monicalavern</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>omolade.abebi</t>
+          <t>mz.jada0</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3500,24 +3500,24 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-17 10:33:35</t>
+          <t>2026-09-07 21:15:37</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@omolade.abebi</t>
+          <t>https://www.tiktok.com/@mz.jada0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>monicalavern</t>
+          <t>moon19867</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3534,24 +3534,24 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-15 13:00:13</t>
+          <t>2026-09-11 19:21:54</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@monicalavern</t>
+          <t>https://www.tiktok.com/@moon19867</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mz.jada0</t>
+          <t>muhammadsha110</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3568,24 +3568,24 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-07 21:15:37</t>
+          <t>2026-09-11 15:36:47</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mz.jada0</t>
+          <t>https://www.tiktok.com/@muhammadsha110</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>moon19867</t>
+          <t>mymojomindset</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3602,24 +3602,24 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:54</t>
+          <t>2026-09-15 10:29:05</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moon19867</t>
+          <t>https://www.tiktok.com/@mymojomindset</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>muhammadsha110</t>
+          <t>padnerkupakuwana</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3636,24 +3636,24 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-11 15:36:47</t>
+          <t>2026-09-13 02:02:06</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@muhammadsha110</t>
+          <t>https://www.tiktok.com/@padnerkupakuwana</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mymojomindset</t>
+          <t>oyetunji.sunday</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3670,31 +3670,31 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-15 10:29:05</t>
+          <t>2026-09-12 13:08:25</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mymojomindset</t>
+          <t>https://www.tiktok.com/@oyetunji.sunday</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>positiveproductsuk</t>
+          <t>ornellabeauty25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3704,17 +3704,17 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-15 11:53:04</t>
+          <t>2026-09-07 22:41:47</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@positiveproductsuk</t>
+          <t>https://www.tiktok.com/@ornellabeauty25</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -3755,7 +3755,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>padnerkupakuwana</t>
+          <t>r4xla15</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3772,65 +3772,65 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-13 02:02:06</t>
+          <t>2026-09-20 15:22:42</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@padnerkupakuwana</t>
+          <t>https://www.tiktok.com/@r4xla15</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ranifarooq_3</t>
+          <t>queeen_0f_hearts</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-13 22:37:56</t>
+          <t>2026-09-13 23:51:38</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ranifarooq_3</t>
+          <t>https://www.tiktok.com/@queeen_0f_hearts</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>queeen_0f_hearts</t>
+          <t>positiveproductsuk</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3840,31 +3840,31 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-13 23:51:38</t>
+          <t>2026-09-15 11:53:04</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queeen_0f_hearts</t>
+          <t>https://www.tiktok.com/@positiveproductsuk</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>rory.the.cocker</t>
+          <t>ranifarooq_3</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3874,58 +3874,58 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-18 18:13:02</t>
+          <t>2026-09-13 22:37:56</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rory.the.cocker</t>
+          <t>https://www.tiktok.com/@ranifarooq_3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rozana2026</t>
+          <t>rory.the.cocker</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-19 15:08:34</t>
+          <t>2026-09-18 18:13:02</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rozana2026</t>
+          <t>https://www.tiktok.com/@rory.the.cocker</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ruksi1607</t>
+          <t>rozana2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3942,24 +3942,24 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-13 20:49:20</t>
+          <t>2026-09-19 15:08:34</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ruksi1607</t>
+          <t>https://www.tiktok.com/@rozana2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>saadia7166</t>
+          <t>ruksi1607</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -3976,58 +3976,58 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-10 11:16:51</t>
+          <t>2026-09-13 20:49:20</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saadia7166</t>
+          <t>https://www.tiktok.com/@ruksi1607</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>sajarshed</t>
+          <t>oluwatoyosiabayom</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-19 10:17:35</t>
+          <t>2026-09-14 17:04:02</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sajarshed</t>
+          <t>https://www.tiktok.com/@oluwatoyosiabayom</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>samirakarim24</t>
+          <t>omolade.abebi</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4044,24 +4044,24 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-11 11:10:48</t>
+          <t>2026-09-17 10:33:35</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samirakarim24</t>
+          <t>https://www.tiktok.com/@omolade.abebi</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ornellabeauty25</t>
+          <t>na2706_1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4078,24 +4078,24 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-07 22:41:47</t>
+          <t>2026-09-20 23:38:18</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ornellabeauty25</t>
+          <t>https://www.tiktok.com/@na2706_1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>oyetunji.sunday</t>
+          <t>nanahdaramy</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4112,24 +4112,24 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-12 13:08:25</t>
+          <t>2026-09-14 00:12:20</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oyetunji.sunday</t>
+          <t>https://www.tiktok.com/@nanahdaramy</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>nanahdaramy</t>
+          <t>nancymm52</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4146,31 +4146,31 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-14 00:12:20</t>
+          <t>2026-09-18 07:04:23</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nanahdaramy</t>
+          <t>https://www.tiktok.com/@nancymm52</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>nancymm52</t>
+          <t>sehrish2015</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4180,58 +4180,58 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-18 07:04:23</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nancymm52</t>
+          <t>https://www.tiktok.com/@sehrish2015</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>oladayomartins</t>
+          <t>sedi546</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-17 21:17:16</t>
+          <t>2026-09-13 15:46:07</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oladayomartins</t>
+          <t>https://www.tiktok.com/@sedi546</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>shoni1984</t>
+          <t>samirakarim24</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-10 08:20:01</t>
+          <t>2026-09-11 11:10:48</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4258,21 +4258,21 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shoni1984</t>
+          <t>https://www.tiktok.com/@samirakarim24</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>shazzbegum0</t>
+          <t>sajarshed</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4282,24 +4282,24 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-15 11:58:02</t>
+          <t>2026-09-19 10:17:35</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shazzbegum0</t>
+          <t>https://www.tiktok.com/@sajarshed</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>sexybaby7657</t>
+          <t>saadia7166</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-09 21:00:27</t>
+          <t>2026-09-10 11:16:51</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4326,21 +4326,21 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sexybaby7657</t>
+          <t>https://www.tiktok.com/@saadia7166</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>sehrish2015</t>
+          <t>ste.baby6</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4350,24 +4350,24 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-09 16:28:17</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sehrish2015</t>
+          <t>https://www.tiktok.com/@ste.baby6</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>sedi546</t>
+          <t>sjahan83</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4384,58 +4384,58 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-13 15:46:07</t>
+          <t>2026-09-12 13:46:48</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sedi546</t>
+          <t>https://www.tiktok.com/@sjahan83</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>sweetshez1</t>
+          <t>sexybaby7657</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-05 18:50:17</t>
+          <t>2026-09-09 21:00:27</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sweetshez1</t>
+          <t>https://www.tiktok.com/@sexybaby7657</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ste.baby6</t>
+          <t>syrashid</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4452,126 +4452,126 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-09 16:28:17</t>
+          <t>2026-09-11 12:35:39</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ste.baby6</t>
+          <t>https://www.tiktok.com/@syrashid</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>sjahan83</t>
+          <t>su.k806</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-12 13:46:48</t>
+          <t>2026-09-17 20:34:02</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sjahan83</t>
+          <t>https://www.tiktok.com/@su.k806</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>thehomelylondon</t>
+          <t>themamadee</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-18 15:51:23</t>
+          <t>2026-09-10 19:23:49</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thehomelylondon</t>
+          <t>https://www.tiktok.com/@themamadee</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>theartofprospering</t>
+          <t>thehomelylondon</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-15 11:53:04</t>
+          <t>2026-09-18 15:51:23</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@theartofprospering</t>
+          <t>https://www.tiktok.com/@thehomelylondon</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>syrashid</t>
+          <t>tifetito02</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4588,58 +4588,58 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-11 12:35:39</t>
+          <t>2026-09-16 21:55:36</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@syrashid</t>
+          <t>https://www.tiktok.com/@tifetito02</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>themamadee</t>
+          <t>tixtok148</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-10 19:23:49</t>
+          <t>2026-09-19 18:20:29</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@themamadee</t>
+          <t>https://www.tiktok.com/@tixtok148</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>tixtok148</t>
+          <t>shazzbegum0</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4651,29 +4651,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-19 18:20:29</t>
+          <t>2026-09-15 11:58:02</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tixtok148</t>
+          <t>https://www.tiktok.com/@shazzbegum0</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>tifetito02</t>
+          <t>shoni1984</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -4690,133 +4690,133 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:36</t>
+          <t>2026-09-10 08:20:01</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tifetito02</t>
+          <t>https://www.tiktok.com/@shoni1984</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>treeboyltd</t>
+          <t>uksaleshop</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-19 13:31:02</t>
+          <t>2026-09-16 15:22:03</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@treeboyltd</t>
+          <t>https://www.tiktok.com/@uksaleshop</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>su.k806</t>
+          <t>treeboyltd</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-17 20:34:02</t>
+          <t>2026-09-19 13:31:02</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@su.k806</t>
+          <t>https://www.tiktok.com/@treeboyltd</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>uksaleshop</t>
+          <t>user5251816210173</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-16 15:22:03</t>
+          <t>2026-09-15 20:13:06</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uksaleshop</t>
+          <t>https://www.tiktok.com/@user5251816210173</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>unshoped</t>
+          <t>user13457g</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4826,24 +4826,24 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:04</t>
+          <t>2026-09-10 08:04:29</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@unshoped</t>
+          <t>https://www.tiktok.com/@user13457g</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>user5251816210173</t>
+          <t>user806865620814</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -4860,24 +4860,24 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-15 20:13:06</t>
+          <t>2026-09-20 17:13:54</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user5251816210173</t>
+          <t>https://www.tiktok.com/@user806865620814</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>user13457g</t>
+          <t>user8318338677754</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -4894,85 +4894,85 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-10 08:04:29</t>
+          <t>2026-09-16 23:49:09</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user13457g</t>
+          <t>https://www.tiktok.com/@user8318338677754</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>user8318338677754</t>
+          <t>user9199380</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-09-16 23:49:09</t>
+          <t>2026-09-08 15:02:55</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8318338677754</t>
+          <t>https://www.tiktok.com/@user9199380</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>user9199380</t>
+          <t>user7271293811175</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-08 15:02:55</t>
+          <t>2026-09-11 08:42:27</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9199380</t>
+          <t>https://www.tiktok.com/@user7271293811175</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>user7271293811175</t>
+          <t>vera77524</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5030,24 +5030,24 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-11 08:42:27</t>
+          <t>2026-09-09 07:38:35</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user7271293811175</t>
+          <t>https://www.tiktok.com/@vera77524</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>vera77524</t>
+          <t>yemi.bello3</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5064,17 +5064,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-09 07:38:35</t>
+          <t>2026-09-17 07:22:35</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vera77524</t>
+          <t>https://www.tiktok.com/@yemi.bello3</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5149,7 +5149,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>yemi.bello3</t>
+          <t>yourfindz0</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5166,24 +5166,24 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-17 07:22:35</t>
+          <t>2026-09-19 13:38:02</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemi.bello3</t>
+          <t>https://www.tiktok.com/@yourfindz0</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>yourfindz0</t>
+          <t>yvonne21197</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5200,28 +5200,36 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-19 13:38:02</t>
+          <t>2026-09-16 22:41:43</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yourfindz0</t>
+          <t>https://www.tiktok.com/@yvonne21197</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>yvonne21197</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
+          <t>zahidaparveen624</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D138" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5234,93 +5242,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-09-16 22:41:43</t>
+          <t>2026-09-11 13:42:26</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yvonne21197</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>zahidaparveen624</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-09-11 13:42:26</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
           <t>https://www.tiktok.com/@zahidaparveen624</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>zubairianaz15</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-09-05 22:51:12</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@zubairianaz15</t>
         </is>
       </c>
     </row>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tofanirina</t>
+          <t>shannonroberts16595</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>100K-250K</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -523,29 +523,29 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-12 19:42:02</t>
+          <t>2026-09-21 10:52:02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tofanirina</t>
+          <t>https://www.tiktok.com/@shannonroberts16595</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>iboughtyousomething</t>
+          <t>sue_cole</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,39 +555,39 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-14 06:52:02</t>
+          <t>2026-09-21 22:34:02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iboughtyousomething</t>
+          <t>https://www.tiktok.com/@sue_cole</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>reviewedbysam</t>
+          <t>tofanirina</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -607,29 +607,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-14 06:50:09</t>
+          <t>2026-09-12 19:42:02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reviewedbysam</t>
+          <t>https://www.tiktok.com/@tofanirina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>martzarmy</t>
+          <t>iboughtyousomething</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>50K-100K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -649,29 +649,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:04</t>
+          <t>2026-09-14 06:52:02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@martzarmy</t>
+          <t>https://www.tiktok.com/@iboughtyousomething</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tiktokshopadvice</t>
+          <t>reviewedbysam</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -691,29 +691,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:04</t>
+          <t>2026-09-14 06:50:09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiktokshopadvice</t>
+          <t>https://www.tiktok.com/@reviewedbysam</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rk_uk3</t>
+          <t>martzarmy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -733,29 +733,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-14 05:38:02</t>
+          <t>2026-09-16 09:42:04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rk_uk3</t>
+          <t>https://www.tiktok.com/@martzarmy</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>angelinas.finds</t>
+          <t>tiktokshopadvice</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -775,29 +775,29 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-14 05:38:02</t>
+          <t>2026-09-16 09:42:04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angelinas.finds</t>
+          <t>https://www.tiktok.com/@tiktokshopadvice</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>jenna_g_tiktok</t>
+          <t>rk_uk3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -822,34 +822,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-17 15:30:26</t>
+          <t>2026-09-14 05:38:02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jenna_g_tiktok</t>
+          <t>https://www.tiktok.com/@rk_uk3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ziab442</t>
+          <t>angelinas.finds</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -869,66 +869,66 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ziab442</t>
+          <t>https://www.tiktok.com/@angelinas.finds</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>inayapicks123</t>
+          <t>jenna_g_tiktok</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-14 11:03:03</t>
+          <t>2026-09-17 15:30:26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@inayapicks123</t>
+          <t>https://www.tiktok.com/@jenna_g_tiktok</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>realabdu</t>
+          <t>ziab442</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -948,76 +948,76 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-14 06:36:02</t>
+          <t>2026-09-14 05:38:02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@realabdu</t>
+          <t>https://www.tiktok.com/@ziab442</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>eminence4009</t>
+          <t>inayapicks123</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:05</t>
+          <t>2026-09-14 11:03:03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eminence4009</t>
+          <t>https://www.tiktok.com/@inayapicks123</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>manvsparkins0n</t>
+          <t>realabdu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>250K-500K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1032,29 +1032,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-14 06:51:02</t>
+          <t>2026-09-14 06:36:02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@manvsparkins0n</t>
+          <t>https://www.tiktok.com/@realabdu</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>uncutwithice</t>
+          <t>eminence4009</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1074,35 +1074,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-12 12:02:03</t>
+          <t>2026-09-08 10:27:05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uncutwithice</t>
+          <t>https://www.tiktok.com/@eminence4009</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>akiatuconteh</t>
+          <t>manvsparkins0n</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>250K-500K</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1112,28 +1116,36 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-09 07:32:58</t>
+          <t>2026-09-14 06:51:02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akiatuconteh</t>
+          <t>https://www.tiktok.com/@manvsparkins0n</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>a13dde</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+          <t>uncutwithice</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -1146,24 +1158,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-14 08:25:14</t>
+          <t>2026-09-12 12:02:03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@a13dde</t>
+          <t>https://www.tiktok.com/@uncutwithice</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>atokeade053</t>
+          <t>_dosah</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1180,24 +1192,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-14 20:29:27</t>
+          <t>2026-09-21 14:58:25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@atokeade053</t>
+          <t>https://www.tiktok.com/@_dosah</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>anita.wils</t>
+          <t>1sultan786</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1214,24 +1226,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-21 10:45:04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@anita.wils</t>
+          <t>https://www.tiktok.com/@1sultan786</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>angelaugochinyere</t>
+          <t>a13dde</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1248,31 +1260,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-16 22:04:31</t>
+          <t>2026-09-14 08:25:14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angelaugochinyere</t>
+          <t>https://www.tiktok.com/@a13dde</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>allthingscutziee</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>akiatuconteh</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1282,24 +1298,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-15 11:51:03</t>
+          <t>2026-09-09 07:32:58</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@allthingscutziee</t>
+          <t>https://www.tiktok.com/@akiatuconteh</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>alemap9</t>
+          <t>ali.syed873</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1316,24 +1332,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-14 00:26:00</t>
+          <t>2026-09-17 03:47:33</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@alemap9</t>
+          <t>https://www.tiktok.com/@ali.syed873</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ali.syed873</t>
+          <t>alemap9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1350,31 +1366,31 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-17 03:47:33</t>
+          <t>2026-09-14 00:26:00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ali.syed873</t>
+          <t>https://www.tiktok.com/@alemap9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>barbaraasiedu771</t>
+          <t>allthingscutziee</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1384,24 +1400,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-09 21:11:27</t>
+          <t>2026-09-15 11:51:03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@barbaraasiedu771</t>
+          <t>https://www.tiktok.com/@allthingscutziee</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>badmashi.007</t>
+          <t>angelaugochinyere</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1418,24 +1434,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-14 18:24:25</t>
+          <t>2026-09-16 22:04:31</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@badmashi.007</t>
+          <t>https://www.tiktok.com/@angelaugochinyere</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>courageous527</t>
+          <t>anita.wils</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1452,24 +1468,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-11 19:24:33</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courageous527</t>
+          <t>https://www.tiktok.com/@anita.wils</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dabrat1138</t>
+          <t>atokeade053</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1486,58 +1502,58 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-10 01:03:04</t>
+          <t>2026-09-14 20:29:27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dabrat1138</t>
+          <t>https://www.tiktok.com/@atokeade053</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>deckynla</t>
+          <t>climax.scenes</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-09 11:52:15</t>
+          <t>2026-09-21 06:20:00</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@deckynla</t>
+          <t>https://www.tiktok.com/@climax.scenes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dailymusthaves20</t>
+          <t>claudia.claudia970</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1549,12 +1565,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-19 13:38:02</t>
+          <t>2026-09-20 22:09:26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1564,82 +1580,82 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailymusthaves20</t>
+          <t>https://www.tiktok.com/@claudia.claudia970</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dollywithplaits73</t>
+          <t>clare.w4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-16 16:47:28</t>
+          <t>2026-09-10 14:06:31</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dollywithplaits73</t>
+          <t>https://www.tiktok.com/@clare.w4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>donsnewchapter</t>
+          <t>clairedipple66</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-16 09:45:02</t>
+          <t>2026-09-16 07:44:02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@donsnewchapter</t>
+          <t>https://www.tiktok.com/@clairedipple66</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>drantero_10</t>
+          <t>chucky692</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1656,31 +1672,31 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-17 14:48:32</t>
+          <t>2026-09-15 07:29:48</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@drantero_10</t>
+          <t>https://www.tiktok.com/@chucky692</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>diane.docherty</t>
+          <t>chloeeflynnx</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1690,7 +1706,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-15 09:50:59</t>
+          <t>2026-09-16 11:07:02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1700,89 +1716,89 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@diane.docherty</t>
+          <t>https://www.tiktok.com/@chloeeflynnx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bex_lifeafter40</t>
+          <t>bgee2345</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-17 15:30:23</t>
+          <t>2026-09-19 22:31:01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bex_lifeafter40</t>
+          <t>https://www.tiktok.com/@bgee2345</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bgee2345</t>
+          <t>bex_lifeafter40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-19 22:31:01</t>
+          <t>2026-09-17 15:30:23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bgee2345</t>
+          <t>https://www.tiktok.com/@bex_lifeafter40</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>chloeeflynnx</t>
+          <t>bettyaddo398</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1792,31 +1808,31 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-16 11:07:02</t>
+          <t>2026-09-14 14:52:28</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chloeeflynnx</t>
+          <t>https://www.tiktok.com/@bettyaddo398</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bantzuk</t>
+          <t>bellasbeauty07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1826,24 +1842,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-15 11:51:02</t>
+          <t>2026-09-08 10:16:05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bantzuk</t>
+          <t>https://www.tiktok.com/@bellasbeauty07</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>beauty20208</t>
+          <t>beemahempire</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1860,24 +1876,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-18 19:31:55</t>
+          <t>2026-09-15 11:52:03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty20208</t>
+          <t>https://www.tiktok.com/@beemahempire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>beemahempire</t>
+          <t>beauty20208</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1894,24 +1910,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-15 11:52:03</t>
+          <t>2026-09-18 19:31:55</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beemahempire</t>
+          <t>https://www.tiktok.com/@beauty20208</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bellasbeauty07</t>
+          <t>be__beauty1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1923,46 +1939,46 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-08 10:16:05</t>
+          <t>2026-09-08 17:18:23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bellasbeauty07</t>
+          <t>https://www.tiktok.com/@be__beauty1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>be__beauty1</t>
+          <t>barbaraasiedu771</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-08 17:18:23</t>
+          <t>2026-09-09 21:11:27</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1972,14 +1988,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@be__beauty1</t>
+          <t>https://www.tiktok.com/@barbaraasiedu771</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>gella4573</t>
+          <t>bantzuk</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1996,24 +2012,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-16 07:50:13</t>
+          <t>2026-09-15 11:51:02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gella4573</t>
+          <t>https://www.tiktok.com/@bantzuk</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>fernandasprivy</t>
+          <t>badmashi.007</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2030,85 +2046,85 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-15 19:00:52</t>
+          <t>2026-09-14 18:24:25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fernandasprivy</t>
+          <t>https://www.tiktok.com/@badmashi.007</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>eni_folabi</t>
+          <t>emaanttshop</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-09 11:38:46</t>
+          <t>2026-09-15 21:32:02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eni_folabi</t>
+          <t>https://www.tiktok.com/@emaanttshop</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>emaanttshop</t>
+          <t>elizabetho001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-15 21:32:02</t>
+          <t>2026-09-08 17:27:54</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emaanttshop</t>
+          <t>https://www.tiktok.com/@elizabetho001</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2153,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2149,41 +2165,41 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hinas_beauty_buys</t>
+          <t>eni_folabi</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-18 09:46:05</t>
+          <t>2026-09-09 11:38:46</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hinas_beauty_buys</t>
+          <t>https://www.tiktok.com/@eni_folabi</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>hchahal80</t>
+          <t>georgiafergg</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2200,7 +2216,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-15 20:35:21</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2210,14 +2226,14 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hchahal80</t>
+          <t>https://www.tiktok.com/@georgiafergg</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>georgiafergg</t>
+          <t>gl80.31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2234,24 +2250,24 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-10 23:30:20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@georgiafergg</t>
+          <t>https://www.tiktok.com/@gl80.31</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>i.couldnt.give.a.fuckkkk</t>
+          <t>dailymusthaves20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2268,126 +2284,126 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-12 11:58:47</t>
+          <t>2026-09-19 13:38:02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@i.couldnt.give.a.fuckkkk</t>
+          <t>https://www.tiktok.com/@dailymusthaves20</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>hrahmancookings</t>
+          <t>cosyhomewithsteph</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-08 19:45:29</t>
+          <t>2026-09-21 23:32:02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hrahmancookings</t>
+          <t>https://www.tiktok.com/@cosyhomewithsteph</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>iqrasumman19</t>
+          <t>dollywithplaits73</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-19 22:51:02</t>
+          <t>2026-09-16 16:47:28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iqrasumman19</t>
+          <t>https://www.tiktok.com/@dollywithplaits73</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>janetaliciac</t>
+          <t>donsnewchapter</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-18 18:16:03</t>
+          <t>2026-09-16 09:45:02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@janetaliciac</t>
+          <t>https://www.tiktok.com/@donsnewchapter</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>joandusabe</t>
+          <t>drantero_10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2404,24 +2420,24 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-19 08:31:29</t>
+          <t>2026-09-17 14:48:32</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@joandusabe</t>
+          <t>https://www.tiktok.com/@drantero_10</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>julietogu5</t>
+          <t>dulal.miah2471</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2438,31 +2454,31 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-14 01:42:26</t>
+          <t>2026-09-14 07:26:09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@julietogu5</t>
+          <t>https://www.tiktok.com/@dulal.miah2471</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>haseeb.mum</t>
+          <t>dy7yobwohcu6</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2472,24 +2488,24 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-18 21:30:44</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@haseeb.mum</t>
+          <t>https://www.tiktok.com/@dy7yobwohcu6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>gl80.31</t>
+          <t>courageous527</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2506,7 +2522,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-10 23:30:20</t>
+          <t>2026-09-11 19:24:33</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2516,14 +2532,14 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gl80.31</t>
+          <t>https://www.tiktok.com/@courageous527</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>k.tee146</t>
+          <t>dabrat1138</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2540,58 +2556,58 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-10 09:41:07</t>
+          <t>2026-09-10 01:03:04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@k.tee146</t>
+          <t>https://www.tiktok.com/@dabrat1138</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>jxnxxkxk</t>
+          <t>dailydealsuk03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-15 12:32:04</t>
+          <t>2026-09-21 10:45:03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jxnxxkxk</t>
+          <t>https://www.tiktok.com/@dailydealsuk03</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kamo76710</t>
+          <t>jem17363</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2608,7 +2624,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-20 05:21:24</t>
+          <t>2026-09-21 17:28:16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2618,21 +2634,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kamo76710</t>
+          <t>https://www.tiktok.com/@jem17363</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>katseyelocer</t>
+          <t>janetaliciac</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2642,31 +2658,31 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-15 22:58:52</t>
+          <t>2026-09-18 18:16:03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katseyelocer</t>
+          <t>https://www.tiktok.com/@janetaliciac</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>keeskloset</t>
+          <t>hrahmancookings</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2676,24 +2692,24 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-16 09:57:04</t>
+          <t>2026-09-08 19:45:29</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@keeskloset</t>
+          <t>https://www.tiktok.com/@hrahmancookings</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kennybabe692</t>
+          <t>joandusabe</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2710,41 +2726,41 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-10 11:43:02</t>
+          <t>2026-09-19 08:31:29</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kennybabe692</t>
+          <t>https://www.tiktok.com/@joandusabe</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kay.h0</t>
+          <t>k.tee146</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-09 04:27:35</t>
+          <t>2026-09-10 09:41:07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2754,14 +2770,14 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kay.h0</t>
+          <t>https://www.tiktok.com/@k.tee146</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kayyu247</t>
+          <t>kamo76710</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2778,24 +2794,24 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-09 09:42:51</t>
+          <t>2026-09-20 05:21:24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kayyu247</t>
+          <t>https://www.tiktok.com/@kamo76710</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>dulal.miah2471</t>
+          <t>julietogu5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2812,24 +2828,24 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-14 07:26:09</t>
+          <t>2026-09-14 01:42:26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dulal.miah2471</t>
+          <t>https://www.tiktok.com/@julietogu5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>dy7yobwohcu6</t>
+          <t>jxnxxkxk</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2846,24 +2862,24 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-18 21:30:44</t>
+          <t>2026-09-15 12:32:04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dy7yobwohcu6</t>
+          <t>https://www.tiktok.com/@jxnxxkxk</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>elizabetho001</t>
+          <t>kayyu247</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2880,7 +2896,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-08 17:27:54</t>
+          <t>2026-09-09 09:42:51</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2890,21 +2906,21 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elizabetho001</t>
+          <t>https://www.tiktok.com/@kayyu247</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>chucky692</t>
+          <t>keeskloset</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2914,7 +2930,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-15 07:29:48</t>
+          <t>2026-09-16 09:57:04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2924,48 +2940,48 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chucky692</t>
+          <t>https://www.tiktok.com/@keeskloset</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>clairedipple66</t>
+          <t>kennybabe692</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:02</t>
+          <t>2026-09-10 11:43:02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairedipple66</t>
+          <t>https://www.tiktok.com/@kennybabe692</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>clare.w4</t>
+          <t>kofoworola2853</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2982,7 +2998,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-10 14:06:31</t>
+          <t>2026-09-11 10:52:59</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2992,48 +3008,48 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clare.w4</t>
+          <t>https://www.tiktok.com/@kofoworola2853</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>claudia.claudia970</t>
+          <t>konaduroi</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-20 22:09:26</t>
+          <t>2026-09-15 03:00:44</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@claudia.claudia970</t>
+          <t>https://www.tiktok.com/@konaduroi</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>bettyaddo398</t>
+          <t>ladydonigbinosa</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3050,133 +3066,133 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-14 14:52:28</t>
+          <t>2026-09-14 07:25:08</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bettyaddo398</t>
+          <t>https://www.tiktok.com/@ladydonigbinosa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>missyspranno12</t>
+          <t>katseyelocer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-15 13:31:44</t>
+          <t>2026-09-15 22:58:52</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@missyspranno12</t>
+          <t>https://www.tiktok.com/@katseyelocer</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>mehmoonaali238</t>
+          <t>kay.h0</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-17 11:42:05</t>
+          <t>2026-09-09 04:27:35</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mehmoonaali238</t>
+          <t>https://www.tiktok.com/@kay.h0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>markh_8</t>
+          <t>lucia25070</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-09 16:07:49</t>
+          <t>2026-09-18 09:46:03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@markh_8</t>
+          <t>https://www.tiktok.com/@lucia25070</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>maish1002</t>
+          <t>life52551</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3186,65 +3202,65 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-19 13:31:02</t>
+          <t>2026-09-21 22:10:02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maish1002</t>
+          <t>https://www.tiktok.com/@life52551</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ladydonigbinosa</t>
+          <t>maish1002</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-14 07:25:08</t>
+          <t>2026-09-19 13:31:02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ladydonigbinosa</t>
+          <t>https://www.tiktok.com/@maish1002</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>lucia25070</t>
+          <t>m.3384</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3254,24 +3270,24 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-18 09:46:03</t>
+          <t>2026-09-21 10:22:24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lucia25070</t>
+          <t>https://www.tiktok.com/@m.3384</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kofoworola2853</t>
+          <t>markh_8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3288,24 +3304,24 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-11 10:52:59</t>
+          <t>2026-09-09 16:07:49</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kofoworola2853</t>
+          <t>https://www.tiktok.com/@markh_8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>konaduroi</t>
+          <t>mehmoonaali238</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3322,24 +3338,24 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-15 03:00:44</t>
+          <t>2026-09-17 11:42:05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@konaduroi</t>
+          <t>https://www.tiktok.com/@mehmoonaali238</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>nrahi28</t>
+          <t>fernandasprivy</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3356,107 +3372,99 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-20 14:59:29</t>
+          <t>2026-09-15 19:00:52</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nrahi28</t>
+          <t>https://www.tiktok.com/@fernandasprivy</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>oladayomartins</t>
+          <t>gella4573</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-17 21:17:16</t>
+          <t>2026-09-16 07:50:13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oladayomartins</t>
+          <t>https://www.tiktok.com/@gella4573</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>olascornerpage</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>hashirahmed784</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-12 21:52:02</t>
+          <t>2026-09-21 21:16:02</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@olascornerpage</t>
+          <t>https://www.tiktok.com/@hashirahmed784</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>monicalavern</t>
+          <t>haseeb.mum</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3466,7 +3474,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-15 13:00:13</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3476,14 +3484,14 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@monicalavern</t>
+          <t>https://www.tiktok.com/@haseeb.mum</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>mz.jada0</t>
+          <t>hchahal80</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3500,65 +3508,65 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-07 21:15:37</t>
+          <t>2026-09-15 20:35:21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mz.jada0</t>
+          <t>https://www.tiktok.com/@hchahal80</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>moon19867</t>
+          <t>hinas_beauty_buys</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:54</t>
+          <t>2026-09-18 09:46:05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moon19867</t>
+          <t>https://www.tiktok.com/@hinas_beauty_buys</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>muhammadsha110</t>
+          <t>i.couldnt.give.a.fuckkkk</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3568,7 +3576,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-11 15:36:47</t>
+          <t>2026-09-12 11:58:47</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3578,14 +3586,14 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@muhammadsha110</t>
+          <t>https://www.tiktok.com/@i.couldnt.give.a.fuckkkk</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mymojomindset</t>
+          <t>deckynla</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3602,24 +3610,24 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-15 10:29:05</t>
+          <t>2026-09-09 11:52:15</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mymojomindset</t>
+          <t>https://www.tiktok.com/@deckynla</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>padnerkupakuwana</t>
+          <t>diane.docherty</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3636,31 +3644,31 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-13 02:02:06</t>
+          <t>2026-09-15 09:50:59</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@padnerkupakuwana</t>
+          <t>https://www.tiktok.com/@diane.docherty</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>oyetunji.sunday</t>
+          <t>dillytwinmum</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3670,24 +3678,24 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-12 13:08:25</t>
+          <t>2026-09-21 09:55:02</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oyetunji.sunday</t>
+          <t>https://www.tiktok.com/@dillytwinmum</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ornellabeauty25</t>
+          <t>nrahi28</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3704,31 +3712,31 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-07 22:41:47</t>
+          <t>2026-09-20 14:59:29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ornellabeauty25</t>
+          <t>https://www.tiktok.com/@nrahi28</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>paultiktokshopuk</t>
+          <t>nancymm52</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3738,24 +3746,24 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-15 10:29:04</t>
+          <t>2026-09-18 07:04:23</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@paultiktokshopuk</t>
+          <t>https://www.tiktok.com/@nancymm52</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>r4xla15</t>
+          <t>nanahdaramy</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3772,24 +3780,24 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-20 15:22:42</t>
+          <t>2026-09-14 00:12:20</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@r4xla15</t>
+          <t>https://www.tiktok.com/@nanahdaramy</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>queeen_0f_hearts</t>
+          <t>na2706_1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3806,31 +3814,31 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-13 23:51:38</t>
+          <t>2026-09-20 23:38:18</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queeen_0f_hearts</t>
+          <t>https://www.tiktok.com/@na2706_1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>positiveproductsuk</t>
+          <t>mz.jada0</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3840,92 +3848,92 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-15 11:53:04</t>
+          <t>2026-09-07 21:15:37</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@positiveproductsuk</t>
+          <t>https://www.tiktok.com/@mz.jada0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ranifarooq_3</t>
+          <t>mymojomindset</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-13 22:37:56</t>
+          <t>2026-09-15 10:29:05</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ranifarooq_3</t>
+          <t>https://www.tiktok.com/@mymojomindset</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rory.the.cocker</t>
+          <t>muhammadsha110</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-18 18:13:02</t>
+          <t>2026-09-11 15:36:47</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rory.the.cocker</t>
+          <t>https://www.tiktok.com/@muhammadsha110</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>rozana2026</t>
+          <t>moon19867</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3942,24 +3950,24 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-19 15:08:34</t>
+          <t>2026-09-11 19:21:54</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rozana2026</t>
+          <t>https://www.tiktok.com/@moon19867</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ruksi1607</t>
+          <t>monicalavern</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -3976,41 +3984,41 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-13 20:49:20</t>
+          <t>2026-09-15 13:00:13</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ruksi1607</t>
+          <t>https://www.tiktok.com/@monicalavern</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>oluwatoyosiabayom</t>
+          <t>missyspranno12</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-14 17:04:02</t>
+          <t>2026-09-15 13:31:44</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4020,21 +4028,21 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwatoyosiabayom</t>
+          <t>https://www.tiktok.com/@missyspranno12</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>omolade.abebi</t>
+          <t>positiveproductsuk</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4044,24 +4052,24 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-17 10:33:35</t>
+          <t>2026-09-15 11:53:04</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@omolade.abebi</t>
+          <t>https://www.tiktok.com/@positiveproductsuk</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>na2706_1</t>
+          <t>padnerkupakuwana</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4078,24 +4086,24 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-20 23:38:18</t>
+          <t>2026-09-13 02:02:06</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@na2706_1</t>
+          <t>https://www.tiktok.com/@padnerkupakuwana</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>nanahdaramy</t>
+          <t>ornellabeauty25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4112,31 +4120,39 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-14 00:12:20</t>
+          <t>2026-09-07 22:41:47</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nanahdaramy</t>
+          <t>https://www.tiktok.com/@ornellabeauty25</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>nancymm52</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
+          <t>olascornerpage</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4146,24 +4162,24 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-18 07:04:23</t>
+          <t>2026-09-12 21:52:02</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nancymm52</t>
+          <t>https://www.tiktok.com/@olascornerpage</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>sehrish2015</t>
+          <t>oluwatoyosiabayom</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4175,131 +4191,131 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-14 17:04:02</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sehrish2015</t>
+          <t>https://www.tiktok.com/@oluwatoyosiabayom</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>sedi546</t>
+          <t>oladayomartins</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-13 15:46:07</t>
+          <t>2026-09-17 21:17:16</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sedi546</t>
+          <t>https://www.tiktok.com/@oladayomartins</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>samirakarim24</t>
+          <t>ranifarooq_3</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-11 11:10:48</t>
+          <t>2026-09-13 22:37:56</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samirakarim24</t>
+          <t>https://www.tiktok.com/@ranifarooq_3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>sajarshed</t>
+          <t>rory.the.cocker</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-19 10:17:35</t>
+          <t>2026-09-18 18:13:02</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sajarshed</t>
+          <t>https://www.tiktok.com/@rory.the.cocker</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>saadia7166</t>
+          <t>ruksi1607</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4316,24 +4332,24 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-10 11:16:51</t>
+          <t>2026-09-13 20:49:20</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saadia7166</t>
+          <t>https://www.tiktok.com/@ruksi1607</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ste.baby6</t>
+          <t>rozana2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4350,24 +4366,24 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-09 16:28:17</t>
+          <t>2026-09-19 15:08:34</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ste.baby6</t>
+          <t>https://www.tiktok.com/@rozana2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>sjahan83</t>
+          <t>sajarshed</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4384,24 +4400,24 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-12 13:46:48</t>
+          <t>2026-09-19 10:17:35</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sjahan83</t>
+          <t>https://www.tiktok.com/@sajarshed</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>sexybaby7657</t>
+          <t>samirakarim24</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4418,92 +4434,92 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-09 21:00:27</t>
+          <t>2026-09-11 11:10:48</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sexybaby7657</t>
+          <t>https://www.tiktok.com/@samirakarim24</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>syrashid</t>
+          <t>sbegum.79</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-11 12:35:39</t>
+          <t>2026-09-21 17:38:25</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@syrashid</t>
+          <t>https://www.tiktok.com/@sbegum.79</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>su.k806</t>
+          <t>saadia7166</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-17 20:34:02</t>
+          <t>2026-09-10 11:16:51</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@su.k806</t>
+          <t>https://www.tiktok.com/@saadia7166</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>themamadee</t>
+          <t>sedi546</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4520,58 +4536,58 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-10 19:23:49</t>
+          <t>2026-09-13 15:46:07</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@themamadee</t>
+          <t>https://www.tiktok.com/@sedi546</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>thehomelylondon</t>
+          <t>seffshops</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-18 15:51:23</t>
+          <t>2026-09-21 10:52:04</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thehomelylondon</t>
+          <t>https://www.tiktok.com/@seffshops</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>tifetito02</t>
+          <t>oyetunji.sunday</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4588,65 +4604,65 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:36</t>
+          <t>2026-09-12 13:08:25</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tifetito02</t>
+          <t>https://www.tiktok.com/@oyetunji.sunday</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>tixtok148</t>
+          <t>positivevibeonly62</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-19 18:20:29</t>
+          <t>2026-09-21 10:52:02</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tixtok148</t>
+          <t>https://www.tiktok.com/@positivevibeonly62</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>shazzbegum0</t>
+          <t>radhekrishna_11</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4656,24 +4672,24 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-15 11:58:02</t>
+          <t>2026-09-21 11:21:47</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shazzbegum0</t>
+          <t>https://www.tiktok.com/@radhekrishna_11</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>shoni1984</t>
+          <t>r4xla15</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -4690,58 +4706,58 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-10 08:20:01</t>
+          <t>2026-09-20 15:22:42</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shoni1984</t>
+          <t>https://www.tiktok.com/@r4xla15</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>uksaleshop</t>
+          <t>queeen_0f_hearts</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-16 15:22:03</t>
+          <t>2026-09-13 23:51:38</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uksaleshop</t>
+          <t>https://www.tiktok.com/@queeen_0f_hearts</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>treeboyltd</t>
+          <t>omolade.abebi</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4758,24 +4774,24 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-19 13:31:02</t>
+          <t>2026-09-17 10:33:35</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@treeboyltd</t>
+          <t>https://www.tiktok.com/@omolade.abebi</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>user5251816210173</t>
+          <t>shopforfiver</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -4792,24 +4808,24 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-15 20:13:06</t>
+          <t>2026-09-21 15:01:03</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user5251816210173</t>
+          <t>https://www.tiktok.com/@shopforfiver</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>user13457g</t>
+          <t>shoni1984</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4826,31 +4842,31 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-10 08:04:29</t>
+          <t>2026-09-10 08:20:01</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user13457g</t>
+          <t>https://www.tiktok.com/@shoni1984</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>user806865620814</t>
+          <t>shazzbegum0</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4860,24 +4876,24 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-20 17:13:54</t>
+          <t>2026-09-15 11:58:02</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user806865620814</t>
+          <t>https://www.tiktok.com/@shazzbegum0</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>user8318338677754</t>
+          <t>sexybaby7657</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -4894,31 +4910,31 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-16 23:49:09</t>
+          <t>2026-09-09 21:00:27</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8318338677754</t>
+          <t>https://www.tiktok.com/@sexybaby7657</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>user9199380</t>
+          <t>sehnamiee</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4928,31 +4944,31 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-09-08 15:02:55</t>
+          <t>2026-09-21 20:46:02</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9199380</t>
+          <t>https://www.tiktok.com/@sehnamiee</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>user7271293811175</t>
+          <t>sehrish2015</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4962,24 +4978,24 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-11 08:42:27</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user7271293811175</t>
+          <t>https://www.tiktok.com/@sehrish2015</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>vain119</t>
+          <t>ste.baby6</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -4996,58 +5012,58 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-15 09:25:05</t>
+          <t>2026-09-09 16:28:17</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vain119</t>
+          <t>https://www.tiktok.com/@ste.baby6</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>vera77524</t>
+          <t>su.k806</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-09 07:38:35</t>
+          <t>2026-09-17 20:34:02</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vera77524</t>
+          <t>https://www.tiktok.com/@su.k806</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>yemi.bello3</t>
+          <t>themamadee</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5064,31 +5080,31 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-17 07:22:35</t>
+          <t>2026-09-10 19:23:49</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemi.bello3</t>
+          <t>https://www.tiktok.com/@themamadee</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>vikingbeardshop</t>
+          <t>thehomelylondon</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5098,24 +5114,24 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-19 13:38:02</t>
+          <t>2026-09-18 15:51:23</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vikingbeardshop</t>
+          <t>https://www.tiktok.com/@thehomelylondon</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>yemishittuedemayibo</t>
+          <t>syrashid</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5132,24 +5148,24 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-19 00:15:14</t>
+          <t>2026-09-11 12:35:39</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemishittuedemayibo</t>
+          <t>https://www.tiktok.com/@syrashid</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>yourfindz0</t>
+          <t>tifetito02</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5166,91 +5182,703 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-19 13:38:02</t>
+          <t>2026-09-16 21:55:36</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yourfindz0</t>
+          <t>https://www.tiktok.com/@tifetito02</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>yvonne21197</t>
+          <t>tixtok148</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-16 22:41:43</t>
+          <t>2026-09-19 18:20:29</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yvonne21197</t>
+          <t>https://www.tiktok.com/@tixtok148</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>treeboyltd</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-09-19 13:31:02</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@treeboyltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>uksaleshop</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Free sample from seller</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:22:03</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@uksaleshop</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>sjahan83</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-09-12 13:46:48</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sjahan83</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>user13457g</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-09-10 08:04:29</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user13457g</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>user2182373993526</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:26:17</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user2182373993526</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>user5251816210173</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:13:06</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user5251816210173</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>user2773140226152</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-09-21 20:00:10</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user2773140226152</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>user806865620814</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:13:54</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user806865620814</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>user8318338677754</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-09-16 23:49:09</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user8318338677754</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>user9199380</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Ashwagandha Coffee</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Free sample from seller</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:02:55</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user9199380</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>user7271293811175</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-09-11 08:42:27</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user7271293811175</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>vain119</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-09-15 09:25:05</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@vain119</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>vera77524</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-09-09 07:38:35</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@vera77524</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>yemi.bello3</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-09-17 07:22:35</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yemi.bello3</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>vikingbeardshop</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Shatavari 1300mg Extra Strength</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Free sample from seller</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-09-19 13:38:02</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@vikingbeardshop</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>yemishittuedemayibo</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:15:14</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yemishittuedemayibo</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>yourfindz0</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-09-19 13:38:02</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yourfindz0</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>yvonne21197</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-09-16 22:41:43</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yvonne21197</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
           <t>zahidaparveen624</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>1K-5K</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
         <is>
           <t>2026-09-11 13:42:26</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zahidaparveen624</t>
         </is>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -2313,7 +2313,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H156"/>
+  <dimension ref="A1:H167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -503,32 +503,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>shannonroberts16595</t>
+          <t>janejohnstonharland</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-21 10:52:02</t>
+          <t>2026-09-22 03:53:02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -538,14 +538,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shannonroberts16595</t>
+          <t>https://www.tiktok.com/@janejohnstonharland</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sue_cole</t>
+          <t>shannonroberts16595</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,39 +555,39 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>100K-250K</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-21 22:34:02</t>
+          <t>2026-09-21 10:52:02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sue_cole</t>
+          <t>https://www.tiktok.com/@shannonroberts16595</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tofanirina</t>
+          <t>sue_cole</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,12 +597,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -612,24 +612,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-12 19:42:02</t>
+          <t>2026-09-21 22:34:02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tofanirina</t>
+          <t>https://www.tiktok.com/@sue_cole</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>iboughtyousomething</t>
+          <t>tofanirina</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -649,29 +649,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-14 06:52:02</t>
+          <t>2026-09-12 19:42:02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iboughtyousomething</t>
+          <t>https://www.tiktok.com/@tofanirina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>reviewedbysam</t>
+          <t>iboughtyousomething</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -696,24 +696,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-14 06:50:09</t>
+          <t>2026-09-14 06:52:02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reviewedbysam</t>
+          <t>https://www.tiktok.com/@iboughtyousomething</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>martzarmy</t>
+          <t>reviewedbysam</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>50K-100K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -733,29 +733,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:04</t>
+          <t>2026-09-14 06:50:09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@martzarmy</t>
+          <t>https://www.tiktok.com/@reviewedbysam</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tiktokshopadvice</t>
+          <t>martzarmy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiktokshopadvice</t>
+          <t>https://www.tiktok.com/@martzarmy</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>_dosah</t>
+          <t>bettyaddo398</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1192,58 +1192,58 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-21 14:58:25</t>
+          <t>2026-09-14 14:52:28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_dosah</t>
+          <t>https://www.tiktok.com/@bettyaddo398</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1sultan786</t>
+          <t>bex_lifeafter40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-21 10:45:04</t>
+          <t>2026-09-17 15:30:23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@1sultan786</t>
+          <t>https://www.tiktok.com/@bex_lifeafter40</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>a13dde</t>
+          <t>bgee2345</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1260,69 +1260,65 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-14 08:25:14</t>
+          <t>2026-09-19 22:31:01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@a13dde</t>
+          <t>https://www.tiktok.com/@bgee2345</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>akiatuconteh</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>chek_mi_shocase</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-09 07:32:58</t>
+          <t>2026-09-22 17:56:02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akiatuconteh</t>
+          <t>https://www.tiktok.com/@chek_mi_shocase</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ali.syed873</t>
+          <t>chloeeflynnx</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1332,24 +1328,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-17 03:47:33</t>
+          <t>2026-09-16 11:07:02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ali.syed873</t>
+          <t>https://www.tiktok.com/@chloeeflynnx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>alemap9</t>
+          <t>ali.syed873</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1366,31 +1362,31 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-14 00:26:00</t>
+          <t>2026-09-17 03:47:33</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@alemap9</t>
+          <t>https://www.tiktok.com/@ali.syed873</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>allthingscutziee</t>
+          <t>angelaugochinyere</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1400,7 +1396,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-15 11:51:03</t>
+          <t>2026-09-16 22:04:31</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1410,14 +1406,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@allthingscutziee</t>
+          <t>https://www.tiktok.com/@angelaugochinyere</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>angelaugochinyere</t>
+          <t>anita.wils</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1434,24 +1430,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-16 22:04:31</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angelaugochinyere</t>
+          <t>https://www.tiktok.com/@anita.wils</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>anita.wils</t>
+          <t>atokeade053</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1468,24 +1464,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-14 20:29:27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@anita.wils</t>
+          <t>https://www.tiktok.com/@atokeade053</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>atokeade053</t>
+          <t>badmashi.007</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1502,160 +1498,160 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-14 20:29:27</t>
+          <t>2026-09-14 18:24:25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@atokeade053</t>
+          <t>https://www.tiktok.com/@badmashi.007</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>climax.scenes</t>
+          <t>bantzuk</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-21 06:20:00</t>
+          <t>2026-09-15 11:51:02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@climax.scenes</t>
+          <t>https://www.tiktok.com/@bantzuk</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>claudia.claudia970</t>
+          <t>barbaraasiedu771</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-20 22:09:26</t>
+          <t>2026-09-09 21:11:27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@claudia.claudia970</t>
+          <t>https://www.tiktok.com/@barbaraasiedu771</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>clare.w4</t>
+          <t>be__beauty1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-10 14:06:31</t>
+          <t>2026-09-08 17:18:23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clare.w4</t>
+          <t>https://www.tiktok.com/@be__beauty1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>clairedipple66</t>
+          <t>beauty20208</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:02</t>
+          <t>2026-09-18 19:31:55</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairedipple66</t>
+          <t>https://www.tiktok.com/@beauty20208</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>chucky692</t>
+          <t>beemahempire</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1672,24 +1668,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-15 07:29:48</t>
+          <t>2026-09-15 11:52:03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chucky692</t>
+          <t>https://www.tiktok.com/@beemahempire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>chloeeflynnx</t>
+          <t>bellasbeauty07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1706,24 +1702,24 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-16 11:07:02</t>
+          <t>2026-09-08 10:16:05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chloeeflynnx</t>
+          <t>https://www.tiktok.com/@bellasbeauty07</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bgee2345</t>
+          <t>1sultan786</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1740,61 +1736,65 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-19 22:31:01</t>
+          <t>2026-09-21 10:45:04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bgee2345</t>
+          <t>https://www.tiktok.com/@1sultan786</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bex_lifeafter40</t>
+          <t>a13dde</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-17 15:30:23</t>
+          <t>2026-09-14 08:25:14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bex_lifeafter40</t>
+          <t>https://www.tiktok.com/@a13dde</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bettyaddo398</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>akiatuconteh</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
@@ -1808,31 +1808,31 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-14 14:52:28</t>
+          <t>2026-09-09 07:32:58</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bettyaddo398</t>
+          <t>https://www.tiktok.com/@akiatuconteh</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bellasbeauty07</t>
+          <t>alemap9</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1842,24 +1842,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-08 10:16:05</t>
+          <t>2026-09-14 00:26:00</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bellasbeauty07</t>
+          <t>https://www.tiktok.com/@alemap9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>beemahempire</t>
+          <t>_dosah</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1876,24 +1876,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-15 11:52:03</t>
+          <t>2026-09-21 14:58:25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beemahempire</t>
+          <t>https://www.tiktok.com/@_dosah</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>beauty20208</t>
+          <t>dy7yobwohcu6</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1910,58 +1910,58 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-18 19:31:55</t>
+          <t>2026-09-18 21:30:44</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty20208</t>
+          <t>https://www.tiktok.com/@dy7yobwohcu6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>be__beauty1</t>
+          <t>dulal.miah2471</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-08 17:18:23</t>
+          <t>2026-09-14 07:26:09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@be__beauty1</t>
+          <t>https://www.tiktok.com/@dulal.miah2471</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>barbaraasiedu771</t>
+          <t>drantero_10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1978,24 +1978,24 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-09 21:11:27</t>
+          <t>2026-09-17 14:48:32</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@barbaraasiedu771</t>
+          <t>https://www.tiktok.com/@drantero_10</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bantzuk</t>
+          <t>donsnewchapter</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-15 11:51:02</t>
+          <t>2026-09-16 09:45:02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2022,48 +2022,48 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bantzuk</t>
+          <t>https://www.tiktok.com/@donsnewchapter</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>badmashi.007</t>
+          <t>dollywithplaits73</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-14 18:24:25</t>
+          <t>2026-09-16 16:47:28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@badmashi.007</t>
+          <t>https://www.tiktok.com/@dollywithplaits73</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>emaanttshop</t>
+          <t>dillytwinmum</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2075,29 +2075,29 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-15 21:32:02</t>
+          <t>2026-09-21 09:55:02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emaanttshop</t>
+          <t>https://www.tiktok.com/@dillytwinmum</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>elizabetho001</t>
+          <t>diane.docherty</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2114,92 +2114,92 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-08 17:27:54</t>
+          <t>2026-09-15 09:50:59</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elizabetho001</t>
+          <t>https://www.tiktok.com/@diane.docherty</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>elizabethj27</t>
+          <t>deckynla</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-10 23:49:16</t>
+          <t>2026-09-09 11:52:15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elizabethj27</t>
+          <t>https://www.tiktok.com/@deckynla</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>eni_folabi</t>
+          <t>dailydealsuk03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-09 11:38:46</t>
+          <t>2026-09-21 10:45:03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eni_folabi</t>
+          <t>https://www.tiktok.com/@dailydealsuk03</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>georgiafergg</t>
+          <t>dabrat1138</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2216,24 +2216,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-10 01:03:04</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@georgiafergg</t>
+          <t>https://www.tiktok.com/@dabrat1138</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>gl80.31</t>
+          <t>courageous527</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-10 23:30:20</t>
+          <t>2026-09-11 19:24:33</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2260,14 +2260,14 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gl80.31</t>
+          <t>https://www.tiktok.com/@courageous527</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dailymusthaves20</t>
+          <t>climax.scenes</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2279,29 +2279,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-19 13:38:02</t>
+          <t>2026-09-21 06:20:00</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailymusthaves20</t>
+          <t>https://www.tiktok.com/@climax.scenes</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cosyhomewithsteph</t>
+          <t>claudia.claudia970</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2313,97 +2313,97 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-21 23:32:02</t>
+          <t>2026-09-20 22:09:26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cosyhomewithsteph</t>
+          <t>https://www.tiktok.com/@claudia.claudia970</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>dollywithplaits73</t>
+          <t>clare.w4</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-16 16:47:28</t>
+          <t>2026-09-10 14:06:31</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dollywithplaits73</t>
+          <t>https://www.tiktok.com/@clare.w4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>donsnewchapter</t>
+          <t>clairedipple66</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-16 09:45:02</t>
+          <t>2026-09-16 07:44:02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@donsnewchapter</t>
+          <t>https://www.tiktok.com/@clairedipple66</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>drantero_10</t>
+          <t>chucky692</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2420,31 +2420,31 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-17 14:48:32</t>
+          <t>2026-09-15 07:29:48</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@drantero_10</t>
+          <t>https://www.tiktok.com/@chucky692</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>dulal.miah2471</t>
+          <t>i.couldnt.give.a.fuckkkk</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2454,24 +2454,24 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-14 07:26:09</t>
+          <t>2026-09-12 11:58:47</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dulal.miah2471</t>
+          <t>https://www.tiktok.com/@i.couldnt.give.a.fuckkkk</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>dy7yobwohcu6</t>
+          <t>hrahmancookings</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2488,58 +2488,58 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-18 21:30:44</t>
+          <t>2026-09-08 19:45:29</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dy7yobwohcu6</t>
+          <t>https://www.tiktok.com/@hrahmancookings</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>courageous527</t>
+          <t>hinas_beauty_buys</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-11 19:24:33</t>
+          <t>2026-09-18 09:46:05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courageous527</t>
+          <t>https://www.tiktok.com/@hinas_beauty_buys</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dabrat1138</t>
+          <t>hchahal80</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2556,41 +2556,41 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-10 01:03:04</t>
+          <t>2026-09-15 20:35:21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dabrat1138</t>
+          <t>https://www.tiktok.com/@hchahal80</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>dailydealsuk03</t>
+          <t>jagjeetsinghkhals28</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-21 10:45:03</t>
+          <t>2026-09-22 19:57:03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2600,116 +2600,116 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailydealsuk03</t>
+          <t>https://www.tiktok.com/@jagjeetsinghkhals28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>jem17363</t>
+          <t>janetaliciac</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-21 17:28:16</t>
+          <t>2026-09-18 18:16:03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jem17363</t>
+          <t>https://www.tiktok.com/@janetaliciac</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>janetaliciac</t>
+          <t>jem17363</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-18 18:16:03</t>
+          <t>2026-09-21 17:28:16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@janetaliciac</t>
+          <t>https://www.tiktok.com/@jem17363</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>hrahmancookings</t>
+          <t>elizabethj27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-08 19:45:29</t>
+          <t>2026-09-10 23:49:16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hrahmancookings</t>
+          <t>https://www.tiktok.com/@elizabethj27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>joandusabe</t>
+          <t>georgiafergg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2726,24 +2726,24 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-19 08:31:29</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@joandusabe</t>
+          <t>https://www.tiktok.com/@georgiafergg</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>k.tee146</t>
+          <t>gl80.31</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2760,31 +2760,31 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-10 09:41:07</t>
+          <t>2026-09-10 23:30:20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@k.tee146</t>
+          <t>https://www.tiktok.com/@gl80.31</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kamo76710</t>
+          <t>haseeb.mum</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2794,58 +2794,58 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-20 05:21:24</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kamo76710</t>
+          <t>https://www.tiktok.com/@haseeb.mum</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>julietogu5</t>
+          <t>hashirahmed784</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-14 01:42:26</t>
+          <t>2026-09-21 21:16:02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@julietogu5</t>
+          <t>https://www.tiktok.com/@hashirahmed784</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>jxnxxkxk</t>
+          <t>eni_folabi</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2862,65 +2862,65 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-15 12:32:04</t>
+          <t>2026-09-09 11:38:46</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jxnxxkxk</t>
+          <t>https://www.tiktok.com/@eni_folabi</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kayyu247</t>
+          <t>feesdeals</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-09 09:42:51</t>
+          <t>2026-09-22 22:40:02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kayyu247</t>
+          <t>https://www.tiktok.com/@feesdeals</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>keeskloset</t>
+          <t>elizabetho001</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2930,330 +2930,330 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-16 09:57:04</t>
+          <t>2026-09-08 17:27:54</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@keeskloset</t>
+          <t>https://www.tiktok.com/@elizabetho001</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kennybabe692</t>
+          <t>emaanttshop</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-10 11:43:02</t>
+          <t>2026-09-15 21:32:02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kennybabe692</t>
+          <t>https://www.tiktok.com/@emaanttshop</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kofoworola2853</t>
+          <t>kaylee_dexter</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-11 10:52:59</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kofoworola2853</t>
+          <t>https://www.tiktok.com/@kaylee_dexter</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>konaduroi</t>
+          <t>kay.h0</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-15 03:00:44</t>
+          <t>2026-09-09 04:27:35</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@konaduroi</t>
+          <t>https://www.tiktok.com/@kay.h0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ladydonigbinosa</t>
+          <t>kayne202104</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-14 07:25:08</t>
+          <t>2026-09-22 21:46:02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ladydonigbinosa</t>
+          <t>https://www.tiktok.com/@kayne202104</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>katseyelocer</t>
+          <t>kayyu247</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-15 22:58:52</t>
+          <t>2026-09-09 09:42:51</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katseyelocer</t>
+          <t>https://www.tiktok.com/@kayyu247</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kay.h0</t>
+          <t>kofoworola2853</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-09 04:27:35</t>
+          <t>2026-09-11 10:52:59</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kay.h0</t>
+          <t>https://www.tiktok.com/@kofoworola2853</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>lucia25070</t>
+          <t>konaduroi</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-18 09:46:03</t>
+          <t>2026-09-15 03:00:44</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lucia25070</t>
+          <t>https://www.tiktok.com/@konaduroi</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>life52551</t>
+          <t>keeskloset</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-21 22:10:02</t>
+          <t>2026-09-16 09:57:04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@life52551</t>
+          <t>https://www.tiktok.com/@keeskloset</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>maish1002</t>
+          <t>kennybabe692</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-19 13:31:02</t>
+          <t>2026-09-10 11:43:02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maish1002</t>
+          <t>https://www.tiktok.com/@kennybabe692</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>m.3384</t>
+          <t>leerobert123</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3265,12 +3265,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-21 10:22:24</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3280,14 +3280,14 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@m.3384</t>
+          <t>https://www.tiktok.com/@leerobert123</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>markh_8</t>
+          <t>ladydonigbinosa</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3304,133 +3304,133 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-09 16:07:49</t>
+          <t>2026-09-14 07:25:08</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@markh_8</t>
+          <t>https://www.tiktok.com/@ladydonigbinosa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>mehmoonaali238</t>
+          <t>life52551</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-17 11:42:05</t>
+          <t>2026-09-21 22:10:02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mehmoonaali238</t>
+          <t>https://www.tiktok.com/@life52551</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>fernandasprivy</t>
+          <t>lucia25070</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-15 19:00:52</t>
+          <t>2026-09-18 09:46:03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fernandasprivy</t>
+          <t>https://www.tiktok.com/@lucia25070</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>gella4573</t>
+          <t>maish1002</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-16 07:50:13</t>
+          <t>2026-09-19 13:31:02</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gella4573</t>
+          <t>https://www.tiktok.com/@maish1002</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>hashirahmed784</t>
+          <t>m.3384</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3440,31 +3440,31 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-21 21:16:02</t>
+          <t>2026-09-21 10:22:24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hashirahmed784</t>
+          <t>https://www.tiktok.com/@m.3384</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>haseeb.mum</t>
+          <t>markh_8</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3474,24 +3474,24 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-09 16:07:49</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@haseeb.mum</t>
+          <t>https://www.tiktok.com/@markh_8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>hchahal80</t>
+          <t>maxi_berrie</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3508,65 +3508,65 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-15 20:35:21</t>
+          <t>2026-09-22 23:20:40</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hchahal80</t>
+          <t>https://www.tiktok.com/@maxi_berrie</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>hinas_beauty_buys</t>
+          <t>mehmoonaali238</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-18 09:46:05</t>
+          <t>2026-09-17 11:42:05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hinas_beauty_buys</t>
+          <t>https://www.tiktok.com/@mehmoonaali238</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>i.couldnt.give.a.fuckkkk</t>
+          <t>merz3859</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-12 11:58:47</t>
+          <t>2026-09-22 21:09:48</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@i.couldnt.give.a.fuckkkk</t>
+          <t>https://www.tiktok.com/@merz3859</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>deckynla</t>
+          <t>missyspranno12</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3610,24 +3610,24 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-09 11:52:15</t>
+          <t>2026-09-15 13:31:44</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@deckynla</t>
+          <t>https://www.tiktok.com/@missyspranno12</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>diane.docherty</t>
+          <t>monicalavern</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3644,31 +3644,31 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-15 09:50:59</t>
+          <t>2026-09-15 13:00:13</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@diane.docherty</t>
+          <t>https://www.tiktok.com/@monicalavern</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>dillytwinmum</t>
+          <t>moon19867</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3678,24 +3678,24 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-21 09:55:02</t>
+          <t>2026-09-11 19:21:54</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dillytwinmum</t>
+          <t>https://www.tiktok.com/@moon19867</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>nrahi28</t>
+          <t>muhammadsha110</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3712,24 +3712,24 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-20 14:59:29</t>
+          <t>2026-09-11 15:36:47</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nrahi28</t>
+          <t>https://www.tiktok.com/@muhammadsha110</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>nancymm52</t>
+          <t>mymojomindset</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3746,24 +3746,24 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-18 07:04:23</t>
+          <t>2026-09-15 10:29:05</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nancymm52</t>
+          <t>https://www.tiktok.com/@mymojomindset</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>nanahdaramy</t>
+          <t>joandusabe</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3780,58 +3780,58 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-14 00:12:20</t>
+          <t>2026-09-19 08:31:29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nanahdaramy</t>
+          <t>https://www.tiktok.com/@joandusabe</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>na2706_1</t>
+          <t>journey2debtfree</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-20 23:38:18</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@na2706_1</t>
+          <t>https://www.tiktok.com/@journey2debtfree</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mz.jada0</t>
+          <t>julietogu5</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3848,24 +3848,24 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-07 21:15:37</t>
+          <t>2026-09-14 01:42:26</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mz.jada0</t>
+          <t>https://www.tiktok.com/@julietogu5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mymojomindset</t>
+          <t>jxnxxkxk</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3882,24 +3882,24 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-15 10:29:05</t>
+          <t>2026-09-15 12:32:04</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mymojomindset</t>
+          <t>https://www.tiktok.com/@jxnxxkxk</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>muhammadsha110</t>
+          <t>k.tee146</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3916,24 +3916,24 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-11 15:36:47</t>
+          <t>2026-09-10 09:41:07</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@muhammadsha110</t>
+          <t>https://www.tiktok.com/@k.tee146</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>moon19867</t>
+          <t>kamo76710</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3950,58 +3950,58 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:54</t>
+          <t>2026-09-20 05:21:24</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moon19867</t>
+          <t>https://www.tiktok.com/@kamo76710</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>monicalavern</t>
+          <t>katseyelocer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-15 13:00:13</t>
+          <t>2026-09-15 22:58:52</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@monicalavern</t>
+          <t>https://www.tiktok.com/@katseyelocer</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>missyspranno12</t>
+          <t>fernandasprivy</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4018,31 +4018,31 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-15 13:31:44</t>
+          <t>2026-09-15 19:00:52</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@missyspranno12</t>
+          <t>https://www.tiktok.com/@fernandasprivy</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>positiveproductsuk</t>
+          <t>gella4573</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-15 11:53:04</t>
+          <t>2026-09-16 07:50:13</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4062,14 +4062,14 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@positiveproductsuk</t>
+          <t>https://www.tiktok.com/@gella4573</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>padnerkupakuwana</t>
+          <t>omolade.abebi</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4086,51 +4086,51 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-13 02:02:06</t>
+          <t>2026-09-17 10:33:35</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@padnerkupakuwana</t>
+          <t>https://www.tiktok.com/@omolade.abebi</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ornellabeauty25</t>
+          <t>oluwatoyosiabayom</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-07 22:41:47</t>
+          <t>2026-09-14 17:04:02</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ornellabeauty25</t>
+          <t>https://www.tiktok.com/@oluwatoyosiabayom</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4179,7 +4179,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>oluwatoyosiabayom</t>
+          <t>oladayomartins</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4196,24 +4196,24 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-14 17:04:02</t>
+          <t>2026-09-17 21:17:16</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwatoyosiabayom</t>
+          <t>https://www.tiktok.com/@oladayomartins</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>oladayomartins</t>
+          <t>nxthxnfrxmdxy</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4225,97 +4225,97 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-17 21:17:16</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oladayomartins</t>
+          <t>https://www.tiktok.com/@nxthxnfrxmdxy</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ranifarooq_3</t>
+          <t>nrahi28</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-13 22:37:56</t>
+          <t>2026-09-20 14:59:29</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ranifarooq_3</t>
+          <t>https://www.tiktok.com/@nrahi28</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>rory.the.cocker</t>
+          <t>nancymm52</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-18 18:13:02</t>
+          <t>2026-09-18 07:04:23</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rory.the.cocker</t>
+          <t>https://www.tiktok.com/@nancymm52</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ruksi1607</t>
+          <t>nanahdaramy</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-13 20:49:20</t>
+          <t>2026-09-14 00:12:20</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4342,14 +4342,14 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ruksi1607</t>
+          <t>https://www.tiktok.com/@nanahdaramy</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>rozana2026</t>
+          <t>na2706_1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-19 15:08:34</t>
+          <t>2026-09-20 23:38:18</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4376,14 +4376,14 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rozana2026</t>
+          <t>https://www.tiktok.com/@na2706_1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>sajarshed</t>
+          <t>r4xla15</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-19 10:17:35</t>
+          <t>2026-09-20 15:22:42</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4410,14 +4410,14 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sajarshed</t>
+          <t>https://www.tiktok.com/@r4xla15</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>samirakarim24</t>
+          <t>queeen_0f_hearts</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4434,24 +4434,24 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-11 11:10:48</t>
+          <t>2026-09-13 23:51:38</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samirakarim24</t>
+          <t>https://www.tiktok.com/@queeen_0f_hearts</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>sbegum.79</t>
+          <t>ranifarooq_3</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4468,24 +4468,24 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-21 17:38:25</t>
+          <t>2026-09-13 22:37:56</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sbegum.79</t>
+          <t>https://www.tiktok.com/@ranifarooq_3</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>saadia7166</t>
+          <t>radhekrishna_11</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4502,24 +4502,24 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-10 11:16:51</t>
+          <t>2026-09-21 11:21:47</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saadia7166</t>
+          <t>https://www.tiktok.com/@radhekrishna_11</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>sedi546</t>
+          <t>oyetunji.sunday</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4536,31 +4536,31 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-13 15:46:07</t>
+          <t>2026-09-12 13:08:25</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sedi546</t>
+          <t>https://www.tiktok.com/@oyetunji.sunday</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>seffshops</t>
+          <t>positivevibeonly62</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4570,31 +4570,31 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-21 10:52:04</t>
+          <t>2026-09-21 10:52:02</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seffshops</t>
+          <t>https://www.tiktok.com/@positivevibeonly62</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>oyetunji.sunday</t>
+          <t>online.shop8292</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4604,24 +4604,24 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-12 13:08:25</t>
+          <t>2026-09-22 19:57:03</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oyetunji.sunday</t>
+          <t>https://www.tiktok.com/@online.shop8292</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>positivevibeonly62</t>
+          <t>ruksi1607</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4638,24 +4638,24 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-21 10:52:02</t>
+          <t>2026-09-13 20:49:20</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@positivevibeonly62</t>
+          <t>https://www.tiktok.com/@ruksi1607</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>radhekrishna_11</t>
+          <t>rozana2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4672,24 +4672,24 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-21 11:21:47</t>
+          <t>2026-09-19 15:08:34</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@radhekrishna_11</t>
+          <t>https://www.tiktok.com/@rozana2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>r4xla15</t>
+          <t>saadia7166</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -4706,24 +4706,24 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-20 15:22:42</t>
+          <t>2026-09-10 11:16:51</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@r4xla15</t>
+          <t>https://www.tiktok.com/@saadia7166</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>queeen_0f_hearts</t>
+          <t>sajarshed</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4740,24 +4740,24 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-13 23:51:38</t>
+          <t>2026-09-19 10:17:35</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queeen_0f_hearts</t>
+          <t>https://www.tiktok.com/@sajarshed</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>omolade.abebi</t>
+          <t>sedi546</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4774,31 +4774,31 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-17 10:33:35</t>
+          <t>2026-09-13 15:46:07</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@omolade.abebi</t>
+          <t>https://www.tiktok.com/@sedi546</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>shopforfiver</t>
+          <t>seffshops</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4808,24 +4808,24 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-21 15:01:03</t>
+          <t>2026-09-21 10:52:04</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shopforfiver</t>
+          <t>https://www.tiktok.com/@seffshops</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>shoni1984</t>
+          <t>samirakarim24</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-10 08:20:01</t>
+          <t>2026-09-11 11:10:48</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4852,14 +4852,14 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shoni1984</t>
+          <t>https://www.tiktok.com/@samirakarim24</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>shazzbegum0</t>
+          <t>sbegum.79</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -4871,36 +4871,36 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-15 11:58:02</t>
+          <t>2026-09-21 17:38:25</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shazzbegum0</t>
+          <t>https://www.tiktok.com/@sbegum.79</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>sexybaby7657</t>
+          <t>sehrish2015</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4910,17 +4910,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-09 21:00:27</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sexybaby7657</t>
+          <t>https://www.tiktok.com/@sehrish2015</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -4961,7 +4961,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>sehrish2015</t>
+          <t>shazzbegum0</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -4978,24 +4978,24 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-15 11:58:02</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sehrish2015</t>
+          <t>https://www.tiktok.com/@shazzbegum0</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ste.baby6</t>
+          <t>sexybaby7657</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5012,133 +5012,133 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-09 16:28:17</t>
+          <t>2026-09-09 21:00:27</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ste.baby6</t>
+          <t>https://www.tiktok.com/@sexybaby7657</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>su.k806</t>
+          <t>reems_ttsshop</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-17 20:34:02</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@su.k806</t>
+          <t>https://www.tiktok.com/@reems_ttsshop</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>themamadee</t>
+          <t>rory.the.cocker</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-10 19:23:49</t>
+          <t>2026-09-18 18:13:02</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@themamadee</t>
+          <t>https://www.tiktok.com/@rory.the.cocker</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>thehomelylondon</t>
+          <t>padnerkupakuwana</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-18 15:51:23</t>
+          <t>2026-09-13 02:02:06</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thehomelylondon</t>
+          <t>https://www.tiktok.com/@padnerkupakuwana</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>syrashid</t>
+          <t>positiveproductsuk</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5148,24 +5148,24 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-11 12:35:39</t>
+          <t>2026-09-15 11:53:04</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@syrashid</t>
+          <t>https://www.tiktok.com/@positiveproductsuk</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>tifetito02</t>
+          <t>sjahan83</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5182,58 +5182,58 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:36</t>
+          <t>2026-09-12 13:46:48</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tifetito02</t>
+          <t>https://www.tiktok.com/@sjahan83</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>tixtok148</t>
+          <t>shukar7860</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-19 18:20:29</t>
+          <t>2026-09-22 09:29:34</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tixtok148</t>
+          <t>https://www.tiktok.com/@shukar7860</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>treeboyltd</t>
+          <t>shopforfiver</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5250,58 +5250,58 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-09-19 13:31:02</t>
+          <t>2026-09-21 15:01:03</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@treeboyltd</t>
+          <t>https://www.tiktok.com/@shopforfiver</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>uksaleshop</t>
+          <t>shoni1984</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-09-16 15:22:03</t>
+          <t>2026-09-10 08:20:01</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uksaleshop</t>
+          <t>https://www.tiktok.com/@shoni1984</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>sjahan83</t>
+          <t>syrashid</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5318,75 +5318,75 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-09-12 13:46:48</t>
+          <t>2026-09-11 12:35:39</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sjahan83</t>
+          <t>https://www.tiktok.com/@syrashid</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>user13457g</t>
+          <t>thehomelylondon</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-09-10 08:04:29</t>
+          <t>2026-09-18 15:51:23</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user13457g</t>
+          <t>https://www.tiktok.com/@thehomelylondon</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>user2182373993526</t>
+          <t>steffispicks</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-09-21 12:26:17</t>
+          <t>2026-09-22 19:57:03</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5396,14 +5396,14 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2182373993526</t>
+          <t>https://www.tiktok.com/@steffispicks</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>user5251816210173</t>
+          <t>ste.baby6</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -5420,24 +5420,24 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-15 20:13:06</t>
+          <t>2026-09-09 16:28:17</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user5251816210173</t>
+          <t>https://www.tiktok.com/@ste.baby6</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>user2773140226152</t>
+          <t>tifetito02</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5454,24 +5454,24 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-21 20:00:10</t>
+          <t>2026-09-16 21:55:36</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2773140226152</t>
+          <t>https://www.tiktok.com/@tifetito02</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>user806865620814</t>
+          <t>themamadee</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5488,24 +5488,24 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-09-20 17:13:54</t>
+          <t>2026-09-10 19:23:49</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user806865620814</t>
+          <t>https://www.tiktok.com/@themamadee</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>user8318338677754</t>
+          <t>trendtokshop88</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -5522,24 +5522,24 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-16 23:49:09</t>
+          <t>2026-09-22 19:57:03</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8318338677754</t>
+          <t>https://www.tiktok.com/@trendtokshop88</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>user9199380</t>
+          <t>tixtok148</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -5556,24 +5556,24 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-09-08 15:02:55</t>
+          <t>2026-09-19 18:20:29</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9199380</t>
+          <t>https://www.tiktok.com/@tixtok148</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>user7271293811175</t>
+          <t>tyanie1703</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -5590,41 +5590,41 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-11 08:42:27</t>
+          <t>2026-09-22 14:51:38</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user7271293811175</t>
+          <t>https://www.tiktok.com/@tyanie1703</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>vain119</t>
+          <t>uksaleshop</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-09-15 09:25:05</t>
+          <t>2026-09-16 15:22:03</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5634,14 +5634,14 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vain119</t>
+          <t>https://www.tiktok.com/@uksaleshop</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>vera77524</t>
+          <t>user13457g</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-09 07:38:35</t>
+          <t>2026-09-10 08:04:29</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5668,82 +5668,82 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vera77524</t>
+          <t>https://www.tiktok.com/@user13457g</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>yemi.bello3</t>
+          <t>su.k806</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-09-17 07:22:35</t>
+          <t>2026-09-17 20:34:02</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemi.bello3</t>
+          <t>https://www.tiktok.com/@su.k806</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>vikingbeardshop</t>
+          <t>user2182373993526</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-19 13:38:02</t>
+          <t>2026-09-21 12:26:17</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vikingbeardshop</t>
+          <t>https://www.tiktok.com/@user2182373993526</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>yemishittuedemayibo</t>
+          <t>user2773140226152</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -5760,24 +5760,24 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-09-19 00:15:14</t>
+          <t>2026-09-21 20:00:10</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemishittuedemayibo</t>
+          <t>https://www.tiktok.com/@user2773140226152</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>yourfindz0</t>
+          <t>user7271293811175</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -5794,24 +5794,24 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-09-19 13:38:02</t>
+          <t>2026-09-11 08:42:27</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yourfindz0</t>
+          <t>https://www.tiktok.com/@user7271293811175</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>yvonne21197</t>
+          <t>user5251816210173</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -5828,57 +5828,431 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-09-16 22:41:43</t>
+          <t>2026-09-15 20:13:06</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yvonne21197</t>
+          <t>https://www.tiktok.com/@user5251816210173</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
+          <t>user8318338677754</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-09-16 23:49:09</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user8318338677754</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>user9199380</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Ashwagandha Coffee</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Free sample from seller</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:02:55</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user9199380</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>user_78602223</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Ashwagandha Coffee</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Free sample from seller</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:40:46</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user_78602223</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>user806865620814</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:13:54</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user806865620814</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>vain119</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-09-15 09:25:05</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@vain119</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>vera77524</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-09-09 07:38:35</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@vera77524</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>yemi.bello3</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-09-17 07:22:35</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yemi.bello3</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>vikingbeardshop</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Shatavari 1300mg Extra Strength</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Free sample from seller</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-09-19 13:38:02</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@vikingbeardshop</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>yemishittuedemayibo</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:15:14</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yemishittuedemayibo</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>yourfindz0</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-09-19 13:38:02</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yourfindz0</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>yvonne21197</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-09-16 22:41:43</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yvonne21197</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
           <t>zahidaparveen624</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C167" t="inlineStr">
         <is>
           <t>1K-5K</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
         <is>
           <t>2026-09-11 13:42:26</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zahidaparveen624</t>
         </is>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H167"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1175,75 +1175,75 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bettyaddo398</t>
+          <t>bex_lifeafter40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-14 14:52:28</t>
+          <t>2026-09-17 15:30:23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bettyaddo398</t>
+          <t>https://www.tiktok.com/@bex_lifeafter40</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bex_lifeafter40</t>
+          <t>bgee2345</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-17 15:30:23</t>
+          <t>2026-09-19 22:31:01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bex_lifeafter40</t>
+          <t>https://www.tiktok.com/@bgee2345</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bgee2345</t>
+          <t>a13dde</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1260,65 +1260,69 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-19 22:31:01</t>
+          <t>2026-09-14 08:25:14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bgee2345</t>
+          <t>https://www.tiktok.com/@a13dde</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>chek_mi_shocase</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>akiatuconteh</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-22 17:56:02</t>
+          <t>2026-09-09 07:32:58</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chek_mi_shocase</t>
+          <t>https://www.tiktok.com/@akiatuconteh</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>chloeeflynnx</t>
+          <t>ali.syed873</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1328,24 +1332,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-16 11:07:02</t>
+          <t>2026-09-17 03:47:33</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chloeeflynnx</t>
+          <t>https://www.tiktok.com/@ali.syed873</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ali.syed873</t>
+          <t>alemap9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1362,17 +1366,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-17 03:47:33</t>
+          <t>2026-09-14 00:26:00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ali.syed873</t>
+          <t>https://www.tiktok.com/@alemap9</t>
         </is>
       </c>
     </row>
@@ -1549,75 +1553,75 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>barbaraasiedu771</t>
+          <t>be__beauty1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-09 21:11:27</t>
+          <t>2026-09-08 17:18:23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@barbaraasiedu771</t>
+          <t>https://www.tiktok.com/@be__beauty1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>be__beauty1</t>
+          <t>beauty20208</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-08 17:18:23</t>
+          <t>2026-09-18 19:31:55</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@be__beauty1</t>
+          <t>https://www.tiktok.com/@beauty20208</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>beauty20208</t>
+          <t>beemahempire</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1634,31 +1638,31 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-18 19:31:55</t>
+          <t>2026-09-15 11:52:03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty20208</t>
+          <t>https://www.tiktok.com/@beemahempire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>beemahempire</t>
+          <t>bellasbeauty07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1668,31 +1672,31 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-15 11:52:03</t>
+          <t>2026-09-08 10:16:05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beemahempire</t>
+          <t>https://www.tiktok.com/@bellasbeauty07</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bellasbeauty07</t>
+          <t>bettyaddo398</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1702,24 +1706,24 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-08 10:16:05</t>
+          <t>2026-09-14 14:52:28</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bellasbeauty07</t>
+          <t>https://www.tiktok.com/@bettyaddo398</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1sultan786</t>
+          <t>_dosah</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1736,7 +1740,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-21 10:45:04</t>
+          <t>2026-09-21 14:58:25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1746,14 +1750,14 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@1sultan786</t>
+          <t>https://www.tiktok.com/@_dosah</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>a13dde</t>
+          <t>1sultan786</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1770,31 +1774,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-14 08:25:14</t>
+          <t>2026-09-21 10:45:04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@a13dde</t>
+          <t>https://www.tiktok.com/@1sultan786</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>akiatuconteh</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>dulal.miah2471</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
@@ -1808,24 +1808,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-09 07:32:58</t>
+          <t>2026-09-14 07:26:09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akiatuconteh</t>
+          <t>https://www.tiktok.com/@dulal.miah2471</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>alemap9</t>
+          <t>drantero_10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1842,24 +1842,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-14 00:26:00</t>
+          <t>2026-09-17 14:48:32</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@alemap9</t>
+          <t>https://www.tiktok.com/@drantero_10</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>_dosah</t>
+          <t>donsnewchapter</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1876,65 +1876,65 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-21 14:58:25</t>
+          <t>2026-09-16 09:45:02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_dosah</t>
+          <t>https://www.tiktok.com/@donsnewchapter</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dy7yobwohcu6</t>
+          <t>dollywithplaits73</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-18 21:30:44</t>
+          <t>2026-09-16 16:47:28</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dy7yobwohcu6</t>
+          <t>https://www.tiktok.com/@dollywithplaits73</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>dulal.miah2471</t>
+          <t>dillytwinmum</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1944,24 +1944,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-14 07:26:09</t>
+          <t>2026-09-21 09:55:02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dulal.miah2471</t>
+          <t>https://www.tiktok.com/@dillytwinmum</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>drantero_10</t>
+          <t>diane.docherty</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1978,24 +1978,24 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-17 14:48:32</t>
+          <t>2026-09-15 09:50:59</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@drantero_10</t>
+          <t>https://www.tiktok.com/@diane.docherty</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>donsnewchapter</t>
+          <t>deckynla</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2012,31 +2012,31 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-16 09:45:02</t>
+          <t>2026-09-09 11:52:15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@donsnewchapter</t>
+          <t>https://www.tiktok.com/@deckynla</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>dollywithplaits73</t>
+          <t>dailydealsuk03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2046,31 +2046,31 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-16 16:47:28</t>
+          <t>2026-09-21 10:45:03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dollywithplaits73</t>
+          <t>https://www.tiktok.com/@dailydealsuk03</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>dillytwinmum</t>
+          <t>courageous527</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2080,160 +2080,160 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-21 09:55:02</t>
+          <t>2026-09-11 19:24:33</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dillytwinmum</t>
+          <t>https://www.tiktok.com/@courageous527</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>diane.docherty</t>
+          <t>climax.scenes</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-15 09:50:59</t>
+          <t>2026-09-21 06:20:00</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@diane.docherty</t>
+          <t>https://www.tiktok.com/@climax.scenes</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>deckynla</t>
+          <t>claudia.claudia970</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-09 11:52:15</t>
+          <t>2026-09-20 22:09:26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@deckynla</t>
+          <t>https://www.tiktok.com/@claudia.claudia970</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>dailydealsuk03</t>
+          <t>clare.w4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-21 10:45:03</t>
+          <t>2026-09-10 14:06:31</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailydealsuk03</t>
+          <t>https://www.tiktok.com/@clare.w4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>dabrat1138</t>
+          <t>clairedipple66</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-10 01:03:04</t>
+          <t>2026-09-16 07:44:02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dabrat1138</t>
+          <t>https://www.tiktok.com/@clairedipple66</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>courageous527</t>
+          <t>chucky692</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2250,24 +2250,24 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-11 19:24:33</t>
+          <t>2026-09-15 07:29:48</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courageous527</t>
+          <t>https://www.tiktok.com/@chucky692</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>climax.scenes</t>
+          <t>chloeeflynnx</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2279,36 +2279,36 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-21 06:20:00</t>
+          <t>2026-09-16 11:07:02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@climax.scenes</t>
+          <t>https://www.tiktok.com/@chloeeflynnx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>claudia.claudia970</t>
+          <t>chek_mi_shocase</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-20 22:09:26</t>
+          <t>2026-09-22 17:56:02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@claudia.claudia970</t>
+          <t>https://www.tiktok.com/@chek_mi_shocase</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>clare.w4</t>
+          <t>hrahmancookings</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2352,31 +2352,31 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-10 14:06:31</t>
+          <t>2026-09-08 19:45:29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clare.w4</t>
+          <t>https://www.tiktok.com/@hrahmancookings</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>clairedipple66</t>
+          <t>hinas_beauty_buys</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:02</t>
+          <t>2026-09-18 09:46:05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairedipple66</t>
+          <t>https://www.tiktok.com/@hinas_beauty_buys</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>chucky692</t>
+          <t>hchahal80</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-15 07:29:48</t>
+          <t>2026-09-15 20:35:21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2430,55 +2430,55 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chucky692</t>
+          <t>https://www.tiktok.com/@hchahal80</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>i.couldnt.give.a.fuckkkk</t>
+          <t>hashirahmed784</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-12 11:58:47</t>
+          <t>2026-09-21 21:16:02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@i.couldnt.give.a.fuckkkk</t>
+          <t>https://www.tiktok.com/@hashirahmed784</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>hrahmancookings</t>
+          <t>jagjeetsinghkhals28</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2488,99 +2488,99 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-08 19:45:29</t>
+          <t>2026-09-22 19:57:03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hrahmancookings</t>
+          <t>https://www.tiktok.com/@jagjeetsinghkhals28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>hinas_beauty_buys</t>
+          <t>i.couldnt.give.a.fuckkkk</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-18 09:46:05</t>
+          <t>2026-09-12 11:58:47</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hinas_beauty_buys</t>
+          <t>https://www.tiktok.com/@i.couldnt.give.a.fuckkkk</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>hchahal80</t>
+          <t>janetaliciac</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-15 20:35:21</t>
+          <t>2026-09-18 18:16:03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hchahal80</t>
+          <t>https://www.tiktok.com/@janetaliciac</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>jagjeetsinghkhals28</t>
+          <t>dy7yobwohcu6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2590,58 +2590,58 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:03</t>
+          <t>2026-09-18 21:30:44</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jagjeetsinghkhals28</t>
+          <t>https://www.tiktok.com/@dy7yobwohcu6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>janetaliciac</t>
+          <t>gella4573</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-18 18:16:03</t>
+          <t>2026-09-16 07:50:13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@janetaliciac</t>
+          <t>https://www.tiktok.com/@gella4573</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>jem17363</t>
+          <t>georgiafergg</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2658,41 +2658,41 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-21 17:28:16</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jem17363</t>
+          <t>https://www.tiktok.com/@georgiafergg</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>elizabethj27</t>
+          <t>gl80.31</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-10 23:49:16</t>
+          <t>2026-09-10 23:30:20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2702,21 +2702,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elizabethj27</t>
+          <t>https://www.tiktok.com/@gl80.31</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>georgiafergg</t>
+          <t>haseeb.mum</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2736,55 +2736,55 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@georgiafergg</t>
+          <t>https://www.tiktok.com/@haseeb.mum</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>gl80.31</t>
+          <t>emaanttshop</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-10 23:30:20</t>
+          <t>2026-09-15 21:32:02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gl80.31</t>
+          <t>https://www.tiktok.com/@emaanttshop</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>haseeb.mum</t>
+          <t>eni_folabi</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2794,99 +2794,99 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-09 11:38:46</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@haseeb.mum</t>
+          <t>https://www.tiktok.com/@eni_folabi</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>hashirahmed784</t>
+          <t>elizabetho001</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-21 21:16:02</t>
+          <t>2026-09-08 17:27:54</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hashirahmed784</t>
+          <t>https://www.tiktok.com/@elizabetho001</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>eni_folabi</t>
+          <t>elizabethj27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-09 11:38:46</t>
+          <t>2026-09-10 23:49:16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eni_folabi</t>
+          <t>https://www.tiktok.com/@elizabethj27</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>feesdeals</t>
+          <t>kay.h0</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2896,65 +2896,65 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-22 22:40:02</t>
+          <t>2026-09-09 04:27:35</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@feesdeals</t>
+          <t>https://www.tiktok.com/@kay.h0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>elizabetho001</t>
+          <t>katseyelocer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-08 17:27:54</t>
+          <t>2026-09-15 22:58:52</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elizabetho001</t>
+          <t>https://www.tiktok.com/@katseyelocer</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>emaanttshop</t>
+          <t>kaylee_dexter</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2964,24 +2964,24 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-15 21:32:02</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emaanttshop</t>
+          <t>https://www.tiktok.com/@kaylee_dexter</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kaylee_dexter</t>
+          <t>kayne202104</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-22 21:46:02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3008,75 +3008,75 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaylee_dexter</t>
+          <t>https://www.tiktok.com/@kayne202104</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kay.h0</t>
+          <t>kennybabe692</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-09 04:27:35</t>
+          <t>2026-09-10 11:43:02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kay.h0</t>
+          <t>https://www.tiktok.com/@kennybabe692</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kayne202104</t>
+          <t>kofoworola2853</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-22 21:46:02</t>
+          <t>2026-09-11 10:52:59</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kayne202104</t>
+          <t>https://www.tiktok.com/@kofoworola2853</t>
         </is>
       </c>
     </row>
@@ -3117,14 +3117,14 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kofoworola2853</t>
+          <t>keeskloset</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3134,24 +3134,24 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-11 10:52:59</t>
+          <t>2026-09-16 09:57:04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kofoworola2853</t>
+          <t>https://www.tiktok.com/@keeskloset</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>konaduroi</t>
+          <t>ladydonigbinosa</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3168,31 +3168,31 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-15 03:00:44</t>
+          <t>2026-09-14 07:25:08</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@konaduroi</t>
+          <t>https://www.tiktok.com/@ladydonigbinosa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>keeskloset</t>
+          <t>konaduroi</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3202,31 +3202,31 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-16 09:57:04</t>
+          <t>2026-09-15 03:00:44</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@keeskloset</t>
+          <t>https://www.tiktok.com/@konaduroi</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kennybabe692</t>
+          <t>leerobert123</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3236,92 +3236,92 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-10 11:43:02</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kennybabe692</t>
+          <t>https://www.tiktok.com/@leerobert123</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>leerobert123</t>
+          <t>life52551</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-21 22:10:02</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@leerobert123</t>
+          <t>https://www.tiktok.com/@life52551</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ladydonigbinosa</t>
+          <t>m.3384</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-14 07:25:08</t>
+          <t>2026-09-21 10:22:24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ladydonigbinosa</t>
+          <t>https://www.tiktok.com/@m.3384</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>life52551</t>
+          <t>lucia25070</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3338,31 +3338,31 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-21 22:10:02</t>
+          <t>2026-09-18 09:46:03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@life52551</t>
+          <t>https://www.tiktok.com/@lucia25070</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>lucia25070</t>
+          <t>maish1002</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3372,92 +3372,92 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-18 09:46:03</t>
+          <t>2026-09-19 13:31:02</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lucia25070</t>
+          <t>https://www.tiktok.com/@maish1002</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>maish1002</t>
+          <t>markh_8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-19 13:31:02</t>
+          <t>2026-09-09 16:07:49</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maish1002</t>
+          <t>https://www.tiktok.com/@markh_8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>m.3384</t>
+          <t>maxi_berrie</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-21 10:22:24</t>
+          <t>2026-09-22 23:20:40</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@m.3384</t>
+          <t>https://www.tiktok.com/@maxi_berrie</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>markh_8</t>
+          <t>mehmoonaali238</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3474,24 +3474,24 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-09 16:07:49</t>
+          <t>2026-09-17 11:42:05</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@markh_8</t>
+          <t>https://www.tiktok.com/@mehmoonaali238</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>maxi_berrie</t>
+          <t>merz3859</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-22 23:20:40</t>
+          <t>2026-09-22 21:09:48</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3518,14 +3518,14 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maxi_berrie</t>
+          <t>https://www.tiktok.com/@merz3859</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mehmoonaali238</t>
+          <t>missyspranno12</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3542,24 +3542,24 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-17 11:42:05</t>
+          <t>2026-09-15 13:31:44</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mehmoonaali238</t>
+          <t>https://www.tiktok.com/@missyspranno12</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>merz3859</t>
+          <t>monicalavern</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3576,24 +3576,24 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-22 21:09:48</t>
+          <t>2026-09-15 13:00:13</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@merz3859</t>
+          <t>https://www.tiktok.com/@monicalavern</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>missyspranno12</t>
+          <t>moon19867</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3610,24 +3610,24 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-15 13:31:44</t>
+          <t>2026-09-11 19:21:54</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@missyspranno12</t>
+          <t>https://www.tiktok.com/@moon19867</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>monicalavern</t>
+          <t>muhammadsha110</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3644,24 +3644,24 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-15 13:00:13</t>
+          <t>2026-09-11 15:36:47</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@monicalavern</t>
+          <t>https://www.tiktok.com/@muhammadsha110</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>moon19867</t>
+          <t>jem17363</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3678,24 +3678,24 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:54</t>
+          <t>2026-09-21 17:28:16</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moon19867</t>
+          <t>https://www.tiktok.com/@jem17363</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>muhammadsha110</t>
+          <t>joandusabe</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3712,58 +3712,58 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-11 15:36:47</t>
+          <t>2026-09-19 08:31:29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@muhammadsha110</t>
+          <t>https://www.tiktok.com/@joandusabe</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mymojomindset</t>
+          <t>journey2debtfree</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-15 10:29:05</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mymojomindset</t>
+          <t>https://www.tiktok.com/@journey2debtfree</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>joandusabe</t>
+          <t>julietogu5</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3780,58 +3780,58 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-19 08:31:29</t>
+          <t>2026-09-14 01:42:26</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@joandusabe</t>
+          <t>https://www.tiktok.com/@julietogu5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>journey2debtfree</t>
+          <t>jxnxxkxk</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-15 12:32:04</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@journey2debtfree</t>
+          <t>https://www.tiktok.com/@jxnxxkxk</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>julietogu5</t>
+          <t>k.tee146</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3848,24 +3848,24 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-14 01:42:26</t>
+          <t>2026-09-10 09:41:07</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@julietogu5</t>
+          <t>https://www.tiktok.com/@k.tee146</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>jxnxxkxk</t>
+          <t>kamo76710</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3882,58 +3882,58 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-15 12:32:04</t>
+          <t>2026-09-20 05:21:24</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jxnxxkxk</t>
+          <t>https://www.tiktok.com/@kamo76710</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>k.tee146</t>
+          <t>feesdeals</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-10 09:41:07</t>
+          <t>2026-09-22 22:40:02</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@k.tee146</t>
+          <t>https://www.tiktok.com/@feesdeals</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kamo76710</t>
+          <t>fernandasprivy</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3950,24 +3950,24 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-20 05:21:24</t>
+          <t>2026-09-15 19:00:52</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kamo76710</t>
+          <t>https://www.tiktok.com/@fernandasprivy</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>katseyelocer</t>
+          <t>oluwatoyosiabayom</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -3984,31 +3984,39 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-15 22:58:52</t>
+          <t>2026-09-14 17:04:02</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katseyelocer</t>
+          <t>https://www.tiktok.com/@oluwatoyosiabayom</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>fernandasprivy</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
+          <t>olascornerpage</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4018,65 +4026,65 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-15 19:00:52</t>
+          <t>2026-09-12 21:52:02</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fernandasprivy</t>
+          <t>https://www.tiktok.com/@olascornerpage</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>gella4573</t>
+          <t>oladayomartins</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-16 07:50:13</t>
+          <t>2026-09-17 21:17:16</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gella4573</t>
+          <t>https://www.tiktok.com/@oladayomartins</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>omolade.abebi</t>
+          <t>nxthxnfrxmdxy</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4086,73 +4094,65 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-17 10:33:35</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@omolade.abebi</t>
+          <t>https://www.tiktok.com/@nxthxnfrxmdxy</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>oluwatoyosiabayom</t>
+          <t>nrahi28</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-14 17:04:02</t>
+          <t>2026-09-20 14:59:29</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwatoyosiabayom</t>
+          <t>https://www.tiktok.com/@nrahi28</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>olascornerpage</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>nancymm52</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4162,65 +4162,65 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-12 21:52:02</t>
+          <t>2026-09-18 07:04:23</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@olascornerpage</t>
+          <t>https://www.tiktok.com/@nancymm52</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>oladayomartins</t>
+          <t>nanahdaramy</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-17 21:17:16</t>
+          <t>2026-09-14 00:12:20</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oladayomartins</t>
+          <t>https://www.tiktok.com/@nanahdaramy</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>nxthxnfrxmdxy</t>
+          <t>na2706_1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4230,24 +4230,24 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-20 23:38:18</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nxthxnfrxmdxy</t>
+          <t>https://www.tiktok.com/@na2706_1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>nrahi28</t>
+          <t>mymojomindset</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4264,24 +4264,24 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-20 14:59:29</t>
+          <t>2026-09-15 10:29:05</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nrahi28</t>
+          <t>https://www.tiktok.com/@mymojomindset</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>nancymm52</t>
+          <t>queeen_0f_hearts</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4298,24 +4298,24 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-18 07:04:23</t>
+          <t>2026-09-13 23:51:38</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nancymm52</t>
+          <t>https://www.tiktok.com/@queeen_0f_hearts</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>nanahdaramy</t>
+          <t>positivevibeonly62</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4332,24 +4332,24 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-14 00:12:20</t>
+          <t>2026-09-21 10:52:02</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nanahdaramy</t>
+          <t>https://www.tiktok.com/@positivevibeonly62</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>na2706_1</t>
+          <t>radhekrishna_11</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4366,17 +4366,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-20 23:38:18</t>
+          <t>2026-09-21 11:21:47</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@na2706_1</t>
+          <t>https://www.tiktok.com/@radhekrishna_11</t>
         </is>
       </c>
     </row>
@@ -4417,14 +4417,14 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>queeen_0f_hearts</t>
+          <t>online.shop8292</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4434,24 +4434,24 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-13 23:51:38</t>
+          <t>2026-09-22 19:57:03</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queeen_0f_hearts</t>
+          <t>https://www.tiktok.com/@online.shop8292</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ranifarooq_3</t>
+          <t>positiveproductsuk</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4463,29 +4463,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-13 22:37:56</t>
+          <t>2026-09-15 11:53:04</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ranifarooq_3</t>
+          <t>https://www.tiktok.com/@positiveproductsuk</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>radhekrishna_11</t>
+          <t>omolade.abebi</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4502,24 +4502,24 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-21 11:21:47</t>
+          <t>2026-09-17 10:33:35</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@radhekrishna_11</t>
+          <t>https://www.tiktok.com/@omolade.abebi</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>oyetunji.sunday</t>
+          <t>rozana2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4536,65 +4536,65 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-12 13:08:25</t>
+          <t>2026-09-19 15:08:34</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oyetunji.sunday</t>
+          <t>https://www.tiktok.com/@rozana2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>positivevibeonly62</t>
+          <t>rory.the.cocker</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-21 10:52:02</t>
+          <t>2026-09-18 18:13:02</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@positivevibeonly62</t>
+          <t>https://www.tiktok.com/@rory.the.cocker</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>online.shop8292</t>
+          <t>ruksi1607</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4604,24 +4604,24 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:03</t>
+          <t>2026-09-13 20:49:20</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@online.shop8292</t>
+          <t>https://www.tiktok.com/@ruksi1607</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ruksi1607</t>
+          <t>saadia7166</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4638,58 +4638,58 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-13 20:49:20</t>
+          <t>2026-09-10 11:16:51</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ruksi1607</t>
+          <t>https://www.tiktok.com/@saadia7166</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>rozana2026</t>
+          <t>sbegum.79</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-19 15:08:34</t>
+          <t>2026-09-21 17:38:25</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rozana2026</t>
+          <t>https://www.tiktok.com/@sbegum.79</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>saadia7166</t>
+          <t>sedi546</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -4706,17 +4706,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-10 11:16:51</t>
+          <t>2026-09-13 15:46:07</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saadia7166</t>
+          <t>https://www.tiktok.com/@sedi546</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>sedi546</t>
+          <t>samirakarim24</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4774,41 +4774,41 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-13 15:46:07</t>
+          <t>2026-09-11 11:10:48</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sedi546</t>
+          <t>https://www.tiktok.com/@samirakarim24</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>seffshops</t>
+          <t>sehnamiee</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-21 10:52:04</t>
+          <t>2026-09-21 20:46:02</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4818,21 +4818,21 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seffshops</t>
+          <t>https://www.tiktok.com/@sehnamiee</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>samirakarim24</t>
+          <t>seffshops</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4842,51 +4842,51 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-11 11:10:48</t>
+          <t>2026-09-21 10:52:04</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samirakarim24</t>
+          <t>https://www.tiktok.com/@seffshops</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>sbegum.79</t>
+          <t>sexybaby7657</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-21 17:38:25</t>
+          <t>2026-09-09 21:00:27</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sbegum.79</t>
+          <t>https://www.tiktok.com/@sexybaby7657</t>
         </is>
       </c>
     </row>
@@ -4927,41 +4927,41 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>sehnamiee</t>
+          <t>reems_ttsshop</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-09-21 20:46:02</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sehnamiee</t>
+          <t>https://www.tiktok.com/@reems_ttsshop</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>shazzbegum0</t>
+          <t>ranifarooq_3</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -4973,29 +4973,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-15 11:58:02</t>
+          <t>2026-09-13 22:37:56</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shazzbegum0</t>
+          <t>https://www.tiktok.com/@ranifarooq_3</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>sexybaby7657</t>
+          <t>oyetunji.sunday</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5012,31 +5012,31 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-09 21:00:27</t>
+          <t>2026-09-12 13:08:25</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sexybaby7657</t>
+          <t>https://www.tiktok.com/@oyetunji.sunday</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>reems_ttsshop</t>
+          <t>padnerkupakuwana</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5046,58 +5046,58 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-13 02:02:06</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reems_ttsshop</t>
+          <t>https://www.tiktok.com/@padnerkupakuwana</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rory.the.cocker</t>
+          <t>sjahan83</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-18 18:13:02</t>
+          <t>2026-09-12 13:46:48</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rory.the.cocker</t>
+          <t>https://www.tiktok.com/@sjahan83</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>padnerkupakuwana</t>
+          <t>shukar7860</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5114,31 +5114,31 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-13 02:02:06</t>
+          <t>2026-09-22 09:29:34</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@padnerkupakuwana</t>
+          <t>https://www.tiktok.com/@shukar7860</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>positiveproductsuk</t>
+          <t>shopforfiver</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5148,24 +5148,24 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-15 11:53:04</t>
+          <t>2026-09-21 15:01:03</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@positiveproductsuk</t>
+          <t>https://www.tiktok.com/@shopforfiver</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>sjahan83</t>
+          <t>shoni1984</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5182,24 +5182,24 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-12 13:46:48</t>
+          <t>2026-09-10 08:20:01</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sjahan83</t>
+          <t>https://www.tiktok.com/@shoni1984</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>shukar7860</t>
+          <t>syrashid</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5216,92 +5216,92 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-22 09:29:34</t>
+          <t>2026-09-11 12:35:39</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shukar7860</t>
+          <t>https://www.tiktok.com/@syrashid</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>shopforfiver</t>
+          <t>thehomelylondon</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-09-21 15:01:03</t>
+          <t>2026-09-18 15:51:23</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shopforfiver</t>
+          <t>https://www.tiktok.com/@thehomelylondon</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>shoni1984</t>
+          <t>steffispicks</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-09-10 08:20:01</t>
+          <t>2026-09-22 19:57:03</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shoni1984</t>
+          <t>https://www.tiktok.com/@steffispicks</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>syrashid</t>
+          <t>ste.baby6</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5318,92 +5318,92 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-09-11 12:35:39</t>
+          <t>2026-09-09 16:28:17</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@syrashid</t>
+          <t>https://www.tiktok.com/@ste.baby6</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>thehomelylondon</t>
+          <t>tifetito02</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-09-18 15:51:23</t>
+          <t>2026-09-16 21:55:36</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thehomelylondon</t>
+          <t>https://www.tiktok.com/@tifetito02</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>steffispicks</t>
+          <t>themamadee</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:03</t>
+          <t>2026-09-10 19:23:49</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@steffispicks</t>
+          <t>https://www.tiktok.com/@themamadee</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ste.baby6</t>
+          <t>trendtokshop88</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -5420,58 +5420,58 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-09 16:28:17</t>
+          <t>2026-09-22 19:57:03</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ste.baby6</t>
+          <t>https://www.tiktok.com/@trendtokshop88</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>tifetito02</t>
+          <t>tixtok148</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:36</t>
+          <t>2026-09-19 18:20:29</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tifetito02</t>
+          <t>https://www.tiktok.com/@tixtok148</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>themamadee</t>
+          <t>tyanie1703</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5488,160 +5488,160 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-09-10 19:23:49</t>
+          <t>2026-09-22 14:51:38</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@themamadee</t>
+          <t>https://www.tiktok.com/@tyanie1703</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>trendtokshop88</t>
+          <t>uksaleshop</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:03</t>
+          <t>2026-09-16 15:22:03</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@trendtokshop88</t>
+          <t>https://www.tiktok.com/@uksaleshop</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tixtok148</t>
+          <t>user13457g</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-09-19 18:20:29</t>
+          <t>2026-09-10 08:04:29</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tixtok148</t>
+          <t>https://www.tiktok.com/@user13457g</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>tyanie1703</t>
+          <t>su.k806</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-22 14:51:38</t>
+          <t>2026-09-17 20:34:02</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tyanie1703</t>
+          <t>https://www.tiktok.com/@su.k806</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>uksaleshop</t>
+          <t>user2182373993526</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-09-16 15:22:03</t>
+          <t>2026-09-21 12:26:17</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uksaleshop</t>
+          <t>https://www.tiktok.com/@user2182373993526</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>user13457g</t>
+          <t>user2773140226152</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -5658,58 +5658,58 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-10 08:04:29</t>
+          <t>2026-09-21 20:00:10</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user13457g</t>
+          <t>https://www.tiktok.com/@user2773140226152</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>su.k806</t>
+          <t>user7271293811175</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-09-17 20:34:02</t>
+          <t>2026-09-11 08:42:27</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@su.k806</t>
+          <t>https://www.tiktok.com/@user7271293811175</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>user2182373993526</t>
+          <t>user5251816210173</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -5726,24 +5726,24 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-21 12:26:17</t>
+          <t>2026-09-15 20:13:06</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2182373993526</t>
+          <t>https://www.tiktok.com/@user5251816210173</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>user2773140226152</t>
+          <t>user8318338677754</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -5760,92 +5760,92 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-09-21 20:00:10</t>
+          <t>2026-09-16 23:49:09</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2773140226152</t>
+          <t>https://www.tiktok.com/@user8318338677754</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>user7271293811175</t>
+          <t>user9199380</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-09-11 08:42:27</t>
+          <t>2026-09-08 15:02:55</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user7271293811175</t>
+          <t>https://www.tiktok.com/@user9199380</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>user5251816210173</t>
+          <t>user_78602223</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-09-15 20:13:06</t>
+          <t>2026-09-22 17:40:46</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user5251816210173</t>
+          <t>https://www.tiktok.com/@user_78602223</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>user8318338677754</t>
+          <t>user806865620814</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -5862,92 +5862,92 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-09-16 23:49:09</t>
+          <t>2026-09-20 17:13:54</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8318338677754</t>
+          <t>https://www.tiktok.com/@user806865620814</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>user9199380</t>
+          <t>vain119</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-09-08 15:02:55</t>
+          <t>2026-09-15 09:25:05</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9199380</t>
+          <t>https://www.tiktok.com/@vain119</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>user_78602223</t>
+          <t>vera77524</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-09-22 17:40:46</t>
+          <t>2026-09-09 07:38:35</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user_78602223</t>
+          <t>https://www.tiktok.com/@vera77524</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>user806865620814</t>
+          <t>yemi.bello3</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -5964,58 +5964,58 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-09-20 17:13:54</t>
+          <t>2026-09-17 07:22:35</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user806865620814</t>
+          <t>https://www.tiktok.com/@yemi.bello3</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>vain119</t>
+          <t>vikingbeardshop</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-09-15 09:25:05</t>
+          <t>2026-09-19 13:38:02</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vain119</t>
+          <t>https://www.tiktok.com/@vikingbeardshop</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>vera77524</t>
+          <t>yemishittuedemayibo</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -6032,24 +6032,24 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-09-09 07:38:35</t>
+          <t>2026-09-19 00:15:14</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vera77524</t>
+          <t>https://www.tiktok.com/@yemishittuedemayibo</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>yemi.bello3</t>
+          <t>yourfindz0</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -6066,62 +6066,70 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-09-17 07:22:35</t>
+          <t>2026-09-19 13:38:02</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemi.bello3</t>
+          <t>https://www.tiktok.com/@yourfindz0</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>vikingbeardshop</t>
+          <t>yvonne21197</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-09-19 13:38:02</t>
+          <t>2026-09-16 22:41:43</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vikingbeardshop</t>
+          <t>https://www.tiktok.com/@yvonne21197</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>yemishittuedemayibo</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr"/>
-      <c r="C164" t="inlineStr"/>
+          <t>zahidaparveen624</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D164" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6134,125 +6142,15 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-09-19 00:15:14</t>
+          <t>2026-09-11 13:42:26</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@yemishittuedemayibo</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>yourfindz0</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr"/>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-09-19 13:38:02</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@yourfindz0</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>yvonne21197</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr"/>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-09-16 22:41:43</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@yvonne21197</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>zahidaparveen624</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-09-11 13:42:26</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zahidaparveen624</t>
         </is>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -545,49 +545,49 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shannonroberts16595</t>
+          <t>brynnaellen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-21 10:52:02</t>
+          <t>2026-09-24 00:22:02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shannonroberts16595</t>
+          <t>https://www.tiktok.com/@brynnaellen</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sue_cole</t>
+          <t>shannonroberts16595</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,39 +597,39 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>100K-250K</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-21 22:34:02</t>
+          <t>2026-09-21 10:52:02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sue_cole</t>
+          <t>https://www.tiktok.com/@shannonroberts16595</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tofanirina</t>
+          <t>1sultan786</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -639,39 +639,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-12 19:42:02</t>
+          <t>2026-09-21 10:45:04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tofanirina</t>
+          <t>https://www.tiktok.com/@1sultan786</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>iboughtyousomething</t>
+          <t>sehnamiee</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -681,32 +681,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-14 06:52:02</t>
+          <t>2026-09-21 20:46:02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iboughtyousomething</t>
+          <t>https://www.tiktok.com/@sehnamiee</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rk_uk3</t>
+          <t>miaweb7new</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -822,24 +822,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-14 05:38:02</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rk_uk3</t>
+          <t>https://www.tiktok.com/@miaweb7new</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>angelinas.finds</t>
+          <t>kirsten_mum_of_3_tts</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -849,39 +849,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-14 05:38:02</t>
+          <t>2026-09-23 20:18:02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angelinas.finds</t>
+          <t>https://www.tiktok.com/@kirsten_mum_of_3_tts</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>jenna_g_tiktok</t>
+          <t>hashirahmed784</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -891,49 +891,49 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-17 15:30:26</t>
+          <t>2026-09-21 21:16:02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jenna_g_tiktok</t>
+          <t>https://www.tiktok.com/@hashirahmed784</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ziab442</t>
+          <t>angelinas.finds</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -953,29 +953,29 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ziab442</t>
+          <t>https://www.tiktok.com/@angelinas.finds</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inayapicks123</t>
+          <t>bex_lifeafter40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -990,29 +990,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-14 11:03:03</t>
+          <t>2026-09-17 15:30:23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@inayapicks123</t>
+          <t>https://www.tiktok.com/@bex_lifeafter40</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>realabdu</t>
+          <t>jenna_g_tiktok</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1032,29 +1032,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-14 06:36:02</t>
+          <t>2026-09-17 15:30:26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@realabdu</t>
+          <t>https://www.tiktok.com/@jenna_g_tiktok</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>eminence4009</t>
+          <t>fairyfaryal11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1074,34 +1074,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-08 10:27:05</t>
+          <t>2026-09-24 20:07:02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eminence4009</t>
+          <t>https://www.tiktok.com/@fairyfaryal11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>manvsparkins0n</t>
+          <t>ziab442</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>250K-500K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1116,29 +1116,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-14 06:51:02</t>
+          <t>2026-09-14 05:38:02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@manvsparkins0n</t>
+          <t>https://www.tiktok.com/@ziab442</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>uncutwithice</t>
+          <t>emaanttshop</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1153,104 +1153,128 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-12 12:02:03</t>
+          <t>2026-09-15 21:32:02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uncutwithice</t>
+          <t>https://www.tiktok.com/@emaanttshop</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bex_lifeafter40</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+          <t>seffshops</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-17 15:30:23</t>
+          <t>2026-09-21 10:52:04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bex_lifeafter40</t>
+          <t>https://www.tiktok.com/@seffshops</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bgee2345</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+          <t>inayapicks123</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>25K-50K</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-19 22:31:01</t>
+          <t>2026-09-14 11:03:03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bgee2345</t>
+          <t>https://www.tiktok.com/@inayapicks123</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>a13dde</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
+          <t>realabdu</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1260,113 +1284,133 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-14 08:25:14</t>
+          <t>2026-09-14 06:36:02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@a13dde</t>
+          <t>https://www.tiktok.com/@realabdu</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>akiatuconteh</t>
+          <t>janetaliciac</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-09 07:32:58</t>
+          <t>2026-09-18 18:16:03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@akiatuconteh</t>
+          <t>https://www.tiktok.com/@janetaliciac</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ali.syed873</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+          <t>dailydealsuk03</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-17 03:47:33</t>
+          <t>2026-09-21 10:45:03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ali.syed873</t>
+          <t>https://www.tiktok.com/@dailydealsuk03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>alemap9</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
+          <t>vikingbeardshop</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-14 00:26:00</t>
+          <t>2026-09-19 13:38:02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1376,18 +1420,26 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@alemap9</t>
+          <t>https://www.tiktok.com/@vikingbeardshop</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>angelaugochinyere</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+          <t>georgiaxx___</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>50K-100K</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -1400,28 +1452,36 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-16 22:04:31</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angelaugochinyere</t>
+          <t>https://www.tiktok.com/@georgiaxx___</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>anita.wils</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
+          <t>haseeb.mum</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -1439,23 +1499,31 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@anita.wils</t>
+          <t>https://www.tiktok.com/@haseeb.mum</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>atokeade053</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+          <t>bantzuk</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -1468,31 +1536,39 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-14 20:29:27</t>
+          <t>2026-09-15 11:51:02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@atokeade053</t>
+          <t>https://www.tiktok.com/@bantzuk</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>badmashi.007</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
+          <t>positiveproductsuk</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1502,31 +1578,39 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-14 18:24:25</t>
+          <t>2026-09-15 11:53:04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@badmashi.007</t>
+          <t>https://www.tiktok.com/@positiveproductsuk</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bantzuk</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
+          <t>chloeeflynnx</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1536,31 +1620,39 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-15 11:51:02</t>
+          <t>2026-09-16 11:07:02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bantzuk</t>
+          <t>https://www.tiktok.com/@chloeeflynnx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>be__beauty1</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
+          <t>kimmbyb28</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1570,99 +1662,123 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-08 17:18:23</t>
+          <t>2026-09-23 13:44:02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@be__beauty1</t>
+          <t>https://www.tiktok.com/@kimmbyb28</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>beauty20208</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+          <t>hinas_beauty_buys</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-18 19:31:55</t>
+          <t>2026-09-18 09:46:05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty20208</t>
+          <t>https://www.tiktok.com/@hinas_beauty_buys</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>beemahempire</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+          <t>su.k806</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-15 11:52:03</t>
+          <t>2026-09-17 20:34:02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beemahempire</t>
+          <t>https://www.tiktok.com/@su.k806</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bellasbeauty07</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+          <t>donsnewchapter</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1672,65 +1788,81 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-08 10:16:05</t>
+          <t>2026-09-16 09:45:02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bellasbeauty07</t>
+          <t>https://www.tiktok.com/@donsnewchapter</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bettyaddo398</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+          <t>scottishginger0</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-14 14:52:28</t>
+          <t>2026-09-23 15:18:02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bettyaddo398</t>
+          <t>https://www.tiktok.com/@scottishginger0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>_dosah</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+          <t>manvsparkins0n</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>250K-500K</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1740,27 +1872,31 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-21 14:58:25</t>
+          <t>2026-09-14 06:51:02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_dosah</t>
+          <t>https://www.tiktok.com/@manvsparkins0n</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1sultan786</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>crestworld.cooks</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
@@ -1774,28 +1910,36 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-21 10:45:04</t>
+          <t>2026-09-27 08:26:05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@1sultan786</t>
+          <t>https://www.tiktok.com/@crestworld.cooks</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dulal.miah2471</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+          <t>beauty20208</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -1808,31 +1952,39 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-14 07:26:09</t>
+          <t>2026-09-18 19:31:55</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dulal.miah2471</t>
+          <t>https://www.tiktok.com/@beauty20208</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>drantero_10</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+          <t>dillytwinmum</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1842,24 +1994,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-17 14:48:32</t>
+          <t>2026-09-21 09:55:02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@drantero_10</t>
+          <t>https://www.tiktok.com/@dillytwinmum</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>donsnewchapter</t>
+          <t>balletdeo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1876,65 +2028,65 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-16 09:45:02</t>
+          <t>2026-09-26 01:45:10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@donsnewchapter</t>
+          <t>https://www.tiktok.com/@balletdeo</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dollywithplaits73</t>
+          <t>badmashi.007</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-16 16:47:28</t>
+          <t>2026-09-14 18:24:25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dollywithplaits73</t>
+          <t>https://www.tiktok.com/@badmashi.007</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>dillytwinmum</t>
+          <t>atokeade053</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1944,24 +2096,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-21 09:55:02</t>
+          <t>2026-09-14 20:29:27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dillytwinmum</t>
+          <t>https://www.tiktok.com/@atokeade053</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>diane.docherty</t>
+          <t>angelaugochinyere</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1978,24 +2130,24 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-15 09:50:59</t>
+          <t>2026-09-16 22:04:31</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@diane.docherty</t>
+          <t>https://www.tiktok.com/@angelaugochinyere</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>deckynla</t>
+          <t>ali.syed873</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2012,58 +2164,58 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-09 11:52:15</t>
+          <t>2026-09-17 03:47:33</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@deckynla</t>
+          <t>https://www.tiktok.com/@ali.syed873</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>dailydealsuk03</t>
+          <t>aminajeylani</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-21 10:45:03</t>
+          <t>2026-09-23 14:42:07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailydealsuk03</t>
+          <t>https://www.tiktok.com/@aminajeylani</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>courageous527</t>
+          <t>aemanshehryar</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2080,58 +2232,58 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-11 19:24:33</t>
+          <t>2026-09-26 17:35:02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@courageous527</t>
+          <t>https://www.tiktok.com/@aemanshehryar</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>climax.scenes</t>
+          <t>_dosah</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-21 06:20:00</t>
+          <t>2026-09-21 14:58:25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@climax.scenes</t>
+          <t>https://www.tiktok.com/@_dosah</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>claudia.claudia970</t>
+          <t>everyday.edit.sho.andrea</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2148,92 +2300,92 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-20 22:09:26</t>
+          <t>2026-09-24 21:53:02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@claudia.claudia970</t>
+          <t>https://www.tiktok.com/@everyday.edit.sho.andrea</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>clare.w4</t>
+          <t>emanjutt740</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ceremonial Matcha Powder</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-10 14:06:31</t>
+          <t>2026-09-24 13:02:03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clare.w4</t>
+          <t>https://www.tiktok.com/@emanjutt740</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>clairedipple66</t>
+          <t>dy7yobwohcu6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:02</t>
+          <t>2026-09-18 21:30:44</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairedipple66</t>
+          <t>https://www.tiktok.com/@dy7yobwohcu6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>chucky692</t>
+          <t>dulal.miah2471</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2250,24 +2402,24 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-15 07:29:48</t>
+          <t>2026-09-14 07:26:09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chucky692</t>
+          <t>https://www.tiktok.com/@dulal.miah2471</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>chloeeflynnx</t>
+          <t>dollywithplaits73</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2279,63 +2431,63 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-16 11:07:02</t>
+          <t>2026-09-16 16:47:28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chloeeflynnx</t>
+          <t>https://www.tiktok.com/@dollywithplaits73</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>chek_mi_shocase</t>
+          <t>drantero_10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-22 17:56:02</t>
+          <t>2026-09-17 14:48:32</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chek_mi_shocase</t>
+          <t>https://www.tiktok.com/@drantero_10</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>hrahmancookings</t>
+          <t>dimpleddp</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2352,31 +2504,31 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-08 19:45:29</t>
+          <t>2026-09-25 12:30:06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hrahmancookings</t>
+          <t>https://www.tiktok.com/@dimpleddp</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>hinas_beauty_buys</t>
+          <t>dinexheese</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2386,24 +2538,24 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-18 09:46:05</t>
+          <t>2026-09-26 12:16:35</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hinas_beauty_buys</t>
+          <t>https://www.tiktok.com/@dinexheese</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>hchahal80</t>
+          <t>desylviaa1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2420,99 +2572,99 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-15 20:35:21</t>
+          <t>2026-09-27 10:40:10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hchahal80</t>
+          <t>https://www.tiktok.com/@desylviaa1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>hashirahmed784</t>
+          <t>diane.docherty</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-21 21:16:02</t>
+          <t>2026-09-15 09:50:59</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hashirahmed784</t>
+          <t>https://www.tiktok.com/@diane.docherty</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>jagjeetsinghkhals28</t>
+          <t>diddlyidi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:03</t>
+          <t>2026-09-23 08:16:02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jagjeetsinghkhals28</t>
+          <t>https://www.tiktok.com/@diddlyidi</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>i.couldnt.give.a.fuckkkk</t>
+          <t>chucky692</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2522,31 +2674,31 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-12 11:58:47</t>
+          <t>2026-09-15 07:29:48</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@i.couldnt.give.a.fuckkkk</t>
+          <t>https://www.tiktok.com/@chucky692</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>janetaliciac</t>
+          <t>clairedipple66</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2556,75 +2708,75 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-18 18:16:03</t>
+          <t>2026-09-16 07:44:02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@janetaliciac</t>
+          <t>https://www.tiktok.com/@clairedipple66</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>dy7yobwohcu6</t>
+          <t>claudia.claudia970</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-18 21:30:44</t>
+          <t>2026-09-20 22:09:26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dy7yobwohcu6</t>
+          <t>https://www.tiktok.com/@claudia.claudia970</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>gella4573</t>
+          <t>climax.scenes</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-16 07:50:13</t>
+          <t>2026-09-21 06:20:00</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2634,48 +2786,48 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gella4573</t>
+          <t>https://www.tiktok.com/@climax.scenes</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>georgiafergg</t>
+          <t>corina.creates</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-23 08:16:05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@georgiafergg</t>
+          <t>https://www.tiktok.com/@corina.creates</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>gl80.31</t>
+          <t>beemahempire</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2692,7 +2844,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-10 23:30:20</t>
+          <t>2026-09-15 11:52:03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2702,82 +2854,82 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gl80.31</t>
+          <t>https://www.tiktok.com/@beemahempire</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>haseeb.mum</t>
+          <t>bianca.doing.tiktok</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-24 20:37:02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@haseeb.mum</t>
+          <t>https://www.tiktok.com/@bianca.doing.tiktok</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>emaanttshop</t>
+          <t>bgee2345</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-15 21:32:02</t>
+          <t>2026-09-19 22:31:01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emaanttshop</t>
+          <t>https://www.tiktok.com/@bgee2345</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>eni_folabi</t>
+          <t>bettyaddo398</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2794,7 +2946,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-09 11:38:46</t>
+          <t>2026-09-14 14:52:28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2804,48 +2956,48 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eni_folabi</t>
+          <t>https://www.tiktok.com/@bettyaddo398</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>elizabetho001</t>
+          <t>chek_mi_shocase</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-08 17:27:54</t>
+          <t>2026-09-22 17:56:02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elizabetho001</t>
+          <t>https://www.tiktok.com/@chek_mi_shocase</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>elizabethj27</t>
+          <t>chezzy954</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2857,29 +3009,29 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-10 23:49:16</t>
+          <t>2026-09-25 13:21:47</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elizabethj27</t>
+          <t>https://www.tiktok.com/@chezzy954</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kay.h0</t>
+          <t>charliegirl860</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2896,126 +3048,126 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-09 04:27:35</t>
+          <t>2026-09-26 10:54:39</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kay.h0</t>
+          <t>https://www.tiktok.com/@charliegirl860</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>katseyelocer</t>
+          <t>a13dde</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-15 22:58:52</t>
+          <t>2026-09-14 08:25:14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katseyelocer</t>
+          <t>https://www.tiktok.com/@a13dde</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kaylee_dexter</t>
+          <t>alemap9</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-14 00:26:00</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaylee_dexter</t>
+          <t>https://www.tiktok.com/@alemap9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kayne202104</t>
+          <t>homemadefood2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-22 21:46:02</t>
+          <t>2026-09-23 16:44:22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kayne202104</t>
+          <t>https://www.tiktok.com/@homemadefood2024</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kennybabe692</t>
+          <t>gella4573</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3032,24 +3184,24 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-10 11:43:02</t>
+          <t>2026-09-16 07:50:13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kennybabe692</t>
+          <t>https://www.tiktok.com/@gella4573</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kofoworola2853</t>
+          <t>fernandasprivy</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3066,24 +3218,24 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-11 10:52:59</t>
+          <t>2026-09-15 19:00:52</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kofoworola2853</t>
+          <t>https://www.tiktok.com/@fernandasprivy</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kayyu247</t>
+          <t>fittokfinds88</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3100,31 +3252,31 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-09 09:42:51</t>
+          <t>2026-09-23 16:18:03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kayyu247</t>
+          <t>https://www.tiktok.com/@fittokfinds88</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>keeskloset</t>
+          <t>hchahal80</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3134,24 +3286,24 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-16 09:57:04</t>
+          <t>2026-09-15 20:35:21</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@keeskloset</t>
+          <t>https://www.tiktok.com/@hchahal80</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ladydonigbinosa</t>
+          <t>fmrasalhossain</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3168,24 +3320,24 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-14 07:25:08</t>
+          <t>2026-09-25 22:32:12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ladydonigbinosa</t>
+          <t>https://www.tiktok.com/@fmrasalhossain</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>konaduroi</t>
+          <t>fkprima123</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3202,36 +3354,36 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-15 03:00:44</t>
+          <t>2026-09-26 17:32:35</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@konaduroi</t>
+          <t>https://www.tiktok.com/@fkprima123</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>leerobert123</t>
+          <t>kaylee_dexter</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3241,128 +3393,128 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@leerobert123</t>
+          <t>https://www.tiktok.com/@kaylee_dexter</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>life52551</t>
+          <t>keyratio</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-21 22:10:02</t>
+          <t>2026-09-27 13:35:02</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@life52551</t>
+          <t>https://www.tiktok.com/@keyratio</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>m.3384</t>
+          <t>kamo76710</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-21 10:22:24</t>
+          <t>2026-09-20 05:21:24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@m.3384</t>
+          <t>https://www.tiktok.com/@kamo76710</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>lucia25070</t>
+          <t>konaduroi</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-18 09:46:03</t>
+          <t>2026-09-15 03:00:44</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lucia25070</t>
+          <t>https://www.tiktok.com/@konaduroi</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>maish1002</t>
+          <t>letsmakeitkentlimited</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3372,24 +3524,24 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-19 13:31:02</t>
+          <t>2026-09-26 08:39:02</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maish1002</t>
+          <t>https://www.tiktok.com/@letsmakeitkentlimited</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>markh_8</t>
+          <t>lindaefionayi</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3406,31 +3558,31 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-09 16:07:49</t>
+          <t>2026-09-23 20:46:33</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@markh_8</t>
+          <t>https://www.tiktok.com/@lindaefionayi</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>maxi_berrie</t>
+          <t>laurywilliams</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3440,24 +3592,24 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-22 23:20:40</t>
+          <t>2026-09-26 16:59:35</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maxi_berrie</t>
+          <t>https://www.tiktok.com/@laurywilliams</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mehmoonaali238</t>
+          <t>ladydonigbinosa</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3474,31 +3626,31 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-17 11:42:05</t>
+          <t>2026-09-14 07:25:08</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mehmoonaali238</t>
+          <t>https://www.tiktok.com/@ladydonigbinosa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>merz3859</t>
+          <t>louzreviewz</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3508,24 +3660,24 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-22 21:09:48</t>
+          <t>2026-09-26 17:35:02</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@merz3859</t>
+          <t>https://www.tiktok.com/@louzreviewz</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>missyspranno12</t>
+          <t>lissssaxxx</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3542,92 +3694,92 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-15 13:31:44</t>
+          <t>2026-09-23 08:17:25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@missyspranno12</t>
+          <t>https://www.tiktok.com/@lissssaxxx</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>monicalavern</t>
+          <t>lovecats7112</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-15 13:00:13</t>
+          <t>2026-09-26 19:59:48</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@monicalavern</t>
+          <t>https://www.tiktok.com/@lovecats7112</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>moon19867</t>
+          <t>m.3384</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-11 19:21:54</t>
+          <t>2026-09-21 10:22:24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moon19867</t>
+          <t>https://www.tiktok.com/@m.3384</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>muhammadsha110</t>
+          <t>manvinder318</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3644,24 +3796,24 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-11 15:36:47</t>
+          <t>2026-09-25 14:14:56</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@muhammadsha110</t>
+          <t>https://www.tiktok.com/@manvinder318</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>jem17363</t>
+          <t>mahi.rani421</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3678,24 +3830,24 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-21 17:28:16</t>
+          <t>2026-09-24 13:02:03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jem17363</t>
+          <t>https://www.tiktok.com/@mahi.rani421</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>joandusabe</t>
+          <t>maxi_berrie</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3712,36 +3864,36 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-19 08:31:29</t>
+          <t>2026-09-22 23:20:40</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@joandusabe</t>
+          <t>https://www.tiktok.com/@maxi_berrie</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>journey2debtfree</t>
+          <t>leerobert123</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3751,60 +3903,60 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@journey2debtfree</t>
+          <t>https://www.tiktok.com/@leerobert123</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>julietogu5</t>
+          <t>mayma3747</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-14 01:42:26</t>
+          <t>2026-09-26 15:22:17</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@julietogu5</t>
+          <t>https://www.tiktok.com/@mayma3747</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>jxnxxkxk</t>
+          <t>megandbellaxx</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3814,31 +3966,31 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-15 12:32:04</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jxnxxkxk</t>
+          <t>https://www.tiktok.com/@megandbellaxx</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>k.tee146</t>
+          <t>mersoo712</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3848,24 +4000,24 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-10 09:41:07</t>
+          <t>2026-09-24 12:56:04</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@k.tee146</t>
+          <t>https://www.tiktok.com/@mersoo712</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kamo76710</t>
+          <t>mehmoonaali238</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3882,92 +4034,92 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-20 05:21:24</t>
+          <t>2026-09-17 11:42:05</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kamo76710</t>
+          <t>https://www.tiktok.com/@mehmoonaali238</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>feesdeals</t>
+          <t>merz3859</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-22 22:40:02</t>
+          <t>2026-09-22 21:09:48</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@feesdeals</t>
+          <t>https://www.tiktok.com/@merz3859</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>fernandasprivy</t>
+          <t>inspiringtanya83</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-15 19:00:52</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fernandasprivy</t>
+          <t>https://www.tiktok.com/@inspiringtanya83</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>oluwatoyosiabayom</t>
+          <t>jadepa90</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -3984,39 +4136,31 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-14 17:04:02</t>
+          <t>2026-09-26 09:09:09</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwatoyosiabayom</t>
+          <t>https://www.tiktok.com/@jadepa90</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>olascornerpage</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>inspirednoor</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4026,65 +4170,65 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-12 21:52:02</t>
+          <t>2026-09-26 17:35:02</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@olascornerpage</t>
+          <t>https://www.tiktok.com/@inspirednoor</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>oladayomartins</t>
+          <t>joandusabe</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-17 21:17:16</t>
+          <t>2026-09-19 08:31:29</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oladayomartins</t>
+          <t>https://www.tiktok.com/@joandusabe</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>nxthxnfrxmdxy</t>
+          <t>jem17363</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4094,24 +4238,24 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-21 17:28:16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nxthxnfrxmdxy</t>
+          <t>https://www.tiktok.com/@jem17363</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>nrahi28</t>
+          <t>julietogu5</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4128,24 +4272,24 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-20 14:59:29</t>
+          <t>2026-09-14 01:42:26</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nrahi28</t>
+          <t>https://www.tiktok.com/@julietogu5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>nancymm52</t>
+          <t>jxnxxkxk</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4162,92 +4306,92 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-18 07:04:23</t>
+          <t>2026-09-15 12:32:04</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nancymm52</t>
+          <t>https://www.tiktok.com/@jxnxxkxk</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>nanahdaramy</t>
+          <t>katseyelocer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-14 00:12:20</t>
+          <t>2026-09-15 22:58:52</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nanahdaramy</t>
+          <t>https://www.tiktok.com/@katseyelocer</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>na2706_1</t>
+          <t>flash_finds1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-20 23:38:18</t>
+          <t>2026-09-27 13:35:02</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@na2706_1</t>
+          <t>https://www.tiktok.com/@flash_finds1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>mymojomindset</t>
+          <t>fellykemmy3</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4264,65 +4408,65 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-15 10:29:05</t>
+          <t>2026-09-24 20:39:00</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mymojomindset</t>
+          <t>https://www.tiktok.com/@fellykemmy3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>queeen_0f_hearts</t>
+          <t>fahmidaislam2120</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-13 23:51:38</t>
+          <t>2026-09-23 15:26:11</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queeen_0f_hearts</t>
+          <t>https://www.tiktok.com/@fahmidaislam2120</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>positivevibeonly62</t>
+          <t>nomzy.gladys</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4332,24 +4476,24 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-21 10:52:02</t>
+          <t>2026-09-25 10:26:03</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@positivevibeonly62</t>
+          <t>https://www.tiktok.com/@nomzy.gladys</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>radhekrishna_11</t>
+          <t>neatshops</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4366,7 +4510,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-21 11:21:47</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4376,14 +4520,14 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@radhekrishna_11</t>
+          <t>https://www.tiktok.com/@neatshops</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>r4xla15</t>
+          <t>naveed19.88</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4400,7 +4544,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-20 15:22:42</t>
+          <t>2026-09-25 22:46:15</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4410,21 +4554,21 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@r4xla15</t>
+          <t>https://www.tiktok.com/@naveed19.88</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>online.shop8292</t>
+          <t>nancymm52</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4434,31 +4578,31 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:03</t>
+          <t>2026-09-18 07:04:23</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@online.shop8292</t>
+          <t>https://www.tiktok.com/@nancymm52</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>positiveproductsuk</t>
+          <t>nanahdaramy</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4468,24 +4612,24 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-15 11:53:04</t>
+          <t>2026-09-14 00:12:20</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@positiveproductsuk</t>
+          <t>https://www.tiktok.com/@nanahdaramy</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>omolade.abebi</t>
+          <t>na2706_1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4502,24 +4646,24 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-17 10:33:35</t>
+          <t>2026-09-20 23:38:18</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@omolade.abebi</t>
+          <t>https://www.tiktok.com/@na2706_1</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>rozana2026</t>
+          <t>munasheish</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4536,41 +4680,41 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-19 15:08:34</t>
+          <t>2026-09-25 10:27:59</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rozana2026</t>
+          <t>https://www.tiktok.com/@munasheish</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>rory.the.cocker</t>
+          <t>mummyzaraa</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-18 18:13:02</t>
+          <t>2026-09-23 08:16:05</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4580,14 +4724,14 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rory.the.cocker</t>
+          <t>https://www.tiktok.com/@mummyzaraa</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ruksi1607</t>
+          <t>mum3tees</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4604,24 +4748,24 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-13 20:49:20</t>
+          <t>2026-09-26 15:28:17</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ruksi1607</t>
+          <t>https://www.tiktok.com/@mum3tees</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>saadia7166</t>
+          <t>monicalavern</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4638,7 +4782,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-10 11:16:51</t>
+          <t>2026-09-15 13:00:13</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4648,48 +4792,48 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@saadia7166</t>
+          <t>https://www.tiktok.com/@monicalavern</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>sbegum.79</t>
+          <t>missyspranno12</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-21 17:38:25</t>
+          <t>2026-09-15 13:31:44</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sbegum.79</t>
+          <t>https://www.tiktok.com/@missyspranno12</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>sedi546</t>
+          <t>princessanna1738</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -4706,24 +4850,24 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-13 15:46:07</t>
+          <t>2026-09-25 07:04:05</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sedi546</t>
+          <t>https://www.tiktok.com/@princessanna1738</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>sajarshed</t>
+          <t>patriciaappiah280</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4740,31 +4884,31 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-19 10:17:35</t>
+          <t>2026-09-23 10:08:56</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sajarshed</t>
+          <t>https://www.tiktok.com/@patriciaappiah280</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>samirakarim24</t>
+          <t>paul.d.awson</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4774,65 +4918,65 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-11 11:10:48</t>
+          <t>2026-09-26 18:18:04</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samirakarim24</t>
+          <t>https://www.tiktok.com/@paul.d.awson</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>sehnamiee</t>
+          <t>ola.oluwatoyin.ad</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-21 20:46:02</t>
+          <t>2026-09-25 13:50:20</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sehnamiee</t>
+          <t>https://www.tiktok.com/@ola.oluwatoyin.ad</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>seffshops</t>
+          <t>nrahi28</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4842,65 +4986,65 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-21 10:52:04</t>
+          <t>2026-09-20 14:59:29</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seffshops</t>
+          <t>https://www.tiktok.com/@nrahi28</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>sexybaby7657</t>
+          <t>ranifarooq_3</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-09 21:00:27</t>
+          <t>2026-09-13 22:37:56</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sexybaby7657</t>
+          <t>https://www.tiktok.com/@ranifarooq_3</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>sehrish2015</t>
+          <t>radhekrishna_11</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4910,7 +5054,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-21 11:21:47</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4920,21 +5064,21 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sehrish2015</t>
+          <t>https://www.tiktok.com/@radhekrishna_11</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>reems_ttsshop</t>
+          <t>rabbit_pm12</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4944,58 +5088,58 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-25 19:17:46</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reems_ttsshop</t>
+          <t>https://www.tiktok.com/@rabbit_pm12</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ranifarooq_3</t>
+          <t>r4xla15</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-13 22:37:56</t>
+          <t>2026-09-20 15:22:42</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ranifarooq_3</t>
+          <t>https://www.tiktok.com/@r4xla15</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>oyetunji.sunday</t>
+          <t>queeen_0f_hearts</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5012,24 +5156,24 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-12 13:08:25</t>
+          <t>2026-09-13 23:51:38</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oyetunji.sunday</t>
+          <t>https://www.tiktok.com/@queeen_0f_hearts</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>padnerkupakuwana</t>
+          <t>riderrrr70</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5046,31 +5190,31 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-13 02:02:06</t>
+          <t>2026-09-27 14:15:10</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@padnerkupakuwana</t>
+          <t>https://www.tiktok.com/@riderrrr70</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>sjahan83</t>
+          <t>reems_ttsshop</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5080,24 +5224,24 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-12 13:46:48</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sjahan83</t>
+          <t>https://www.tiktok.com/@reems_ttsshop</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>shukar7860</t>
+          <t>reykkhan</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5114,24 +5258,24 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-22 09:29:34</t>
+          <t>2026-09-25 17:53:08</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shukar7860</t>
+          <t>https://www.tiktok.com/@reykkhan</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>shopforfiver</t>
+          <t>ruksi1607</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5148,24 +5292,24 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-21 15:01:03</t>
+          <t>2026-09-13 20:49:20</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shopforfiver</t>
+          <t>https://www.tiktok.com/@ruksi1607</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>shoni1984</t>
+          <t>ruas_dream</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5182,24 +5326,24 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-10 08:20:01</t>
+          <t>2026-09-27 11:00:34</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shoni1984</t>
+          <t>https://www.tiktok.com/@ruas_dream</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>syrashid</t>
+          <t>rozana2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5216,65 +5360,65 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-11 12:35:39</t>
+          <t>2026-09-19 15:08:34</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@syrashid</t>
+          <t>https://www.tiktok.com/@rozana2026</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>thehomelylondon</t>
+          <t>nxthxnfrxmdxy</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-09-18 15:51:23</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thehomelylondon</t>
+          <t>https://www.tiktok.com/@nxthxnfrxmdxy</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>steffispicks</t>
+          <t>oluwatoyosiabayom</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5284,24 +5428,24 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:03</t>
+          <t>2026-09-14 17:04:02</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@steffispicks</t>
+          <t>https://www.tiktok.com/@oluwatoyosiabayom</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ste.baby6</t>
+          <t>omolade.abebi</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5318,24 +5462,24 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-09-09 16:28:17</t>
+          <t>2026-09-17 10:33:35</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ste.baby6</t>
+          <t>https://www.tiktok.com/@omolade.abebi</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>tifetito02</t>
+          <t>padnerkupakuwana</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5352,58 +5496,58 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:36</t>
+          <t>2026-09-13 02:02:06</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tifetito02</t>
+          <t>https://www.tiktok.com/@padnerkupakuwana</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>themamadee</t>
+          <t>oladayomartins</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-09-10 19:23:49</t>
+          <t>2026-09-17 21:17:16</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@themamadee</t>
+          <t>https://www.tiktok.com/@oladayomartins</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>trendtokshop88</t>
+          <t>sedi546</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -5420,65 +5564,65 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:03</t>
+          <t>2026-09-13 15:46:07</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@trendtokshop88</t>
+          <t>https://www.tiktok.com/@sedi546</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>tixtok148</t>
+          <t>samiahajam</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-19 18:20:29</t>
+          <t>2026-09-25 10:39:07</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tixtok148</t>
+          <t>https://www.tiktok.com/@samiahajam</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>tyanie1703</t>
+          <t>samstrendingdeals</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5488,31 +5632,31 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-09-22 14:51:38</t>
+          <t>2026-09-26 17:38:02</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tyanie1703</t>
+          <t>https://www.tiktok.com/@samstrendingdeals</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>uksaleshop</t>
+          <t>sbegum.79</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5522,7 +5666,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-16 15:22:03</t>
+          <t>2026-09-21 17:38:25</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5532,14 +5676,14 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uksaleshop</t>
+          <t>https://www.tiktok.com/@sbegum.79</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>user13457g</t>
+          <t>sajarshed</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -5556,58 +5700,58 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-09-10 08:04:29</t>
+          <t>2026-09-19 10:17:35</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user13457g</t>
+          <t>https://www.tiktok.com/@sajarshed</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>su.k806</t>
+          <t>shopforfiver</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-17 20:34:02</t>
+          <t>2026-09-21 15:01:03</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@su.k806</t>
+          <t>https://www.tiktok.com/@shopforfiver</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>user2182373993526</t>
+          <t>shazia11235</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -5624,31 +5768,31 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-09-21 12:26:17</t>
+          <t>2026-09-24 23:21:59</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2182373993526</t>
+          <t>https://www.tiktok.com/@shazia11235</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>user2773140226152</t>
+          <t>shasha.0891</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5658,31 +5802,31 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-21 20:00:10</t>
+          <t>2026-09-23 13:48:02</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2773140226152</t>
+          <t>https://www.tiktok.com/@shasha.0891</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>user7271293811175</t>
+          <t>sopharella.loves</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5692,92 +5836,92 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-09-11 08:42:27</t>
+          <t>2026-09-26 17:35:02</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user7271293811175</t>
+          <t>https://www.tiktok.com/@sopharella.loves</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>user5251816210173</t>
+          <t>steffispicks</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-15 20:13:06</t>
+          <t>2026-09-22 19:57:03</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user5251816210173</t>
+          <t>https://www.tiktok.com/@steffispicks</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>user8318338677754</t>
+          <t>suziefenton</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-09-16 23:49:09</t>
+          <t>2026-09-23 10:47:02</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8318338677754</t>
+          <t>https://www.tiktok.com/@suziefenton</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>user9199380</t>
+          <t>taiwooluyemitaiwo</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -5794,92 +5938,92 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-09-08 15:02:55</t>
+          <t>2026-09-23 16:28:21</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9199380</t>
+          <t>https://www.tiktok.com/@taiwooluyemitaiwo</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>user_78602223</t>
+          <t>teeyworld_confectionery</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-09-22 17:40:46</t>
+          <t>2026-09-25 19:30:28</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user_78602223</t>
+          <t>https://www.tiktok.com/@teeyworld_confectionery</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>user806865620814</t>
+          <t>thehomelylondon</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-09-20 17:13:54</t>
+          <t>2026-09-18 15:51:23</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user806865620814</t>
+          <t>https://www.tiktok.com/@thehomelylondon</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>vain119</t>
+          <t>shukar7860</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -5896,24 +6040,24 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-09-15 09:25:05</t>
+          <t>2026-09-22 09:29:34</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vain119</t>
+          <t>https://www.tiktok.com/@shukar7860</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>vera77524</t>
+          <t>seyiedeliciouscocktails</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -5930,24 +6074,24 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-09-09 07:38:35</t>
+          <t>2026-09-25 06:38:51</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vera77524</t>
+          <t>https://www.tiktok.com/@seyiedeliciouscocktails</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>yemi.bello3</t>
+          <t>tinku78616</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -5964,92 +6108,92 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-09-17 07:22:35</t>
+          <t>2026-09-25 17:21:23</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemi.bello3</t>
+          <t>https://www.tiktok.com/@tinku78616</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>vikingbeardshop</t>
+          <t>tifetito02</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-09-19 13:38:02</t>
+          <t>2026-09-16 21:55:36</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vikingbeardshop</t>
+          <t>https://www.tiktok.com/@tifetito02</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>yemishittuedemayibo</t>
+          <t>tixtok148</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-09-19 00:15:14</t>
+          <t>2026-09-19 18:20:29</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemishittuedemayibo</t>
+          <t>https://www.tiktok.com/@tixtok148</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>yourfindz0</t>
+          <t>triciaebun</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -6066,24 +6210,24 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-09-19 13:38:02</t>
+          <t>2026-09-25 16:57:55</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yourfindz0</t>
+          <t>https://www.tiktok.com/@triciaebun</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>yvonne21197</t>
+          <t>user2773140226152</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -6100,7 +6244,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-09-16 22:41:43</t>
+          <t>2026-09-21 20:00:10</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6110,49 +6254,397 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yvonne21197</t>
+          <t>https://www.tiktok.com/@user2773140226152</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>zahidaparveen624</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
+          <t>user5251816210173</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:13:06</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user5251816210173</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>tyanie1703</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
         <is>
           <t>£0-£50</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C165" t="inlineStr">
         <is>
           <t>1K-5K</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-09-11 13:42:26</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:51:38</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tyanie1703</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>user2182373993526</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:26:17</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user2182373993526</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>user8318338677754</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-09-16 23:49:09</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@zahidaparveen624</t>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user8318338677754</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>user806865620814</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:13:54</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user806865620814</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>vain119</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-09-15 09:25:05</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@vain119</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>user_78602223</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Ashwagandha Coffee</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Free sample from seller</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:40:46</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user_78602223</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>yemi.bello3</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-09-17 07:22:35</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yemi.bello3</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>yemishittuedemayibo</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:15:14</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yemishittuedemayibo</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>yvonne21197</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-09-16 22:41:43</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yvonne21197</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>zara1508ahmed</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-09-23 03:28:52</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@zara1508ahmed</t>
         </is>
       </c>
     </row>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>miaweb7new</t>
+          <t>colin_harding</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -822,24 +822,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-26 17:37:02</t>
+          <t>2026-09-28 10:10:06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@miaweb7new</t>
+          <t>https://www.tiktok.com/@colin_harding</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kirsten_mum_of_3_tts</t>
+          <t>miaweb7new</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -849,39 +849,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-23 20:18:02</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kirsten_mum_of_3_tts</t>
+          <t>https://www.tiktok.com/@miaweb7new</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hashirahmed784</t>
+          <t>kirsten_mum_of_3_tts</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -906,17 +906,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-21 21:16:02</t>
+          <t>2026-09-23 20:18:02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hashirahmed784</t>
+          <t>https://www.tiktok.com/@kirsten_mum_of_3_tts</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bex_lifeafter40</t>
+          <t>jenna_g_tiktok</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -975,54 +975,54 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-17 15:30:23</t>
+          <t>2026-09-17 15:30:26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bex_lifeafter40</t>
+          <t>https://www.tiktok.com/@jenna_g_tiktok</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>jenna_g_tiktok</t>
+          <t>fairyfaryal11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1032,24 +1032,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-17 15:30:26</t>
+          <t>2026-09-24 20:07:02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jenna_g_tiktok</t>
+          <t>https://www.tiktok.com/@fairyfaryal11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fairyfaryal11</t>
+          <t>ziab442</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1074,24 +1074,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-24 20:07:02</t>
+          <t>2026-09-14 05:38:02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fairyfaryal11</t>
+          <t>https://www.tiktok.com/@ziab442</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ziab442</t>
+          <t>emaanttshop</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-14 05:38:02</t>
+          <t>2026-09-15 21:32:02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ziab442</t>
+          <t>https://www.tiktok.com/@emaanttshop</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emaanttshop</t>
+          <t>seffshops</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1153,29 +1153,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-15 21:32:02</t>
+          <t>2026-09-21 10:52:04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emaanttshop</t>
+          <t>https://www.tiktok.com/@seffshops</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>seffshops</t>
+          <t>inayapicks123</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1185,81 +1185,81 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-21 10:52:04</t>
+          <t>2026-09-14 11:03:03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seffshops</t>
+          <t>https://www.tiktok.com/@inayapicks123</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>inayapicks123</t>
+          <t>realabdu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-14 11:03:03</t>
+          <t>2026-09-14 06:36:02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@inayapicks123</t>
+          <t>https://www.tiktok.com/@realabdu</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>realabdu</t>
+          <t>janetaliciac</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1269,39 +1269,39 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-14 06:36:02</t>
+          <t>2026-09-18 18:16:03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@realabdu</t>
+          <t>https://www.tiktok.com/@janetaliciac</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>janetaliciac</t>
+          <t>dailydealsuk03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1326,24 +1326,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-18 18:16:03</t>
+          <t>2026-09-21 10:45:03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@janetaliciac</t>
+          <t>https://www.tiktok.com/@dailydealsuk03</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dailydealsuk03</t>
+          <t>vikingbeardshop</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1368,24 +1368,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-21 10:45:03</t>
+          <t>2026-09-19 13:38:02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailydealsuk03</t>
+          <t>https://www.tiktok.com/@vikingbeardshop</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>vikingbeardshop</t>
+          <t>georgiaxx___</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1395,39 +1395,39 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-19 13:38:02</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vikingbeardshop</t>
+          <t>https://www.tiktok.com/@georgiaxx___</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>georgiaxx___</t>
+          <t>haseeb.mum</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>50K-100K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1452,24 +1452,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-26 17:37:02</t>
+          <t>2026-09-16 09:42:03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@georgiaxx___</t>
+          <t>https://www.tiktok.com/@haseeb.mum</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>haseeb.mum</t>
+          <t>bantzuk</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1494,24 +1494,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-16 09:42:03</t>
+          <t>2026-09-15 11:51:02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@haseeb.mum</t>
+          <t>https://www.tiktok.com/@bantzuk</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bantzuk</t>
+          <t>positiveproductsuk</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1536,24 +1536,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-15 11:51:02</t>
+          <t>2026-09-15 11:53:04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bantzuk</t>
+          <t>https://www.tiktok.com/@positiveproductsuk</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>positiveproductsuk</t>
+          <t>kimmbyb28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1563,39 +1563,39 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-15 11:53:04</t>
+          <t>2026-09-23 13:44:02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@positiveproductsuk</t>
+          <t>https://www.tiktok.com/@kimmbyb28</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>chloeeflynnx</t>
+          <t>hinas_beauty_buys</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1610,49 +1610,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-16 11:07:02</t>
+          <t>2026-09-18 09:46:05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chloeeflynnx</t>
+          <t>https://www.tiktok.com/@hinas_beauty_buys</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kimmbyb28</t>
+          <t>scottishginger0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1662,118 +1662,114 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-23 13:44:02</t>
+          <t>2026-09-23 15:18:02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kimmbyb28</t>
+          <t>https://www.tiktok.com/@scottishginger0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hinas_beauty_buys</t>
+          <t>manvsparkins0n</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>250K-500K</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-18 09:46:05</t>
+          <t>2026-09-14 06:51:02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hinas_beauty_buys</t>
+          <t>https://www.tiktok.com/@manvsparkins0n</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>su.k806</t>
+          <t>crestworld.cooks</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-17 20:34:02</t>
+          <t>2026-09-27 08:26:05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@su.k806</t>
+          <t>https://www.tiktok.com/@crestworld.cooks</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>donsnewchapter</t>
+          <t>beauty20208</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1788,34 +1784,34 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-16 09:45:02</t>
+          <t>2026-09-18 19:31:55</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@donsnewchapter</t>
+          <t>https://www.tiktok.com/@beauty20208</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>scottishginger0</t>
+          <t>dillytwinmum</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1825,41 +1821,33 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-23 15:18:02</t>
+          <t>2026-09-21 09:55:02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@scottishginger0</t>
+          <t>https://www.tiktok.com/@dillytwinmum</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>manvsparkins0n</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>£200-£500</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>250K-500K</t>
-        </is>
-      </c>
+          <t>charliegirl860</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -1867,36 +1855,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-14 06:51:02</t>
+          <t>2026-09-26 10:54:39</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@manvsparkins0n</t>
+          <t>https://www.tiktok.com/@charliegirl860</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>crestworld.cooks</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>by_martalewandowska</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
@@ -1910,7 +1894,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-27 08:26:05</t>
+          <t>2026-09-28 10:15:02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1920,68 +1904,52 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@crestworld.cooks</t>
+          <t>https://www.tiktok.com/@by_martalewandowska</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>beauty20208</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>corina.creates</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-18 19:31:55</t>
+          <t>2026-09-23 08:16:05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty20208</t>
+          <t>https://www.tiktok.com/@corina.creates</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dillytwinmum</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>climax.scenes</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -1989,29 +1957,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-21 09:55:02</t>
+          <t>2026-09-21 06:20:00</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dillytwinmum</t>
+          <t>https://www.tiktok.com/@climax.scenes</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>balletdeo</t>
+          <t>buhat_alla_deals</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2028,31 +1996,31 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-26 01:45:10</t>
+          <t>2026-09-28 10:10:04</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@balletdeo</t>
+          <t>https://www.tiktok.com/@buhat_alla_deals</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>badmashi.007</t>
+          <t>blessing.tv.and.l</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2062,24 +2030,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-14 18:24:25</t>
+          <t>2026-09-28 10:13:02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@badmashi.007</t>
+          <t>https://www.tiktok.com/@blessing.tv.and.l</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>atokeade053</t>
+          <t>bgee2345</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2096,126 +2064,126 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-14 20:29:27</t>
+          <t>2026-09-19 22:31:01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@atokeade053</t>
+          <t>https://www.tiktok.com/@bgee2345</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>angelaugochinyere</t>
+          <t>bianca.doing.tiktok</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-16 22:04:31</t>
+          <t>2026-09-24 20:37:02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angelaugochinyere</t>
+          <t>https://www.tiktok.com/@bianca.doing.tiktok</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ali.syed873</t>
+          <t>clairedipple66</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-17 03:47:33</t>
+          <t>2026-09-16 07:44:02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ali.syed873</t>
+          <t>https://www.tiktok.com/@clairedipple66</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>aminajeylani</t>
+          <t>chek_mi_shocase</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-23 14:42:07</t>
+          <t>2026-09-22 17:56:02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aminajeylani</t>
+          <t>https://www.tiktok.com/@chek_mi_shocase</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>aemanshehryar</t>
+          <t>atokeade053</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2232,24 +2200,24 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-26 17:35:02</t>
+          <t>2026-09-14 20:29:27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aemanshehryar</t>
+          <t>https://www.tiktok.com/@atokeade053</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>_dosah</t>
+          <t>angelaugochinyere</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2266,92 +2234,92 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-21 14:58:25</t>
+          <t>2026-09-16 22:04:31</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_dosah</t>
+          <t>https://www.tiktok.com/@angelaugochinyere</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>everyday.edit.sho.andrea</t>
+          <t>aminajeylani</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-24 21:53:02</t>
+          <t>2026-09-23 14:42:07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@everyday.edit.sho.andrea</t>
+          <t>https://www.tiktok.com/@aminajeylani</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>emanjutt740</t>
+          <t>azlanzaynahzayrahuk</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ceremonial Matcha Powder</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-24 13:02:03</t>
+          <t>2026-09-28 10:10:05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@emanjutt740</t>
+          <t>https://www.tiktok.com/@azlanzaynahzayrahuk</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>dy7yobwohcu6</t>
+          <t>balletdeo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2368,24 +2336,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-18 21:30:44</t>
+          <t>2026-09-26 01:45:10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dy7yobwohcu6</t>
+          <t>https://www.tiktok.com/@balletdeo</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>dulal.miah2471</t>
+          <t>badmashi.007</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2402,24 +2370,24 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-14 07:26:09</t>
+          <t>2026-09-14 18:24:25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dulal.miah2471</t>
+          <t>https://www.tiktok.com/@badmashi.007</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dollywithplaits73</t>
+          <t>becky.mawunyo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2436,24 +2404,24 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-16 16:47:28</t>
+          <t>2026-09-28 10:19:04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dollywithplaits73</t>
+          <t>https://www.tiktok.com/@becky.mawunyo</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>drantero_10</t>
+          <t>babbyzozo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2470,24 +2438,24 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-17 14:48:32</t>
+          <t>2026-09-28 18:28:13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@drantero_10</t>
+          <t>https://www.tiktok.com/@babbyzozo</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>dimpleddp</t>
+          <t>beemahempire</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2504,58 +2472,58 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-25 12:30:06</t>
+          <t>2026-09-15 11:52:03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dimpleddp</t>
+          <t>https://www.tiktok.com/@beemahempire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>dinexheese</t>
+          <t>bettyaddo398</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-26 12:16:35</t>
+          <t>2026-09-14 14:52:28</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dinexheese</t>
+          <t>https://www.tiktok.com/@bettyaddo398</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>desylviaa1</t>
+          <t>a13dde</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2572,24 +2540,24 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-27 10:40:10</t>
+          <t>2026-09-14 08:25:14</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@desylviaa1</t>
+          <t>https://www.tiktok.com/@a13dde</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>diane.docherty</t>
+          <t>alemap9</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2606,58 +2574,58 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-15 09:50:59</t>
+          <t>2026-09-14 00:26:00</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@diane.docherty</t>
+          <t>https://www.tiktok.com/@alemap9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>diddlyidi</t>
+          <t>amena.akter3665</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-23 08:16:02</t>
+          <t>2026-09-28 12:23:28</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@diddlyidi</t>
+          <t>https://www.tiktok.com/@amena.akter3665</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>chucky692</t>
+          <t>aemanshehryar</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2674,41 +2642,41 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-15 07:29:48</t>
+          <t>2026-09-26 17:35:02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chucky692</t>
+          <t>https://www.tiktok.com/@aemanshehryar</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>clairedipple66</t>
+          <t>ali.syed873</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:02</t>
+          <t>2026-09-17 03:47:33</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2718,31 +2686,31 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@clairedipple66</t>
+          <t>https://www.tiktok.com/@ali.syed873</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>claudia.claudia970</t>
+          <t>_dosah</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-20 22:09:26</t>
+          <t>2026-09-21 14:58:25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2752,21 +2720,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@claudia.claudia970</t>
+          <t>https://www.tiktok.com/@_dosah</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>climax.scenes</t>
+          <t>funmumshops</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2776,126 +2744,126 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-21 06:20:00</t>
+          <t>2026-09-28 10:19:02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@climax.scenes</t>
+          <t>https://www.tiktok.com/@funmumshops</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>corina.creates</t>
+          <t>fmrasalhossain</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-23 08:16:05</t>
+          <t>2026-09-25 22:32:12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@corina.creates</t>
+          <t>https://www.tiktok.com/@fmrasalhossain</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>beemahempire</t>
+          <t>flash_finds1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-15 11:52:03</t>
+          <t>2026-09-27 13:35:02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beemahempire</t>
+          <t>https://www.tiktok.com/@flash_finds1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bianca.doing.tiktok</t>
+          <t>fkprima123</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-24 20:37:02</t>
+          <t>2026-09-26 17:32:35</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bianca.doing.tiktok</t>
+          <t>https://www.tiktok.com/@fkprima123</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bgee2345</t>
+          <t>fittokfinds88</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2912,24 +2880,24 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-19 22:31:01</t>
+          <t>2026-09-23 16:18:03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bgee2345</t>
+          <t>https://www.tiktok.com/@fittokfinds88</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>bettyaddo398</t>
+          <t>fernandasprivy</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2946,7 +2914,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-14 14:52:28</t>
+          <t>2026-09-15 19:00:52</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2956,48 +2924,48 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bettyaddo398</t>
+          <t>https://www.tiktok.com/@fernandasprivy</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>chek_mi_shocase</t>
+          <t>fellykemmy3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-22 17:56:02</t>
+          <t>2026-09-24 20:39:00</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chek_mi_shocase</t>
+          <t>https://www.tiktok.com/@fellykemmy3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>chezzy954</t>
+          <t>fahmidaislam2120</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -3009,131 +2977,131 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-25 13:21:47</t>
+          <t>2026-09-23 15:26:11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chezzy954</t>
+          <t>https://www.tiktok.com/@fahmidaislam2120</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>charliegirl860</t>
+          <t>drantero_10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-26 10:54:39</t>
+          <t>2026-09-17 14:48:32</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@charliegirl860</t>
+          <t>https://www.tiktok.com/@drantero_10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>a13dde</t>
+          <t>everyday.edit.sho.andrea</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-14 08:25:14</t>
+          <t>2026-09-24 21:53:02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@a13dde</t>
+          <t>https://www.tiktok.com/@everyday.edit.sho.andrea</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>alemap9</t>
+          <t>emanjutt740</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ceremonial Matcha Powder</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-14 00:26:00</t>
+          <t>2026-09-24 13:02:03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@alemap9</t>
+          <t>https://www.tiktok.com/@emanjutt740</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>homemadefood2024</t>
+          <t>dy7yobwohcu6</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3150,58 +3118,58 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-23 16:44:22</t>
+          <t>2026-09-18 21:30:44</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@homemadefood2024</t>
+          <t>https://www.tiktok.com/@dy7yobwohcu6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>gella4573</t>
+          <t>dollywithplaits73</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-16 07:50:13</t>
+          <t>2026-09-16 16:47:28</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gella4573</t>
+          <t>https://www.tiktok.com/@dollywithplaits73</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>fernandasprivy</t>
+          <t>dulal.miah2471</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3218,24 +3186,24 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-15 19:00:52</t>
+          <t>2026-09-14 07:26:09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fernandasprivy</t>
+          <t>https://www.tiktok.com/@dulal.miah2471</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>fittokfinds88</t>
+          <t>dimpleddp</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3252,65 +3220,65 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-23 16:18:03</t>
+          <t>2026-09-25 12:30:06</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fittokfinds88</t>
+          <t>https://www.tiktok.com/@dimpleddp</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>hchahal80</t>
+          <t>dinexheese</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-15 20:35:21</t>
+          <t>2026-09-26 12:16:35</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hchahal80</t>
+          <t>https://www.tiktok.com/@dinexheese</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>fmrasalhossain</t>
+          <t>chezzy954</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3320,24 +3288,24 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-25 22:32:12</t>
+          <t>2026-09-25 13:21:47</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fmrasalhossain</t>
+          <t>https://www.tiktok.com/@chezzy954</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>fkprima123</t>
+          <t>chucky692</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3354,31 +3322,31 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-26 17:32:35</t>
+          <t>2026-09-15 07:29:48</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fkprima123</t>
+          <t>https://www.tiktok.com/@chucky692</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kaylee_dexter</t>
+          <t>diddlyidi</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3388,7 +3356,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-23 08:16:02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3398,21 +3366,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaylee_dexter</t>
+          <t>https://www.tiktok.com/@diddlyidi</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>keyratio</t>
+          <t>diane.docherty</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3422,24 +3390,24 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-27 13:35:02</t>
+          <t>2026-09-15 09:50:59</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@keyratio</t>
+          <t>https://www.tiktok.com/@diane.docherty</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kamo76710</t>
+          <t>desylviaa1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3456,65 +3424,65 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-20 05:21:24</t>
+          <t>2026-09-27 10:40:10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kamo76710</t>
+          <t>https://www.tiktok.com/@desylviaa1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>konaduroi</t>
+          <t>claudia.claudia970</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-15 03:00:44</t>
+          <t>2026-09-20 22:09:26</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@konaduroi</t>
+          <t>https://www.tiktok.com/@claudia.claudia970</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>letsmakeitkentlimited</t>
+          <t>katseyelocer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3524,65 +3492,65 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-26 08:39:02</t>
+          <t>2026-09-15 22:58:52</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@letsmakeitkentlimited</t>
+          <t>https://www.tiktok.com/@katseyelocer</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>lindaefionayi</t>
+          <t>kaylee_dexter</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-23 20:46:33</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lindaefionayi</t>
+          <t>https://www.tiktok.com/@kaylee_dexter</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>laurywilliams</t>
+          <t>jem17363</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3592,24 +3560,24 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-26 16:59:35</t>
+          <t>2026-09-21 17:28:16</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@laurywilliams</t>
+          <t>https://www.tiktok.com/@jem17363</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ladydonigbinosa</t>
+          <t>inspirednoor</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3626,31 +3594,31 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-14 07:25:08</t>
+          <t>2026-09-26 17:35:02</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ladydonigbinosa</t>
+          <t>https://www.tiktok.com/@inspirednoor</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>louzreviewz</t>
+          <t>joandusabe</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3660,24 +3628,24 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-26 17:35:02</t>
+          <t>2026-09-19 08:31:29</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@louzreviewz</t>
+          <t>https://www.tiktok.com/@joandusabe</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>lissssaxxx</t>
+          <t>julietogu5</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3694,24 +3662,24 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-23 08:17:25</t>
+          <t>2026-09-14 01:42:26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lissssaxxx</t>
+          <t>https://www.tiktok.com/@julietogu5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>lovecats7112</t>
+          <t>jadepa90</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3728,31 +3696,31 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-26 19:59:48</t>
+          <t>2026-09-26 09:09:09</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lovecats7112</t>
+          <t>https://www.tiktok.com/@jadepa90</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>m.3384</t>
+          <t>hinamalik0611</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3762,24 +3730,24 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-21 10:22:24</t>
+          <t>2026-09-28 10:19:03</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@m.3384</t>
+          <t>https://www.tiktok.com/@hinamalik0611</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>manvinder318</t>
+          <t>homemadefood2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3796,24 +3764,24 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-25 14:14:56</t>
+          <t>2026-09-23 16:44:22</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@manvinder318</t>
+          <t>https://www.tiktok.com/@homemadefood2024</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mahi.rani421</t>
+          <t>hadi.haniya1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3830,24 +3798,24 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-24 13:02:03</t>
+          <t>2026-09-28 10:15:05</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mahi.rani421</t>
+          <t>https://www.tiktok.com/@hadi.haniya1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>maxi_berrie</t>
+          <t>lindaefionayi</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3864,7 +3832,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-22 23:20:40</t>
+          <t>2026-09-23 20:46:33</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3874,48 +3842,48 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maxi_berrie</t>
+          <t>https://www.tiktok.com/@lindaefionayi</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>leerobert123</t>
+          <t>letsmakeitkentlimited</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-26 08:39:02</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@leerobert123</t>
+          <t>https://www.tiktok.com/@letsmakeitkentlimited</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mayma3747</t>
+          <t>leerobert123</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3927,36 +3895,36 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-26 15:22:17</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mayma3747</t>
+          <t>https://www.tiktok.com/@leerobert123</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>megandbellaxx</t>
+          <t>lissssaxxx</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3966,24 +3934,24 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-26 17:37:02</t>
+          <t>2026-09-23 08:17:25</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@megandbellaxx</t>
+          <t>https://www.tiktok.com/@lissssaxxx</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mersoo712</t>
+          <t>m.3384</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3995,63 +3963,63 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-24 12:56:04</t>
+          <t>2026-09-21 10:22:24</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mersoo712</t>
+          <t>https://www.tiktok.com/@m.3384</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mehmoonaali238</t>
+          <t>lovecats7112</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-17 11:42:05</t>
+          <t>2026-09-26 19:59:48</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mehmoonaali238</t>
+          <t>https://www.tiktok.com/@lovecats7112</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>merz3859</t>
+          <t>manvinder318</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4068,92 +4036,92 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-22 21:09:48</t>
+          <t>2026-09-25 14:14:56</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@merz3859</t>
+          <t>https://www.tiktok.com/@manvinder318</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>inspiringtanya83</t>
+          <t>louzreviewz</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-26 17:37:02</t>
+          <t>2026-09-26 17:35:02</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@inspiringtanya83</t>
+          <t>https://www.tiktok.com/@louzreviewz</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>jadepa90</t>
+          <t>mahi.rani421</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-26 09:09:09</t>
+          <t>2026-09-24 13:02:03</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jadepa90</t>
+          <t>https://www.tiktok.com/@mahi.rani421</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>inspirednoor</t>
+          <t>maxi_berrie</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4170,24 +4138,24 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-26 17:35:02</t>
+          <t>2026-09-22 23:20:40</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@inspirednoor</t>
+          <t>https://www.tiktok.com/@maxi_berrie</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>joandusabe</t>
+          <t>mehmoonaali238</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4204,65 +4172,65 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-19 08:31:29</t>
+          <t>2026-09-17 11:42:05</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@joandusabe</t>
+          <t>https://www.tiktok.com/@mehmoonaali238</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>jem17363</t>
+          <t>mayma3747</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-21 17:28:16</t>
+          <t>2026-09-26 15:22:17</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jem17363</t>
+          <t>https://www.tiktok.com/@mayma3747</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>julietogu5</t>
+          <t>mersoo712</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4272,24 +4240,24 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-14 01:42:26</t>
+          <t>2026-09-24 12:56:04</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@julietogu5</t>
+          <t>https://www.tiktok.com/@mersoo712</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>jxnxxkxk</t>
+          <t>merz3859</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4306,31 +4274,31 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-15 12:32:04</t>
+          <t>2026-09-22 21:09:48</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jxnxxkxk</t>
+          <t>https://www.tiktok.com/@merz3859</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>katseyelocer</t>
+          <t>mi55marie</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4340,58 +4308,58 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-15 22:58:52</t>
+          <t>2026-09-28 09:31:04</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@katseyelocer</t>
+          <t>https://www.tiktok.com/@mi55marie</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>flash_finds1</t>
+          <t>missyspranno12</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-27 13:35:02</t>
+          <t>2026-09-15 13:31:44</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@flash_finds1</t>
+          <t>https://www.tiktok.com/@missyspranno12</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>fellykemmy3</t>
+          <t>monicalavern</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4408,65 +4376,65 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-24 20:39:00</t>
+          <t>2026-09-15 13:00:13</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fellykemmy3</t>
+          <t>https://www.tiktok.com/@monicalavern</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>fahmidaislam2120</t>
+          <t>mum3tees</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-23 15:26:11</t>
+          <t>2026-09-26 15:28:17</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fahmidaislam2120</t>
+          <t>https://www.tiktok.com/@mum3tees</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>nomzy.gladys</t>
+          <t>mummyzaraa</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4476,24 +4444,24 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-25 10:26:03</t>
+          <t>2026-09-23 08:16:05</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nomzy.gladys</t>
+          <t>https://www.tiktok.com/@mummyzaraa</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>neatshops</t>
+          <t>munasheish</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4510,24 +4478,24 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-26 17:37:02</t>
+          <t>2026-09-25 10:27:59</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@neatshops</t>
+          <t>https://www.tiktok.com/@munasheish</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>naveed19.88</t>
+          <t>na2706_1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4544,24 +4512,24 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-25 22:46:15</t>
+          <t>2026-09-20 23:38:18</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@naveed19.88</t>
+          <t>https://www.tiktok.com/@na2706_1</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>nancymm52</t>
+          <t>nanahdaramy</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4578,24 +4546,24 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-18 07:04:23</t>
+          <t>2026-09-14 00:12:20</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nancymm52</t>
+          <t>https://www.tiktok.com/@nanahdaramy</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>nanahdaramy</t>
+          <t>jxnxxkxk</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4612,7 +4580,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-14 00:12:20</t>
+          <t>2026-09-15 12:32:04</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4622,14 +4590,14 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nanahdaramy</t>
+          <t>https://www.tiktok.com/@jxnxxkxk</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>na2706_1</t>
+          <t>kamo76710</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4646,31 +4614,31 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-20 23:38:18</t>
+          <t>2026-09-20 05:21:24</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@na2706_1</t>
+          <t>https://www.tiktok.com/@kamo76710</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>munasheish</t>
+          <t>keyratio</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4680,24 +4648,24 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-25 10:27:59</t>
+          <t>2026-09-27 13:35:02</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@munasheish</t>
+          <t>https://www.tiktok.com/@keyratio</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>mummyzaraa</t>
+          <t>kayyasin87</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4714,24 +4682,24 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-23 08:16:05</t>
+          <t>2026-09-28 10:10:05</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mummyzaraa</t>
+          <t>https://www.tiktok.com/@kayyasin87</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>mum3tees</t>
+          <t>konaduroi</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4748,24 +4716,24 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-26 15:28:17</t>
+          <t>2026-09-15 03:00:44</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mum3tees</t>
+          <t>https://www.tiktok.com/@konaduroi</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>monicalavern</t>
+          <t>ladydonigbinosa</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4782,31 +4750,31 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-15 13:00:13</t>
+          <t>2026-09-14 07:25:08</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@monicalavern</t>
+          <t>https://www.tiktok.com/@ladydonigbinosa</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>missyspranno12</t>
+          <t>laurywilliams</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4816,41 +4784,41 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-15 13:31:44</t>
+          <t>2026-09-26 16:59:35</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@missyspranno12</t>
+          <t>https://www.tiktok.com/@laurywilliams</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>princessanna1738</t>
+          <t>inspiringtanya83</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-25 07:04:05</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4860,14 +4828,14 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princessanna1738</t>
+          <t>https://www.tiktok.com/@inspiringtanya83</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>patriciaappiah280</t>
+          <t>hchahal80</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4884,31 +4852,31 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-23 10:08:56</t>
+          <t>2026-09-15 20:35:21</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@patriciaappiah280</t>
+          <t>https://www.tiktok.com/@hchahal80</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>paul.d.awson</t>
+          <t>gella4573</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4918,58 +4886,58 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-26 18:18:04</t>
+          <t>2026-09-16 07:50:13</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@paul.d.awson</t>
+          <t>https://www.tiktok.com/@gella4573</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ola.oluwatoyin.ad</t>
+          <t>oladayomartins</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-25 13:50:20</t>
+          <t>2026-09-17 21:17:16</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ola.oluwatoyin.ad</t>
+          <t>https://www.tiktok.com/@oladayomartins</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>nrahi28</t>
+          <t>ola.oluwatoyin.ad</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4986,24 +4954,24 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-20 14:59:29</t>
+          <t>2026-09-25 13:50:20</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nrahi28</t>
+          <t>https://www.tiktok.com/@ola.oluwatoyin.ad</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ranifarooq_3</t>
+          <t>obaa_yaaasantewaa0</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5015,36 +4983,36 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-13 22:37:56</t>
+          <t>2026-09-28 10:10:05</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ranifarooq_3</t>
+          <t>https://www.tiktok.com/@obaa_yaaasantewaa0</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>radhekrishna_11</t>
+          <t>nxthxnfrxmdxy</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5054,7 +5022,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-21 11:21:47</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5064,14 +5032,14 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@radhekrishna_11</t>
+          <t>https://www.tiktok.com/@nxthxnfrxmdxy</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rabbit_pm12</t>
+          <t>nrahi28</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5088,24 +5056,24 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-09-25 19:17:46</t>
+          <t>2026-09-20 14:59:29</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rabbit_pm12</t>
+          <t>https://www.tiktok.com/@nrahi28</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>r4xla15</t>
+          <t>nonochou12</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5122,31 +5090,31 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-20 15:22:42</t>
+          <t>2026-09-28 00:42:49</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@r4xla15</t>
+          <t>https://www.tiktok.com/@nonochou12</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>queeen_0f_hearts</t>
+          <t>nomzy.gladys</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5156,41 +5124,41 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-13 23:51:38</t>
+          <t>2026-09-25 10:26:03</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queeen_0f_hearts</t>
+          <t>https://www.tiktok.com/@nomzy.gladys</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>riderrrr70</t>
+          <t>nickymademebuyit</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-27 14:15:10</t>
+          <t>2026-09-28 10:16:04</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5200,21 +5168,21 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@riderrrr70</t>
+          <t>https://www.tiktok.com/@nickymademebuyit</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>reems_ttsshop</t>
+          <t>naveed19.88</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5224,24 +5192,24 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-25 22:46:15</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reems_ttsshop</t>
+          <t>https://www.tiktok.com/@naveed19.88</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>reykkhan</t>
+          <t>nancymm52</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5258,24 +5226,24 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-25 17:53:08</t>
+          <t>2026-09-18 07:04:23</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reykkhan</t>
+          <t>https://www.tiktok.com/@nancymm52</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ruksi1607</t>
+          <t>r4xla15</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5292,24 +5260,24 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-13 20:49:20</t>
+          <t>2026-09-20 15:22:42</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ruksi1607</t>
+          <t>https://www.tiktok.com/@r4xla15</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ruas_dream</t>
+          <t>princessanna1738</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5326,24 +5294,24 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-27 11:00:34</t>
+          <t>2026-09-25 07:04:05</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ruas_dream</t>
+          <t>https://www.tiktok.com/@princessanna1738</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rozana2026</t>
+          <t>patriciaappiah280</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5360,24 +5328,24 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-19 15:08:34</t>
+          <t>2026-09-23 10:08:56</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rozana2026</t>
+          <t>https://www.tiktok.com/@patriciaappiah280</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>nxthxnfrxmdxy</t>
+          <t>paul.d.awson</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5394,58 +5362,58 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-26 18:18:04</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nxthxnfrxmdxy</t>
+          <t>https://www.tiktok.com/@paul.d.awson</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>oluwatoyosiabayom</t>
+          <t>radhekrishna_11</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-09-14 17:04:02</t>
+          <t>2026-09-21 11:21:47</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwatoyosiabayom</t>
+          <t>https://www.tiktok.com/@radhekrishna_11</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>omolade.abebi</t>
+          <t>oluwatoyin0322</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5462,24 +5430,24 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-09-17 10:33:35</t>
+          <t>2026-09-28 23:38:06</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@omolade.abebi</t>
+          <t>https://www.tiktok.com/@oluwatoyin0322</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>padnerkupakuwana</t>
+          <t>rozana2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5496,58 +5464,58 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-09-13 02:02:06</t>
+          <t>2026-09-19 15:08:34</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@padnerkupakuwana</t>
+          <t>https://www.tiktok.com/@rozana2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>oladayomartins</t>
+          <t>riderrrr70</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-09-17 21:17:16</t>
+          <t>2026-09-27 14:15:10</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oladayomartins</t>
+          <t>https://www.tiktok.com/@riderrrr70</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>sedi546</t>
+          <t>reykkhan</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -5564,31 +5532,31 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-13 15:46:07</t>
+          <t>2026-09-25 17:53:08</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sedi546</t>
+          <t>https://www.tiktok.com/@reykkhan</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>samiahajam</t>
+          <t>reems_ttsshop</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5598,31 +5566,31 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-25 10:39:07</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samiahajam</t>
+          <t>https://www.tiktok.com/@reems_ttsshop</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>samstrendingdeals</t>
+          <t>rabbit_pm12</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5632,65 +5600,65 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-09-26 17:38:02</t>
+          <t>2026-09-25 19:17:46</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samstrendingdeals</t>
+          <t>https://www.tiktok.com/@rabbit_pm12</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>sbegum.79</t>
+          <t>samiahajam</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-21 17:38:25</t>
+          <t>2026-09-25 10:39:07</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sbegum.79</t>
+          <t>https://www.tiktok.com/@samiahajam</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sajarshed</t>
+          <t>samstrendingdeals</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5700,24 +5668,24 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-09-19 10:17:35</t>
+          <t>2026-09-26 17:38:02</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sajarshed</t>
+          <t>https://www.tiktok.com/@samstrendingdeals</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>shopforfiver</t>
+          <t>ruas_dream</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -5734,65 +5702,65 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-21 15:01:03</t>
+          <t>2026-09-27 11:00:34</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shopforfiver</t>
+          <t>https://www.tiktok.com/@ruas_dream</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>shazia11235</t>
+          <t>sbegum.79</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-09-24 23:21:59</t>
+          <t>2026-09-21 17:38:25</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shazia11235</t>
+          <t>https://www.tiktok.com/@sbegum.79</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>shasha.0891</t>
+          <t>sajarshed</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5802,24 +5770,24 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-23 13:48:02</t>
+          <t>2026-09-19 10:17:35</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shasha.0891</t>
+          <t>https://www.tiktok.com/@sajarshed</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>sopharella.loves</t>
+          <t>shasha.0891</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -5836,75 +5804,75 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-09-26 17:35:02</t>
+          <t>2026-09-23 13:48:02</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sopharella.loves</t>
+          <t>https://www.tiktok.com/@shasha.0891</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>steffispicks</t>
+          <t>seyiedeliciouscocktails</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:03</t>
+          <t>2026-09-25 06:38:51</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@steffispicks</t>
+          <t>https://www.tiktok.com/@seyiedeliciouscocktails</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>suziefenton</t>
+          <t>shazia11235</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-09-23 10:47:02</t>
+          <t>2026-09-24 23:21:59</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5914,48 +5882,48 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@suziefenton</t>
+          <t>https://www.tiktok.com/@shazia11235</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>taiwooluyemitaiwo</t>
+          <t>shopforfiver</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-09-23 16:28:21</t>
+          <t>2026-09-21 15:01:03</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@taiwooluyemitaiwo</t>
+          <t>https://www.tiktok.com/@shopforfiver</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>teeyworld_confectionery</t>
+          <t>omolade.abebi</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -5972,31 +5940,31 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-09-25 19:30:28</t>
+          <t>2026-09-17 10:33:35</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teeyworld_confectionery</t>
+          <t>https://www.tiktok.com/@omolade.abebi</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>thehomelylondon</t>
+          <t>oluwatoyosiabayom</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -6006,31 +5974,31 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-09-18 15:51:23</t>
+          <t>2026-09-14 17:04:02</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thehomelylondon</t>
+          <t>https://www.tiktok.com/@oluwatoyosiabayom</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>shukar7860</t>
+          <t>simplydivinedeals</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6040,24 +6008,24 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-09-22 09:29:34</t>
+          <t>2026-09-28 10:13:03</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shukar7860</t>
+          <t>https://www.tiktok.com/@simplydivinedeals</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>seyiedeliciouscocktails</t>
+          <t>shukar7860</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -6074,24 +6042,24 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-09-25 06:38:51</t>
+          <t>2026-09-22 09:29:34</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seyiedeliciouscocktails</t>
+          <t>https://www.tiktok.com/@shukar7860</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tinku78616</t>
+          <t>sparkle22227</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -6108,206 +6076,198 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-09-25 17:21:23</t>
+          <t>2026-09-28 10:15:05</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinku78616</t>
+          <t>https://www.tiktok.com/@sparkle22227</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>tifetito02</t>
+          <t>steffispicks</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-09-16 21:55:36</t>
+          <t>2026-09-22 19:57:03</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tifetito02</t>
+          <t>https://www.tiktok.com/@steffispicks</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tixtok148</t>
+          <t>teeyworld_confectionery</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-09-19 18:20:29</t>
+          <t>2026-09-25 19:30:28</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tixtok148</t>
+          <t>https://www.tiktok.com/@teeyworld_confectionery</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>triciaebun</t>
+          <t>thehomelylondon</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-09-25 16:57:55</t>
+          <t>2026-09-18 15:51:23</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@triciaebun</t>
+          <t>https://www.tiktok.com/@thehomelylondon</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>user2773140226152</t>
+          <t>suziefenton</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-09-21 20:00:10</t>
+          <t>2026-09-23 10:47:02</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2773140226152</t>
+          <t>https://www.tiktok.com/@suziefenton</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>user5251816210173</t>
+          <t>taiwooluyemitaiwo</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-09-15 20:13:06</t>
+          <t>2026-09-23 16:28:21</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user5251816210173</t>
+          <t>https://www.tiktok.com/@taiwooluyemitaiwo</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>tyanie1703</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>tinku78616</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6320,92 +6280,92 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-09-22 14:51:38</t>
+          <t>2026-09-25 17:21:23</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tyanie1703</t>
+          <t>https://www.tiktok.com/@tinku78616</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>user2182373993526</t>
+          <t>tixtok148</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-21 12:26:17</t>
+          <t>2026-09-19 18:20:29</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2182373993526</t>
+          <t>https://www.tiktok.com/@tixtok148</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>user8318338677754</t>
+          <t>touhaselects</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-09-16 23:49:09</t>
+          <t>2026-09-28 10:12:02</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8318338677754</t>
+          <t>https://www.tiktok.com/@touhaselects</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>user806865620814</t>
+          <t>triciaebun</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -6422,28 +6382,36 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-09-20 17:13:54</t>
+          <t>2026-09-25 16:57:55</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user806865620814</t>
+          <t>https://www.tiktok.com/@triciaebun</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>vain119</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr"/>
-      <c r="C169" t="inlineStr"/>
+          <t>tyanie1703</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D169" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6456,58 +6424,58 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-09-15 09:25:05</t>
+          <t>2026-09-22 14:51:38</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vain119</t>
+          <t>https://www.tiktok.com/@tyanie1703</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>user_78602223</t>
+          <t>ucbabe13</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-09-22 17:40:46</t>
+          <t>2026-09-28 10:10:03</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user_78602223</t>
+          <t>https://www.tiktok.com/@ucbabe13</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>yemi.bello3</t>
+          <t>theloyalsoul1</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -6524,36 +6492,28 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-09-17 07:22:35</t>
+          <t>2026-09-28 20:53:18</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemi.bello3</t>
+          <t>https://www.tiktok.com/@theloyalsoul1</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>yemishittuedemayibo</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>tifetito02</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6566,24 +6526,24 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-09-19 00:15:14</t>
+          <t>2026-09-16 21:55:36</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yemishittuedemayibo</t>
+          <t>https://www.tiktok.com/@tifetito02</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>yvonne21197</t>
+          <t>user2182373993526</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -6600,31 +6560,31 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-09-16 22:41:43</t>
+          <t>2026-09-21 12:26:17</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yvonne21197</t>
+          <t>https://www.tiktok.com/@user2182373993526</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>zara1508ahmed</t>
+          <t>updateinabundance</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6634,15 +6594,499 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
+          <t>2026-09-28 10:11:04</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@updateinabundance</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>user2773140226152</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-09-21 20:00:10</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user2773140226152</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>user35110093</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-09-28 20:20:27</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user35110093</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>user8318338677754</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-09-16 23:49:09</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user8318338677754</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>user99851967341610</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-09-28 16:59:33</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user99851967341610</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>user5251816210173</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:13:06</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user5251816210173</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>user806865620814</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:13:54</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user806865620814</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>vain119</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-09-15 09:25:05</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@vain119</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>user_78602223</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Ashwagandha Coffee</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Free sample from seller</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:40:46</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user_78602223</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>yemi.bello3</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-09-17 07:22:35</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yemi.bello3</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>viralbuysontiktok</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Ashwagandha Coffee</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:13:03</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@viralbuysontiktok</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>yemishittuedemayibo</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:15:14</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yemishittuedemayibo</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>yumnazlife</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:15:06</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yumnazlife</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>yvonne21197</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-09-16 22:41:43</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yvonne21197</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>zara1508ahmed</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
           <t>2026-09-23 03:28:52</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zara1508ahmed</t>
         </is>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -6207,7 +6207,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H237"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sehnamiee</t>
+          <t>zentarauk</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -595,14 +595,10 @@
           <t>£10K-£25K</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -612,24 +608,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-21 20:46:02</t>
+          <t>2026-09-30 11:39:02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sehnamiee</t>
+          <t>https://www.tiktok.com/@zentarauk</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>zentarauk</t>
+          <t>colin_harding</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -637,37 +633,41 @@
           <t>£10K-£25K</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Triphala Capsules with Amla,</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-30 11:39:02</t>
+          <t>2026-09-28 10:10:06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zentarauk</t>
+          <t>https://www.tiktok.com/@colin_harding</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>colin_harding</t>
+          <t>miaweb7new</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -692,24 +692,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-28 10:10:06</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@colin_harding</t>
+          <t>https://www.tiktok.com/@miaweb7new</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>miaweb7new</t>
+          <t>holliedolli94shopsugc0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -719,81 +719,81 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-26 17:37:02</t>
+          <t>2026-09-29 14:37:02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@miaweb7new</t>
+          <t>https://www.tiktok.com/@holliedolli94shopsugc0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>holliedolli94shopsugc0</t>
+          <t>fairyfaryal11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-29 14:37:02</t>
+          <t>2026-09-24 20:07:02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@holliedolli94shopsugc0</t>
+          <t>https://www.tiktok.com/@fairyfaryal11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fairyfaryal11</t>
+          <t>seffshops</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -818,29 +818,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-24 20:07:02</t>
+          <t>2026-09-21 10:52:04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fairyfaryal11</t>
+          <t>https://www.tiktok.com/@seffshops</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>seffshops</t>
+          <t>shelleybelle26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -855,29 +855,29 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-21 10:52:04</t>
+          <t>2026-09-30 14:56:03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seffshops</t>
+          <t>https://www.tiktok.com/@shelleybelle26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>shelleybelle26</t>
+          <t>jasminehagen3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -902,24 +902,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:03</t>
+          <t>2026-09-30 14:59:02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shelleybelle26</t>
+          <t>https://www.tiktok.com/@jasminehagen3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>jasminehagen3</t>
+          <t>dailydealsuk03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -944,24 +944,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-30 14:59:02</t>
+          <t>2026-09-21 10:45:03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jasminehagen3</t>
+          <t>https://www.tiktok.com/@dailydealsuk03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dailydealsuk03</t>
+          <t>georgiaxx___</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -971,39 +971,39 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-21 10:45:03</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailydealsuk03</t>
+          <t>https://www.tiktok.com/@georgiaxx___</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>georgiaxx___</t>
+          <t>callmequeencossy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>50K-100K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-26 17:37:02</t>
+          <t>2026-09-30 14:56:05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@georgiaxx___</t>
+          <t>https://www.tiktok.com/@callmequeencossy</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>callmequeencossy</t>
+          <t>75b.lainey</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1070,24 +1070,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:05</t>
+          <t>2026-09-30 14:58:02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@callmequeencossy</t>
+          <t>https://www.tiktok.com/@75b.lainey</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>75b.lainey</t>
+          <t>tiktok.shopmahi</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1095,41 +1095,37 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-30 14:58:02</t>
+          <t>2026-09-30 14:56:06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@75b.lainey</t>
+          <t>https://www.tiktok.com/@tiktok.shopmahi</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tiktok.shopmahi</t>
+          <t>biancaselects</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1140,34 +1136,34 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:06</t>
+          <t>2026-09-30 14:56:03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiktok.shopmahi</t>
+          <t>https://www.tiktok.com/@biancaselects</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>biancaselects</t>
+          <t>raeganfurness</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1175,10 +1171,14 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1188,24 +1188,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:03</t>
+          <t>2026-09-30 14:59:02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@biancaselects</t>
+          <t>https://www.tiktok.com/@raeganfurness</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>raeganfurness</t>
+          <t>andreeamaria1828</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1213,41 +1213,37 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-30 14:59:02</t>
+          <t>2026-09-30 14:57:02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@raeganfurness</t>
+          <t>https://www.tiktok.com/@andreeamaria1828</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>midlifemakeupmarie</t>
+          <t>sarahs.worldx</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1257,7 +1253,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1272,24 +1268,24 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:03</t>
+          <t>2026-09-30 14:57:02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@midlifemakeupmarie</t>
+          <t>https://www.tiktok.com/@sarahs.worldx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>andreeamaria1828</t>
+          <t>lifeofflozy1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1300,49 +1296,49 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:02</t>
+          <t>2026-09-30 14:57:04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@andreeamaria1828</t>
+          <t>https://www.tiktok.com/@lifeofflozy1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sarahs.worldx</t>
+          <t>hulubasul</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1357,57 +1353,61 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahs.worldx</t>
+          <t>https://www.tiktok.com/@hulubasul</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>lifeofflozy1</t>
+          <t>latina_shops</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:04</t>
+          <t>2026-09-30 14:56:06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeofflozy1</t>
+          <t>https://www.tiktok.com/@latina_shops</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hulubasul</t>
+          <t>shopwithdanz0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:02</t>
+          <t>2026-09-30 14:57:03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hulubasul</t>
+          <t>https://www.tiktok.com/@shopwithdanz0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>latina_shops</t>
+          <t>hinamalik0611</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1474,24 +1474,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:06</t>
+          <t>2026-09-28 10:19:03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@latina_shops</t>
+          <t>https://www.tiktok.com/@hinamalik0611</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>shopwithdanz0</t>
+          <t>demyrobbo01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1521,19 +1521,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shopwithdanz0</t>
+          <t>https://www.tiktok.com/@demyrobbo01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hinamalik0611</t>
+          <t>abdulawwal470</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1558,165 +1558,153 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-28 10:19:03</t>
+          <t>2026-09-30 14:57:03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hinamalik0611</t>
+          <t>https://www.tiktok.com/@abdulawwal470</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>demyrobbo01</t>
+          <t>andreeatts</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:03</t>
+          <t>2026-09-30 14:56:05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@demyrobbo01</t>
+          <t>https://www.tiktok.com/@andreeatts</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ivy_ttsfinds</t>
+          <t>crestworld.cooks</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-01 10:53:02</t>
+          <t>2026-09-27 08:26:05</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ivy_ttsfinds</t>
+          <t>https://www.tiktok.com/@crestworld.cooks</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>abdulawwal470</t>
+          <t>dillytwinmum</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:03</t>
+          <t>2026-09-21 09:55:02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abdulawwal470</t>
+          <t>https://www.tiktok.com/@dillytwinmum</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>andreeatts</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>£200-£500</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>amena.akter3665</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1726,74 +1714,62 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:05</t>
+          <t>2026-09-28 12:23:28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@andreeatts</t>
+          <t>https://www.tiktok.com/@amena.akter3665</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>crestworld.cooks</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>claudia.claudia970</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-27 08:26:05</t>
+          <t>2026-09-20 22:09:26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@crestworld.cooks</t>
+          <t>https://www.tiktok.com/@claudia.claudia970</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dillytwinmum</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>chezzy954</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -1806,141 +1782,133 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-21 09:55:02</t>
+          <t>2026-09-25 13:21:47</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dillytwinmum</t>
+          <t>https://www.tiktok.com/@chezzy954</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>buhat_alla_deals</t>
+          <t>chek_mi_shocase</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-28 10:10:04</t>
+          <t>2026-09-22 17:56:02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@buhat_alla_deals</t>
+          <t>https://www.tiktok.com/@chek_mi_shocase</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>_dosah</t>
+          <t>charliegirl860</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-21 14:58:25</t>
+          <t>2026-09-26 10:54:39</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_dosah</t>
+          <t>https://www.tiktok.com/@charliegirl860</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>_unique_kashmiri_</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>25K-50K</t>
-        </is>
-      </c>
+          <t>carfoon767</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-29 10:25:02</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_unique_kashmiri_</t>
+          <t>https://www.tiktok.com/@carfoon767</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>charliegirl860</t>
+          <t>bukky.yoyo</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1950,24 +1918,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-26 10:54:39</t>
+          <t>2026-10-04 16:50:32</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@charliegirl860</t>
+          <t>https://www.tiktok.com/@bukky.yoyo</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>carfoon767</t>
+          <t>builtfindsuk</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1984,58 +1952,58 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-01 10:47:03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@carfoon767</t>
+          <t>https://www.tiktok.com/@builtfindsuk</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>camaliceward12</t>
+          <t>beauty_shine07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-01 10:53:02</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@camaliceward12</t>
+          <t>https://www.tiktok.com/@beauty_shine07</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>builtfindsuk</t>
+          <t>azlanzaynahzayrahuk</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2052,58 +2020,58 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-01 10:47:03</t>
+          <t>2026-09-28 10:10:05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@builtfindsuk</t>
+          <t>https://www.tiktok.com/@azlanzaynahzayrahuk</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>adeede1</t>
+          <t>diddlyidi</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-03 06:37:25</t>
+          <t>2026-09-23 08:16:02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adeede1</t>
+          <t>https://www.tiktok.com/@diddlyidi</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>amena.akter3665</t>
+          <t>dimpleddp</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2120,24 +2088,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-28 12:23:28</t>
+          <t>2026-09-25 12:30:06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amena.akter3665</t>
+          <t>https://www.tiktok.com/@dimpleddp</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>amanmegbu</t>
+          <t>dinexheese</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2149,29 +2117,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:03</t>
+          <t>2026-09-26 12:16:35</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amanmegbu</t>
+          <t>https://www.tiktok.com/@dinexheese</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>aminajeylani</t>
+          <t>desylviaa1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2188,58 +2156,58 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-23 14:42:07</t>
+          <t>2026-09-27 10:40:10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aminajeylani</t>
+          <t>https://www.tiktok.com/@desylviaa1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>dsda0786</t>
+          <t>corina.creates</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-29 09:46:30</t>
+          <t>2026-09-23 08:16:05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dsda0786</t>
+          <t>https://www.tiktok.com/@corina.creates</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>dinexheese</t>
+          <t>dearlola45</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2256,262 +2224,262 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-26 12:16:35</t>
+          <t>2026-10-01 11:28:54</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dinexheese</t>
+          <t>https://www.tiktok.com/@dearlola45</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>dimpleddp</t>
+          <t>climax.scenes</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-25 12:30:06</t>
+          <t>2026-09-21 06:20:00</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dimpleddp</t>
+          <t>https://www.tiktok.com/@climax.scenes</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>diddlyidi</t>
+          <t>explorewithmex10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-23 08:16:02</t>
+          <t>2026-10-02 09:06:56</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@diddlyidi</t>
+          <t>https://www.tiktok.com/@explorewithmex10</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>dearlola45</t>
+          <t>explore.with.em4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-01 11:28:54</t>
+          <t>2026-10-01 14:44:03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dearlola45</t>
+          <t>https://www.tiktok.com/@explore.with.em4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>desylviaa1</t>
+          <t>duaanoor080120</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-27 10:40:10</t>
+          <t>2026-10-02 06:26:32</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@desylviaa1</t>
+          <t>https://www.tiktok.com/@duaanoor080120</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>chezzy954</t>
+          <t>angelhairstylist1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-25 13:21:47</t>
+          <t>2026-10-04 20:43:03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chezzy954</t>
+          <t>https://www.tiktok.com/@angelhairstylist1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>corina.creates</t>
+          <t>balletdeo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-23 08:16:05</t>
+          <t>2026-09-26 01:45:10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@corina.creates</t>
+          <t>https://www.tiktok.com/@balletdeo</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>chek_mi_shocase</t>
+          <t>babbyzozo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Triphala Capsules with Amla,</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-22 17:56:02</t>
+          <t>2026-09-28 18:28:13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chek_mi_shocase</t>
+          <t>https://www.tiktok.com/@babbyzozo</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>climax.scenes</t>
+          <t>becky.mawunyo</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2528,31 +2496,31 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-21 06:20:00</t>
+          <t>2026-09-28 10:19:04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@climax.scenes</t>
+          <t>https://www.tiktok.com/@becky.mawunyo</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>claudia.claudia970</t>
+          <t>armaan.ahmed37</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2562,31 +2530,31 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-20 22:09:26</t>
+          <t>2026-10-03 19:49:39</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@claudia.claudia970</t>
+          <t>https://www.tiktok.com/@armaan.ahmed37</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>flash_finds1</t>
+          <t>angiereviewslife</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2596,24 +2564,24 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-27 13:35:02</t>
+          <t>2026-10-01 11:04:03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@flash_finds1</t>
+          <t>https://www.tiktok.com/@angiereviewslife</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>fittokfinds88</t>
+          <t>adeede1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2630,31 +2598,31 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-23 16:18:03</t>
+          <t>2026-10-03 06:37:25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fittokfinds88</t>
+          <t>https://www.tiktok.com/@adeede1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>fellykemmy3</t>
+          <t>amanmegbu</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2664,28 +2632,36 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-24 20:39:00</t>
+          <t>2026-09-29 14:41:03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fellykemmy3</t>
+          <t>https://www.tiktok.com/@amanmegbu</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>fkprima123</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
+          <t>amap000</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2693,70 +2669,78 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-26 17:32:35</t>
+          <t>2026-10-03 10:59:49</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fkprima123</t>
+          <t>https://www.tiktok.com/@amap000</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>duaanoor080120</t>
+          <t>aminajeylani</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-02 06:26:32</t>
+          <t>2026-09-23 14:42:07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@duaanoor080120</t>
+          <t>https://www.tiktok.com/@aminajeylani</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>hazels_open_diary</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
+          <t>_unique_kashmiri_</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>25K-50K</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2766,24 +2750,24 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-29 10:25:02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hazels_open_diary</t>
+          <t>https://www.tiktok.com/@_unique_kashmiri_</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>gbm.sees</t>
+          <t>_dosah</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2800,28 +2784,36 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-01 09:00:38</t>
+          <t>2026-09-21 14:58:25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gbm.sees</t>
+          <t>https://www.tiktok.com/@_dosah</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>fmrasalhossain</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
+          <t>_mohlad</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2829,36 +2821,36 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-25 22:32:12</t>
+          <t>2026-10-04 18:10:30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fmrasalhossain</t>
+          <t>https://www.tiktok.com/@_mohlad</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>funmumshops</t>
+          <t>hu123342425</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2868,58 +2860,58 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-28 10:19:02</t>
+          <t>2026-10-04 15:47:04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@funmumshops</t>
+          <t>https://www.tiktok.com/@hu123342425</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>iamvickyshurwen_</t>
+          <t>homemadefood2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-29 10:25:06</t>
+          <t>2026-09-23 16:44:22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iamvickyshurwen_</t>
+          <t>https://www.tiktok.com/@homemadefood2024</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>idrissasesay7</t>
+          <t>gbm.sees</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2936,24 +2928,24 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-02 23:30:18</t>
+          <t>2026-10-01 09:00:38</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@idrissasesay7</t>
+          <t>https://www.tiktok.com/@gbm.sees</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>inspirednoor</t>
+          <t>hazels_open_diary</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2965,104 +2957,104 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-26 17:35:02</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@inspirednoor</t>
+          <t>https://www.tiktok.com/@hazels_open_diary</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>homemadefood2024</t>
+          <t>funmumshops</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-23 16:44:22</t>
+          <t>2026-09-28 10:19:02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@homemadefood2024</t>
+          <t>https://www.tiktok.com/@funmumshops</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>itsjulesmurph</t>
+          <t>fkprima123</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:05</t>
+          <t>2026-09-26 17:32:35</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsjulesmurph</t>
+          <t>https://www.tiktok.com/@fkprima123</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>jadepa90</t>
+          <t>flash_finds1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3072,7 +3064,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-26 09:09:09</t>
+          <t>2026-09-27 13:35:02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3082,14 +3074,14 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jadepa90</t>
+          <t>https://www.tiktok.com/@flash_finds1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>jean.makin</t>
+          <t>fmrasalhossain</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3101,29 +3093,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-03 14:41:36</t>
+          <t>2026-09-25 22:32:12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jean.makin</t>
+          <t>https://www.tiktok.com/@fmrasalhossain</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>jem17363</t>
+          <t>fellykemmy3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3140,92 +3132,92 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-21 17:28:16</t>
+          <t>2026-09-24 20:39:00</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jem17363</t>
+          <t>https://www.tiktok.com/@fellykemmy3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>f.chowdhury15</t>
+          <t>fahmidaislam2120</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-29 23:20:53</t>
+          <t>2026-09-23 15:26:11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@f.chowdhury15</t>
+          <t>https://www.tiktok.com/@fahmidaislam2120</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>fahmidaislam2120</t>
+          <t>f.chowdhury15</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-23 15:26:11</t>
+          <t>2026-09-29 23:20:53</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fahmidaislam2120</t>
+          <t>https://www.tiktok.com/@f.chowdhury15</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>explorewithmex10</t>
+          <t>fittokfinds88</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3242,31 +3234,31 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-10-02 09:06:56</t>
+          <t>2026-09-23 16:18:03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@explorewithmex10</t>
+          <t>https://www.tiktok.com/@fittokfinds88</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>explore.with.em4</t>
+          <t>dsda0786</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3276,58 +3268,58 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-10-01 14:44:03</t>
+          <t>2026-09-29 09:46:30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@explore.with.em4</t>
+          <t>https://www.tiktok.com/@dsda0786</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>juliana_armoh</t>
+          <t>inspirednoor</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-10-01 21:22:31</t>
+          <t>2026-09-26 17:35:02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@juliana_armoh</t>
+          <t>https://www.tiktok.com/@inspirednoor</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>jones23350</t>
+          <t>idrissasesay7</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3344,7 +3336,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:04</t>
+          <t>2026-10-02 23:30:18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3354,14 +3346,14 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jones23350</t>
+          <t>https://www.tiktok.com/@idrissasesay7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>jodijudejj</t>
+          <t>itsjulesmurph</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3378,24 +3370,24 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-01 11:14:02</t>
+          <t>2026-10-01 10:52:05</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jodijudejj</t>
+          <t>https://www.tiktok.com/@itsjulesmurph</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>joandusabe</t>
+          <t>kayyasin87</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3412,31 +3404,31 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-19 08:31:29</t>
+          <t>2026-09-28 10:10:05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@joandusabe</t>
+          <t>https://www.tiktok.com/@kayyasin87</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kerrycavan</t>
+          <t>kaylee_dexter</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3446,17 +3438,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kerrycavan</t>
+          <t>https://www.tiktok.com/@kaylee_dexter</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3477,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3497,7 +3489,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kamo76710</t>
+          <t>kennyshekoni</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3514,51 +3506,51 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-20 05:21:24</t>
+          <t>2026-10-01 19:41:15</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kamo76710</t>
+          <t>https://www.tiktok.com/@kennyshekoni</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kaylee_dexter</t>
+          <t>kimmys_kitchen_garden</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaylee_dexter</t>
+          <t>https://www.tiktok.com/@kimmys_kitchen_garden</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3579,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3599,82 +3591,82 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kimmys_kitchen_garden</t>
+          <t>laurywilliams</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-26 16:59:35</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kimmys_kitchen_garden</t>
+          <t>https://www.tiktok.com/@laurywilliams</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>laurywilliams</t>
+          <t>kerrycavan</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-26 16:59:35</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@laurywilliams</t>
+          <t>https://www.tiktok.com/@kerrycavan</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>letsmakeitkentlimited</t>
+          <t>jean.makin</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3684,24 +3676,24 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-26 08:39:02</t>
+          <t>2026-10-03 14:41:36</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@letsmakeitkentlimited</t>
+          <t>https://www.tiktok.com/@jean.makin</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>lindaefionayi</t>
+          <t>jem17363</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3718,58 +3710,58 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-23 20:46:33</t>
+          <t>2026-09-21 17:28:16</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lindaefionayi</t>
+          <t>https://www.tiktok.com/@jem17363</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>lissssaxxx</t>
+          <t>jodijudejj</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-23 08:17:25</t>
+          <t>2026-10-01 11:14:02</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lissssaxxx</t>
+          <t>https://www.tiktok.com/@jodijudejj</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kayyasin87</t>
+          <t>jones23350</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3786,65 +3778,65 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-28 10:10:05</t>
+          <t>2026-10-01 10:52:04</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kayyasin87</t>
+          <t>https://www.tiktok.com/@jones23350</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kennyshekoni</t>
+          <t>juliana_armoh</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-10-01 19:41:15</t>
+          <t>2026-10-01 21:22:31</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kennyshekoni</t>
+          <t>https://www.tiktok.com/@juliana_armoh</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>louzreviewz</t>
+          <t>kamo76710</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3854,24 +3846,24 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-26 17:35:02</t>
+          <t>2026-09-20 05:21:24</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@louzreviewz</t>
+          <t>https://www.tiktok.com/@kamo76710</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>lolaclothier</t>
+          <t>jadepa90</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3888,24 +3880,24 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-10-01 20:17:12</t>
+          <t>2026-09-26 09:09:09</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lolaclothier</t>
+          <t>https://www.tiktok.com/@jadepa90</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>lovecats7112</t>
+          <t>iamvickyshurwen_</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3922,58 +3914,58 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-26 19:59:48</t>
+          <t>2026-09-29 10:25:06</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lovecats7112</t>
+          <t>https://www.tiktok.com/@iamvickyshurwen_</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>m.3384</t>
+          <t>mahi.rani421</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-21 10:22:24</t>
+          <t>2026-09-24 13:02:03</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@m.3384</t>
+          <t>https://www.tiktok.com/@mahi.rani421</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mariamabdi579</t>
+          <t>manvinder318</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3990,58 +3982,58 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-29 09:01:08</t>
+          <t>2026-09-25 14:14:56</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mariamabdi579</t>
+          <t>https://www.tiktok.com/@manvinder318</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>maxi_berrie</t>
+          <t>mariatincuta11</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-22 23:20:40</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maxi_berrie</t>
+          <t>https://www.tiktok.com/@mariatincuta11</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mahi.rani421</t>
+          <t>mariamabdi579</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4058,36 +4050,28 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-24 13:02:03</t>
+          <t>2026-09-29 09:01:08</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mahi.rani421</t>
+          <t>https://www.tiktok.com/@mariamabdi579</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>amap000</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>maxi_berrie</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4095,36 +4079,36 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-10-03 10:59:49</t>
+          <t>2026-09-22 23:20:40</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amap000</t>
+          <t>https://www.tiktok.com/@maxi_berrie</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>bianca.doing.tiktok</t>
+          <t>mayma3747</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4134,31 +4118,31 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-24 20:37:02</t>
+          <t>2026-09-26 15:22:17</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bianca.doing.tiktok</t>
+          <t>https://www.tiktok.com/@mayma3747</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>bgee2345</t>
+          <t>mersoo712</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4168,65 +4152,65 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-19 22:31:01</t>
+          <t>2026-09-24 12:56:04</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bgee2345</t>
+          <t>https://www.tiktok.com/@mersoo712</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>becky.mawunyo</t>
+          <t>merz3859</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-28 10:19:04</t>
+          <t>2026-09-22 21:09:48</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@becky.mawunyo</t>
+          <t>https://www.tiktok.com/@merz3859</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>angiereviewslife</t>
+          <t>miss_quenny1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4236,58 +4220,58 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-10-01 11:04:03</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angiereviewslife</t>
+          <t>https://www.tiktok.com/@miss_quenny1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>balletdeo</t>
+          <t>moodymarbsandshadow</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-26 01:45:10</t>
+          <t>2026-10-01 10:47:02</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@balletdeo</t>
+          <t>https://www.tiktok.com/@moodymarbsandshadow</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>armaan.ahmed37</t>
+          <t>mr.liverpool885</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4304,7 +4288,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-10-03 19:49:39</t>
+          <t>2026-10-04 09:00:20</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4314,48 +4298,48 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@armaan.ahmed37</t>
+          <t>https://www.tiktok.com/@mr.liverpool885</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>azlanzaynahzayrahuk</t>
+          <t>mrm.foods.opeyemi</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-28 10:10:05</t>
+          <t>2026-10-04 20:07:11</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@azlanzaynahzayrahuk</t>
+          <t>https://www.tiktok.com/@mrm.foods.opeyemi</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>babbyzozo</t>
+          <t>mum3tees</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4372,17 +4356,17 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-28 18:28:13</t>
+          <t>2026-09-26 15:28:17</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@babbyzozo</t>
+          <t>https://www.tiktok.com/@mum3tees</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4395,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4423,7 +4407,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>mum3tees</t>
+          <t>munasheish</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4440,24 +4424,24 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-26 15:28:17</t>
+          <t>2026-09-25 10:27:59</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mum3tees</t>
+          <t>https://www.tiktok.com/@munasheish</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>moodymarbsandshadow</t>
+          <t>mycontemporarylifeinuk</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4474,58 +4458,58 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-10-01 10:47:02</t>
+          <t>2026-10-01 14:55:02</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moodymarbsandshadow</t>
+          <t>https://www.tiktok.com/@mycontemporarylifeinuk</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>miss_quenny1</t>
+          <t>n.raja83</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-29 10:14:04</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@miss_quenny1</t>
+          <t>https://www.tiktok.com/@n.raja83</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>merz3859</t>
+          <t>na2706_1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4542,65 +4526,65 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-22 21:09:48</t>
+          <t>2026-09-20 23:38:18</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@merz3859</t>
+          <t>https://www.tiktok.com/@na2706_1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>mi55marie</t>
+          <t>naveed19.88</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-28 09:31:04</t>
+          <t>2026-09-25 22:46:15</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mi55marie</t>
+          <t>https://www.tiktok.com/@naveed19.88</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>mayma3747</t>
+          <t>nevertoooldnanaxx</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4610,24 +4594,24 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-26 15:22:17</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mayma3747</t>
+          <t>https://www.tiktok.com/@nevertoooldnanaxx</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>mersoo712</t>
+          <t>nomzy.gladys</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4644,7 +4628,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-24 12:56:04</t>
+          <t>2026-09-25 10:26:03</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4654,14 +4638,14 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mersoo712</t>
+          <t>https://www.tiktok.com/@nomzy.gladys</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>manvinder318</t>
+          <t>nonochou12</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4678,31 +4662,31 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-25 14:14:56</t>
+          <t>2026-09-28 00:42:49</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@manvinder318</t>
+          <t>https://www.tiktok.com/@nonochou12</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>obaa_yaaasantewaa0</t>
+          <t>nrahi28</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4712,24 +4696,24 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-28 10:10:05</t>
+          <t>2026-09-20 14:59:29</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@obaa_yaaasantewaa0</t>
+          <t>https://www.tiktok.com/@nrahi28</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>munasheish</t>
+          <t>ola.oluwatoyin.ad</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4746,41 +4730,41 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-25 10:27:59</t>
+          <t>2026-09-25 13:50:20</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@munasheish</t>
+          <t>https://www.tiktok.com/@ola.oluwatoyin.ad</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ola.oluwatoyin.ad</t>
+          <t>letsmakeitkentlimited</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-25 13:50:20</t>
+          <t>2026-09-26 08:39:02</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4790,55 +4774,55 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ola.oluwatoyin.ad</t>
+          <t>https://www.tiktok.com/@letsmakeitkentlimited</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>naveed19.88</t>
+          <t>lifeofhamzaa</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-25 22:46:15</t>
+          <t>2026-10-04 18:28:02</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@naveed19.88</t>
+          <t>https://www.tiktok.com/@lifeofhamzaa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>nomzy.gladys</t>
+          <t>lindaefionayi</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4848,24 +4832,24 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-25 10:26:03</t>
+          <t>2026-09-23 20:46:33</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nomzy.gladys</t>
+          <t>https://www.tiktok.com/@lindaefionayi</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>n.raja83</t>
+          <t>lissssaxxx</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4882,31 +4866,31 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-29 10:14:04</t>
+          <t>2026-09-23 08:17:25</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@n.raja83</t>
+          <t>https://www.tiktok.com/@lissssaxxx</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>mycontemporarylifeinuk</t>
+          <t>lolaclothier</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4916,99 +4900,99 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-10-01 14:55:02</t>
+          <t>2026-10-01 20:17:12</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mycontemporarylifeinuk</t>
+          <t>https://www.tiktok.com/@lolaclothier</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>queenbabe_78</t>
+          <t>lovecats7112</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-10-02 15:22:41</t>
+          <t>2026-09-26 19:59:48</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queenbabe_78</t>
+          <t>https://www.tiktok.com/@lovecats7112</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>princessanna1738</t>
+          <t>m.3384</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-25 07:04:05</t>
+          <t>2026-09-21 10:22:24</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princessanna1738</t>
+          <t>https://www.tiktok.com/@m.3384</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>rachellejane2</t>
+          <t>janet.osayande</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5018,17 +5002,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-10-01 11:04:02</t>
+          <t>2026-10-04 18:25:02</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rachellejane2</t>
+          <t>https://www.tiktok.com/@janet.osayande</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5041,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5069,7 +5053,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>radhekrishna_11</t>
+          <t>queenbabe_78</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5086,31 +5070,31 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-21 11:21:47</t>
+          <t>2026-10-02 15:22:41</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@radhekrishna_11</t>
+          <t>https://www.tiktok.com/@queenbabe_78</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>reems_ttsshop</t>
+          <t>princessanna1738</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5120,31 +5104,31 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-25 07:04:05</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reems_ttsshop</t>
+          <t>https://www.tiktok.com/@princessanna1738</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>reykkhan</t>
+          <t>paul.d.awson</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5154,7 +5138,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-25 17:53:08</t>
+          <t>2026-09-26 18:18:04</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5164,14 +5148,14 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reykkhan</t>
+          <t>https://www.tiktok.com/@paul.d.awson</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rabbit_pm12</t>
+          <t>patriciaappiah280</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5188,24 +5172,24 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-25 19:17:46</t>
+          <t>2026-09-23 10:08:56</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rabbit_pm12</t>
+          <t>https://www.tiktok.com/@patriciaappiah280</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>riderrrr70</t>
+          <t>onos282</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5217,56 +5201,56 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-27 14:15:10</t>
+          <t>2026-10-04 23:21:40</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@riderrrr70</t>
+          <t>https://www.tiktok.com/@onos282</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>rosemthapamagar</t>
+          <t>oluyewi</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-29 10:25:02</t>
+          <t>2026-10-03 19:19:51</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rosemthapamagar</t>
+          <t>https://www.tiktok.com/@oluyewi</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5279,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5307,41 +5291,41 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>oluyewi</t>
+          <t>rosemthapamagar</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-03 19:19:51</t>
+          <t>2026-09-29 10:25:02</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluyewi</t>
+          <t>https://www.tiktok.com/@rosemthapamagar</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>patriciaappiah280</t>
+          <t>ruas_dream</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5358,58 +5342,58 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-09-23 10:08:56</t>
+          <t>2026-09-27 11:00:34</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@patriciaappiah280</t>
+          <t>https://www.tiktok.com/@ruas_dream</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>paul.d.awson</t>
+          <t>sammummyconqueringanxiet</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-09-26 18:18:04</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@paul.d.awson</t>
+          <t>https://www.tiktok.com/@sammummyconqueringanxiet</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>nonochou12</t>
+          <t>samiahajam</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5426,31 +5410,31 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-09-28 00:42:49</t>
+          <t>2026-09-25 10:39:07</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nonochou12</t>
+          <t>https://www.tiktok.com/@samiahajam</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>na2706_1</t>
+          <t>reems_ttsshop</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5460,31 +5444,31 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-09-20 23:38:18</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@na2706_1</t>
+          <t>https://www.tiktok.com/@reems_ttsshop</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>samstrendingdeals</t>
+          <t>reykkhan</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5494,58 +5478,58 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-09-26 17:38:02</t>
+          <t>2026-09-25 17:53:08</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samstrendingdeals</t>
+          <t>https://www.tiktok.com/@reykkhan</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>samiahajam</t>
+          <t>rachellejane2</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-25 10:39:07</t>
+          <t>2026-10-01 11:04:02</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samiahajam</t>
+          <t>https://www.tiktok.com/@rachellejane2</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>sajarshed</t>
+          <t>rabbit_pm12</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5562,126 +5546,126 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-19 10:17:35</t>
+          <t>2026-09-25 19:17:46</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sajarshed</t>
+          <t>https://www.tiktok.com/@rabbit_pm12</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>sabinaesthetic_ldn</t>
+          <t>sbegum.79</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:10</t>
+          <t>2026-09-21 17:38:25</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sabinaesthetic_ldn</t>
+          <t>https://www.tiktok.com/@sbegum.79</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>rozana2026</t>
+          <t>sarahwulatarawa</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-19 15:08:34</t>
+          <t>2026-10-02 06:49:42</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rozana2026</t>
+          <t>https://www.tiktok.com/@sarahwulatarawa</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ruas_dream</t>
+          <t>sarahswhimsyfits</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-09-27 11:00:34</t>
+          <t>2026-10-01 10:50:06</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ruas_dream</t>
+          <t>https://www.tiktok.com/@sarahswhimsyfits</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>sarahwulatarawa</t>
+          <t>samstrendingdeals</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -5693,36 +5677,36 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-10-02 06:49:42</t>
+          <t>2026-09-26 17:38:02</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahwulatarawa</t>
+          <t>https://www.tiktok.com/@samstrendingdeals</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>sbegum.79</t>
+          <t>shannonlou8991</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5732,24 +5716,24 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-09-21 17:38:25</t>
+          <t>2026-10-01 10:50:05</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sbegum.79</t>
+          <t>https://www.tiktok.com/@shannonlou8991</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>shalom_mercy1</t>
+          <t>shareenyousaf</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -5766,17 +5750,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-10-01 09:00:38</t>
+          <t>2026-09-29 10:13:11</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shalom_mercy1</t>
+          <t>https://www.tiktok.com/@shareenyousaf</t>
         </is>
       </c>
     </row>
@@ -5805,7 +5789,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -5839,7 +5823,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -5851,34 +5835,34 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>shannonlou8991</t>
+          <t>shazia11235</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:05</t>
+          <t>2026-09-24 23:21:59</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shannonlou8991</t>
+          <t>https://www.tiktok.com/@shazia11235</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5891,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -5919,7 +5903,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>shareenyousaf</t>
+          <t>shukar7860</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -5936,167 +5920,167 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-09-29 10:13:11</t>
+          <t>2026-09-22 09:29:34</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shareenyousaf</t>
+          <t>https://www.tiktok.com/@shukar7860</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>shazia11235</t>
+          <t>sidkam58</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-09-24 23:21:59</t>
+          <t>2026-10-01 07:57:16</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shazia11235</t>
+          <t>https://www.tiktok.com/@sidkam58</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>sarahswhimsyfits</t>
+          <t>smartfindsuk1</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:06</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahswhimsyfits</t>
+          <t>https://www.tiktok.com/@smartfindsuk1</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>shukar7860</t>
+          <t>smoothshelly</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-09-22 09:29:34</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shukar7860</t>
+          <t>https://www.tiktok.com/@smoothshelly</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>sidkam58</t>
+          <t>riderrrr70</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-10-01 07:57:16</t>
+          <t>2026-09-27 14:15:10</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sidkam58</t>
+          <t>https://www.tiktok.com/@riderrrr70</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>smartfindsuk1</t>
+          <t>radhekrishna_11</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6106,51 +6090,51 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-21 11:21:47</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@smartfindsuk1</t>
+          <t>https://www.tiktok.com/@radhekrishna_11</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>simplysimi_x</t>
+          <t>suziefenton</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-09-29 10:25:02</t>
+          <t>2026-09-23 10:47:02</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@simplysimi_x</t>
+          <t>https://www.tiktok.com/@suziefenton</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6163,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6191,34 +6175,34 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>suziefenton</t>
+          <t>teeyworld_confectionery</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-09-23 10:47:02</t>
+          <t>2026-09-25 19:30:28</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@suziefenton</t>
+          <t>https://www.tiktok.com/@teeyworld_confectionery</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6231,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6259,48 +6243,48 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>smoothshelly</t>
+          <t>theloyalsoul1</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-28 20:53:18</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@smoothshelly</t>
+          <t>https://www.tiktok.com/@theloyalsoul1</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>tara57855</t>
+          <t>themelfords</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6310,31 +6294,31 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-10-01 20:24:02</t>
+          <t>2026-09-29 14:37:03</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tara57855</t>
+          <t>https://www.tiktok.com/@themelfords</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>teensoultalkisback</t>
+          <t>theweebelfastman</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6344,58 +6328,58 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-10-01 14:53:02</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teensoultalkisback</t>
+          <t>https://www.tiktok.com/@theweebelfastman</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>theloyalsoul1</t>
+          <t>tara57855</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-09-28 20:53:18</t>
+          <t>2026-10-01 20:24:02</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@theloyalsoul1</t>
+          <t>https://www.tiktok.com/@tara57855</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>teeyworld_confectionery</t>
+          <t>tinku78616</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -6412,31 +6396,31 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-09-25 19:30:28</t>
+          <t>2026-09-25 17:21:23</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teeyworld_confectionery</t>
+          <t>https://www.tiktok.com/@tinku78616</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>themelfords</t>
+          <t>toryannaxo</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6446,31 +6430,31 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-09-29 14:37:03</t>
+          <t>2026-09-29 14:44:02</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@themelfords</t>
+          <t>https://www.tiktok.com/@toryannaxo</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>theweebelfastman</t>
+          <t>triciaebun</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6480,92 +6464,100 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-25 16:57:55</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@theweebelfastman</t>
+          <t>https://www.tiktok.com/@triciaebun</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>tiadinamakeup</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr"/>
-      <c r="C172" t="inlineStr"/>
+          <t>tyanie1703</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:02</t>
+          <t>2026-09-22 14:51:38</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiadinamakeup</t>
+          <t>https://www.tiktok.com/@tyanie1703</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>nrahi28</t>
+          <t>uk.life.moments</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-09-20 14:59:29</t>
+          <t>2026-10-01 10:50:06</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nrahi28</t>
+          <t>https://www.tiktok.com/@uk.life.moments</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>tinku78616</t>
+          <t>user2182373993526</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -6582,240 +6574,232 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-09-25 17:21:23</t>
+          <t>2026-09-21 12:26:17</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinku78616</t>
+          <t>https://www.tiktok.com/@user2182373993526</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>tixtok148</t>
+          <t>user2773140226152</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-09-19 18:20:29</t>
+          <t>2026-09-21 20:00:10</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tixtok148</t>
+          <t>https://www.tiktok.com/@user2773140226152</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>triciaebun</t>
+          <t>tiadinamakeup</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-09-25 16:57:55</t>
+          <t>2026-09-29 14:41:02</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@triciaebun</t>
+          <t>https://www.tiktok.com/@tiadinamakeup</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>toryannaxo</t>
+          <t>user35110093</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-09-29 14:44:02</t>
+          <t>2026-09-28 20:20:27</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@toryannaxo</t>
+          <t>https://www.tiktok.com/@user35110093</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>uid_7493990254405913333</t>
+          <t>user3998147688485</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:02</t>
+          <t>2026-09-29 09:40:30</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uid_7493990254405913333</t>
+          <t>https://www.tiktok.com/@user3998147688485</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>uid_7493990685109094895</t>
+          <t>user806865620814</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-10-01 07:57:16</t>
+          <t>2026-09-20 17:13:54</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uid_7493990685109094895</t>
+          <t>https://www.tiktok.com/@user806865620814</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>uid_7493992885051951631</t>
+          <t>user6931802591156</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-10-01 11:04:02</t>
+          <t>2026-10-01 16:26:50</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uid_7493992885051951631</t>
+          <t>https://www.tiktok.com/@user6931802591156</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>tyanie1703</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>user9310370027124</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6828,24 +6812,24 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-09-22 14:51:38</t>
+          <t>2026-10-01 19:05:18</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tyanie1703</t>
+          <t>https://www.tiktok.com/@user9310370027124</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>uid_7493993719729589113</t>
+          <t>user99851967341610</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -6862,31 +6846,31 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:02</t>
+          <t>2026-09-28 16:59:33</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uid_7493993719729589113</t>
+          <t>https://www.tiktok.com/@user99851967341610</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>uid_7493994632533608726</t>
+          <t>user_78602223</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6896,65 +6880,65 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-10-01 11:04:02</t>
+          <t>2026-09-22 17:40:46</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uid_7493994632533608726</t>
+          <t>https://www.tiktok.com/@user_78602223</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>uid_7493994686928487673</t>
+          <t>user8258556352859</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-03 10:13:16</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uid_7493994686928487673</t>
+          <t>https://www.tiktok.com/@user8258556352859</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>uid_7494001760527682520</t>
+          <t>veeover40</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6964,24 +6948,24 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-10-01 10:47:02</t>
+          <t>2026-10-01 10:50:04</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uid_7494001760527682520</t>
+          <t>https://www.tiktok.com/@veeover40</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>uid_7494003058839555009</t>
+          <t>viralbuysontiktok</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -6993,29 +6977,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-10-02 06:49:42</t>
+          <t>2026-09-28 10:13:03</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uid_7494003058839555009</t>
+          <t>https://www.tiktok.com/@viralbuysontiktok</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>uid_7494010325181760766</t>
+          <t>www.tiktokhafsaqueen169</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
@@ -7032,109 +7016,109 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-29 14:46:03</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uid_7494010325181760766</t>
+          <t>https://www.tiktok.com/@www.tiktokhafsaqueen169</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>uid_7494010754385675369</t>
+          <t>waboti</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:04</t>
+          <t>2026-10-01 18:00:40</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uid_7494010754385675369</t>
+          <t>https://www.tiktok.com/@waboti</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>uid_7493993713735207066</t>
+          <t>xx_jessl_xx</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-01 11:04:02</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uid_7493993713735207066</t>
+          <t>https://www.tiktok.com/@xx_jessl_xx</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>uid_7494015442443011383</t>
+          <t>yeterecipe</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-10-01 10:53:02</t>
+          <t>2026-10-02 16:32:43</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -7144,21 +7128,21 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uid_7494015442443011383</t>
+          <t>https://www.tiktok.com/@yeterecipe</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>uid_7494022628127441978</t>
+          <t>zainyzee39</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Psyllium Husk Daily Fiber</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -7168,24 +7152,24 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-10-01 11:14:02</t>
+          <t>2026-10-04 10:59:50</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uid_7494022628127441978</t>
+          <t>https://www.tiktok.com/@zainyzee39</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>uid_7494093731061204724</t>
+          <t>zara1508ahmed</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -7202,1553 +7186,15 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-10-01 11:30:23</t>
+          <t>2026-09-23 03:28:52</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7494093731061204724</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>uid_7494144730278102650</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr"/>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Psyllium Husk Daily Fiber</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:52:05</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7494144730278102650</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>uid_7494171640978965704</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr"/>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Hibiscus</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2026-10-01 14:55:02</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7494171640978965704</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>uid_7494190442305782918</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr"/>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-10-01 14:53:02</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7494190442305782918</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>uid_7494270672661546471</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr"/>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Hibiscus</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:52:06</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7494270672661546471</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>uid_7494341222673778227</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr"/>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:52:06</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7494341222673778227</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>uid_7494435599867872683</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr"/>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>Hibiscus</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2026-10-01 20:24:02</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7494435599867872683</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>uid_7494503807812078243</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr"/>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>2026-10-02 06:26:32</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7494503807812078243</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>uid_7494524014108968954</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr"/>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>2026-10-01 14:44:03</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7494524014108968954</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>uid_7494536176088746275</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr"/>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>Psyllium Husk Daily Fiber</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:50:04</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7494536176088746275</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>uid_7494864156781087050</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr"/>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Hibiscus</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:48:02</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7494864156781087050</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>uid_7494918922747151493</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr"/>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>2026-10-03 19:19:51</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7494918922747151493</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>uid_7495483992104995390</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr"/>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>2026-10-01 19:41:15</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7495483992104995390</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>uid_7494010876264678929</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr"/>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>Hibiscus</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:48:02</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7494010876264678929</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>uid_7495509025722304818</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr"/>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Hibiscus</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:50:05</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7495509025722304818</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>uid_7495753604111436589</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr"/>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Psyllium Husk Daily Fiber</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:48:02</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7495753604111436589</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>uid_7495895140345285355</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr"/>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:52:10</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7495895140345285355</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>uid_7495859736242195366</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr"/>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>Hibiscus</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:48:02</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7495859736242195366</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>uid_7495942795493738649</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr"/>
-      <c r="C210" t="inlineStr"/>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>2026-10-01 11:28:54</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7495942795493738649</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>uid_7495947491136211048</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr"/>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:48:02</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7495947491136211048</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>uid_7496094410972564037</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr"/>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:47:03</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7496094410972564037</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>uid_7495941499504920924</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr"/>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Hibiscus</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:50:06</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7495941499504920924</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>uid_7496255604319422953</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr"/>
-      <c r="C214" t="inlineStr"/>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>Hibiscus</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:50:06</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7496255604319422953</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>uid_7496268653971540008</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr"/>
-      <c r="C215" t="inlineStr"/>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:48:02</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7496268653971540008</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>uid_7496284670731979705</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr"/>
-      <c r="C216" t="inlineStr"/>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>Hibiscus</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:52:11</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7496284670731979705</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>uk.life.moments</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr"/>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>Hibiscus</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:50:06</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uk.life.moments</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>user2182373993526</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr"/>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:26:17</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user2182373993526</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>user2773140226152</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr"/>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>2026-09-21 20:00:10</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user2773140226152</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>user35110093</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr"/>
-      <c r="C220" t="inlineStr"/>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>2026-09-28 20:20:27</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user35110093</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>uid_7496208753557407928</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr"/>
-      <c r="C221" t="inlineStr"/>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>Psyllium Husk Daily Fiber</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>2026-10-01 11:04:03</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@uid_7496208753557407928</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>user3998147688485</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr"/>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>2026-09-29 09:40:30</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user3998147688485</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>user6931802591156</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr"/>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>2026-10-01 16:26:50</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user6931802591156</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>user8258556352859</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr"/>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>2026-10-03 10:13:16</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user8258556352859</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>user806865620814</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr"/>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>2026-09-20 17:13:54</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user806865620814</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>user99851967341610</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr"/>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>2026-09-28 16:59:33</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user99851967341610</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>user_78602223</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr"/>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>2026-09-22 17:40:46</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user_78602223</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>veeover40</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr"/>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:50:04</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@veeover40</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>user9310370027124</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr"/>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>2026-10-01 19:05:18</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@user9310370027124</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>vikingfindsuk</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr"/>
-      <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>Shatavari 1300mg Extra Strength</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>2026-09-19 13:38:02</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@vikingfindsuk</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>viralbuysontiktok</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr"/>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>2026-09-28 10:13:03</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@viralbuysontiktok</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>www.tiktokhafsaqueen169</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr"/>
-      <c r="C232" t="inlineStr"/>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>2026-09-29 14:46:03</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@www.tiktokhafsaqueen169</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>waboti</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr"/>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>2026-10-01 18:00:40</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@waboti</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>xx_jessl_xx</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr"/>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>2026-10-01 11:04:02</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@xx_jessl_xx</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>yemishittuedemayibo</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>2026-09-19 00:15:14</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@yemishittuedemayibo</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>yeterecipe</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr"/>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>2026-10-02 16:32:43</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@yeterecipe</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>zara1508ahmed</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr"/>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>2026-09-23 03:28:52</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zara1508ahmed</t>
         </is>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>zentarauk</t>
+          <t>miaweb7new</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -595,37 +595,41 @@
           <t>£10K-£25K</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-30 11:39:02</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zentarauk</t>
+          <t>https://www.tiktok.com/@miaweb7new</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>colin_harding</t>
+          <t>holliedolli94shopsugc0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,22 +639,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-28 10:10:06</t>
+          <t>2026-09-29 14:37:02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -660,24 +664,24 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@colin_harding</t>
+          <t>https://www.tiktok.com/@holliedolli94shopsugc0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>miaweb7new</t>
+          <t>fairyfaryal11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,71 +696,71 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-26 17:37:02</t>
+          <t>2026-09-24 20:07:02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@miaweb7new</t>
+          <t>https://www.tiktok.com/@fairyfaryal11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>holliedolli94shopsugc0</t>
+          <t>seffshops</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-29 14:37:02</t>
+          <t>2026-09-21 10:52:04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@holliedolli94shopsugc0</t>
+          <t>https://www.tiktok.com/@seffshops</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fairyfaryal11</t>
+          <t>shelleybelle26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -766,39 +770,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-24 20:07:02</t>
+          <t>2026-09-30 14:56:03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fairyfaryal11</t>
+          <t>https://www.tiktok.com/@shelleybelle26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>seffshops</t>
+          <t>jasminehagen3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -808,34 +812,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-21 10:52:04</t>
+          <t>2026-09-30 14:59:02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seffshops</t>
+          <t>https://www.tiktok.com/@jasminehagen3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>shelleybelle26</t>
+          <t>dailydealsuk03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -845,12 +849,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -860,24 +864,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:03</t>
+          <t>2026-09-21 10:45:03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shelleybelle26</t>
+          <t>https://www.tiktok.com/@dailydealsuk03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>jasminehagen3</t>
+          <t>georgiaxx___</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -887,39 +891,39 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-30 14:59:02</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jasminehagen3</t>
+          <t>https://www.tiktok.com/@georgiaxx___</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dailydealsuk03</t>
+          <t>callmequeencossy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -929,12 +933,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -944,24 +948,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-21 10:45:03</t>
+          <t>2026-09-30 14:56:05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailydealsuk03</t>
+          <t>https://www.tiktok.com/@callmequeencossy</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>georgiaxx___</t>
+          <t>tiktok.shopmahi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -969,11 +973,7 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>50K-100K</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -986,24 +986,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-26 17:37:02</t>
+          <t>2026-09-30 14:56:06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@georgiaxx___</t>
+          <t>https://www.tiktok.com/@tiktok.shopmahi</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>callmequeencossy</t>
+          <t>biancaselects</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1011,14 +1011,10 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1028,24 +1024,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:05</t>
+          <t>2026-09-30 14:56:03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@callmequeencossy</t>
+          <t>https://www.tiktok.com/@biancaselects</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>75b.lainey</t>
+          <t>raeganfurness</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1055,7 +1051,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1070,24 +1066,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-30 14:58:02</t>
+          <t>2026-09-30 14:59:02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@75b.lainey</t>
+          <t>https://www.tiktok.com/@raeganfurness</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tiktok.shopmahi</t>
+          <t>andreeamaria1828</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1098,7 +1094,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1108,24 +1104,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:06</t>
+          <t>2026-09-30 14:57:02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiktok.shopmahi</t>
+          <t>https://www.tiktok.com/@andreeamaria1828</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>biancaselects</t>
+          <t>sarahs.worldx</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1133,10 +1129,14 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1146,39 +1146,39 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:03</t>
+          <t>2026-09-30 14:57:02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@biancaselects</t>
+          <t>https://www.tiktok.com/@sarahs.worldx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>raeganfurness</t>
+          <t>hulubasul</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1188,72 +1188,76 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-30 14:59:02</t>
+          <t>2026-09-30 14:57:02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@raeganfurness</t>
+          <t>https://www.tiktok.com/@hulubasul</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>andreeamaria1828</t>
+          <t>latina_shops</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:02</t>
+          <t>2026-09-30 14:56:06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@andreeamaria1828</t>
+          <t>https://www.tiktok.com/@latina_shops</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sarahs.worldx</t>
+          <t>shopwithdanz0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1268,35 +1272,39 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:02</t>
+          <t>2026-09-30 14:57:03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahs.worldx</t>
+          <t>https://www.tiktok.com/@shopwithdanz0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>lifeofflozy1</t>
+          <t>hinamalik0611</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1306,24 +1314,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:04</t>
+          <t>2026-09-28 10:19:03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeofflozy1</t>
+          <t>https://www.tiktok.com/@hinamalik0611</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hulubasul</t>
+          <t>demyrobbo01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1333,39 +1341,39 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:02</t>
+          <t>2026-09-30 14:57:03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hulubasul</t>
+          <t>https://www.tiktok.com/@demyrobbo01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>latina_shops</t>
+          <t>abdulawwal470</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1375,12 +1383,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1390,34 +1398,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:06</t>
+          <t>2026-09-30 14:57:03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@latina_shops</t>
+          <t>https://www.tiktok.com/@abdulawwal470</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>shopwithdanz0</t>
+          <t>andreeatts</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1432,29 +1440,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:03</t>
+          <t>2026-09-30 14:56:05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shopwithdanz0</t>
+          <t>https://www.tiktok.com/@andreeatts</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hinamalik0611</t>
+          <t>tonirooney19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1464,7 +1472,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1474,39 +1482,35 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-28 10:19:03</t>
+          <t>2026-10-05 23:00:07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hinamalik0611</t>
+          <t>https://www.tiktok.com/@tonirooney19</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>demyrobbo01</t>
+          <t>crestworld.cooks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1516,91 +1520,83 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:03</t>
+          <t>2026-09-27 08:26:05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@demyrobbo01</t>
+          <t>https://www.tiktok.com/@crestworld.cooks</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>abdulawwal470</t>
+          <t>dillytwinmum</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:03</t>
+          <t>2026-09-21 09:55:02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abdulawwal470</t>
+          <t>https://www.tiktok.com/@dillytwinmum</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>andreeatts</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>£200-£500</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>builtfindsuk</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:05</t>
+          <t>2026-10-01 10:47:03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1610,21 +1606,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@andreeatts</t>
+          <t>https://www.tiktok.com/@builtfindsuk</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>crestworld.cooks</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
+          <t>bukky.yoyo</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
@@ -1633,44 +1625,36 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-27 08:26:05</t>
+          <t>2026-10-04 16:50:32</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@crestworld.cooks</t>
+          <t>https://www.tiktok.com/@bukky.yoyo</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dillytwinmum</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>babbyzozo</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1680,24 +1664,24 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-21 09:55:02</t>
+          <t>2026-09-28 18:28:13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dillytwinmum</t>
+          <t>https://www.tiktok.com/@babbyzozo</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>amena.akter3665</t>
+          <t>armaan.ahmed37</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1709,29 +1693,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-28 12:23:28</t>
+          <t>2026-10-03 19:49:39</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amena.akter3665</t>
+          <t>https://www.tiktok.com/@armaan.ahmed37</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>claudia.claudia970</t>
+          <t>charliegirl860</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1748,17 +1732,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-20 22:09:26</t>
+          <t>2026-09-26 10:54:39</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@claudia.claudia970</t>
+          <t>https://www.tiktok.com/@charliegirl860</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1771,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1799,7 +1783,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>chek_mi_shocase</t>
+          <t>climax.scenes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1816,24 +1800,24 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-22 17:56:02</t>
+          <t>2026-09-21 06:20:00</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chek_mi_shocase</t>
+          <t>https://www.tiktok.com/@climax.scenes</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>charliegirl860</t>
+          <t>dearlola45</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1850,24 +1834,24 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-26 10:54:39</t>
+          <t>2026-10-01 11:28:54</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@charliegirl860</t>
+          <t>https://www.tiktok.com/@dearlola45</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>carfoon767</t>
+          <t>damsel755</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1879,29 +1863,29 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-05 20:02:55</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@carfoon767</t>
+          <t>https://www.tiktok.com/@damsel755</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bukky.yoyo</t>
+          <t>desylviaa1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1913,63 +1897,63 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-04 16:50:32</t>
+          <t>2026-09-27 10:40:10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bukky.yoyo</t>
+          <t>https://www.tiktok.com/@desylviaa1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>builtfindsuk</t>
+          <t>diddlyidi</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-01 10:47:03</t>
+          <t>2026-09-23 08:16:02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@builtfindsuk</t>
+          <t>https://www.tiktok.com/@diddlyidi</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>beauty_shine07</t>
+          <t>chek_mi_shocase</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1981,29 +1965,29 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-09-22 17:56:02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty_shine07</t>
+          <t>https://www.tiktok.com/@chek_mi_shocase</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>azlanzaynahzayrahuk</t>
+          <t>carfoon767</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2020,31 +2004,31 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-28 10:10:05</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@azlanzaynahzayrahuk</t>
+          <t>https://www.tiktok.com/@carfoon767</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>diddlyidi</t>
+          <t>dinexheese</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2054,17 +2038,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-23 08:16:02</t>
+          <t>2026-09-26 12:16:35</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@diddlyidi</t>
+          <t>https://www.tiktok.com/@dinexheese</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2077,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2105,7 +2089,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>dinexheese</t>
+          <t>beauty_shine07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2117,46 +2101,46 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-26 12:16:35</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dinexheese</t>
+          <t>https://www.tiktok.com/@beauty_shine07</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>desylviaa1</t>
+          <t>becky.mawunyo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-27 10:40:10</t>
+          <t>2026-09-28 10:19:04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2166,55 +2150,63 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@desylviaa1</t>
+          <t>https://www.tiktok.com/@becky.mawunyo</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>corina.creates</t>
+          <t>balletdeo</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-23 08:16:05</t>
+          <t>2026-09-26 01:45:10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@corina.creates</t>
+          <t>https://www.tiktok.com/@balletdeo</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>dearlola45</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
+          <t>amap000</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2224,58 +2216,58 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-01 11:28:54</t>
+          <t>2026-10-03 10:59:49</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dearlola45</t>
+          <t>https://www.tiktok.com/@amap000</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>climax.scenes</t>
+          <t>aminajeylani</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-21 06:20:00</t>
+          <t>2026-09-23 14:42:07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@climax.scenes</t>
+          <t>https://www.tiktok.com/@aminajeylani</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>explorewithmex10</t>
+          <t>amena.akter3665</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2292,31 +2284,31 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-02 09:06:56</t>
+          <t>2026-09-28 12:23:28</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@explorewithmex10</t>
+          <t>https://www.tiktok.com/@amena.akter3665</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>explore.with.em4</t>
+          <t>azlanzaynahzayrahuk</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2326,24 +2318,24 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-01 14:44:03</t>
+          <t>2026-09-28 10:10:05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@explore.with.em4</t>
+          <t>https://www.tiktok.com/@azlanzaynahzayrahuk</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>duaanoor080120</t>
+          <t>amanmegbu</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2355,29 +2347,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-02 06:26:32</t>
+          <t>2026-09-29 14:41:03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@duaanoor080120</t>
+          <t>https://www.tiktok.com/@amanmegbu</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>angelhairstylist1</t>
+          <t>adeede1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2389,63 +2381,71 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-04 20:43:03</t>
+          <t>2026-10-03 06:37:25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angelhairstylist1</t>
+          <t>https://www.tiktok.com/@adeede1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>balletdeo</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
+          <t>_unique_kashmiri_</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>25K-50K</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-26 01:45:10</t>
+          <t>2026-09-29 10:25:02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@balletdeo</t>
+          <t>https://www.tiktok.com/@_unique_kashmiri_</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>babbyzozo</t>
+          <t>angelhairstylist1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2457,36 +2457,36 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-28 18:28:13</t>
+          <t>2026-10-04 20:43:03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@babbyzozo</t>
+          <t>https://www.tiktok.com/@angelhairstylist1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>becky.mawunyo</t>
+          <t>angiereviewslife</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2496,28 +2496,36 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-28 10:19:04</t>
+          <t>2026-10-01 11:04:03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@becky.mawunyo</t>
+          <t>https://www.tiktok.com/@angiereviewslife</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>armaan.ahmed37</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
+          <t>_mohlad</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2530,7 +2538,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-03 19:49:39</t>
+          <t>2026-10-04 18:10:30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2540,48 +2548,48 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@armaan.ahmed37</t>
+          <t>https://www.tiktok.com/@_mohlad</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>angiereviewslife</t>
+          <t>_dosah</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-01 11:04:03</t>
+          <t>2026-09-21 14:58:25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angiereviewslife</t>
+          <t>https://www.tiktok.com/@_dosah</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>adeede1</t>
+          <t>gbm.sees</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2598,70 +2606,62 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-03 06:37:25</t>
+          <t>2026-10-01 09:00:38</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adeede1</t>
+          <t>https://www.tiktok.com/@gbm.sees</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>amanmegbu</t>
+          <t>funmumshops</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:03</t>
+          <t>2026-09-28 10:19:02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amanmegbu</t>
+          <t>https://www.tiktok.com/@funmumshops</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>amap000</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>fmrasalhossain</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2669,105 +2669,97 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-03 10:59:49</t>
+          <t>2026-09-25 22:32:12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amap000</t>
+          <t>https://www.tiktok.com/@fmrasalhossain</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>aminajeylani</t>
+          <t>flash_finds1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-23 14:42:07</t>
+          <t>2026-09-27 13:35:02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aminajeylani</t>
+          <t>https://www.tiktok.com/@flash_finds1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>_unique_kashmiri_</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>25K-50K</t>
-        </is>
-      </c>
+          <t>fittokfinds88</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-29 10:25:02</t>
+          <t>2026-09-23 16:18:03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_unique_kashmiri_</t>
+          <t>https://www.tiktok.com/@fittokfinds88</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>_dosah</t>
+          <t>fkprima123</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2784,36 +2776,28 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-21 14:58:25</t>
+          <t>2026-09-26 17:32:35</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_dosah</t>
+          <t>https://www.tiktok.com/@fkprima123</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>_mohlad</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>fellykemmy3</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2821,36 +2805,36 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-10-04 18:10:30</t>
+          <t>2026-09-24 20:39:00</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_mohlad</t>
+          <t>https://www.tiktok.com/@fellykemmy3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>hu123342425</t>
+          <t>fahmidaislam2120</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2860,58 +2844,58 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-04 15:47:04</t>
+          <t>2026-09-23 15:26:11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hu123342425</t>
+          <t>https://www.tiktok.com/@fahmidaislam2120</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>homemadefood2024</t>
+          <t>duaanoor080120</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-23 16:44:22</t>
+          <t>2026-10-02 06:26:32</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@homemadefood2024</t>
+          <t>https://www.tiktok.com/@duaanoor080120</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>gbm.sees</t>
+          <t>f.chowdhury15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2928,24 +2912,24 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-01 09:00:38</t>
+          <t>2026-09-29 23:20:53</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gbm.sees</t>
+          <t>https://www.tiktok.com/@f.chowdhury15</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>hazels_open_diary</t>
+          <t>explorewithmex10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2957,12 +2941,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-02 09:06:56</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2972,21 +2956,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hazels_open_diary</t>
+          <t>https://www.tiktok.com/@explorewithmex10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>funmumshops</t>
+          <t>explore.with.em4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2996,24 +2980,24 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-28 10:19:02</t>
+          <t>2026-10-01 14:44:03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@funmumshops</t>
+          <t>https://www.tiktok.com/@explore.with.em4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>fkprima123</t>
+          <t>dsda0786</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3030,31 +3014,31 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-26 17:32:35</t>
+          <t>2026-09-29 09:46:30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fkprima123</t>
+          <t>https://www.tiktok.com/@dsda0786</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>flash_finds1</t>
+          <t>egooyibo41</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3064,58 +3048,58 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-27 13:35:02</t>
+          <t>2026-10-05 13:55:48</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@flash_finds1</t>
+          <t>https://www.tiktok.com/@egooyibo41</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>fmrasalhossain</t>
+          <t>iamvickyshurwen_</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-25 22:32:12</t>
+          <t>2026-09-29 10:25:06</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fmrasalhossain</t>
+          <t>https://www.tiktok.com/@iamvickyshurwen_</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>fellykemmy3</t>
+          <t>homemadefood2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3132,126 +3116,126 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-24 20:39:00</t>
+          <t>2026-09-23 16:44:22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fellykemmy3</t>
+          <t>https://www.tiktok.com/@homemadefood2024</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>fahmidaislam2120</t>
+          <t>jem17363</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-23 15:26:11</t>
+          <t>2026-09-21 17:28:16</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fahmidaislam2120</t>
+          <t>https://www.tiktok.com/@jem17363</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>f.chowdhury15</t>
+          <t>jodijudejj</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-29 23:20:53</t>
+          <t>2026-10-01 11:14:02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@f.chowdhury15</t>
+          <t>https://www.tiktok.com/@jodijudejj</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>fittokfinds88</t>
+          <t>juliana_armoh</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-23 16:18:03</t>
+          <t>2026-10-01 21:22:31</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fittokfinds88</t>
+          <t>https://www.tiktok.com/@juliana_armoh</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>dsda0786</t>
+          <t>jones23350</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3268,24 +3252,24 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-29 09:46:30</t>
+          <t>2026-10-01 10:52:04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dsda0786</t>
+          <t>https://www.tiktok.com/@jones23350</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>inspirednoor</t>
+          <t>kayyasin87</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3302,24 +3286,24 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-26 17:35:02</t>
+          <t>2026-09-28 10:10:05</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@inspirednoor</t>
+          <t>https://www.tiktok.com/@kayyasin87</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>idrissasesay7</t>
+          <t>kaz.gym82</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3331,199 +3315,199 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-02 23:30:18</t>
+          <t>2026-10-05 08:29:56</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@idrissasesay7</t>
+          <t>https://www.tiktok.com/@kaz.gym82</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>itsjulesmurph</t>
+          <t>kennyshekoni</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:05</t>
+          <t>2026-10-01 19:41:15</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsjulesmurph</t>
+          <t>https://www.tiktok.com/@kennyshekoni</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kayyasin87</t>
+          <t>kaylee_dexter</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-28 10:10:05</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kayyasin87</t>
+          <t>https://www.tiktok.com/@kaylee_dexter</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kaylee_dexter</t>
+          <t>idrissasesay7</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-10-02 23:30:18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaylee_dexter</t>
+          <t>https://www.tiktok.com/@idrissasesay7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>keyratio</t>
+          <t>ilzb7</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-27 13:35:02</t>
+          <t>2026-10-05 16:59:43</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@keyratio</t>
+          <t>https://www.tiktok.com/@ilzb7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kennyshekoni</t>
+          <t>itsjulesmurph</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-10-01 19:41:15</t>
+          <t>2026-10-01 10:52:05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kennyshekoni</t>
+          <t>https://www.tiktok.com/@itsjulesmurph</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kimmys_kitchen_garden</t>
+          <t>inspirednoor</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3540,99 +3524,99 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-26 17:35:02</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kimmys_kitchen_garden</t>
+          <t>https://www.tiktok.com/@inspirednoor</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>knicksmakeuppro</t>
+          <t>jadepa90</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-10-01 11:30:23</t>
+          <t>2026-09-26 09:09:09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@knicksmakeuppro</t>
+          <t>https://www.tiktok.com/@jadepa90</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>laurywilliams</t>
+          <t>janet.osayande</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-26 16:59:35</t>
+          <t>2026-10-04 18:25:02</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@laurywilliams</t>
+          <t>https://www.tiktok.com/@janet.osayande</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kerrycavan</t>
+          <t>jean.makin</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3642,24 +3626,24 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-03 14:41:36</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kerrycavan</t>
+          <t>https://www.tiktok.com/@jean.makin</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>jean.makin</t>
+          <t>hu123342425</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3676,7 +3660,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-03 14:41:36</t>
+          <t>2026-10-04 15:47:04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3686,167 +3670,167 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jean.makin</t>
+          <t>https://www.tiktok.com/@hu123342425</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>jem17363</t>
+          <t>lifeofhamzaa</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-21 17:28:16</t>
+          <t>2026-10-04 18:28:02</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jem17363</t>
+          <t>https://www.tiktok.com/@lifeofhamzaa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>jodijudejj</t>
+          <t>lindaefionayi</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-10-01 11:14:02</t>
+          <t>2026-09-23 20:46:33</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jodijudejj</t>
+          <t>https://www.tiktok.com/@lindaefionayi</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>jones23350</t>
+          <t>lolaclothier</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:04</t>
+          <t>2026-10-01 20:17:12</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jones23350</t>
+          <t>https://www.tiktok.com/@lolaclothier</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>juliana_armoh</t>
+          <t>lissssaxxx</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-10-01 21:22:31</t>
+          <t>2026-09-23 08:17:25</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@juliana_armoh</t>
+          <t>https://www.tiktok.com/@lissssaxxx</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kamo76710</t>
+          <t>m.3384</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-20 05:21:24</t>
+          <t>2026-09-21 10:22:24</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3856,191 +3840,191 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kamo76710</t>
+          <t>https://www.tiktok.com/@m.3384</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>jadepa90</t>
+          <t>mahi.rani421</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-26 09:09:09</t>
+          <t>2026-09-24 13:02:03</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jadepa90</t>
+          <t>https://www.tiktok.com/@mahi.rani421</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>iamvickyshurwen_</t>
+          <t>manvinder318</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-29 10:25:06</t>
+          <t>2026-09-25 14:14:56</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iamvickyshurwen_</t>
+          <t>https://www.tiktok.com/@manvinder318</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mahi.rani421</t>
+          <t>lovecats7112</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-24 13:02:03</t>
+          <t>2026-09-26 19:59:48</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mahi.rani421</t>
+          <t>https://www.tiktok.com/@lovecats7112</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>manvinder318</t>
+          <t>mariatincuta11</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-25 14:14:56</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@manvinder318</t>
+          <t>https://www.tiktok.com/@mariatincuta11</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mariatincuta11</t>
+          <t>maxi_berrie</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-09-22 23:20:40</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mariatincuta11</t>
+          <t>https://www.tiktok.com/@maxi_berrie</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mariamabdi579</t>
+          <t>mersoo712</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4050,167 +4034,167 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-29 09:01:08</t>
+          <t>2026-09-24 12:56:04</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mariamabdi579</t>
+          <t>https://www.tiktok.com/@mersoo712</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>maxi_berrie</t>
+          <t>mayma3747</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-22 23:20:40</t>
+          <t>2026-09-26 15:22:17</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maxi_berrie</t>
+          <t>https://www.tiktok.com/@mayma3747</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mayma3747</t>
+          <t>merz3859</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-26 15:22:17</t>
+          <t>2026-09-22 21:09:48</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mayma3747</t>
+          <t>https://www.tiktok.com/@merz3859</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mersoo712</t>
+          <t>miss_quenny1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-24 12:56:04</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mersoo712</t>
+          <t>https://www.tiktok.com/@miss_quenny1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>merz3859</t>
+          <t>moodymarbsandshadow</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-22 21:09:48</t>
+          <t>2026-10-01 10:47:02</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@merz3859</t>
+          <t>https://www.tiktok.com/@moodymarbsandshadow</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>miss_quenny1</t>
+          <t>mr.liverpool885</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4220,31 +4204,31 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-04 09:00:20</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@miss_quenny1</t>
+          <t>https://www.tiktok.com/@mr.liverpool885</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>moodymarbsandshadow</t>
+          <t>mrm.foods.opeyemi</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4254,24 +4238,24 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-10-01 10:47:02</t>
+          <t>2026-10-04 20:07:11</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moodymarbsandshadow</t>
+          <t>https://www.tiktok.com/@mrm.foods.opeyemi</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>mr.liverpool885</t>
+          <t>mum3tees</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4283,29 +4267,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-10-04 09:00:20</t>
+          <t>2026-09-26 15:28:17</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mr.liverpool885</t>
+          <t>https://www.tiktok.com/@mum3tees</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>mrm.foods.opeyemi</t>
+          <t>mummyzaraa</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4317,29 +4301,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-10-04 20:07:11</t>
+          <t>2026-09-23 08:16:05</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mrm.foods.opeyemi</t>
+          <t>https://www.tiktok.com/@mummyzaraa</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>mum3tees</t>
+          <t>munasheish</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4356,58 +4340,58 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-26 15:28:17</t>
+          <t>2026-09-25 10:27:59</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mum3tees</t>
+          <t>https://www.tiktok.com/@munasheish</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>mummyzaraa</t>
+          <t>mycontemporarylifeinuk</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-23 08:16:05</t>
+          <t>2026-10-01 14:55:02</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mummyzaraa</t>
+          <t>https://www.tiktok.com/@mycontemporarylifeinuk</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>munasheish</t>
+          <t>n.raja83</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4424,133 +4408,133 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-25 10:27:59</t>
+          <t>2026-09-29 10:14:04</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@munasheish</t>
+          <t>https://www.tiktok.com/@n.raja83</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>mycontemporarylifeinuk</t>
+          <t>naveed19.88</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-10-01 14:55:02</t>
+          <t>2026-09-25 22:46:15</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mycontemporarylifeinuk</t>
+          <t>https://www.tiktok.com/@naveed19.88</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>n.raja83</t>
+          <t>nevertoooldnanaxx</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-29 10:14:04</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@n.raja83</t>
+          <t>https://www.tiktok.com/@nevertoooldnanaxx</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>na2706_1</t>
+          <t>kerrycavan</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-20 23:38:18</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@na2706_1</t>
+          <t>https://www.tiktok.com/@kerrycavan</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>naveed19.88</t>
+          <t>keyratio</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4560,65 +4544,65 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-25 22:46:15</t>
+          <t>2026-09-27 13:35:02</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@naveed19.88</t>
+          <t>https://www.tiktok.com/@keyratio</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>nevertoooldnanaxx</t>
+          <t>knicksmakeuppro</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-10-01 11:30:23</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nevertoooldnanaxx</t>
+          <t>https://www.tiktok.com/@knicksmakeuppro</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>nomzy.gladys</t>
+          <t>kimmys_kitchen_garden</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4628,24 +4612,24 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-25 10:26:03</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nomzy.gladys</t>
+          <t>https://www.tiktok.com/@kimmys_kitchen_garden</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>nonochou12</t>
+          <t>kulwinderrani5</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4657,36 +4641,36 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-28 00:42:49</t>
+          <t>2026-10-05 09:00:08</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nonochou12</t>
+          <t>https://www.tiktok.com/@kulwinderrani5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>nrahi28</t>
+          <t>laurywilliams</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4696,41 +4680,41 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-20 14:59:29</t>
+          <t>2026-09-26 16:59:35</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nrahi28</t>
+          <t>https://www.tiktok.com/@laurywilliams</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ola.oluwatoyin.ad</t>
+          <t>letsmakeitkentlimited</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-25 13:50:20</t>
+          <t>2026-09-26 08:39:02</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4740,21 +4724,21 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ola.oluwatoyin.ad</t>
+          <t>https://www.tiktok.com/@letsmakeitkentlimited</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>letsmakeitkentlimited</t>
+          <t>hazels_open_diary</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4764,58 +4748,58 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-26 08:39:02</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@letsmakeitkentlimited</t>
+          <t>https://www.tiktok.com/@hazels_open_diary</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>lifeofhamzaa</t>
+          <t>paul.d.awson</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-10-04 18:28:02</t>
+          <t>2026-09-26 18:18:04</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeofhamzaa</t>
+          <t>https://www.tiktok.com/@paul.d.awson</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>lindaefionayi</t>
+          <t>patriciaappiah280</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4832,24 +4816,24 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-23 20:46:33</t>
+          <t>2026-09-23 10:08:56</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lindaefionayi</t>
+          <t>https://www.tiktok.com/@patriciaappiah280</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>lissssaxxx</t>
+          <t>onos282</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4861,36 +4845,36 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-23 08:17:25</t>
+          <t>2026-10-04 23:21:40</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lissssaxxx</t>
+          <t>https://www.tiktok.com/@onos282</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>lolaclothier</t>
+          <t>oluyewi</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4900,133 +4884,133 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-10-01 20:17:12</t>
+          <t>2026-10-03 19:19:51</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lolaclothier</t>
+          <t>https://www.tiktok.com/@oluyewi</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>lovecats7112</t>
+          <t>oluwatoyin0322</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-26 19:59:48</t>
+          <t>2026-09-28 23:38:06</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lovecats7112</t>
+          <t>https://www.tiktok.com/@oluwatoyin0322</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>m.3384</t>
+          <t>ola.oluwatoyin.ad</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-21 10:22:24</t>
+          <t>2026-09-25 13:50:20</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@m.3384</t>
+          <t>https://www.tiktok.com/@ola.oluwatoyin.ad</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>janet.osayande</t>
+          <t>nonochou12</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:02</t>
+          <t>2026-09-28 00:42:49</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@janet.osayande</t>
+          <t>https://www.tiktok.com/@nonochou12</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>r4xla15</t>
+          <t>nomzy.gladys</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5036,24 +5020,24 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-09-20 15:22:42</t>
+          <t>2026-09-25 10:26:03</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@r4xla15</t>
+          <t>https://www.tiktok.com/@nomzy.gladys</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>queenbabe_78</t>
+          <t>riderrrr70</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5070,24 +5054,24 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-10-02 15:22:41</t>
+          <t>2026-09-27 14:15:10</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queenbabe_78</t>
+          <t>https://www.tiktok.com/@riderrrr70</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>princessanna1738</t>
+          <t>rtamakter</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5104,31 +5088,31 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-25 07:04:05</t>
+          <t>2026-10-05 22:45:22</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princessanna1738</t>
+          <t>https://www.tiktok.com/@rtamakter</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>paul.d.awson</t>
+          <t>samiahajam</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5138,24 +5122,24 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-26 18:18:04</t>
+          <t>2026-09-25 10:39:07</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@paul.d.awson</t>
+          <t>https://www.tiktok.com/@samiahajam</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>patriciaappiah280</t>
+          <t>ruas_dream</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5172,24 +5156,24 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-23 10:08:56</t>
+          <t>2026-09-27 11:00:34</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@patriciaappiah280</t>
+          <t>https://www.tiktok.com/@ruas_dream</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>onos282</t>
+          <t>radhekrishna_11</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5201,63 +5185,63 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-10-04 23:21:40</t>
+          <t>2026-09-21 11:21:47</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@onos282</t>
+          <t>https://www.tiktok.com/@radhekrishna_11</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>oluyewi</t>
+          <t>reems_ttsshop</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-10-03 19:19:51</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluyewi</t>
+          <t>https://www.tiktok.com/@reems_ttsshop</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>oluwatoyin0322</t>
+          <t>rabbit_pm12</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5274,31 +5258,31 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-28 23:38:06</t>
+          <t>2026-09-25 19:17:46</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwatoyin0322</t>
+          <t>https://www.tiktok.com/@rabbit_pm12</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rosemthapamagar</t>
+          <t>princessanna1738</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5308,58 +5292,58 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-29 10:25:02</t>
+          <t>2026-09-25 07:04:05</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rosemthapamagar</t>
+          <t>https://www.tiktok.com/@princessanna1738</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ruas_dream</t>
+          <t>sarahwulatarawa</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-09-27 11:00:34</t>
+          <t>2026-10-02 06:49:42</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ruas_dream</t>
+          <t>https://www.tiktok.com/@sarahwulatarawa</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>sammummyconqueringanxiet</t>
+          <t>sarahswhimsyfits</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5376,31 +5360,31 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-10-01 10:50:06</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sammummyconqueringanxiet</t>
+          <t>https://www.tiktok.com/@sarahswhimsyfits</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>samiahajam</t>
+          <t>samstrendingdeals</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5410,7 +5394,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-09-25 10:39:07</t>
+          <t>2026-09-26 17:38:02</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5420,55 +5404,55 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samiahajam</t>
+          <t>https://www.tiktok.com/@samstrendingdeals</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>reems_ttsshop</t>
+          <t>sammummyconqueringanxiet</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reems_ttsshop</t>
+          <t>https://www.tiktok.com/@sammummyconqueringanxiet</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>reykkhan</t>
+          <t>sh28.eat.with.me</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5478,31 +5462,31 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-09-25 17:53:08</t>
+          <t>2026-10-01 10:47:02</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reykkhan</t>
+          <t>https://www.tiktok.com/@sh28.eat.with.me</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>rachellejane2</t>
+          <t>shannonlou8991</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5512,24 +5496,24 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-10-01 11:04:02</t>
+          <t>2026-10-01 10:50:05</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rachellejane2</t>
+          <t>https://www.tiktok.com/@shannonlou8991</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>rabbit_pm12</t>
+          <t>seyiedeliciouscocktails</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5546,17 +5530,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-25 19:17:46</t>
+          <t>2026-09-25 06:38:51</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rabbit_pm12</t>
+          <t>https://www.tiktok.com/@seyiedeliciouscocktails</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5569,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -5597,7 +5581,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>sarahwulatarawa</t>
+          <t>shasha.0891</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -5609,70 +5593,70 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-10-02 06:49:42</t>
+          <t>2026-09-23 13:48:02</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahwulatarawa</t>
+          <t>https://www.tiktok.com/@shasha.0891</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sarahswhimsyfits</t>
+          <t>shareenyousaf</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:06</t>
+          <t>2026-09-29 10:13:11</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahswhimsyfits</t>
+          <t>https://www.tiktok.com/@shareenyousaf</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>samstrendingdeals</t>
+          <t>shazia11235</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5682,99 +5666,99 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-26 17:38:02</t>
+          <t>2026-09-24 23:21:59</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samstrendingdeals</t>
+          <t>https://www.tiktok.com/@shazia11235</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>shannonlou8991</t>
+          <t>shukar7860</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:05</t>
+          <t>2026-09-22 09:29:34</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shannonlou8991</t>
+          <t>https://www.tiktok.com/@shukar7860</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>shareenyousaf</t>
+          <t>sidkam58</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-29 10:13:11</t>
+          <t>2026-10-01 07:57:16</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shareenyousaf</t>
+          <t>https://www.tiktok.com/@sidkam58</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>sh28.eat.with.me</t>
+          <t>smartfindsuk1</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5784,24 +5768,24 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-10-01 10:47:02</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sh28.eat.with.me</t>
+          <t>https://www.tiktok.com/@smartfindsuk1</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>seyiedeliciouscocktails</t>
+          <t>reykkhan</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -5818,24 +5802,24 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-25 06:38:51</t>
+          <t>2026-09-25 17:53:08</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seyiedeliciouscocktails</t>
+          <t>https://www.tiktok.com/@reykkhan</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>shazia11235</t>
+          <t>queenbabe_78</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -5852,126 +5836,126 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-09-24 23:21:59</t>
+          <t>2026-10-02 15:22:41</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shazia11235</t>
+          <t>https://www.tiktok.com/@queenbabe_78</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>shasha.0891</t>
+          <t>sue_never_ending_journey</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-09-23 13:48:02</t>
+          <t>2026-10-01 10:52:06</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shasha.0891</t>
+          <t>https://www.tiktok.com/@sue_never_ending_journey</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>shukar7860</t>
+          <t>smoothshelly</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-09-22 09:29:34</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shukar7860</t>
+          <t>https://www.tiktok.com/@smoothshelly</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>sidkam58</t>
+          <t>teeyworld_confectionery</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-10-01 07:57:16</t>
+          <t>2026-09-25 19:30:28</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sidkam58</t>
+          <t>https://www.tiktok.com/@teeyworld_confectionery</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>smartfindsuk1</t>
+          <t>suziefenton</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -5988,99 +5972,99 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-23 10:47:02</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@smartfindsuk1</t>
+          <t>https://www.tiktok.com/@suziefenton</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>smoothshelly</t>
+          <t>theloyalsoul1</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-28 20:53:18</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@smoothshelly</t>
+          <t>https://www.tiktok.com/@theloyalsoul1</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>riderrrr70</t>
+          <t>themelfords</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-09-27 14:15:10</t>
+          <t>2026-09-29 14:37:03</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@riderrrr70</t>
+          <t>https://www.tiktok.com/@themelfords</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>radhekrishna_11</t>
+          <t>theweebelfastman</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6090,24 +6074,24 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-09-21 11:21:47</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@radhekrishna_11</t>
+          <t>https://www.tiktok.com/@theweebelfastman</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>suziefenton</t>
+          <t>taiwooluyemitaiwo</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -6119,29 +6103,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-09-23 10:47:02</t>
+          <t>2026-09-23 16:28:21</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@suziefenton</t>
+          <t>https://www.tiktok.com/@taiwooluyemitaiwo</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>sue_never_ending_journey</t>
+          <t>tiadinamakeup</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -6158,24 +6142,24 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:06</t>
+          <t>2026-09-29 14:41:02</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sue_never_ending_journey</t>
+          <t>https://www.tiktok.com/@tiadinamakeup</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>teeyworld_confectionery</t>
+          <t>tinku78616</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -6192,31 +6176,31 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-09-25 19:30:28</t>
+          <t>2026-09-25 17:21:23</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teeyworld_confectionery</t>
+          <t>https://www.tiktok.com/@tinku78616</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>taiwooluyemitaiwo</t>
+          <t>tkmama45</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6226,41 +6210,41 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-09-23 16:28:21</t>
+          <t>2026-10-05 07:34:14</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@taiwooluyemitaiwo</t>
+          <t>https://www.tiktok.com/@tkmama45</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>theloyalsoul1</t>
+          <t>toryannaxo</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-09-28 20:53:18</t>
+          <t>2026-09-29 14:44:02</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -6270,55 +6254,63 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@theloyalsoul1</t>
+          <t>https://www.tiktok.com/@toryannaxo</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>themelfords</t>
+          <t>triciaebun</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-29 14:37:03</t>
+          <t>2026-09-25 16:57:55</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@themelfords</t>
+          <t>https://www.tiktok.com/@triciaebun</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>theweebelfastman</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
-      <c r="C167" t="inlineStr"/>
+          <t>tyanie1703</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6328,24 +6320,24 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-22 14:51:38</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@theweebelfastman</t>
+          <t>https://www.tiktok.com/@tyanie1703</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>tara57855</t>
+          <t>uk.life.moments</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -6362,24 +6354,24 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-10-01 20:24:02</t>
+          <t>2026-10-01 10:50:06</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tara57855</t>
+          <t>https://www.tiktok.com/@uk.life.moments</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>tinku78616</t>
+          <t>user2182373993526</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -6396,58 +6388,58 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-09-25 17:21:23</t>
+          <t>2026-09-21 12:26:17</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinku78616</t>
+          <t>https://www.tiktok.com/@user2182373993526</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>toryannaxo</t>
+          <t>user2773140226152</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-09-29 14:44:02</t>
+          <t>2026-09-21 20:00:10</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@toryannaxo</t>
+          <t>https://www.tiktok.com/@user2773140226152</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>triciaebun</t>
+          <t>user35110093</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -6464,36 +6456,28 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-09-25 16:57:55</t>
+          <t>2026-09-28 20:20:27</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@triciaebun</t>
+          <t>https://www.tiktok.com/@user35110093</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>tyanie1703</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>user3998147688485</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6506,58 +6490,58 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-09-22 14:51:38</t>
+          <t>2026-09-29 09:40:30</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tyanie1703</t>
+          <t>https://www.tiktok.com/@user3998147688485</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>uk.life.moments</t>
+          <t>user6931802591156</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:06</t>
+          <t>2026-10-01 16:26:50</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uk.life.moments</t>
+          <t>https://www.tiktok.com/@user6931802591156</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>user2182373993526</t>
+          <t>user8258556352859</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -6574,24 +6558,24 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-09-21 12:26:17</t>
+          <t>2026-10-03 10:13:16</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2182373993526</t>
+          <t>https://www.tiktok.com/@user8258556352859</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>user2773140226152</t>
+          <t>user9310370027124</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -6608,133 +6592,133 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-09-21 20:00:10</t>
+          <t>2026-10-01 19:05:18</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2773140226152</t>
+          <t>https://www.tiktok.com/@user9310370027124</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>tiadinamakeup</t>
+          <t>user99851967341610</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:02</t>
+          <t>2026-09-28 16:59:33</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiadinamakeup</t>
+          <t>https://www.tiktok.com/@user99851967341610</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>user35110093</t>
+          <t>user_78602223</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-09-28 20:20:27</t>
+          <t>2026-09-22 17:40:46</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user35110093</t>
+          <t>https://www.tiktok.com/@user_78602223</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>user3998147688485</t>
+          <t>veeover40</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-09-29 09:40:30</t>
+          <t>2026-10-01 10:50:04</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user3998147688485</t>
+          <t>https://www.tiktok.com/@veeover40</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>user806865620814</t>
+          <t>viralbuysontiktok</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6744,65 +6728,65 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-09-20 17:13:54</t>
+          <t>2026-09-28 10:13:03</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user806865620814</t>
+          <t>https://www.tiktok.com/@viralbuysontiktok</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>user6931802591156</t>
+          <t>waboti</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-10-01 16:26:50</t>
+          <t>2026-10-01 18:00:40</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6931802591156</t>
+          <t>https://www.tiktok.com/@waboti</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>user9310370027124</t>
+          <t>www.tiktokhafsaqueen169</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6812,92 +6796,92 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-10-01 19:05:18</t>
+          <t>2026-09-29 14:46:03</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9310370027124</t>
+          <t>https://www.tiktok.com/@www.tiktokhafsaqueen169</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>user99851967341610</t>
+          <t>xx_jessl_xx</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-09-28 16:59:33</t>
+          <t>2026-10-01 11:04:02</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user99851967341610</t>
+          <t>https://www.tiktok.com/@xx_jessl_xx</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>user_78602223</t>
+          <t>yeterecipe</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-09-22 17:40:46</t>
+          <t>2026-10-02 16:32:43</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user_78602223</t>
+          <t>https://www.tiktok.com/@yeterecipe</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>user8258556352859</t>
+          <t>zainyzee39</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -6909,12 +6893,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-10-03 10:13:16</t>
+          <t>2026-10-04 10:59:50</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -6924,277 +6908,39 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8258556352859</t>
+          <t>https://www.tiktok.com/@zainyzee39</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>veeover40</t>
+          <t>zara1508ahmed</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:04</t>
+          <t>2026-09-23 03:28:52</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@veeover40</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>viralbuysontiktok</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr"/>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-09-28 10:13:03</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@viralbuysontiktok</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>www.tiktokhafsaqueen169</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr"/>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-09-29 14:46:03</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@www.tiktokhafsaqueen169</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>waboti</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr"/>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Ashwagandha Coffee</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-10-01 18:00:40</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@waboti</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>xx_jessl_xx</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr"/>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-10-01 11:04:02</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@xx_jessl_xx</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>yeterecipe</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr"/>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-10-02 16:32:43</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@yeterecipe</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>zainyzee39</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr"/>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-10-04 10:59:50</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@zainyzee39</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>zara1508ahmed</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr"/>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-09-23 03:28:52</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zara1508ahmed</t>
         </is>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -755,12 +755,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>shelleybelle26</t>
+          <t>beauty_shine07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -775,29 +775,29 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:03</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shelleybelle26</t>
+          <t>https://www.tiktok.com/@beauty_shine07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>jasminehagen3</t>
+          <t>shelleybelle26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-30 14:59:02</t>
+          <t>2026-09-30 14:56:03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -832,14 +832,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jasminehagen3</t>
+          <t>https://www.tiktok.com/@shelleybelle26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dailydealsuk03</t>
+          <t>jasminehagen3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -864,24 +864,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-21 10:45:03</t>
+          <t>2026-09-30 14:59:02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailydealsuk03</t>
+          <t>https://www.tiktok.com/@jasminehagen3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>georgiaxx___</t>
+          <t>dailydealsuk03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -891,39 +891,39 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>50K-100K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-26 17:37:02</t>
+          <t>2026-09-21 10:45:03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@georgiaxx___</t>
+          <t>https://www.tiktok.com/@dailydealsuk03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>callmequeencossy</t>
+          <t>georgiaxx___</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -933,39 +933,39 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:05</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@callmequeencossy</t>
+          <t>https://www.tiktok.com/@georgiaxx___</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tiktok.shopmahi</t>
+          <t>callmequeencossy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -973,20 +973,24 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:06</t>
+          <t>2026-09-30 14:56:05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -996,14 +1000,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiktok.shopmahi</t>
+          <t>https://www.tiktok.com/@callmequeencossy</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>biancaselects</t>
+          <t>tiktok.shopmahi</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1014,17 +1018,17 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:03</t>
+          <t>2026-09-30 14:56:06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1034,14 +1038,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@biancaselects</t>
+          <t>https://www.tiktok.com/@tiktok.shopmahi</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>raeganfurness</t>
+          <t>biancaselects</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1049,14 +1053,10 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-30 14:59:02</t>
+          <t>2026-09-30 14:56:03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1076,14 +1076,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@raeganfurness</t>
+          <t>https://www.tiktok.com/@biancaselects</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>andreeamaria1828</t>
+          <t>raeganfurness</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1091,20 +1091,24 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:02</t>
+          <t>2026-09-30 14:59:02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1114,14 +1118,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@andreeamaria1828</t>
+          <t>https://www.tiktok.com/@raeganfurness</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sarahs.worldx</t>
+          <t>sammummyconqueringanxiet</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1131,7 +1135,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1146,39 +1150,39 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:02</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahs.worldx</t>
+          <t>https://www.tiktok.com/@sammummyconqueringanxiet</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hulubasul</t>
+          <t>smoothshelly</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>250K-500K</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1188,91 +1192,87 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:02</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hulubasul</t>
+          <t>https://www.tiktok.com/@smoothshelly</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>latina_shops</t>
+          <t>builtfindsuk</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:06</t>
+          <t>2026-10-01 10:47:03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@latina_shops</t>
+          <t>https://www.tiktok.com/@builtfindsuk</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>shopwithdanz0</t>
+          <t>andreeamaria1828</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:03</t>
+          <t>2026-09-30 14:57:02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1282,24 +1282,24 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shopwithdanz0</t>
+          <t>https://www.tiktok.com/@andreeamaria1828</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hinamalik0611</t>
+          <t>sarahs.worldx</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1314,24 +1314,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-28 10:19:03</t>
+          <t>2026-09-30 14:57:02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hinamalik0611</t>
+          <t>https://www.tiktok.com/@sarahs.worldx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>demyrobbo01</t>
+          <t>moodymarbsandshadow</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1341,39 +1341,39 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:03</t>
+          <t>2026-10-01 10:47:02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@demyrobbo01</t>
+          <t>https://www.tiktok.com/@moodymarbsandshadow</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>abdulawwal470</t>
+          <t>mariatincuta11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1398,39 +1398,39 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:03</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abdulawwal470</t>
+          <t>https://www.tiktok.com/@mariatincuta11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>andreeatts</t>
+          <t>hulubasul</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:05</t>
+          <t>2026-09-30 14:57:02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1450,19 +1450,19 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@andreeatts</t>
+          <t>https://www.tiktok.com/@hulubasul</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tonirooney19</t>
+          <t>latina_shops</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1482,121 +1482,133 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-05 23:00:07</t>
+          <t>2026-09-30 14:56:06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tonirooney19</t>
+          <t>https://www.tiktok.com/@latina_shops</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>crestworld.cooks</t>
+          <t>shopwithdanz0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-27 08:26:05</t>
+          <t>2026-09-30 14:57:03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@crestworld.cooks</t>
+          <t>https://www.tiktok.com/@shopwithdanz0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dillytwinmum</t>
+          <t>hinamalik0611</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-21 09:55:02</t>
+          <t>2026-09-28 10:19:03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dillytwinmum</t>
+          <t>https://www.tiktok.com/@hinamalik0611</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>builtfindsuk</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
+          <t>hazels_open_diary</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-01 10:47:03</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1606,89 +1618,113 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@builtfindsuk</t>
+          <t>https://www.tiktok.com/@hazels_open_diary</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bukky.yoyo</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
+          <t>demyrobbo01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-04 16:50:32</t>
+          <t>2026-09-30 14:57:03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bukky.yoyo</t>
+          <t>https://www.tiktok.com/@demyrobbo01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>babbyzozo</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+          <t>xx_jessl_xx</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-28 18:28:13</t>
+          <t>2026-10-01 11:04:02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@babbyzozo</t>
+          <t>https://www.tiktok.com/@xx_jessl_xx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>armaan.ahmed37</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+          <t>miss_quenny1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1698,31 +1734,39 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-03 19:49:39</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@armaan.ahmed37</t>
+          <t>https://www.tiktok.com/@miss_quenny1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>charliegirl860</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+          <t>abdulawwal470</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1732,31 +1776,39 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-26 10:54:39</t>
+          <t>2026-09-30 14:57:03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@charliegirl860</t>
+          <t>https://www.tiktok.com/@abdulawwal470</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>chezzy954</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+          <t>jones23350</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1766,65 +1818,81 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-25 13:21:47</t>
+          <t>2026-10-01 10:52:04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chezzy954</t>
+          <t>https://www.tiktok.com/@jones23350</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>climax.scenes</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+          <t>smartfindsuk1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-21 06:20:00</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@climax.scenes</t>
+          <t>https://www.tiktok.com/@smartfindsuk1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dearlola45</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
+          <t>janet.osayande</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1834,28 +1902,36 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-01 11:28:54</t>
+          <t>2026-10-04 18:25:02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dearlola45</t>
+          <t>https://www.tiktok.com/@janet.osayande</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>damsel755</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+          <t>carfoon767</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>50K-100K</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -1863,104 +1939,128 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-05 20:02:55</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@damsel755</t>
+          <t>https://www.tiktok.com/@carfoon767</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>desylviaa1</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+          <t>angiereviewslife</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-27 10:40:10</t>
+          <t>2026-10-01 11:04:03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@desylviaa1</t>
+          <t>https://www.tiktok.com/@angiereviewslife</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>diddlyidi</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+          <t>kimmys_kitchen_garden</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-23 08:16:02</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@diddlyidi</t>
+          <t>https://www.tiktok.com/@kimmys_kitchen_garden</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>chek_mi_shocase</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+          <t>mycontemporarylifeinuk</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1970,41 +2070,49 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-22 17:56:02</t>
+          <t>2026-10-01 14:55:02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chek_mi_shocase</t>
+          <t>https://www.tiktok.com/@mycontemporarylifeinuk</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>carfoon767</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
+          <t>itsjulesmurph</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-01 10:52:05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2014,21 +2122,29 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@carfoon767</t>
+          <t>https://www.tiktok.com/@itsjulesmurph</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dinexheese</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
+          <t>kerrycavan</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2038,99 +2154,123 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-26 12:16:35</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dinexheese</t>
+          <t>https://www.tiktok.com/@kerrycavan</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>dimpleddp</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
+          <t>sue_never_ending_journey</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-25 12:30:06</t>
+          <t>2026-10-01 10:52:06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dimpleddp</t>
+          <t>https://www.tiktok.com/@sue_never_ending_journey</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>beauty_shine07</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
+          <t>jodijudejj</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-10-01 11:14:02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty_shine07</t>
+          <t>https://www.tiktok.com/@jodijudejj</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>becky.mawunyo</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
+          <t>andreeatts</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2140,63 +2280,71 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-28 10:19:04</t>
+          <t>2026-09-30 14:56:05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@becky.mawunyo</t>
+          <t>https://www.tiktok.com/@andreeatts</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>balletdeo</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+          <t>uk.life.moments</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-26 01:45:10</t>
+          <t>2026-10-01 10:50:06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@balletdeo</t>
+          <t>https://www.tiktok.com/@uk.life.moments</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>amap000</t>
+          <t>shannonlou8991</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2206,7 +2354,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2216,99 +2364,119 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-03 10:59:49</t>
+          <t>2026-10-01 10:50:05</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amap000</t>
+          <t>https://www.tiktok.com/@shannonlou8991</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>aminajeylani</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
+          <t>tonirooney19</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-23 14:42:07</t>
+          <t>2026-10-05 23:00:07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aminajeylani</t>
+          <t>https://www.tiktok.com/@tonirooney19</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>amena.akter3665</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
+          <t>sarahwulatarawa</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-28 12:23:28</t>
+          <t>2026-10-02 06:49:42</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amena.akter3665</t>
+          <t>https://www.tiktok.com/@sarahwulatarawa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>azlanzaynahzayrahuk</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>crestworld.cooks</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2318,28 +2486,36 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-28 10:10:05</t>
+          <t>2026-09-27 08:26:05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@azlanzaynahzayrahuk</t>
+          <t>https://www.tiktok.com/@crestworld.cooks</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>amanmegbu</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
+          <t>dillytwinmum</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -2352,24 +2528,24 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:03</t>
+          <t>2026-09-21 09:55:02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amanmegbu</t>
+          <t>https://www.tiktok.com/@dillytwinmum</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>adeede1</t>
+          <t>amena.akter3665</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2386,17 +2562,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-03 06:37:25</t>
+          <t>2026-09-28 12:23:28</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adeede1</t>
+          <t>https://www.tiktok.com/@amena.akter3665</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2621,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>angelhairstylist1</t>
+          <t>_dosah</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2457,36 +2633,36 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-04 20:43:03</t>
+          <t>2026-09-21 14:58:25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angelhairstylist1</t>
+          <t>https://www.tiktok.com/@_dosah</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>angiereviewslife</t>
+          <t>funmumshops</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2496,36 +2672,28 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-01 11:04:03</t>
+          <t>2026-09-28 10:19:02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angiereviewslife</t>
+          <t>https://www.tiktok.com/@funmumshops</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>_mohlad</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>fmrasalhossain</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2533,63 +2701,63 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-04 18:10:30</t>
+          <t>2026-09-25 22:32:12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_mohlad</t>
+          <t>https://www.tiktok.com/@fmrasalhossain</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>_dosah</t>
+          <t>flash_finds1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-21 14:58:25</t>
+          <t>2026-09-27 13:35:02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_dosah</t>
+          <t>https://www.tiktok.com/@flash_finds1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>gbm.sees</t>
+          <t>fkprima123</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2606,58 +2774,58 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-01 09:00:38</t>
+          <t>2026-09-26 17:32:35</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gbm.sees</t>
+          <t>https://www.tiktok.com/@fkprima123</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>funmumshops</t>
+          <t>fittokfinds88</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-28 10:19:02</t>
+          <t>2026-09-23 16:18:03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@funmumshops</t>
+          <t>https://www.tiktok.com/@fittokfinds88</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>fmrasalhossain</t>
+          <t>fellykemmy3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2674,31 +2842,31 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-25 22:32:12</t>
+          <t>2026-09-24 20:39:00</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fmrasalhossain</t>
+          <t>https://www.tiktok.com/@fellykemmy3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>flash_finds1</t>
+          <t>fahmidaislam2120</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2708,24 +2876,24 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-27 13:35:02</t>
+          <t>2026-09-23 15:26:11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@flash_finds1</t>
+          <t>https://www.tiktok.com/@fahmidaislam2120</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fittokfinds88</t>
+          <t>f.chowdhury15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2742,58 +2910,58 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-23 16:18:03</t>
+          <t>2026-09-29 23:20:53</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fittokfinds88</t>
+          <t>https://www.tiktok.com/@f.chowdhury15</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fkprima123</t>
+          <t>duaanoor080120</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-26 17:32:35</t>
+          <t>2026-10-02 06:26:32</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fkprima123</t>
+          <t>https://www.tiktok.com/@duaanoor080120</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>fellykemmy3</t>
+          <t>explorewithmex10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2810,31 +2978,31 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-24 20:39:00</t>
+          <t>2026-10-02 09:06:56</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fellykemmy3</t>
+          <t>https://www.tiktok.com/@explorewithmex10</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>fahmidaislam2120</t>
+          <t>explore.with.em4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2844,31 +3012,31 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-23 15:26:11</t>
+          <t>2026-10-01 14:44:03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fahmidaislam2120</t>
+          <t>https://www.tiktok.com/@explore.with.em4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>duaanoor080120</t>
+          <t>egooyibo41</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2878,58 +3046,58 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-02 06:26:32</t>
+          <t>2026-10-05 13:55:48</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@duaanoor080120</t>
+          <t>https://www.tiktok.com/@egooyibo41</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>f.chowdhury15</t>
+          <t>dinexheese</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-29 23:20:53</t>
+          <t>2026-09-26 12:16:35</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@f.chowdhury15</t>
+          <t>https://www.tiktok.com/@dinexheese</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>explorewithmex10</t>
+          <t>dsda0786</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2946,24 +3114,24 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-02 09:06:56</t>
+          <t>2026-09-29 09:46:30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@explorewithmex10</t>
+          <t>https://www.tiktok.com/@dsda0786</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>explore.with.em4</t>
+          <t>dimpleddp</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2975,63 +3143,63 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-01 14:44:03</t>
+          <t>2026-09-25 12:30:06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@explore.with.em4</t>
+          <t>https://www.tiktok.com/@dimpleddp</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>dsda0786</t>
+          <t>diddlyidi</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-29 09:46:30</t>
+          <t>2026-09-23 08:16:02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dsda0786</t>
+          <t>https://www.tiktok.com/@diddlyidi</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>egooyibo41</t>
+          <t>bukky.yoyo</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3048,160 +3216,160 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-05 13:55:48</t>
+          <t>2026-10-04 16:50:32</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@egooyibo41</t>
+          <t>https://www.tiktok.com/@bukky.yoyo</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>iamvickyshurwen_</t>
+          <t>desylviaa1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-29 10:25:06</t>
+          <t>2026-09-27 10:40:10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iamvickyshurwen_</t>
+          <t>https://www.tiktok.com/@desylviaa1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>homemadefood2024</t>
+          <t>damsel755</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-23 16:44:22</t>
+          <t>2026-10-05 20:02:55</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@homemadefood2024</t>
+          <t>https://www.tiktok.com/@damsel755</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>jem17363</t>
+          <t>dearlola45</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-21 17:28:16</t>
+          <t>2026-10-01 11:28:54</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jem17363</t>
+          <t>https://www.tiktok.com/@dearlola45</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>jodijudejj</t>
+          <t>chezzy954</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-01 11:14:02</t>
+          <t>2026-09-25 13:21:47</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jodijudejj</t>
+          <t>https://www.tiktok.com/@chezzy954</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>juliana_armoh</t>
+          <t>charliegirl860</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3218,65 +3386,65 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-10-01 21:22:31</t>
+          <t>2026-09-26 10:54:39</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@juliana_armoh</t>
+          <t>https://www.tiktok.com/@charliegirl860</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>jones23350</t>
+          <t>climax.scenes</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:04</t>
+          <t>2026-09-21 06:20:00</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jones23350</t>
+          <t>https://www.tiktok.com/@climax.scenes</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kayyasin87</t>
+          <t>amanmegbu</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3286,24 +3454,24 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-28 10:10:05</t>
+          <t>2026-09-29 14:41:03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kayyasin87</t>
+          <t>https://www.tiktok.com/@amanmegbu</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kaz.gym82</t>
+          <t>angelhairstylist1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3320,24 +3488,24 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-05 08:29:56</t>
+          <t>2026-10-04 20:43:03</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaz.gym82</t>
+          <t>https://www.tiktok.com/@angelhairstylist1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kennyshekoni</t>
+          <t>aminajeylani</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3354,31 +3522,39 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-01 19:41:15</t>
+          <t>2026-09-23 14:42:07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kennyshekoni</t>
+          <t>https://www.tiktok.com/@aminajeylani</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kaylee_dexter</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
+          <t>amap000</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3388,24 +3564,24 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-10-03 10:59:49</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaylee_dexter</t>
+          <t>https://www.tiktok.com/@amap000</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>idrissasesay7</t>
+          <t>armaan.ahmed37</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3417,29 +3593,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-02 23:30:18</t>
+          <t>2026-10-03 19:49:39</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@idrissasesay7</t>
+          <t>https://www.tiktok.com/@armaan.ahmed37</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ilzb7</t>
+          <t>babbyzozo</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3451,63 +3627,63 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-05 16:59:43</t>
+          <t>2026-09-28 18:28:13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ilzb7</t>
+          <t>https://www.tiktok.com/@babbyzozo</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>itsjulesmurph</t>
+          <t>azlanzaynahzayrahuk</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:05</t>
+          <t>2026-09-28 10:10:05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsjulesmurph</t>
+          <t>https://www.tiktok.com/@azlanzaynahzayrahuk</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>inspirednoor</t>
+          <t>balletdeo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3524,7 +3700,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-26 17:35:02</t>
+          <t>2026-09-26 01:45:10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3534,14 +3710,14 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@inspirednoor</t>
+          <t>https://www.tiktok.com/@balletdeo</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>jadepa90</t>
+          <t>becky.mawunyo</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3558,31 +3734,39 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-26 09:09:09</t>
+          <t>2026-09-28 10:19:04</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jadepa90</t>
+          <t>https://www.tiktok.com/@becky.mawunyo</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>janet.osayande</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
+          <t>_mohlad</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3592,7 +3776,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:02</t>
+          <t>2026-10-04 18:10:30</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3602,14 +3786,14 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@janet.osayande</t>
+          <t>https://www.tiktok.com/@_mohlad</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>jean.makin</t>
+          <t>adeede1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3621,12 +3805,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-10-03 14:41:36</t>
+          <t>2026-10-03 06:37:25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3636,14 +3820,14 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jean.makin</t>
+          <t>https://www.tiktok.com/@adeede1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>hu123342425</t>
+          <t>kulwinderrani5</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3660,65 +3844,65 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-04 15:47:04</t>
+          <t>2026-10-05 09:00:08</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hu123342425</t>
+          <t>https://www.tiktok.com/@kulwinderrani5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>lifeofhamzaa</t>
+          <t>knicksmakeuppro</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-10-04 18:28:02</t>
+          <t>2026-10-01 11:30:23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeofhamzaa</t>
+          <t>https://www.tiktok.com/@knicksmakeuppro</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>lindaefionayi</t>
+          <t>keyratio</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3728,24 +3912,24 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-23 20:46:33</t>
+          <t>2026-09-27 13:35:02</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lindaefionayi</t>
+          <t>https://www.tiktok.com/@keyratio</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>lolaclothier</t>
+          <t>lovecats7112</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3762,92 +3946,92 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-10-01 20:17:12</t>
+          <t>2026-09-26 19:59:48</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lolaclothier</t>
+          <t>https://www.tiktok.com/@lovecats7112</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>lissssaxxx</t>
+          <t>lolaclothier</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-23 08:17:25</t>
+          <t>2026-10-01 20:17:12</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lissssaxxx</t>
+          <t>https://www.tiktok.com/@lolaclothier</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>m.3384</t>
+          <t>lindaefionayi</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-21 10:22:24</t>
+          <t>2026-09-23 20:46:33</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@m.3384</t>
+          <t>https://www.tiktok.com/@lindaefionayi</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mahi.rani421</t>
+          <t>manvinder318</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3864,24 +4048,24 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-24 13:02:03</t>
+          <t>2026-09-25 14:14:56</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mahi.rani421</t>
+          <t>https://www.tiktok.com/@manvinder318</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>manvinder318</t>
+          <t>mahi.rani421</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3898,24 +4082,24 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-25 14:14:56</t>
+          <t>2026-09-24 13:02:03</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@manvinder318</t>
+          <t>https://www.tiktok.com/@mahi.rani421</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>lovecats7112</t>
+          <t>m.3384</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3932,58 +4116,58 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-26 19:59:48</t>
+          <t>2026-09-21 10:22:24</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lovecats7112</t>
+          <t>https://www.tiktok.com/@m.3384</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mariatincuta11</t>
+          <t>maxi_berrie</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-09-22 23:20:40</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mariatincuta11</t>
+          <t>https://www.tiktok.com/@maxi_berrie</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>maxi_berrie</t>
+          <t>merz3859</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4000,7 +4184,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-22 23:20:40</t>
+          <t>2026-09-22 21:09:48</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4010,7 +4194,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maxi_berrie</t>
+          <t>https://www.tiktok.com/@merz3859</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4269,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>merz3859</t>
+          <t>lissssaxxx</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4102,31 +4286,31 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-22 21:09:48</t>
+          <t>2026-09-23 08:17:25</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@merz3859</t>
+          <t>https://www.tiktok.com/@lissssaxxx</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>miss_quenny1</t>
+          <t>lifeofhamzaa</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4136,58 +4320,58 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-04 18:28:02</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@miss_quenny1</t>
+          <t>https://www.tiktok.com/@lifeofhamzaa</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>moodymarbsandshadow</t>
+          <t>laurywilliams</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-10-01 10:47:02</t>
+          <t>2026-09-26 16:59:35</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moodymarbsandshadow</t>
+          <t>https://www.tiktok.com/@laurywilliams</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>mr.liverpool885</t>
+          <t>ilzb7</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4204,31 +4388,31 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-10-04 09:00:20</t>
+          <t>2026-10-05 16:59:43</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mr.liverpool885</t>
+          <t>https://www.tiktok.com/@ilzb7</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mrm.foods.opeyemi</t>
+          <t>jadepa90</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4238,24 +4422,24 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-10-04 20:07:11</t>
+          <t>2026-09-26 09:09:09</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mrm.foods.opeyemi</t>
+          <t>https://www.tiktok.com/@jadepa90</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>mum3tees</t>
+          <t>jean.makin</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4267,63 +4451,63 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-26 15:28:17</t>
+          <t>2026-10-03 14:41:36</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mum3tees</t>
+          <t>https://www.tiktok.com/@jean.makin</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>mummyzaraa</t>
+          <t>kaylee_dexter</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-23 08:16:05</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mummyzaraa</t>
+          <t>https://www.tiktok.com/@kaylee_dexter</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>munasheish</t>
+          <t>jem17363</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4340,31 +4524,31 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-25 10:27:59</t>
+          <t>2026-09-21 17:28:16</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@munasheish</t>
+          <t>https://www.tiktok.com/@jem17363</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>mycontemporarylifeinuk</t>
+          <t>juliana_armoh</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4374,7 +4558,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-10-01 14:55:02</t>
+          <t>2026-10-01 21:22:31</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4384,14 +4568,14 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mycontemporarylifeinuk</t>
+          <t>https://www.tiktok.com/@juliana_armoh</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>n.raja83</t>
+          <t>kennyshekoni</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4408,24 +4592,24 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-29 10:14:04</t>
+          <t>2026-10-01 19:41:15</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@n.raja83</t>
+          <t>https://www.tiktok.com/@kennyshekoni</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>naveed19.88</t>
+          <t>kaz.gym82</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4437,104 +4621,104 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-25 22:46:15</t>
+          <t>2026-10-05 08:29:56</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@naveed19.88</t>
+          <t>https://www.tiktok.com/@kaz.gym82</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>nevertoooldnanaxx</t>
+          <t>kayyasin87</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-09-28 10:10:05</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nevertoooldnanaxx</t>
+          <t>https://www.tiktok.com/@kayyasin87</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kerrycavan</t>
+          <t>inspirednoor</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-26 17:35:02</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kerrycavan</t>
+          <t>https://www.tiktok.com/@inspirednoor</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>keyratio</t>
+          <t>idrissasesay7</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4544,58 +4728,58 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-27 13:35:02</t>
+          <t>2026-10-02 23:30:18</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@keyratio</t>
+          <t>https://www.tiktok.com/@idrissasesay7</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>knicksmakeuppro</t>
+          <t>iamvickyshurwen_</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-10-01 11:30:23</t>
+          <t>2026-09-29 10:25:06</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@knicksmakeuppro</t>
+          <t>https://www.tiktok.com/@iamvickyshurwen_</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kimmys_kitchen_garden</t>
+          <t>homemadefood2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4612,24 +4796,24 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-23 16:44:22</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kimmys_kitchen_garden</t>
+          <t>https://www.tiktok.com/@homemadefood2024</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kulwinderrani5</t>
+          <t>hu123342425</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4646,31 +4830,31 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-10-05 09:00:08</t>
+          <t>2026-10-04 15:47:04</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kulwinderrani5</t>
+          <t>https://www.tiktok.com/@hu123342425</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>laurywilliams</t>
+          <t>patriciaappiah280</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4680,31 +4864,31 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-26 16:59:35</t>
+          <t>2026-09-23 10:08:56</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@laurywilliams</t>
+          <t>https://www.tiktok.com/@patriciaappiah280</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>letsmakeitkentlimited</t>
+          <t>onos282</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4714,24 +4898,24 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-26 08:39:02</t>
+          <t>2026-10-04 23:21:40</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@letsmakeitkentlimited</t>
+          <t>https://www.tiktok.com/@onos282</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>hazels_open_diary</t>
+          <t>oluyewi</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4748,31 +4932,31 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-03 19:19:51</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hazels_open_diary</t>
+          <t>https://www.tiktok.com/@oluyewi</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>paul.d.awson</t>
+          <t>oluwatoyin0322</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4782,24 +4966,24 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-26 18:18:04</t>
+          <t>2026-09-28 23:38:06</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@paul.d.awson</t>
+          <t>https://www.tiktok.com/@oluwatoyin0322</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>patriciaappiah280</t>
+          <t>ola.oluwatoyin.ad</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4816,24 +5000,24 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-23 10:08:56</t>
+          <t>2026-09-25 13:50:20</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@patriciaappiah280</t>
+          <t>https://www.tiktok.com/@ola.oluwatoyin.ad</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>onos282</t>
+          <t>nonochou12</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4845,63 +5029,63 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-10-04 23:21:40</t>
+          <t>2026-09-28 00:42:49</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@onos282</t>
+          <t>https://www.tiktok.com/@nonochou12</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>oluyewi</t>
+          <t>nomzy.gladys</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-10-03 19:19:51</t>
+          <t>2026-09-25 10:26:03</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluyewi</t>
+          <t>https://www.tiktok.com/@nomzy.gladys</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>oluwatoyin0322</t>
+          <t>nevertoooldnanaxx</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4913,29 +5097,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-28 23:38:06</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwatoyin0322</t>
+          <t>https://www.tiktok.com/@nevertoooldnanaxx</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ola.oluwatoyin.ad</t>
+          <t>naveed19.88</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -4952,7 +5136,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-25 13:50:20</t>
+          <t>2026-09-25 22:46:15</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4962,14 +5146,14 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ola.oluwatoyin.ad</t>
+          <t>https://www.tiktok.com/@naveed19.88</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>nonochou12</t>
+          <t>n.raja83</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -4986,31 +5170,31 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-28 00:42:49</t>
+          <t>2026-09-29 10:14:04</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nonochou12</t>
+          <t>https://www.tiktok.com/@n.raja83</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>nomzy.gladys</t>
+          <t>munasheish</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5020,7 +5204,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-09-25 10:26:03</t>
+          <t>2026-09-25 10:27:59</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5030,14 +5214,14 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nomzy.gladys</t>
+          <t>https://www.tiktok.com/@munasheish</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>riderrrr70</t>
+          <t>mummyzaraa</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5054,24 +5238,24 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-27 14:15:10</t>
+          <t>2026-09-23 08:16:05</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@riderrrr70</t>
+          <t>https://www.tiktok.com/@mummyzaraa</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>rtamakter</t>
+          <t>ms_gbm</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5088,24 +5272,24 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-10-05 22:45:22</t>
+          <t>2026-10-01 09:00:38</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rtamakter</t>
+          <t>https://www.tiktok.com/@ms_gbm</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>samiahajam</t>
+          <t>mum3tees</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5122,24 +5306,24 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-25 10:39:07</t>
+          <t>2026-09-26 15:28:17</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samiahajam</t>
+          <t>https://www.tiktok.com/@mum3tees</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ruas_dream</t>
+          <t>mrm.foods.opeyemi</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5151,29 +5335,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-27 11:00:34</t>
+          <t>2026-10-04 20:07:11</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ruas_dream</t>
+          <t>https://www.tiktok.com/@mrm.foods.opeyemi</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>radhekrishna_11</t>
+          <t>mr.liverpool885</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5185,70 +5369,70 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-21 11:21:47</t>
+          <t>2026-10-04 09:00:20</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@radhekrishna_11</t>
+          <t>https://www.tiktok.com/@mr.liverpool885</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>reems_ttsshop</t>
+          <t>sarahswhimsyfits</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-10-01 10:50:06</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reems_ttsshop</t>
+          <t>https://www.tiktok.com/@sarahswhimsyfits</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>rabbit_pm12</t>
+          <t>samstrendingdeals</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5258,24 +5442,24 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-25 19:17:46</t>
+          <t>2026-09-26 17:38:02</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rabbit_pm12</t>
+          <t>https://www.tiktok.com/@samstrendingdeals</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>princessanna1738</t>
+          <t>ruas_dream</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5292,99 +5476,99 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-25 07:04:05</t>
+          <t>2026-09-27 11:00:34</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princessanna1738</t>
+          <t>https://www.tiktok.com/@ruas_dream</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>sarahwulatarawa</t>
+          <t>samiahajam</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-10-02 06:49:42</t>
+          <t>2026-09-25 10:39:07</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahwulatarawa</t>
+          <t>https://www.tiktok.com/@samiahajam</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>sarahswhimsyfits</t>
+          <t>rtamakter</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:06</t>
+          <t>2026-10-05 22:45:22</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahswhimsyfits</t>
+          <t>https://www.tiktok.com/@rtamakter</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>samstrendingdeals</t>
+          <t>riderrrr70</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5394,65 +5578,65 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-09-26 17:38:02</t>
+          <t>2026-09-27 14:15:10</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samstrendingdeals</t>
+          <t>https://www.tiktok.com/@riderrrr70</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>sammummyconqueringanxiet</t>
+          <t>reems_ttsshop</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sammummyconqueringanxiet</t>
+          <t>https://www.tiktok.com/@reems_ttsshop</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>sh28.eat.with.me</t>
+          <t>reykkhan</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5462,58 +5646,58 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-10-01 10:47:02</t>
+          <t>2026-09-25 17:53:08</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sh28.eat.with.me</t>
+          <t>https://www.tiktok.com/@reykkhan</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>shannonlou8991</t>
+          <t>princessanna1738</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:05</t>
+          <t>2026-09-25 07:04:05</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shannonlou8991</t>
+          <t>https://www.tiktok.com/@princessanna1738</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>seyiedeliciouscocktails</t>
+          <t>shareenyousaf</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5530,17 +5714,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-25 06:38:51</t>
+          <t>2026-09-29 10:13:11</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seyiedeliciouscocktails</t>
+          <t>https://www.tiktok.com/@shareenyousaf</t>
         </is>
       </c>
     </row>
@@ -5581,14 +5765,14 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>shasha.0891</t>
+          <t>seyiedeliciouscocktails</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5598,24 +5782,24 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-23 13:48:02</t>
+          <t>2026-09-25 06:38:51</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shasha.0891</t>
+          <t>https://www.tiktok.com/@seyiedeliciouscocktails</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>shareenyousaf</t>
+          <t>rabbit_pm12</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -5632,24 +5816,24 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-09-29 10:13:11</t>
+          <t>2026-09-25 19:17:46</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shareenyousaf</t>
+          <t>https://www.tiktok.com/@rabbit_pm12</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>shazia11235</t>
+          <t>radhekrishna_11</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -5666,24 +5850,24 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-24 23:21:59</t>
+          <t>2026-09-21 11:21:47</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shazia11235</t>
+          <t>https://www.tiktok.com/@radhekrishna_11</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>shukar7860</t>
+          <t>queenbabe_78</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -5700,24 +5884,24 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-09-22 09:29:34</t>
+          <t>2026-10-02 15:22:41</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shukar7860</t>
+          <t>https://www.tiktok.com/@queenbabe_78</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>sidkam58</t>
+          <t>paul.d.awson</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -5729,46 +5913,46 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-10-01 07:57:16</t>
+          <t>2026-09-26 18:18:04</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sidkam58</t>
+          <t>https://www.tiktok.com/@paul.d.awson</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>smartfindsuk1</t>
+          <t>sidkam58</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-01 07:57:16</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5778,14 +5962,14 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@smartfindsuk1</t>
+          <t>https://www.tiktok.com/@sidkam58</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>reykkhan</t>
+          <t>shukar7860</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -5802,24 +5986,24 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-25 17:53:08</t>
+          <t>2026-09-22 09:29:34</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reykkhan</t>
+          <t>https://www.tiktok.com/@shukar7860</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>queenbabe_78</t>
+          <t>shazia11235</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -5836,133 +6020,133 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-10-02 15:22:41</t>
+          <t>2026-09-24 23:21:59</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queenbabe_78</t>
+          <t>https://www.tiktok.com/@shazia11235</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>sue_never_ending_journey</t>
+          <t>shasha.0891</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:06</t>
+          <t>2026-09-23 13:48:02</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sue_never_ending_journey</t>
+          <t>https://www.tiktok.com/@shasha.0891</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>smoothshelly</t>
+          <t>theloyalsoul1</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-28 20:53:18</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@smoothshelly</t>
+          <t>https://www.tiktok.com/@theloyalsoul1</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>teeyworld_confectionery</t>
+          <t>themelfords</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-09-25 19:30:28</t>
+          <t>2026-09-29 14:37:03</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teeyworld_confectionery</t>
+          <t>https://www.tiktok.com/@themelfords</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>suziefenton</t>
+          <t>teeyworld_confectionery</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5972,31 +6156,31 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-09-23 10:47:02</t>
+          <t>2026-09-25 19:30:28</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@suziefenton</t>
+          <t>https://www.tiktok.com/@teeyworld_confectionery</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>theloyalsoul1</t>
+          <t>suziefenton</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6006,31 +6190,31 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-09-28 20:53:18</t>
+          <t>2026-09-23 10:47:02</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@theloyalsoul1</t>
+          <t>https://www.tiktok.com/@suziefenton</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>themelfords</t>
+          <t>tiadinamakeup</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6040,7 +6224,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-09-29 14:37:03</t>
+          <t>2026-09-29 14:41:02</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -6050,7 +6234,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@themelfords</t>
+          <t>https://www.tiktok.com/@tiadinamakeup</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6248,7 @@
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6091,14 +6275,14 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>taiwooluyemitaiwo</t>
+          <t>tkmama45</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6108,92 +6292,92 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-09-23 16:28:21</t>
+          <t>2026-10-05 07:34:14</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@taiwooluyemitaiwo</t>
+          <t>https://www.tiktok.com/@tkmama45</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>tiadinamakeup</t>
+          <t>tinku78616</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:02</t>
+          <t>2026-09-25 17:21:23</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiadinamakeup</t>
+          <t>https://www.tiktok.com/@tinku78616</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>tinku78616</t>
+          <t>toryannaxo</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-09-25 17:21:23</t>
+          <t>2026-09-29 14:44:02</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinku78616</t>
+          <t>https://www.tiktok.com/@toryannaxo</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>tkmama45</t>
+          <t>triciaebun</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -6205,109 +6389,109 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-10-05 07:34:14</t>
+          <t>2026-09-25 16:57:55</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tkmama45</t>
+          <t>https://www.tiktok.com/@triciaebun</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>toryannaxo</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr"/>
-      <c r="C165" t="inlineStr"/>
+          <t>tyanie1703</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-09-29 14:44:02</t>
+          <t>2026-09-22 14:51:38</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@toryannaxo</t>
+          <t>https://www.tiktok.com/@tyanie1703</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>triciaebun</t>
+          <t>taiwooluyemitaiwo</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-25 16:57:55</t>
+          <t>2026-09-23 16:28:21</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@triciaebun</t>
+          <t>https://www.tiktok.com/@taiwooluyemitaiwo</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>tyanie1703</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>user2182373993526</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6320,58 +6504,58 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-09-22 14:51:38</t>
+          <t>2026-09-21 12:26:17</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tyanie1703</t>
+          <t>https://www.tiktok.com/@user2182373993526</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>uk.life.moments</t>
+          <t>user2773140226152</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:06</t>
+          <t>2026-09-21 20:00:10</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uk.life.moments</t>
+          <t>https://www.tiktok.com/@user2773140226152</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>user2182373993526</t>
+          <t>user3998147688485</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -6388,24 +6572,24 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-09-21 12:26:17</t>
+          <t>2026-09-29 09:40:30</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2182373993526</t>
+          <t>https://www.tiktok.com/@user3998147688485</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>user2773140226152</t>
+          <t>user35110093</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -6422,24 +6606,24 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-09-21 20:00:10</t>
+          <t>2026-09-28 20:20:27</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2773140226152</t>
+          <t>https://www.tiktok.com/@user35110093</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>user35110093</t>
+          <t>user8258556352859</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -6456,24 +6640,24 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-09-28 20:20:27</t>
+          <t>2026-10-03 10:13:16</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user35110093</t>
+          <t>https://www.tiktok.com/@user8258556352859</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>user3998147688485</t>
+          <t>user9310370027124</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -6490,24 +6674,24 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-09-29 09:40:30</t>
+          <t>2026-10-01 19:05:18</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user3998147688485</t>
+          <t>https://www.tiktok.com/@user9310370027124</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>user6931802591156</t>
+          <t>user99851967341610</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -6524,24 +6708,24 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-10-01 16:26:50</t>
+          <t>2026-09-28 16:59:33</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6931802591156</t>
+          <t>https://www.tiktok.com/@user99851967341610</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>user8258556352859</t>
+          <t>user6931802591156</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -6558,92 +6742,92 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-10-03 10:13:16</t>
+          <t>2026-10-01 16:26:50</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8258556352859</t>
+          <t>https://www.tiktok.com/@user6931802591156</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>user9310370027124</t>
+          <t>user_78602223</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-10-01 19:05:18</t>
+          <t>2026-09-22 17:40:46</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9310370027124</t>
+          <t>https://www.tiktok.com/@user_78602223</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>user99851967341610</t>
+          <t>veeover40</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-09-28 16:59:33</t>
+          <t>2026-10-01 10:50:04</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user99851967341610</t>
+          <t>https://www.tiktok.com/@veeover40</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>user_78602223</t>
+          <t>waboti</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -6660,58 +6844,58 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-09-22 17:40:46</t>
+          <t>2026-10-01 18:00:40</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user_78602223</t>
+          <t>https://www.tiktok.com/@waboti</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>veeover40</t>
+          <t>viralbuysontiktok</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:04</t>
+          <t>2026-09-28 10:13:03</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@veeover40</t>
+          <t>https://www.tiktok.com/@viralbuysontiktok</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>viralbuysontiktok</t>
+          <t>www.tiktokhafsaqueen169</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -6728,219 +6912,117 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-09-28 10:13:03</t>
+          <t>2026-09-29 14:46:03</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@viralbuysontiktok</t>
+          <t>https://www.tiktok.com/@www.tiktokhafsaqueen169</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>waboti</t>
+          <t>yeterecipe</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-10-01 18:00:40</t>
+          <t>2026-10-02 16:32:43</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@waboti</t>
+          <t>https://www.tiktok.com/@yeterecipe</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>www.tiktokhafsaqueen169</t>
+          <t>zainyzee39</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-09-29 14:46:03</t>
+          <t>2026-10-04 10:59:50</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@www.tiktokhafsaqueen169</t>
+          <t>https://www.tiktok.com/@zainyzee39</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>xx_jessl_xx</t>
+          <t>zara1508ahmed</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-10-01 11:04:02</t>
+          <t>2026-09-23 03:28:52</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@xx_jessl_xx</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>yeterecipe</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr"/>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-10-02 16:32:43</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@yeterecipe</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>zainyzee39</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr"/>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Free sample from seller</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-10-04 10:59:50</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@zainyzee39</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>zara1508ahmed</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Green Burner</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-09-23 03:28:52</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zara1508ahmed</t>
         </is>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>brynnaellen</t>
+          <t>keyratio</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -471,81 +471,81 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-24 00:22:02</t>
+          <t>2026-09-27 13:35:02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@brynnaellen</t>
+          <t>https://www.tiktok.com/@keyratio</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>shannonroberts16595</t>
+          <t>brynnaellen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-21 10:52:02</t>
+          <t>2026-09-24 00:22:02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shannonroberts16595</t>
+          <t>https://www.tiktok.com/@brynnaellen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1sultan786</t>
+          <t>inspirednoor</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -570,24 +570,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-21 10:45:04</t>
+          <t>2026-09-26 17:35:02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@1sultan786</t>
+          <t>https://www.tiktok.com/@inspirednoor</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>miaweb7new</t>
+          <t>shannonroberts16595</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,12 +597,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>100K-250K</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -612,24 +612,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-26 17:37:02</t>
+          <t>2026-09-21 10:52:02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@miaweb7new</t>
+          <t>https://www.tiktok.com/@shannonroberts16595</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>holliedolli94shopsugc0</t>
+          <t>1sultan786</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -639,44 +639,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-29 14:37:02</t>
+          <t>2026-09-21 10:45:04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@holliedolli94shopsugc0</t>
+          <t>https://www.tiktok.com/@1sultan786</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fairyfaryal11</t>
+          <t>letsmakeitkentlimited</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -686,49 +686,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-24 20:07:02</t>
+          <t>2026-09-26 08:39:02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fairyfaryal11</t>
+          <t>https://www.tiktok.com/@letsmakeitkentlimited</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>seffshops</t>
+          <t>miaweb7new</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -738,81 +738,81 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-21 10:52:04</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seffshops</t>
+          <t>https://www.tiktok.com/@miaweb7new</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>beauty_shine07</t>
+          <t>flash_finds1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-09-27 13:35:02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty_shine07</t>
+          <t>https://www.tiktok.com/@flash_finds1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>shelleybelle26</t>
+          <t>holliedolli94shopsugc0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -822,123 +822,123 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:03</t>
+          <t>2026-09-29 14:37:02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shelleybelle26</t>
+          <t>https://www.tiktok.com/@holliedolli94shopsugc0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>jasminehagen3</t>
+          <t>azlanzaynahzayrahuk</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-30 14:59:02</t>
+          <t>2026-09-28 10:10:05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jasminehagen3</t>
+          <t>https://www.tiktok.com/@azlanzaynahzayrahuk</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dailydealsuk03</t>
+          <t>samstrendingdeals</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-21 10:45:03</t>
+          <t>2026-09-26 17:38:02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailydealsuk03</t>
+          <t>https://www.tiktok.com/@samstrendingdeals</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>georgiaxx___</t>
+          <t>seffshops</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>50K-100K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -948,66 +948,66 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-26 17:37:02</t>
+          <t>2026-09-21 10:52:04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@georgiaxx___</t>
+          <t>https://www.tiktok.com/@seffshops</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>callmequeencossy</t>
+          <t>beauty_shine07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:05</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@callmequeencossy</t>
+          <t>https://www.tiktok.com/@beauty_shine07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tiktok.shopmahi</t>
+          <t>mersoo712</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1015,10 +1015,14 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1028,24 +1032,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:06</t>
+          <t>2026-09-24 12:56:04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiktok.shopmahi</t>
+          <t>https://www.tiktok.com/@mersoo712</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>biancaselects</t>
+          <t>shelleybelle26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1053,10 +1057,14 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1076,14 +1084,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@biancaselects</t>
+          <t>https://www.tiktok.com/@shelleybelle26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>raeganfurness</t>
+          <t>fairyfaryal11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1093,39 +1101,39 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-30 14:59:02</t>
+          <t>2026-09-24 20:07:02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@raeganfurness</t>
+          <t>https://www.tiktok.com/@fairyfaryal11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sammummyconqueringanxiet</t>
+          <t>mummyzaraa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1135,39 +1143,39 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-09-23 08:16:05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sammummyconqueringanxiet</t>
+          <t>https://www.tiktok.com/@mummyzaraa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>smoothshelly</t>
+          <t>georgiaxx___</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1177,39 +1185,39 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>250K-500K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@smoothshelly</t>
+          <t>https://www.tiktok.com/@georgiaxx___</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>builtfindsuk</t>
+          <t>jasminehagen3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1219,39 +1227,39 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-01 10:47:03</t>
+          <t>2026-09-30 14:59:02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@builtfindsuk</t>
+          <t>https://www.tiktok.com/@jasminehagen3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>andreeamaria1828</t>
+          <t>shasha.0891</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1267,11 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -1272,24 +1284,24 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:02</t>
+          <t>2026-09-23 13:48:02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@andreeamaria1828</t>
+          <t>https://www.tiktok.com/@shasha.0891</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sarahs.worldx</t>
+          <t>mahi.rani421</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1299,54 +1311,54 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:02</t>
+          <t>2026-09-24 13:02:03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahs.worldx</t>
+          <t>https://www.tiktok.com/@mahi.rani421</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>moodymarbsandshadow</t>
+          <t>dailydealsuk03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1356,39 +1368,39 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-01 10:47:02</t>
+          <t>2026-09-21 10:45:03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moodymarbsandshadow</t>
+          <t>https://www.tiktok.com/@dailydealsuk03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mariatincuta11</t>
+          <t>becky.mawunyo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1398,39 +1410,39 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-09-28 10:19:04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mariatincuta11</t>
+          <t>https://www.tiktok.com/@becky.mawunyo</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hulubasul</t>
+          <t>callmequeencossy</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1440,7 +1452,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:02</t>
+          <t>2026-09-30 14:56:05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1450,19 +1462,19 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hulubasul</t>
+          <t>https://www.tiktok.com/@callmequeencossy</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>latina_shops</t>
+          <t>iamvickyshurwen_</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1472,7 +1484,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1482,29 +1494,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:06</t>
+          <t>2026-09-29 10:25:06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@latina_shops</t>
+          <t>https://www.tiktok.com/@iamvickyshurwen_</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>shopwithdanz0</t>
+          <t>diddlyidi</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1514,7 +1526,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1524,49 +1536,49 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:03</t>
+          <t>2026-09-23 08:16:02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shopwithdanz0</t>
+          <t>https://www.tiktok.com/@diddlyidi</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hinamalik0611</t>
+          <t>kayyasin87</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-28 10:19:03</t>
+          <t>2026-09-28 10:10:05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1576,29 +1588,29 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hinamalik0611</t>
+          <t>https://www.tiktok.com/@kayyasin87</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hazels_open_diary</t>
+          <t>kaylee_dexter</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1608,39 +1620,39 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hazels_open_diary</t>
+          <t>https://www.tiktok.com/@kaylee_dexter</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>demyrobbo01</t>
+          <t>reems_ttsshop</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1650,81 +1662,73 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:03</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@demyrobbo01</t>
+          <t>https://www.tiktok.com/@reems_ttsshop</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>xx_jessl_xx</t>
+          <t>tiktok.shopmahi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-01 11:04:02</t>
+          <t>2026-09-30 14:56:06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@xx_jessl_xx</t>
+          <t>https://www.tiktok.com/@tiktok.shopmahi</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>miss_quenny1</t>
+          <t>biancaselects</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1734,29 +1738,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-30 14:56:03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@miss_quenny1</t>
+          <t>https://www.tiktok.com/@biancaselects</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>abdulawwal470</t>
+          <t>raeganfurness</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1776,7 +1780,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:03</t>
+          <t>2026-09-30 14:59:02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1786,103 +1790,103 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abdulawwal470</t>
+          <t>https://www.tiktok.com/@raeganfurness</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>jones23350</t>
+          <t>themelfords</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:04</t>
+          <t>2026-09-29 14:37:03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jones23350</t>
+          <t>https://www.tiktok.com/@themelfords</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>smartfindsuk1</t>
+          <t>funmumshops</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-28 10:19:02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@smartfindsuk1</t>
+          <t>https://www.tiktok.com/@funmumshops</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>janet.osayande</t>
+          <t>viralbuysontiktok</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1892,91 +1896,91 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:02</t>
+          <t>2026-09-28 10:13:03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@janet.osayande</t>
+          <t>https://www.tiktok.com/@viralbuysontiktok</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>carfoon767</t>
+          <t>sammummyconqueringanxiet</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>50K-100K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@carfoon767</t>
+          <t>https://www.tiktok.com/@sammummyconqueringanxiet</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>angiereviewslife</t>
+          <t>smoothshelly</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>250K-500K</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1986,7 +1990,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-01 11:04:03</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1996,29 +2000,29 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angiereviewslife</t>
+          <t>https://www.tiktok.com/@smoothshelly</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kimmys_kitchen_garden</t>
+          <t>sh28.eat.with.me</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>100K-250K</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2028,7 +2032,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-01 10:47:02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2038,19 +2042,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kimmys_kitchen_garden</t>
+          <t>https://www.tiktok.com/@sh28.eat.with.me</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mycontemporarylifeinuk</t>
+          <t>amanmegbu</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2060,59 +2064,59 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-01 14:55:02</t>
+          <t>2026-09-29 14:41:03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mycontemporarylifeinuk</t>
+          <t>https://www.tiktok.com/@amanmegbu</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>itsjulesmurph</t>
+          <t>builtfindsuk</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:05</t>
+          <t>2026-10-01 10:47:03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2122,66 +2126,62 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsjulesmurph</t>
+          <t>https://www.tiktok.com/@builtfindsuk</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kerrycavan</t>
+          <t>andreeamaria1828</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>£200-£500</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-30 14:57:02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kerrycavan</t>
+          <t>https://www.tiktok.com/@andreeamaria1828</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sue_never_ending_journey</t>
+          <t>sarahs.worldx</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2196,39 +2196,39 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:06</t>
+          <t>2026-09-30 14:57:02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sue_never_ending_journey</t>
+          <t>https://www.tiktok.com/@sarahs.worldx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>jodijudejj</t>
+          <t>_unique_kashmiri_</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2238,39 +2238,39 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-01 11:14:02</t>
+          <t>2026-09-29 10:25:02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jodijudejj</t>
+          <t>https://www.tiktok.com/@_unique_kashmiri_</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>andreeatts</t>
+          <t>chek_mi_shocase</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2280,29 +2280,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:05</t>
+          <t>2026-09-22 17:56:02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@andreeatts</t>
+          <t>https://www.tiktok.com/@chek_mi_shocase</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>uk.life.moments</t>
+          <t>moodymarbsandshadow</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:06</t>
+          <t>2026-10-01 10:47:02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2332,29 +2332,29 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uk.life.moments</t>
+          <t>https://www.tiktok.com/@moodymarbsandshadow</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>shannonlou8991</t>
+          <t>mariatincuta11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2364,29 +2364,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:05</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shannonlou8991</t>
+          <t>https://www.tiktok.com/@mariatincuta11</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>tonirooney19</t>
+          <t>hulubasul</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2406,39 +2406,39 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-05 23:00:07</t>
+          <t>2026-09-30 14:57:02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tonirooney19</t>
+          <t>https://www.tiktok.com/@hulubasul</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>sarahwulatarawa</t>
+          <t>latina_shops</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2448,77 +2448,81 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-02 06:49:42</t>
+          <t>2026-09-30 14:56:06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahwulatarawa</t>
+          <t>https://www.tiktok.com/@latina_shops</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>crestworld.cooks</t>
+          <t>shopwithdanz0</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-27 08:26:05</t>
+          <t>2026-09-30 14:57:03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@crestworld.cooks</t>
+          <t>https://www.tiktok.com/@shopwithdanz0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dillytwinmum</t>
+          <t>fittokfinds88</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2528,41 +2532,49 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-21 09:55:02</t>
+          <t>2026-09-23 16:18:03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dillytwinmum</t>
+          <t>https://www.tiktok.com/@fittokfinds88</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>amena.akter3665</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
+          <t>hinamalik0611</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-28 12:23:28</t>
+          <t>2026-09-28 10:19:03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2572,29 +2584,29 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amena.akter3665</t>
+          <t>https://www.tiktok.com/@hinamalik0611</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>_unique_kashmiri_</t>
+          <t>hazels_open_diary</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2604,31 +2616,39 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-29 10:25:02</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_unique_kashmiri_</t>
+          <t>https://www.tiktok.com/@hazels_open_diary</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>_dosah</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
+          <t>demyrobbo01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2638,31 +2658,39 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-21 14:58:25</t>
+          <t>2026-09-30 14:57:03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_dosah</t>
+          <t>https://www.tiktok.com/@demyrobbo01</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>funmumshops</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
+          <t>xx_jessl_xx</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2672,65 +2700,81 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-28 10:19:02</t>
+          <t>2026-10-01 11:04:02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@funmumshops</t>
+          <t>https://www.tiktok.com/@xx_jessl_xx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>fmrasalhossain</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
+          <t>toryannaxo</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-25 22:32:12</t>
+          <t>2026-09-29 14:44:02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fmrasalhossain</t>
+          <t>https://www.tiktok.com/@toryannaxo</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>flash_finds1</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
+          <t>miss_quenny1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2740,62 +2784,78 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-27 13:35:02</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@flash_finds1</t>
+          <t>https://www.tiktok.com/@miss_quenny1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>fkprima123</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
+          <t>abdulawwal470</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-26 17:32:35</t>
+          <t>2026-09-30 14:57:03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fkprima123</t>
+          <t>https://www.tiktok.com/@abdulawwal470</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>fittokfinds88</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
+          <t>jones23350</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -2808,31 +2868,39 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-23 16:18:03</t>
+          <t>2026-10-01 10:52:04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fittokfinds88</t>
+          <t>https://www.tiktok.com/@jones23350</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>fellykemmy3</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
+          <t>smartfindsuk1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2842,31 +2910,39 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-24 20:39:00</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fellykemmy3</t>
+          <t>https://www.tiktok.com/@smartfindsuk1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>fahmidaislam2120</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
+          <t>janet.osayande</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2876,41 +2952,49 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-23 15:26:11</t>
+          <t>2026-10-04 18:25:02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fahmidaislam2120</t>
+          <t>https://www.tiktok.com/@janet.osayande</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>f.chowdhury15</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
+          <t>tiadinamakeup</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-29 23:20:53</t>
+          <t>2026-09-29 14:41:02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2920,18 +3004,26 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@f.chowdhury15</t>
+          <t>https://www.tiktok.com/@tiadinamakeup</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>duaanoor080120</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
+          <t>carfoon767</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>50K-100K</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -2939,36 +3031,44 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-02 06:26:32</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@duaanoor080120</t>
+          <t>https://www.tiktok.com/@carfoon767</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>explorewithmex10</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
+          <t>nomzy.gladys</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2978,31 +3078,39 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-10-02 09:06:56</t>
+          <t>2026-09-25 10:26:03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@explorewithmex10</t>
+          <t>https://www.tiktok.com/@nomzy.gladys</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>explore.with.em4</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
+          <t>angiereviewslife</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3012,7 +3120,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-01 14:44:03</t>
+          <t>2026-10-01 11:04:03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3022,18 +3130,26 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@explore.with.em4</t>
+          <t>https://www.tiktok.com/@angiereviewslife</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>egooyibo41</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
+          <t>kimmys_kitchen_garden</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3041,36 +3157,44 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-05 13:55:48</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@egooyibo41</t>
+          <t>https://www.tiktok.com/@kimmys_kitchen_garden</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>dinexheese</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
+          <t>mycontemporarylifeinuk</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3080,99 +3204,123 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-26 12:16:35</t>
+          <t>2026-10-01 14:55:02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dinexheese</t>
+          <t>https://www.tiktok.com/@mycontemporarylifeinuk</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>dsda0786</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
+          <t>itsjulesmurph</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-29 09:46:30</t>
+          <t>2026-10-01 10:52:05</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dsda0786</t>
+          <t>https://www.tiktok.com/@itsjulesmurph</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>dimpleddp</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
+          <t>kerrycavan</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-25 12:30:06</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dimpleddp</t>
+          <t>https://www.tiktok.com/@kerrycavan</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>diddlyidi</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
+          <t>sue_never_ending_journey</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3182,31 +3330,39 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-23 08:16:02</t>
+          <t>2026-10-01 10:52:06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@diddlyidi</t>
+          <t>https://www.tiktok.com/@sue_never_ending_journey</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>bukky.yoyo</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
+          <t>jodijudejj</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3216,31 +3372,39 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-04 16:50:32</t>
+          <t>2026-10-01 11:14:02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bukky.yoyo</t>
+          <t>https://www.tiktok.com/@jodijudejj</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>desylviaa1</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
+          <t>andreeatts</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3250,31 +3414,39 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-27 10:40:10</t>
+          <t>2026-09-30 14:56:05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@desylviaa1</t>
+          <t>https://www.tiktok.com/@andreeatts</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>damsel755</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
+          <t>uk.life.moments</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3284,31 +3456,39 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-05 20:02:55</t>
+          <t>2026-10-01 10:50:06</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@damsel755</t>
+          <t>https://www.tiktok.com/@uk.life.moments</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>dearlola45</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
+          <t>shannonlou8991</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>£100-£200</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3318,7 +3498,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-01 11:28:54</t>
+          <t>2026-10-01 10:50:05</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3328,18 +3508,26 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dearlola45</t>
+          <t>https://www.tiktok.com/@shannonlou8991</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>chezzy954</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
+          <t>tonirooney19</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -3347,33 +3535,41 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-25 13:21:47</t>
+          <t>2026-10-05 23:00:07</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chezzy954</t>
+          <t>https://www.tiktok.com/@tonirooney19</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>charliegirl860</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
+          <t>sarahwulatarawa</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -3386,62 +3582,74 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-26 10:54:39</t>
+          <t>2026-10-02 06:49:42</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@charliegirl860</t>
+          <t>https://www.tiktok.com/@sarahwulatarawa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>climax.scenes</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>crestworld.cooks</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-21 06:20:00</t>
+          <t>2026-09-27 08:26:05</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@climax.scenes</t>
+          <t>https://www.tiktok.com/@crestworld.cooks</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>amanmegbu</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
+          <t>dillytwinmum</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -3454,24 +3662,24 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:03</t>
+          <t>2026-09-21 09:55:02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amanmegbu</t>
+          <t>https://www.tiktok.com/@dillytwinmum</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>angelhairstylist1</t>
+          <t>adeede1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3483,29 +3691,29 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-04 20:43:03</t>
+          <t>2026-10-03 06:37:25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angelhairstylist1</t>
+          <t>https://www.tiktok.com/@adeede1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>aminajeylani</t>
+          <t>armaan.ahmed37</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3517,41 +3725,33 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-23 14:42:07</t>
+          <t>2026-10-03 19:49:39</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aminajeylani</t>
+          <t>https://www.tiktok.com/@armaan.ahmed37</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>amap000</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>amena.akter3665</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3559,33 +3759,41 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-03 10:59:49</t>
+          <t>2026-09-28 12:23:28</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amap000</t>
+          <t>https://www.tiktok.com/@amena.akter3665</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>armaan.ahmed37</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
+          <t>amap000</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3598,7 +3806,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-03 19:49:39</t>
+          <t>2026-10-03 10:59:49</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3608,14 +3816,14 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@armaan.ahmed37</t>
+          <t>https://www.tiktok.com/@amap000</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>babbyzozo</t>
+          <t>angelhairstylist1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3627,36 +3835,36 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-28 18:28:13</t>
+          <t>2026-10-04 20:43:03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@babbyzozo</t>
+          <t>https://www.tiktok.com/@angelhairstylist1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>azlanzaynahzayrahuk</t>
+          <t>aminajeylani</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3666,24 +3874,24 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-28 10:10:05</t>
+          <t>2026-09-23 14:42:07</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@azlanzaynahzayrahuk</t>
+          <t>https://www.tiktok.com/@aminajeylani</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>balletdeo</t>
+          <t>bukky.yoyo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3695,46 +3903,46 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-26 01:45:10</t>
+          <t>2026-10-04 16:50:32</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@balletdeo</t>
+          <t>https://www.tiktok.com/@bukky.yoyo</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>becky.mawunyo</t>
+          <t>babbyzozo</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-28 10:19:04</t>
+          <t>2026-09-28 18:28:13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3744,26 +3952,18 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@becky.mawunyo</t>
+          <t>https://www.tiktok.com/@babbyzozo</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>_mohlad</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
+          <t>balletdeo</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3771,29 +3971,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-10-04 18:10:30</t>
+          <t>2026-09-26 01:45:10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_mohlad</t>
+          <t>https://www.tiktok.com/@balletdeo</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>adeede1</t>
+          <t>_dosah</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3810,28 +4010,36 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-10-03 06:37:25</t>
+          <t>2026-09-21 14:58:25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adeede1</t>
+          <t>https://www.tiktok.com/@_dosah</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kulwinderrani5</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
+          <t>_mohlad</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3844,24 +4052,24 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-05 09:00:08</t>
+          <t>2026-10-04 18:10:30</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kulwinderrani5</t>
+          <t>https://www.tiktok.com/@_mohlad</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>knicksmakeuppro</t>
+          <t>gbm.sees</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3878,7 +4086,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-10-01 11:30:23</t>
+          <t>2026-10-01 09:00:38</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3888,21 +4096,21 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@knicksmakeuppro</t>
+          <t>https://www.tiktok.com/@gbm.sees</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>keyratio</t>
+          <t>fmrasalhossain</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3912,92 +4120,92 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-27 13:35:02</t>
+          <t>2026-09-25 22:32:12</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@keyratio</t>
+          <t>https://www.tiktok.com/@fmrasalhossain</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>lovecats7112</t>
+          <t>fellykemmy3</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-26 19:59:48</t>
+          <t>2026-09-24 20:39:00</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lovecats7112</t>
+          <t>https://www.tiktok.com/@fellykemmy3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>lolaclothier</t>
+          <t>fkprima123</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-10-01 20:17:12</t>
+          <t>2026-09-26 17:32:35</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lolaclothier</t>
+          <t>https://www.tiktok.com/@fkprima123</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>lindaefionayi</t>
+          <t>explore.with.em4</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -4009,29 +4217,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-23 20:46:33</t>
+          <t>2026-10-01 14:44:03</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lindaefionayi</t>
+          <t>https://www.tiktok.com/@explore.with.em4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>manvinder318</t>
+          <t>explorewithmex10</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4048,24 +4256,24 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-25 14:14:56</t>
+          <t>2026-10-02 09:06:56</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@manvinder318</t>
+          <t>https://www.tiktok.com/@explorewithmex10</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mahi.rani421</t>
+          <t>f.chowdhury15</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -4082,24 +4290,24 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-24 13:02:03</t>
+          <t>2026-09-29 23:20:53</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mahi.rani421</t>
+          <t>https://www.tiktok.com/@f.chowdhury15</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>m.3384</t>
+          <t>fahmidaislam2120</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4116,58 +4324,58 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-21 10:22:24</t>
+          <t>2026-09-23 15:26:11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@m.3384</t>
+          <t>https://www.tiktok.com/@fahmidaislam2120</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>maxi_berrie</t>
+          <t>duaanoor080120</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-22 23:20:40</t>
+          <t>2026-10-02 06:26:32</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maxi_berrie</t>
+          <t>https://www.tiktok.com/@duaanoor080120</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>merz3859</t>
+          <t>egooyibo41</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4179,36 +4387,36 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-22 21:09:48</t>
+          <t>2026-10-05 13:55:48</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@merz3859</t>
+          <t>https://www.tiktok.com/@egooyibo41</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mersoo712</t>
+          <t>dsda0786</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4218,24 +4426,24 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-24 12:56:04</t>
+          <t>2026-09-29 09:46:30</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mersoo712</t>
+          <t>https://www.tiktok.com/@dsda0786</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mayma3747</t>
+          <t>damsel755</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4252,24 +4460,24 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-26 15:22:17</t>
+          <t>2026-10-05 20:02:55</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mayma3747</t>
+          <t>https://www.tiktok.com/@damsel755</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>lissssaxxx</t>
+          <t>desylviaa1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4286,31 +4494,31 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-23 08:17:25</t>
+          <t>2026-09-27 10:40:10</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lissssaxxx</t>
+          <t>https://www.tiktok.com/@desylviaa1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>lifeofhamzaa</t>
+          <t>dearlola45</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4320,31 +4528,31 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-04 18:28:02</t>
+          <t>2026-10-01 11:28:54</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeofhamzaa</t>
+          <t>https://www.tiktok.com/@dearlola45</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>laurywilliams</t>
+          <t>dimpleddp</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4354,31 +4562,31 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-26 16:59:35</t>
+          <t>2026-09-25 12:30:06</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@laurywilliams</t>
+          <t>https://www.tiktok.com/@dimpleddp</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ilzb7</t>
+          <t>dinexheese</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4388,24 +4596,24 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-10-05 16:59:43</t>
+          <t>2026-09-26 12:16:35</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ilzb7</t>
+          <t>https://www.tiktok.com/@dinexheese</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>jadepa90</t>
+          <t>climax.scenes</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4422,31 +4630,31 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-26 09:09:09</t>
+          <t>2026-09-21 06:20:00</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jadepa90</t>
+          <t>https://www.tiktok.com/@climax.scenes</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>jean.makin</t>
+          <t>charliegirl860</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4456,58 +4664,58 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-10-03 14:41:36</t>
+          <t>2026-09-26 10:54:39</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jean.makin</t>
+          <t>https://www.tiktok.com/@charliegirl860</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kaylee_dexter</t>
+          <t>chezzy954</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-25 13:21:47</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaylee_dexter</t>
+          <t>https://www.tiktok.com/@chezzy954</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>jem17363</t>
+          <t>kulwinderrani5</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4519,36 +4727,36 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-21 17:28:16</t>
+          <t>2026-10-05 09:00:08</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jem17363</t>
+          <t>https://www.tiktok.com/@kulwinderrani5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>juliana_armoh</t>
+          <t>kaz.gym82</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4558,41 +4766,41 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-10-01 21:22:31</t>
+          <t>2026-10-05 08:29:56</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@juliana_armoh</t>
+          <t>https://www.tiktok.com/@kaz.gym82</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kennyshekoni</t>
+          <t>juliana_armoh</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-10-01 19:41:15</t>
+          <t>2026-10-01 21:22:31</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4602,14 +4810,14 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kennyshekoni</t>
+          <t>https://www.tiktok.com/@juliana_armoh</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kaz.gym82</t>
+          <t>kennyshekoni</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4621,29 +4829,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-10-05 08:29:56</t>
+          <t>2026-10-01 19:41:15</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaz.gym82</t>
+          <t>https://www.tiktok.com/@kennyshekoni</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kayyasin87</t>
+          <t>jem17363</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4660,65 +4868,65 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-28 10:10:05</t>
+          <t>2026-09-21 17:28:16</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kayyasin87</t>
+          <t>https://www.tiktok.com/@jem17363</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>inspirednoor</t>
+          <t>lifeofhamzaa</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-26 17:35:02</t>
+          <t>2026-10-04 18:28:02</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@inspirednoor</t>
+          <t>https://www.tiktok.com/@lifeofhamzaa</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>idrissasesay7</t>
+          <t>laurywilliams</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4728,58 +4936,58 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-10-02 23:30:18</t>
+          <t>2026-09-26 16:59:35</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@idrissasesay7</t>
+          <t>https://www.tiktok.com/@laurywilliams</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>iamvickyshurwen_</t>
+          <t>knicksmakeuppro</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-29 10:25:06</t>
+          <t>2026-10-01 11:30:23</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iamvickyshurwen_</t>
+          <t>https://www.tiktok.com/@knicksmakeuppro</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>homemadefood2024</t>
+          <t>ilzb7</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4791,22 +4999,22 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-23 16:44:22</t>
+          <t>2026-10-05 16:59:43</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@homemadefood2024</t>
+          <t>https://www.tiktok.com/@ilzb7</t>
         </is>
       </c>
     </row>
@@ -4847,7 +5055,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>patriciaappiah280</t>
+          <t>homemadefood2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4864,7 +5072,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-23 10:08:56</t>
+          <t>2026-09-23 16:44:22</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4874,14 +5082,14 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@patriciaappiah280</t>
+          <t>https://www.tiktok.com/@homemadefood2024</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>onos282</t>
+          <t>idrissasesay7</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4893,29 +5101,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-10-04 23:21:40</t>
+          <t>2026-10-02 23:30:18</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@onos282</t>
+          <t>https://www.tiktok.com/@idrissasesay7</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>oluyewi</t>
+          <t>jean.makin</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4932,7 +5140,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-10-03 19:19:51</t>
+          <t>2026-10-03 14:41:36</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4942,21 +5150,21 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluyewi</t>
+          <t>https://www.tiktok.com/@jean.makin</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>oluwatoyin0322</t>
+          <t>paul.d.awson</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4966,24 +5174,24 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-28 23:38:06</t>
+          <t>2026-09-26 18:18:04</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwatoyin0322</t>
+          <t>https://www.tiktok.com/@paul.d.awson</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ola.oluwatoyin.ad</t>
+          <t>patriciaappiah280</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -5000,24 +5208,24 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-25 13:50:20</t>
+          <t>2026-09-23 10:08:56</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ola.oluwatoyin.ad</t>
+          <t>https://www.tiktok.com/@patriciaappiah280</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>nonochou12</t>
+          <t>onos282</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -5029,63 +5237,63 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-28 00:42:49</t>
+          <t>2026-10-04 23:21:40</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nonochou12</t>
+          <t>https://www.tiktok.com/@onos282</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>nomzy.gladys</t>
+          <t>oluyewi</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-25 10:26:03</t>
+          <t>2026-10-03 19:19:51</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nomzy.gladys</t>
+          <t>https://www.tiktok.com/@oluyewi</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>nevertoooldnanaxx</t>
+          <t>oluwatoyin0322</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5097,29 +5305,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-09-28 23:38:06</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nevertoooldnanaxx</t>
+          <t>https://www.tiktok.com/@oluwatoyin0322</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>naveed19.88</t>
+          <t>ola.oluwatoyin.ad</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5136,7 +5344,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-25 22:46:15</t>
+          <t>2026-09-25 13:50:20</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5146,14 +5354,14 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@naveed19.88</t>
+          <t>https://www.tiktok.com/@ola.oluwatoyin.ad</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>n.raja83</t>
+          <t>nonochou12</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5170,58 +5378,58 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-29 10:14:04</t>
+          <t>2026-09-28 00:42:49</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@n.raja83</t>
+          <t>https://www.tiktok.com/@nonochou12</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>munasheish</t>
+          <t>nevertoooldnanaxx</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-09-25 10:27:59</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@munasheish</t>
+          <t>https://www.tiktok.com/@nevertoooldnanaxx</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>mummyzaraa</t>
+          <t>mrm.foods.opeyemi</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5233,29 +5441,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-23 08:16:05</t>
+          <t>2026-10-04 20:07:11</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mummyzaraa</t>
+          <t>https://www.tiktok.com/@mrm.foods.opeyemi</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ms_gbm</t>
+          <t>naveed19.88</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5272,24 +5480,24 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-10-01 09:00:38</t>
+          <t>2026-09-25 22:46:15</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ms_gbm</t>
+          <t>https://www.tiktok.com/@naveed19.88</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>mum3tees</t>
+          <t>n.raja83</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5306,24 +5514,24 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-26 15:28:17</t>
+          <t>2026-09-29 10:14:04</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mum3tees</t>
+          <t>https://www.tiktok.com/@n.raja83</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>mrm.foods.opeyemi</t>
+          <t>munasheish</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5335,29 +5543,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-10-04 20:07:11</t>
+          <t>2026-09-25 10:27:59</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mrm.foods.opeyemi</t>
+          <t>https://www.tiktok.com/@munasheish</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>mr.liverpool885</t>
+          <t>mum3tees</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5369,36 +5577,36 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-10-04 09:00:20</t>
+          <t>2026-09-26 15:28:17</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mr.liverpool885</t>
+          <t>https://www.tiktok.com/@mum3tees</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>sarahswhimsyfits</t>
+          <t>mayma3747</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5408,31 +5616,31 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:06</t>
+          <t>2026-09-26 15:22:17</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahswhimsyfits</t>
+          <t>https://www.tiktok.com/@mayma3747</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>samstrendingdeals</t>
+          <t>maxi_berrie</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5442,24 +5650,24 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-26 17:38:02</t>
+          <t>2026-09-22 23:20:40</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samstrendingdeals</t>
+          <t>https://www.tiktok.com/@maxi_berrie</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ruas_dream</t>
+          <t>mr.liverpool885</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5471,29 +5679,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-27 11:00:34</t>
+          <t>2026-10-04 09:00:20</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ruas_dream</t>
+          <t>https://www.tiktok.com/@mr.liverpool885</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>samiahajam</t>
+          <t>lissssaxxx</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5510,24 +5718,24 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-09-25 10:39:07</t>
+          <t>2026-09-23 08:17:25</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samiahajam</t>
+          <t>https://www.tiktok.com/@lissssaxxx</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>rtamakter</t>
+          <t>lindaefionayi</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5544,65 +5752,65 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-10-05 22:45:22</t>
+          <t>2026-09-23 20:46:33</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rtamakter</t>
+          <t>https://www.tiktok.com/@lindaefionayi</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>riderrrr70</t>
+          <t>m.3384</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-09-27 14:15:10</t>
+          <t>2026-09-21 10:22:24</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@riderrrr70</t>
+          <t>https://www.tiktok.com/@m.3384</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>reems_ttsshop</t>
+          <t>merz3859</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5612,7 +5820,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-22 21:09:48</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5622,82 +5830,82 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reems_ttsshop</t>
+          <t>https://www.tiktok.com/@merz3859</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>reykkhan</t>
+          <t>lovecats7112</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-09-25 17:53:08</t>
+          <t>2026-09-26 19:59:48</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reykkhan</t>
+          <t>https://www.tiktok.com/@lovecats7112</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>princessanna1738</t>
+          <t>lolaclothier</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-25 07:04:05</t>
+          <t>2026-10-01 20:17:12</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princessanna1738</t>
+          <t>https://www.tiktok.com/@lolaclothier</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>shareenyousaf</t>
+          <t>manvinder318</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5714,24 +5922,24 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-29 10:13:11</t>
+          <t>2026-09-25 14:14:56</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shareenyousaf</t>
+          <t>https://www.tiktok.com/@manvinder318</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>sbegum.79</t>
+          <t>jadepa90</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5748,58 +5956,58 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-09-21 17:38:25</t>
+          <t>2026-09-26 09:09:09</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sbegum.79</t>
+          <t>https://www.tiktok.com/@jadepa90</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>seyiedeliciouscocktails</t>
+          <t>sarahswhimsyfits</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-25 06:38:51</t>
+          <t>2026-10-01 10:50:06</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seyiedeliciouscocktails</t>
+          <t>https://www.tiktok.com/@sarahswhimsyfits</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>rabbit_pm12</t>
+          <t>rtamakter</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -5816,24 +6024,24 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-09-25 19:17:46</t>
+          <t>2026-10-05 22:45:22</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rabbit_pm12</t>
+          <t>https://www.tiktok.com/@rtamakter</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>radhekrishna_11</t>
+          <t>ruas_dream</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -5850,24 +6058,24 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-21 11:21:47</t>
+          <t>2026-09-27 11:00:34</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@radhekrishna_11</t>
+          <t>https://www.tiktok.com/@ruas_dream</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>queenbabe_78</t>
+          <t>samiahajam</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -5884,31 +6092,31 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-10-02 15:22:41</t>
+          <t>2026-09-25 10:39:07</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queenbabe_78</t>
+          <t>https://www.tiktok.com/@samiahajam</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>paul.d.awson</t>
+          <t>radhekrishna_11</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5918,58 +6126,58 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-26 18:18:04</t>
+          <t>2026-09-21 11:21:47</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@paul.d.awson</t>
+          <t>https://www.tiktok.com/@radhekrishna_11</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>sidkam58</t>
+          <t>rabbit_pm12</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-10-01 07:57:16</t>
+          <t>2026-09-25 19:17:46</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sidkam58</t>
+          <t>https://www.tiktok.com/@rabbit_pm12</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>shukar7860</t>
+          <t>reykkhan</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -5986,24 +6194,24 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-22 09:29:34</t>
+          <t>2026-09-25 17:53:08</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shukar7860</t>
+          <t>https://www.tiktok.com/@reykkhan</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>shazia11235</t>
+          <t>riderrrr70</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -6020,24 +6228,24 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-09-24 23:21:59</t>
+          <t>2026-09-27 14:15:10</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shazia11235</t>
+          <t>https://www.tiktok.com/@riderrrr70</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>shasha.0891</t>
+          <t>sidkam58</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -6049,29 +6257,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-09-23 13:48:02</t>
+          <t>2026-10-01 07:57:16</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shasha.0891</t>
+          <t>https://www.tiktok.com/@sidkam58</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>theloyalsoul1</t>
+          <t>shukar7860</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -6088,58 +6296,58 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-09-28 20:53:18</t>
+          <t>2026-09-22 09:29:34</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@theloyalsoul1</t>
+          <t>https://www.tiktok.com/@shukar7860</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>themelfords</t>
+          <t>shazia11235</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-09-29 14:37:03</t>
+          <t>2026-09-24 23:21:59</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@themelfords</t>
+          <t>https://www.tiktok.com/@shazia11235</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>teeyworld_confectionery</t>
+          <t>shareenyousaf</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -6156,31 +6364,31 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-09-25 19:30:28</t>
+          <t>2026-09-29 10:13:11</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teeyworld_confectionery</t>
+          <t>https://www.tiktok.com/@shareenyousaf</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>suziefenton</t>
+          <t>seyiedeliciouscocktails</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6190,31 +6398,31 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-09-23 10:47:02</t>
+          <t>2026-09-25 06:38:51</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@suziefenton</t>
+          <t>https://www.tiktok.com/@seyiedeliciouscocktails</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tiadinamakeup</t>
+          <t>sbegum.79</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6224,31 +6432,31 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:02</t>
+          <t>2026-09-21 17:38:25</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiadinamakeup</t>
+          <t>https://www.tiktok.com/@sbegum.79</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>theweebelfastman</t>
+          <t>princessanna1738</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6258,24 +6466,24 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-25 07:04:05</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@theweebelfastman</t>
+          <t>https://www.tiktok.com/@princessanna1738</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tkmama45</t>
+          <t>queenbabe_78</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -6287,36 +6495,36 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-10-05 07:34:14</t>
+          <t>2026-10-02 15:22:41</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tkmama45</t>
+          <t>https://www.tiktok.com/@queenbabe_78</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>tinku78616</t>
+          <t>theweebelfastman</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6326,31 +6534,31 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-09-25 17:21:23</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinku78616</t>
+          <t>https://www.tiktok.com/@theweebelfastman</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>toryannaxo</t>
+          <t>taiwooluyemitaiwo</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6360,24 +6568,24 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-09-29 14:44:02</t>
+          <t>2026-09-23 16:28:21</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@toryannaxo</t>
+          <t>https://www.tiktok.com/@taiwooluyemitaiwo</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>triciaebun</t>
+          <t>teeyworld_confectionery</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -6394,7 +6602,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-09-25 16:57:55</t>
+          <t>2026-09-25 19:30:28</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6404,26 +6612,18 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@triciaebun</t>
+          <t>https://www.tiktok.com/@teeyworld_confectionery</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>tyanie1703</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>tkmama45</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6431,63 +6631,63 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-09-22 14:51:38</t>
+          <t>2026-10-05 07:34:14</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tyanie1703</t>
+          <t>https://www.tiktok.com/@tkmama45</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>taiwooluyemitaiwo</t>
+          <t>tinku78616</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-23 16:28:21</t>
+          <t>2026-09-25 17:21:23</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@taiwooluyemitaiwo</t>
+          <t>https://www.tiktok.com/@tinku78616</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>user2182373993526</t>
+          <t>triciaebun</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -6504,24 +6704,24 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-09-21 12:26:17</t>
+          <t>2026-09-25 16:57:55</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2182373993526</t>
+          <t>https://www.tiktok.com/@triciaebun</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>user2773140226152</t>
+          <t>theloyalsoul1</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -6538,31 +6738,31 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-09-21 20:00:10</t>
+          <t>2026-09-28 20:53:18</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2773140226152</t>
+          <t>https://www.tiktok.com/@theloyalsoul1</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>user3998147688485</t>
+          <t>suziefenton</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6572,24 +6772,24 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-09-29 09:40:30</t>
+          <t>2026-09-23 10:47:02</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user3998147688485</t>
+          <t>https://www.tiktok.com/@suziefenton</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>user35110093</t>
+          <t>user2182373993526</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -6606,28 +6806,36 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-09-28 20:20:27</t>
+          <t>2026-09-21 12:26:17</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user35110093</t>
+          <t>https://www.tiktok.com/@user2182373993526</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>user8258556352859</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr"/>
-      <c r="C171" t="inlineStr"/>
+          <t>tyanie1703</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D171" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6640,24 +6848,24 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-10-03 10:13:16</t>
+          <t>2026-09-22 14:51:38</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8258556352859</t>
+          <t>https://www.tiktok.com/@tyanie1703</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>user9310370027124</t>
+          <t>user2773140226152</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -6674,24 +6882,24 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-10-01 19:05:18</t>
+          <t>2026-09-21 20:00:10</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9310370027124</t>
+          <t>https://www.tiktok.com/@user2773140226152</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>user99851967341610</t>
+          <t>user35110093</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -6708,7 +6916,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-09-28 16:59:33</t>
+          <t>2026-09-28 20:20:27</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -6718,14 +6926,14 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user99851967341610</t>
+          <t>https://www.tiktok.com/@user35110093</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>user6931802591156</t>
+          <t>user8258556352859</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -6742,109 +6950,109 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-10-01 16:26:50</t>
+          <t>2026-10-03 10:13:16</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6931802591156</t>
+          <t>https://www.tiktok.com/@user8258556352859</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>user_78602223</t>
+          <t>user9310370027124</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-09-22 17:40:46</t>
+          <t>2026-10-01 19:05:18</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user_78602223</t>
+          <t>https://www.tiktok.com/@user9310370027124</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>veeover40</t>
+          <t>user3998147688485</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:04</t>
+          <t>2026-09-29 09:40:30</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@veeover40</t>
+          <t>https://www.tiktok.com/@user3998147688485</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>waboti</t>
+          <t>user6931802591156</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-10-01 18:00:40</t>
+          <t>2026-10-01 16:26:50</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -6854,14 +7062,14 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@waboti</t>
+          <t>https://www.tiktok.com/@user6931802591156</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>viralbuysontiktok</t>
+          <t>user_78602223</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -6873,36 +7081,36 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-09-28 10:13:03</t>
+          <t>2026-09-22 17:40:46</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@viralbuysontiktok</t>
+          <t>https://www.tiktok.com/@user_78602223</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>www.tiktokhafsaqueen169</t>
+          <t>user99851967341610</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6912,65 +7120,65 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-09-29 14:46:03</t>
+          <t>2026-09-28 16:59:33</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@www.tiktokhafsaqueen169</t>
+          <t>https://www.tiktok.com/@user99851967341610</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>yeterecipe</t>
+          <t>waboti</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-10-02 16:32:43</t>
+          <t>2026-10-01 18:00:40</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yeterecipe</t>
+          <t>https://www.tiktok.com/@waboti</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>zainyzee39</t>
+          <t>veeover40</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6980,31 +7188,31 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-10-04 10:59:50</t>
+          <t>2026-10-01 10:50:04</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zainyzee39</t>
+          <t>https://www.tiktok.com/@veeover40</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>zara1508ahmed</t>
+          <t>www.tiktokhafsaqueen169</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -7014,15 +7222,117 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
+          <t>2026-09-29 14:46:03</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@www.tiktokhafsaqueen169</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>yeterecipe</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:32:43</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yeterecipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>zainyzee39</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Free sample from seller</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-10-04 10:59:50</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@zainyzee39</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>zara1508ahmed</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
           <t>2026-09-23 03:28:52</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="G185" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
+      <c r="H185" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zara1508ahmed</t>
         </is>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>shannonroberts16595</t>
+          <t>letsmakeitkentlimited</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,39 +597,39 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-21 10:52:02</t>
+          <t>2026-09-26 08:39:02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shannonroberts16595</t>
+          <t>https://www.tiktok.com/@letsmakeitkentlimited</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1sultan786</t>
+          <t>miaweb7new</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -654,24 +654,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-21 10:45:04</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@1sultan786</t>
+          <t>https://www.tiktok.com/@miaweb7new</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>letsmakeitkentlimited</t>
+          <t>flash_finds1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-26 08:39:02</t>
+          <t>2026-09-27 13:35:02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@letsmakeitkentlimited</t>
+          <t>https://www.tiktok.com/@flash_finds1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>miaweb7new</t>
+          <t>holliedolli94shopsugc0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -723,44 +723,44 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-26 17:37:02</t>
+          <t>2026-09-29 14:37:02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@miaweb7new</t>
+          <t>https://www.tiktok.com/@holliedolli94shopsugc0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>flash_finds1</t>
+          <t>azlanzaynahzayrahuk</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -770,17 +770,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-27 13:35:02</t>
+          <t>2026-09-28 10:10:05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -790,56 +790,56 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@flash_finds1</t>
+          <t>https://www.tiktok.com/@azlanzaynahzayrahuk</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>holliedolli94shopsugc0</t>
+          <t>brookesbaddestfinds</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-29 14:37:02</t>
+          <t>2026-10-06 11:15:02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@holliedolli94shopsugc0</t>
+          <t>https://www.tiktok.com/@brookesbaddestfinds</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>azlanzaynahzayrahuk</t>
+          <t>samstrendingdeals</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -864,24 +864,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-28 10:10:05</t>
+          <t>2026-09-26 17:38:02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@azlanzaynahzayrahuk</t>
+          <t>https://www.tiktok.com/@samstrendingdeals</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>samstrendingdeals</t>
+          <t>beauty_shine07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -906,29 +906,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-26 17:38:02</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samstrendingdeals</t>
+          <t>https://www.tiktok.com/@beauty_shine07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>seffshops</t>
+          <t>mersoo712</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -948,29 +948,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-21 10:52:04</t>
+          <t>2026-09-24 12:56:04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seffshops</t>
+          <t>https://www.tiktok.com/@mersoo712</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>beauty_shine07</t>
+          <t>shelleybelle26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -985,29 +985,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-09-30 14:56:03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty_shine07</t>
+          <t>https://www.tiktok.com/@shelleybelle26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mersoo712</t>
+          <t>fairyfaryal11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1032,24 +1032,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-24 12:56:04</t>
+          <t>2026-09-24 20:07:02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mersoo712</t>
+          <t>https://www.tiktok.com/@fairyfaryal11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>shelleybelle26</t>
+          <t>mummyzaraa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1059,39 +1059,39 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:03</t>
+          <t>2026-09-23 08:16:05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shelleybelle26</t>
+          <t>https://www.tiktok.com/@mummyzaraa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fairyfaryal11</t>
+          <t>georgiaxx___</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1116,24 +1116,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-24 20:07:02</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fairyfaryal11</t>
+          <t>https://www.tiktok.com/@georgiaxx___</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mummyzaraa</t>
+          <t>lisamercyjones</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1148,34 +1148,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-23 08:16:05</t>
+          <t>2026-10-06 11:15:02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mummyzaraa</t>
+          <t>https://www.tiktok.com/@lisamercyjones</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>georgiaxx___</t>
+          <t>tosinreviews</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>50K-100K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1200,24 +1200,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-26 17:37:02</t>
+          <t>2026-10-06 11:15:04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@georgiaxx___</t>
+          <t>https://www.tiktok.com/@tosinreviews</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>jasminehagen3</t>
+          <t>shannyt30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ceremonial Matcha Powder</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1242,24 +1242,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-30 14:59:02</t>
+          <t>2026-10-06 11:05:02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jasminehagen3</t>
+          <t>https://www.tiktok.com/@shannyt30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>shasha.0891</t>
+          <t>jasminehagen3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1274,34 +1274,34 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-23 13:48:02</t>
+          <t>2026-09-30 14:59:02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shasha.0891</t>
+          <t>https://www.tiktok.com/@jasminehagen3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mahi.rani421</t>
+          <t>shasha.0891</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1326,24 +1326,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-24 13:02:03</t>
+          <t>2026-09-23 13:48:02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mahi.rani421</t>
+          <t>https://www.tiktok.com/@shasha.0891</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dailydealsuk03</t>
+          <t>mahi.rani421</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1353,32 +1353,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-21 10:45:03</t>
+          <t>2026-09-24 13:02:03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dailydealsuk03</t>
+          <t>https://www.tiktok.com/@mahi.rani421</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>callmequeencossy</t>
+          <t>tikymart2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1437,39 +1437,39 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:05</t>
+          <t>2026-10-06 11:15:04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@callmequeencossy</t>
+          <t>https://www.tiktok.com/@tikymart2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iamvickyshurwen_</t>
+          <t>callmequeencossy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-29 10:25:06</t>
+          <t>2026-09-30 14:56:05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1504,14 +1504,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@iamvickyshurwen_</t>
+          <t>https://www.tiktok.com/@callmequeencossy</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>diddlyidi</t>
+          <t>iamvickyshurwen_</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Shatavari 1300mg Extra Strength</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1536,24 +1536,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-23 08:16:02</t>
+          <t>2026-09-29 10:25:06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@diddlyidi</t>
+          <t>https://www.tiktok.com/@iamvickyshurwen_</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kayyasin87</t>
+          <t>diddlyidi</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1563,39 +1563,39 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Shatavari 1300mg Extra Strength</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-28 10:10:05</t>
+          <t>2026-09-23 08:16:02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kayyasin87</t>
+          <t>https://www.tiktok.com/@diddlyidi</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kaylee_dexter</t>
+          <t>kayyasin87</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1605,39 +1605,39 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-09-28 10:10:05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaylee_dexter</t>
+          <t>https://www.tiktok.com/@kayyasin87</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>reems_ttsshop</t>
+          <t>myhonestreviews25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1662,24 +1662,24 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-22 19:57:02</t>
+          <t>2026-10-06 12:38:03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reems_ttsshop</t>
+          <t>https://www.tiktok.com/@myhonestreviews25</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tiktok.shopmahi</t>
+          <t>kaylee_dexter</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1687,37 +1687,41 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:06</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiktok.shopmahi</t>
+          <t>https://www.tiktok.com/@kaylee_dexter</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>biancaselects</t>
+          <t>reems_ttsshop</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1725,37 +1729,41 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:03</t>
+          <t>2026-09-22 19:57:02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@biancaselects</t>
+          <t>https://www.tiktok.com/@reems_ttsshop</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>raeganfurness</t>
+          <t>tiktok.shopmahi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1763,41 +1771,37 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-30 14:59:02</t>
+          <t>2026-09-30 14:56:06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@raeganfurness</t>
+          <t>https://www.tiktok.com/@tiktok.shopmahi</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>themelfords</t>
+          <t>biancaselects</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1805,14 +1809,10 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-29 14:37:03</t>
+          <t>2026-09-30 14:56:03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1832,14 +1832,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@themelfords</t>
+          <t>https://www.tiktok.com/@biancaselects</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>funmumshops</t>
+          <t>laurlaur0306</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-28 10:19:02</t>
+          <t>2026-10-06 12:44:03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@funmumshops</t>
+          <t>https://www.tiktok.com/@laurlaur0306</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>viralbuysontiktok</t>
+          <t>raeganfurness</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1891,39 +1891,39 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-28 10:13:03</t>
+          <t>2026-09-30 14:59:02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@viralbuysontiktok</t>
+          <t>https://www.tiktok.com/@raeganfurness</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sammummyconqueringanxiet</t>
+          <t>themelfords</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1948,24 +1948,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-09-29 14:37:03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sammummyconqueringanxiet</t>
+          <t>https://www.tiktok.com/@themelfords</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>smoothshelly</t>
+          <t>itsnlightning</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1975,39 +1975,39 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>250K-500K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-06 12:38:02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@smoothshelly</t>
+          <t>https://www.tiktok.com/@itsnlightning</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sh28.eat.with.me</t>
+          <t>funmumshops</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2017,39 +2017,39 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>100K-250K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-01 10:47:02</t>
+          <t>2026-09-28 10:19:02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sh28.eat.with.me</t>
+          <t>https://www.tiktok.com/@funmumshops</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>amanmegbu</t>
+          <t>viralbuysontiktok</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2074,24 +2074,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:03</t>
+          <t>2026-09-28 10:13:03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amanmegbu</t>
+          <t>https://www.tiktok.com/@viralbuysontiktok</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>builtfindsuk</t>
+          <t>rad_dads_shop</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2116,24 +2116,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-01 10:47:03</t>
+          <t>2026-10-06 11:05:03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@builtfindsuk</t>
+          <t>https://www.tiktok.com/@rad_dads_shop</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>andreeamaria1828</t>
+          <t>sammummyconqueringanxiet</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2141,37 +2141,41 @@
           <t>£1K-£5K</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:02</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@andreeamaria1828</t>
+          <t>https://www.tiktok.com/@sammummyconqueringanxiet</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sarahs.worldx</t>
+          <t>smoothshelly</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2181,7 +2185,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>250K-500K</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2196,7 +2200,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:02</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2206,14 +2210,14 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahs.worldx</t>
+          <t>https://www.tiktok.com/@smoothshelly</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>_unique_kashmiri_</t>
+          <t>sh28.eat.with.me</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2223,44 +2227,44 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>25K-50K</t>
+          <t>100K-250K</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-29 10:25:02</t>
+          <t>2026-10-01 10:47:02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_unique_kashmiri_</t>
+          <t>https://www.tiktok.com/@sh28.eat.with.me</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>chek_mi_shocase</t>
+          <t>amanmegbu</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2275,118 +2279,114 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-22 17:56:02</t>
+          <t>2026-09-29 14:41:03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chek_mi_shocase</t>
+          <t>https://www.tiktok.com/@amanmegbu</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>moodymarbsandshadow</t>
+          <t>builtfindsuk</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-01 10:47:02</t>
+          <t>2026-10-01 10:47:03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@moodymarbsandshadow</t>
+          <t>https://www.tiktok.com/@builtfindsuk</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>mariatincuta11</t>
+          <t>andreeamaria1828</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>10K-25K</t>
-        </is>
-      </c>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-09-30 14:57:02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mariatincuta11</t>
+          <t>https://www.tiktok.com/@andreeamaria1828</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hulubasul</t>
+          <t>shopwithrani05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2401,81 +2401,81 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:02</t>
+          <t>2026-10-06 12:29:02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hulubasul</t>
+          <t>https://www.tiktok.com/@shopwithrani05</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>latina_shops</t>
+          <t>david_chillzy</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:06</t>
+          <t>2026-10-06 11:05:02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@latina_shops</t>
+          <t>https://www.tiktok.com/@david_chillzy</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>shopwithdanz0</t>
+          <t>sarahs.worldx</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2490,66 +2490,66 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:03</t>
+          <t>2026-09-30 14:57:02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shopwithdanz0</t>
+          <t>https://www.tiktok.com/@sarahs.worldx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fittokfinds88</t>
+          <t>_unique_kashmiri_</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-23 16:18:03</t>
+          <t>2026-09-29 10:25:02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fittokfinds88</t>
+          <t>https://www.tiktok.com/@_unique_kashmiri_</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>hinamalik0611</t>
+          <t>chek_mi_shocase</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2574,24 +2574,24 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-28 10:19:03</t>
+          <t>2026-09-22 17:56:02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hinamalik0611</t>
+          <t>https://www.tiktok.com/@chek_mi_shocase</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>hazels_open_diary</t>
+          <t>moodymarbsandshadow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2616,24 +2616,24 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-01 10:47:02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hazels_open_diary</t>
+          <t>https://www.tiktok.com/@moodymarbsandshadow</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>demyrobbo01</t>
+          <t>mariatincuta11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2643,39 +2643,39 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:03</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@demyrobbo01</t>
+          <t>https://www.tiktok.com/@mariatincuta11</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>xx_jessl_xx</t>
+          <t>hulubasul</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2700,24 +2700,24 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-01 11:04:02</t>
+          <t>2026-09-30 14:57:02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@xx_jessl_xx</t>
+          <t>https://www.tiktok.com/@hulubasul</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>toryannaxo</t>
+          <t>latina_shops</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-29 14:44:02</t>
+          <t>2026-09-30 14:56:06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2752,14 +2752,14 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@toryannaxo</t>
+          <t>https://www.tiktok.com/@latina_shops</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>miss_quenny1</t>
+          <t>shopwithdanz0</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2784,24 +2784,24 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-30 14:57:03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@miss_quenny1</t>
+          <t>https://www.tiktok.com/@shopwithdanz0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>abdulawwal470</t>
+          <t>e_jeh</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2811,39 +2811,39 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-30 14:57:03</t>
+          <t>2026-10-06 12:40:02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@abdulawwal470</t>
+          <t>https://www.tiktok.com/@e_jeh</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>jones23350</t>
+          <t>fittokfinds88</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2868,24 +2868,24 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:04</t>
+          <t>2026-09-23 16:18:03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jones23350</t>
+          <t>https://www.tiktok.com/@fittokfinds88</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>smartfindsuk1</t>
+          <t>hinamalik0611</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2895,39 +2895,39 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-28 10:19:03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@smartfindsuk1</t>
+          <t>https://www.tiktok.com/@hinamalik0611</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>janet.osayande</t>
+          <t>hazels_open_diary</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2952,24 +2952,24 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:02</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@janet.osayande</t>
+          <t>https://www.tiktok.com/@hazels_open_diary</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>tiadinamakeup</t>
+          <t>shamsa2666</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2979,96 +2979,96 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:02</t>
+          <t>2026-10-06 16:32:02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiadinamakeup</t>
+          <t>https://www.tiktok.com/@shamsa2666</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>carfoon767</t>
+          <t>laceyreviewss</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>50K-100K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-06 12:51:02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@carfoon767</t>
+          <t>https://www.tiktok.com/@laceyreviewss</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>nomzy.gladys</t>
+          <t>princess.j2449</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3078,29 +3078,29 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-25 10:26:03</t>
+          <t>2026-10-06 12:40:03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nomzy.gladys</t>
+          <t>https://www.tiktok.com/@princess.j2449</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>angiereviewslife</t>
+          <t>xx_jessl_xx</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3120,29 +3120,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-01 11:04:03</t>
+          <t>2026-10-01 11:04:02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angiereviewslife</t>
+          <t>https://www.tiktok.com/@xx_jessl_xx</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kimmys_kitchen_garden</t>
+          <t>annakonarska86</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3152,39 +3152,39 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-06 12:51:02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kimmys_kitchen_garden</t>
+          <t>https://www.tiktok.com/@annakonarska86</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>mycontemporarylifeinuk</t>
+          <t>toryannaxo</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3204,39 +3204,39 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-01 14:55:02</t>
+          <t>2026-09-29 14:44:02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mycontemporarylifeinuk</t>
+          <t>https://www.tiktok.com/@toryannaxo</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>itsjulesmurph</t>
+          <t>miss_quenny1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3246,34 +3246,34 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:05</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@itsjulesmurph</t>
+          <t>https://www.tiktok.com/@miss_quenny1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kerrycavan</t>
+          <t>abdulawwal470</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3288,123 +3288,123 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-09-30 14:57:03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kerrycavan</t>
+          <t>https://www.tiktok.com/@abdulawwal470</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>sue_never_ending_journey</t>
+          <t>jones23350</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-01 10:52:06</t>
+          <t>2026-10-01 10:52:04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sue_never_ending_journey</t>
+          <t>https://www.tiktok.com/@jones23350</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>jodijudejj</t>
+          <t>louisesoutar44</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-01 11:14:02</t>
+          <t>2026-10-06 12:41:03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jodijudejj</t>
+          <t>https://www.tiktok.com/@louisesoutar44</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>andreeatts</t>
+          <t>smartfindsuk1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:05</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3424,19 +3424,19 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@andreeatts</t>
+          <t>https://www.tiktok.com/@smartfindsuk1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>uk.life.moments</t>
+          <t>janet.osayande</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3456,29 +3456,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:06</t>
+          <t>2026-10-04 18:25:02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uk.life.moments</t>
+          <t>https://www.tiktok.com/@janet.osayande</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>shannonlou8991</t>
+          <t>tiadinamakeup</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3498,39 +3498,39 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:05</t>
+          <t>2026-09-29 14:41:02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shannonlou8991</t>
+          <t>https://www.tiktok.com/@tiadinamakeup</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>tonirooney19</t>
+          <t>bloomwithin7</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>0-1K</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-05 23:00:07</t>
+          <t>2026-10-06 12:40:02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3550,24 +3550,24 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tonirooney19</t>
+          <t>https://www.tiktok.com/@bloomwithin7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>sarahwulatarawa</t>
+          <t>carfoon767</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3577,40 +3577,44 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-10-02 06:49:42</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahwulatarawa</t>
+          <t>https://www.tiktok.com/@carfoon767</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>crestworld.cooks</t>
+          <t>nomzy.gladys</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3620,73 +3624,81 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-27 08:26:05</t>
+          <t>2026-09-25 10:26:03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@crestworld.cooks</t>
+          <t>https://www.tiktok.com/@nomzy.gladys</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>dillytwinmum</t>
+          <t>angiereviewslife</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-21 09:55:02</t>
+          <t>2026-10-01 11:04:03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dillytwinmum</t>
+          <t>https://www.tiktok.com/@angiereviewslife</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>adeede1</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
+          <t>taye_tiktokreviews</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3696,65 +3708,81 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-03 06:37:25</t>
+          <t>2026-10-06 16:34:02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adeede1</t>
+          <t>https://www.tiktok.com/@taye_tiktokreviews</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>armaan.ahmed37</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
+          <t>foxcosplayz</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-03 19:49:39</t>
+          <t>2026-10-06 12:51:02</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@armaan.ahmed37</t>
+          <t>https://www.tiktok.com/@foxcosplayz</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>amena.akter3665</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
+          <t>anitawhitwam</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3764,29 +3792,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-28 12:23:28</t>
+          <t>2026-10-06 12:44:02</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amena.akter3665</t>
+          <t>https://www.tiktok.com/@anitawhitwam</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>amap000</t>
+          <t>kimmys_kitchen_garden</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3801,36 +3829,44 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-03 10:59:49</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@amap000</t>
+          <t>https://www.tiktok.com/@kimmys_kitchen_garden</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>angelhairstylist1</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
+          <t>mycontemporarylifeinuk</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3840,65 +3876,81 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-04 20:43:03</t>
+          <t>2026-10-01 14:55:02</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@angelhairstylist1</t>
+          <t>https://www.tiktok.com/@mycontemporarylifeinuk</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>aminajeylani</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
+          <t>itsjulesmurph</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-23 14:42:07</t>
+          <t>2026-10-01 10:52:05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aminajeylani</t>
+          <t>https://www.tiktok.com/@itsjulesmurph</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>bukky.yoyo</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
+          <t>rosiewilkinson957</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3908,28 +3960,36 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-10-04 16:50:32</t>
+          <t>2026-10-06 12:51:02</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bukky.yoyo</t>
+          <t>https://www.tiktok.com/@rosiewilkinson957</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>babbyzozo</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
+          <t>stephb2.0</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -3942,31 +4002,39 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-28 18:28:13</t>
+          <t>2026-10-06 12:38:03</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@babbyzozo</t>
+          <t>https://www.tiktok.com/@stephb2.0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>balletdeo</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
+          <t>anna.pen5</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3976,73 +4044,81 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-26 01:45:10</t>
+          <t>2026-10-06 12:51:02</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@balletdeo</t>
+          <t>https://www.tiktok.com/@anna.pen5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>_dosah</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
+          <t>itsyagirllyds00</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-21 14:58:25</t>
+          <t>2026-10-06 12:44:03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_dosah</t>
+          <t>https://www.tiktok.com/@itsyagirllyds00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>_mohlad</t>
+          <t>rubikhan00000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>0-1K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4052,269 +4128,333 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-04 18:10:30</t>
+          <t>2026-10-06 12:40:02</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@_mohlad</t>
+          <t>https://www.tiktok.com/@rubikhan00000</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>gbm.sees</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
+          <t>kerrycavan</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-10-01 09:00:38</t>
+          <t>2026-10-01 10:48:02</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gbm.sees</t>
+          <t>https://www.tiktok.com/@kerrycavan</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>fmrasalhossain</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
+          <t>sue_never_ending_journey</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-25 22:32:12</t>
+          <t>2026-10-01 10:52:06</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fmrasalhossain</t>
+          <t>https://www.tiktok.com/@sue_never_ending_journey</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>fellykemmy3</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
+          <t>aizakhan9838</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-24 20:39:00</t>
+          <t>2026-10-06 12:38:03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fellykemmy3</t>
+          <t>https://www.tiktok.com/@aizakhan9838</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>fkprima123</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
+          <t>jodijudejj</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-26 17:32:35</t>
+          <t>2026-10-01 11:14:02</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fkprima123</t>
+          <t>https://www.tiktok.com/@jodijudejj</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>explore.with.em4</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
+          <t>amandanascimentoo09</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-10-01 14:44:03</t>
+          <t>2026-10-06 12:38:03</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@explore.with.em4</t>
+          <t>https://www.tiktok.com/@amandanascimentoo09</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>explorewithmex10</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
+          <t>andreeatts</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-10-02 09:06:56</t>
+          <t>2026-09-30 14:56:05</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@explorewithmex10</t>
+          <t>https://www.tiktok.com/@andreeatts</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>f.chowdhury15</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
+          <t>uk.life.moments</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-29 23:20:53</t>
+          <t>2026-10-01 10:50:06</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@f.chowdhury15</t>
+          <t>https://www.tiktok.com/@uk.life.moments</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>fahmidaislam2120</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
+          <t>shannonlou8991</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>£100-£200</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4324,28 +4464,36 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-23 15:26:11</t>
+          <t>2026-10-01 10:50:05</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fahmidaislam2120</t>
+          <t>https://www.tiktok.com/@shannonlou8991</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>duaanoor080120</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
+          <t>tonirooney19</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>Ashwagandha Coffee</t>
@@ -4358,31 +4506,39 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-10-02 06:26:32</t>
+          <t>2026-10-05 23:00:07</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@duaanoor080120</t>
+          <t>https://www.tiktok.com/@tonirooney19</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>egooyibo41</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr"/>
+          <t>sarahwulatarawa</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4392,27 +4548,31 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-10-05 13:55:48</t>
+          <t>2026-10-02 06:49:42</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@egooyibo41</t>
+          <t>https://www.tiktok.com/@sarahwulatarawa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>dsda0786</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+          <t>crestworld.cooks</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
@@ -4426,31 +4586,31 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-29 09:46:30</t>
+          <t>2026-09-27 08:26:05</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dsda0786</t>
+          <t>https://www.tiktok.com/@crestworld.cooks</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>damsel755</t>
+          <t>ilzb7</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4460,24 +4620,24 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-10-05 20:02:55</t>
+          <t>2026-10-05 16:59:43</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@damsel755</t>
+          <t>https://www.tiktok.com/@ilzb7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>desylviaa1</t>
+          <t>isinfaye456</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4494,99 +4654,107 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-27 10:40:10</t>
+          <t>2026-10-06 14:00:36</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@desylviaa1</t>
+          <t>https://www.tiktok.com/@isinfaye456</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>dearlola45</t>
+          <t>dimpleddp</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-01 11:28:54</t>
+          <t>2026-09-25 12:30:06</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dearlola45</t>
+          <t>https://www.tiktok.com/@dimpleddp</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>dimpleddp</t>
+          <t>damsel755</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-25 12:30:06</t>
+          <t>2026-10-05 20:02:55</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dimpleddp</t>
+          <t>https://www.tiktok.com/@damsel755</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>dinexheese</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
+          <t>amap000</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4596,99 +4764,99 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-26 12:16:35</t>
+          <t>2026-10-03 10:59:49</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dinexheese</t>
+          <t>https://www.tiktok.com/@amap000</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>climax.scenes</t>
+          <t>amena.akter3665</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-21 06:20:00</t>
+          <t>2026-09-28 12:23:28</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@climax.scenes</t>
+          <t>https://www.tiktok.com/@amena.akter3665</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>charliegirl860</t>
+          <t>aminajeylani</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-26 10:54:39</t>
+          <t>2026-09-23 14:42:07</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@charliegirl860</t>
+          <t>https://www.tiktok.com/@aminajeylani</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>chezzy954</t>
+          <t>adeede1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4698,28 +4866,36 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-25 13:21:47</t>
+          <t>2026-10-03 06:37:25</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chezzy954</t>
+          <t>https://www.tiktok.com/@adeede1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kulwinderrani5</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
+          <t>_mohlad</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -4732,24 +4908,24 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-10-05 09:00:08</t>
+          <t>2026-10-04 18:10:30</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kulwinderrani5</t>
+          <t>https://www.tiktok.com/@_mohlad</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kaz.gym82</t>
+          <t>idrissasesay7</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4761,36 +4937,36 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-10-05 08:29:56</t>
+          <t>2026-10-02 23:30:18</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kaz.gym82</t>
+          <t>https://www.tiktok.com/@idrissasesay7</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>juliana_armoh</t>
+          <t>hu123342425</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4800,24 +4976,24 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-10-01 21:22:31</t>
+          <t>2026-10-04 15:47:04</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@juliana_armoh</t>
+          <t>https://www.tiktok.com/@hu123342425</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kennyshekoni</t>
+          <t>homemadefood2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4834,92 +5010,92 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-10-01 19:41:15</t>
+          <t>2026-09-23 16:44:22</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@kennyshekoni</t>
+          <t>https://www.tiktok.com/@homemadefood2024</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>jem17363</t>
+          <t>hair.vendor.in.uk</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-21 17:28:16</t>
+          <t>2026-10-06 19:19:06</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jem17363</t>
+          <t>https://www.tiktok.com/@hair.vendor.in.uk</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>lifeofhamzaa</t>
+          <t>dsda0786</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-10-04 18:28:02</t>
+          <t>2026-09-29 09:46:30</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lifeofhamzaa</t>
+          <t>https://www.tiktok.com/@dsda0786</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>laurywilliams</t>
+          <t>duaanoor080120</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4931,29 +5107,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-26 16:59:35</t>
+          <t>2026-10-02 06:26:32</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@laurywilliams</t>
+          <t>https://www.tiktok.com/@duaanoor080120</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>knicksmakeuppro</t>
+          <t>f.chowdhury15</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4970,24 +5146,24 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-10-01 11:30:23</t>
+          <t>2026-09-29 23:20:53</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@knicksmakeuppro</t>
+          <t>https://www.tiktok.com/@f.chowdhury15</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ilzb7</t>
+          <t>explorewithmex10</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4999,63 +5175,63 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-10-05 16:59:43</t>
+          <t>2026-10-02 09:06:56</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ilzb7</t>
+          <t>https://www.tiktok.com/@explorewithmex10</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>hu123342425</t>
+          <t>explore.with.em4</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-10-04 15:47:04</t>
+          <t>2026-10-01 14:44:03</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hu123342425</t>
+          <t>https://www.tiktok.com/@explore.with.em4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>homemadefood2024</t>
+          <t>egooyibo41</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -5067,29 +5243,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-23 16:44:22</t>
+          <t>2026-10-05 13:55:48</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@homemadefood2024</t>
+          <t>https://www.tiktok.com/@egooyibo41</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>idrissasesay7</t>
+          <t>fellykemmy3</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -5106,31 +5282,31 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-10-02 23:30:18</t>
+          <t>2026-09-24 20:39:00</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@idrissasesay7</t>
+          <t>https://www.tiktok.com/@fellykemmy3</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>jean.makin</t>
+          <t>fahmidaislam2120</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5140,31 +5316,31 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-10-03 14:41:36</t>
+          <t>2026-09-23 15:26:11</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jean.makin</t>
+          <t>https://www.tiktok.com/@fahmidaislam2120</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>paul.d.awson</t>
+          <t>fkprima123</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5174,24 +5350,24 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-26 18:18:04</t>
+          <t>2026-09-26 17:32:35</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@paul.d.awson</t>
+          <t>https://www.tiktok.com/@fkprima123</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>patriciaappiah280</t>
+          <t>fmrasalhossain</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -5208,31 +5384,31 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-23 10:08:56</t>
+          <t>2026-09-25 22:32:12</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@patriciaappiah280</t>
+          <t>https://www.tiktok.com/@fmrasalhossain</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>onos282</t>
+          <t>dinexheese</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5242,31 +5418,31 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-10-04 23:21:40</t>
+          <t>2026-09-26 12:16:35</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@onos282</t>
+          <t>https://www.tiktok.com/@dinexheese</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>oluyewi</t>
+          <t>charliegirl860</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5276,24 +5452,24 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-10-03 19:19:51</t>
+          <t>2026-09-26 10:54:39</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluyewi</t>
+          <t>https://www.tiktok.com/@charliegirl860</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>oluwatoyin0322</t>
+          <t>bukky.yoyo</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5305,33 +5481,41 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-28 23:38:06</t>
+          <t>2026-10-04 16:50:32</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@oluwatoyin0322</t>
+          <t>https://www.tiktok.com/@bukky.yoyo</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ola.oluwatoyin.ad</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr"/>
+          <t>chommy.comfort101</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>5K-10K</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -5344,24 +5528,24 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-25 13:50:20</t>
+          <t>2026-10-06 00:16:02</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ola.oluwatoyin.ad</t>
+          <t>https://www.tiktok.com/@chommy.comfort101</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>nonochou12</t>
+          <t>babbyzozo</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5378,58 +5562,58 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-28 00:42:49</t>
+          <t>2026-09-28 18:28:13</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nonochou12</t>
+          <t>https://www.tiktok.com/@babbyzozo</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>nevertoooldnanaxx</t>
+          <t>balletdeo</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-09-26 01:45:10</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nevertoooldnanaxx</t>
+          <t>https://www.tiktok.com/@balletdeo</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>mrm.foods.opeyemi</t>
+          <t>angelhairstylist1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5446,24 +5630,24 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-10-04 20:07:11</t>
+          <t>2026-10-04 20:43:03</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mrm.foods.opeyemi</t>
+          <t>https://www.tiktok.com/@angelhairstylist1</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>naveed19.88</t>
+          <t>armaan.ahmed37</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5475,36 +5659,36 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-25 22:46:15</t>
+          <t>2026-10-03 19:49:39</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@naveed19.88</t>
+          <t>https://www.tiktok.com/@armaan.ahmed37</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>n.raja83</t>
+          <t>chezzy954</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5514,58 +5698,58 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-29 10:14:04</t>
+          <t>2026-09-25 13:21:47</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@n.raja83</t>
+          <t>https://www.tiktok.com/@chezzy954</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>munasheish</t>
+          <t>dearlola45</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-25 10:27:59</t>
+          <t>2026-10-01 11:28:54</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@munasheish</t>
+          <t>https://www.tiktok.com/@dearlola45</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>mum3tees</t>
+          <t>desylviaa1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5582,7 +5766,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-26 15:28:17</t>
+          <t>2026-09-27 10:40:10</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5592,48 +5776,48 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mum3tees</t>
+          <t>https://www.tiktok.com/@desylviaa1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>mayma3747</t>
+          <t>lissssaxxx</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-26 15:22:17</t>
+          <t>2026-09-23 08:17:25</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mayma3747</t>
+          <t>https://www.tiktok.com/@lissssaxxx</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>maxi_berrie</t>
+          <t>manvinder318</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5650,31 +5834,31 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-22 23:20:40</t>
+          <t>2026-09-25 14:14:56</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maxi_berrie</t>
+          <t>https://www.tiktok.com/@manvinder318</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>mr.liverpool885</t>
+          <t>lovecats7112</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5684,24 +5868,24 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-04 09:00:20</t>
+          <t>2026-09-26 19:59:48</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mr.liverpool885</t>
+          <t>https://www.tiktok.com/@lovecats7112</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>lissssaxxx</t>
+          <t>knicksmakeuppro</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5718,24 +5902,24 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-09-23 08:17:25</t>
+          <t>2026-10-01 11:30:23</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lissssaxxx</t>
+          <t>https://www.tiktok.com/@knicksmakeuppro</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>lindaefionayi</t>
+          <t>kennyshekoni</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5752,65 +5936,65 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-09-23 20:46:33</t>
+          <t>2026-10-01 19:41:15</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lindaefionayi</t>
+          <t>https://www.tiktok.com/@kennyshekoni</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>m.3384</t>
+          <t>rabbit_pm12</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-09-21 10:22:24</t>
+          <t>2026-09-25 19:17:46</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@m.3384</t>
+          <t>https://www.tiktok.com/@rabbit_pm12</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>merz3859</t>
+          <t>paul.d.awson</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5820,75 +6004,75 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-09-22 21:09:48</t>
+          <t>2026-09-26 18:18:04</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@merz3859</t>
+          <t>https://www.tiktok.com/@paul.d.awson</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>lovecats7112</t>
+          <t>princessanna1738</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-09-26 19:59:48</t>
+          <t>2026-09-25 07:04:05</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lovecats7112</t>
+          <t>https://www.tiktok.com/@princessanna1738</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>lolaclothier</t>
+          <t>queenbabe_78</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-10-01 20:17:12</t>
+          <t>2026-10-02 15:22:41</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5898,14 +6082,14 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lolaclothier</t>
+          <t>https://www.tiktok.com/@queenbabe_78</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>manvinder318</t>
+          <t>oluwatoyin0322</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5922,31 +6106,31 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-25 14:14:56</t>
+          <t>2026-09-28 23:38:06</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@manvinder318</t>
+          <t>https://www.tiktok.com/@oluwatoyin0322</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>jadepa90</t>
+          <t>oluyewi</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5956,31 +6140,31 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-09-26 09:09:09</t>
+          <t>2026-10-03 19:19:51</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@jadepa90</t>
+          <t>https://www.tiktok.com/@oluyewi</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>sarahswhimsyfits</t>
+          <t>onos282</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5990,24 +6174,24 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:06</t>
+          <t>2026-10-04 23:21:40</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sarahswhimsyfits</t>
+          <t>https://www.tiktok.com/@onos282</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>rtamakter</t>
+          <t>patriciaappiah280</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -6024,24 +6208,24 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-10-05 22:45:22</t>
+          <t>2026-09-23 10:08:56</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rtamakter</t>
+          <t>https://www.tiktok.com/@patriciaappiah280</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ruas_dream</t>
+          <t>ola.oluwatoyin.ad</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -6058,24 +6242,24 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-27 11:00:34</t>
+          <t>2026-09-25 13:50:20</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ruas_dream</t>
+          <t>https://www.tiktok.com/@ola.oluwatoyin.ad</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>samiahajam</t>
+          <t>nonochou12</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -6092,58 +6276,58 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-09-25 10:39:07</t>
+          <t>2026-09-28 00:42:49</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samiahajam</t>
+          <t>https://www.tiktok.com/@nonochou12</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>radhekrishna_11</t>
+          <t>nevertoooldnanaxx</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-21 11:21:47</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@radhekrishna_11</t>
+          <t>https://www.tiktok.com/@nevertoooldnanaxx</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>rabbit_pm12</t>
+          <t>mrm.foods.opeyemi</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -6155,29 +6339,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-09-25 19:17:46</t>
+          <t>2026-10-04 20:07:11</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rabbit_pm12</t>
+          <t>https://www.tiktok.com/@mrm.foods.opeyemi</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>reykkhan</t>
+          <t>munasheish</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -6194,24 +6378,24 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-25 17:53:08</t>
+          <t>2026-09-25 10:27:59</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@reykkhan</t>
+          <t>https://www.tiktok.com/@munasheish</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>riderrrr70</t>
+          <t>mum3tees</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -6228,58 +6412,58 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-09-27 14:15:10</t>
+          <t>2026-09-26 15:28:17</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@riderrrr70</t>
+          <t>https://www.tiktok.com/@mum3tees</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>sidkam58</t>
+          <t>n.raja83</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-10-01 07:57:16</t>
+          <t>2026-09-29 10:14:04</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sidkam58</t>
+          <t>https://www.tiktok.com/@n.raja83</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>shukar7860</t>
+          <t>naveed19.88</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -6296,24 +6480,24 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-09-22 09:29:34</t>
+          <t>2026-09-25 22:46:15</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shukar7860</t>
+          <t>https://www.tiktok.com/@naveed19.88</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>shazia11235</t>
+          <t>merz3859</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -6330,58 +6514,58 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-09-24 23:21:59</t>
+          <t>2026-09-22 21:09:48</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shazia11235</t>
+          <t>https://www.tiktok.com/@merz3859</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>shareenyousaf</t>
+          <t>mayma3747</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-09-29 10:13:11</t>
+          <t>2026-09-26 15:22:17</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shareenyousaf</t>
+          <t>https://www.tiktok.com/@mayma3747</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>seyiedeliciouscocktails</t>
+          <t>maxi_berrie</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -6398,31 +6582,31 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-09-25 06:38:51</t>
+          <t>2026-09-22 23:20:40</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@seyiedeliciouscocktails</t>
+          <t>https://www.tiktok.com/@maxi_berrie</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>sbegum.79</t>
+          <t>mr.liverpool885</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6432,24 +6616,24 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-09-21 17:38:25</t>
+          <t>2026-10-04 09:00:20</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sbegum.79</t>
+          <t>https://www.tiktok.com/@mr.liverpool885</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>princessanna1738</t>
+          <t>jean.makin</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -6461,97 +6645,97 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-09-25 07:04:05</t>
+          <t>2026-10-03 14:41:36</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@princessanna1738</t>
+          <t>https://www.tiktok.com/@jean.makin</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>queenbabe_78</t>
+          <t>jadepa90</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-10-02 15:22:41</t>
+          <t>2026-09-26 09:09:09</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@queenbabe_78</t>
+          <t>https://www.tiktok.com/@jadepa90</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>theweebelfastman</t>
+          <t>kaz.gym82</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-10-01 10:48:02</t>
+          <t>2026-10-05 08:29:56</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@theweebelfastman</t>
+          <t>https://www.tiktok.com/@kaz.gym82</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>taiwooluyemitaiwo</t>
+          <t>juliana_armoh</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -6568,24 +6752,24 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-09-23 16:28:21</t>
+          <t>2026-10-01 21:22:31</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@taiwooluyemitaiwo</t>
+          <t>https://www.tiktok.com/@juliana_armoh</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>teeyworld_confectionery</t>
+          <t>lindaefionayi</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -6602,31 +6786,31 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-09-25 19:30:28</t>
+          <t>2026-09-23 20:46:33</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@teeyworld_confectionery</t>
+          <t>https://www.tiktok.com/@lindaefionayi</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>tkmama45</t>
+          <t>lifeofhamzaa</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6636,31 +6820,31 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-10-05 07:34:14</t>
+          <t>2026-10-04 18:28:02</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tkmama45</t>
+          <t>https://www.tiktok.com/@lifeofhamzaa</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>tinku78616</t>
+          <t>laurywilliams</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6670,7 +6854,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-25 17:21:23</t>
+          <t>2026-09-26 16:59:35</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -6680,14 +6864,14 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tinku78616</t>
+          <t>https://www.tiktok.com/@laurywilliams</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>triciaebun</t>
+          <t>kulwinderrani5</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -6699,70 +6883,70 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-09-25 16:57:55</t>
+          <t>2026-10-05 09:00:08</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@triciaebun</t>
+          <t>https://www.tiktok.com/@kulwinderrani5</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>theloyalsoul1</t>
+          <t>lolaclothier</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-09-28 20:53:18</t>
+          <t>2026-10-01 20:17:12</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@theloyalsoul1</t>
+          <t>https://www.tiktok.com/@lolaclothier</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>suziefenton</t>
+          <t>riderrrr70</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6772,24 +6956,24 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-09-23 10:47:02</t>
+          <t>2026-09-27 14:15:10</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@suziefenton</t>
+          <t>https://www.tiktok.com/@riderrrr70</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>user2182373993526</t>
+          <t>rtamakter</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -6806,36 +6990,28 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-09-21 12:26:17</t>
+          <t>2026-10-05 22:45:22</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2182373993526</t>
+          <t>https://www.tiktok.com/@rtamakter</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>tyanie1703</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
+          <t>ruas_dream</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>Green Burner</t>
@@ -6848,65 +7024,65 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-09-22 14:51:38</t>
+          <t>2026-09-27 11:00:34</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tyanie1703</t>
+          <t>https://www.tiktok.com/@ruas_dream</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>user2773140226152</t>
+          <t>taiwooluyemitaiwo</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-09-21 20:00:10</t>
+          <t>2026-09-23 16:28:21</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user2773140226152</t>
+          <t>https://www.tiktok.com/@taiwooluyemitaiwo</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>user35110093</t>
+          <t>suziefenton</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6916,58 +7092,58 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-09-28 20:20:27</t>
+          <t>2026-09-23 10:47:02</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user35110093</t>
+          <t>https://www.tiktok.com/@suziefenton</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>user8258556352859</t>
+          <t>sidkam58</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-10-03 10:13:16</t>
+          <t>2026-10-01 07:57:16</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user8258556352859</t>
+          <t>https://www.tiktok.com/@sidkam58</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>user9310370027124</t>
+          <t>shukar7860</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -6984,24 +7160,24 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-10-01 19:05:18</t>
+          <t>2026-09-22 09:29:34</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user9310370027124</t>
+          <t>https://www.tiktok.com/@shukar7860</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>user3998147688485</t>
+          <t>shazia11235</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -7018,24 +7194,24 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-09-29 09:40:30</t>
+          <t>2026-09-24 23:21:59</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user3998147688485</t>
+          <t>https://www.tiktok.com/@shazia11235</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>user6931802591156</t>
+          <t>shareenyousaf</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -7052,31 +7228,31 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-10-01 16:26:50</t>
+          <t>2026-09-29 10:13:11</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user6931802591156</t>
+          <t>https://www.tiktok.com/@shareenyousaf</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>user_78602223</t>
+          <t>sarahswhimsyfits</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -7086,24 +7262,24 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-09-22 17:40:46</t>
+          <t>2026-10-01 10:50:06</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user_78602223</t>
+          <t>https://www.tiktok.com/@sarahswhimsyfits</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>user99851967341610</t>
+          <t>seyiedeliciouscocktails</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -7120,126 +7296,126 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-09-28 16:59:33</t>
+          <t>2026-09-25 06:38:51</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@user99851967341610</t>
+          <t>https://www.tiktok.com/@seyiedeliciouscocktails</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>waboti</t>
+          <t>reykkhan</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-10-01 18:00:40</t>
+          <t>2026-09-25 17:53:08</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@waboti</t>
+          <t>https://www.tiktok.com/@reykkhan</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>veeover40</t>
+          <t>samiahajam</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:04</t>
+          <t>2026-09-25 10:39:07</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@veeover40</t>
+          <t>https://www.tiktok.com/@samiahajam</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>www.tiktokhafsaqueen169</t>
+          <t>tinae38</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-09-29 14:46:03</t>
+          <t>2026-10-06 12:40:02</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@www.tiktokhafsaqueen169</t>
+          <t>https://www.tiktok.com/@tinae38</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>yeterecipe</t>
+          <t>tkmama45</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -7251,29 +7427,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-10-02 16:32:43</t>
+          <t>2026-10-05 07:34:14</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@yeterecipe</t>
+          <t>https://www.tiktok.com/@tkmama45</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>zainyzee39</t>
+          <t>tinku78616</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -7285,29 +7461,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-10-04 10:59:50</t>
+          <t>2026-09-25 17:21:23</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@zainyzee39</t>
+          <t>https://www.tiktok.com/@tinku78616</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>zara1508ahmed</t>
+          <t>teeyworld_confectionery</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -7324,15 +7500,635 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
+          <t>2026-09-25 19:30:28</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@teeyworld_confectionery</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>theloyalsoul1</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-09-28 20:53:18</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theloyalsoul1</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>theweebelfastman</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Hibiscus</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:48:02</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theweebelfastman</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>tyanie1703</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>£0-£50</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:51:38</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tyanie1703</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>triciaebun</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-09-25 16:57:55</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@triciaebun</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>traceyvernon8</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Moringa Capsules By</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Free sample from seller</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:44:02</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@traceyvernon8</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>user35110093</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-09-28 20:20:27</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user35110093</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>user8258556352859</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:13:16</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user8258556352859</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>user9310370027124</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-10-01 19:05:18</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user9310370027124</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>user3998147688485</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:40:30</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user3998147688485</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>user6931802591156</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:26:50</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user6931802591156</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>user_78602223</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Ashwagandha Coffee</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Free sample from seller</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:40:46</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user_78602223</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>user99851967341610</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-09-28 16:59:33</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@user99851967341610</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>waboti</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Ashwagandha Coffee</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Free sample from seller</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-10-01 18:00:40</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@waboti</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>veeover40</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>【GUT SHIFT】Daily Fiber Psyllium</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Free sample from seller</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:50:04</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@veeover40</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>www.tiktokhafsaqueen169</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Ashwagandha Coffee</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:46:03</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@www.tiktokhafsaqueen169</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>yeterecipe</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:32:43</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@yeterecipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>zainyzee39</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Free sample from seller</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-10-04 10:59:50</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@zainyzee39</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>zara1508ahmed</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Green Burner</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Free sample from TikTok Shop (FBT)</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
           <t>2026-09-23 03:28:52</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@zara1508ahmed</t>
         </is>

--- a/chase_list.xlsx
+++ b/chase_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H203"/>
+  <dimension ref="A1:H210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>flash_finds1</t>
+          <t>victoriaafindss</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -681,39 +681,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>25K-50K</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-27 13:35:02</t>
+          <t>2026-10-07 18:18:41</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@flash_finds1</t>
+          <t>https://www.tiktok.com/@victoriaafindss</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>holliedolli94shopsugc0</t>
+          <t>fashion.by.rachel</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -723,44 +723,44 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-29 14:37:02</t>
+          <t>2026-10-07 11:53:03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@holliedolli94shopsugc0</t>
+          <t>https://www.tiktok.com/@fashion.by.rachel</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>azlanzaynahzayrahuk</t>
+          <t>flash_finds1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -770,76 +770,76 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-28 10:10:05</t>
+          <t>2026-09-27 13:35:02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@azlanzaynahzayrahuk</t>
+          <t>https://www.tiktok.com/@flash_finds1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>brookesbaddestfinds</t>
+          <t>holliedolli94shopsugc0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>10K-25K</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15:02</t>
+          <t>2026-09-29 14:37:02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@brookesbaddestfinds</t>
+          <t>https://www.tiktok.com/@holliedolli94shopsugc0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>samstrendingdeals</t>
+          <t>azlanzaynahzayrahuk</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -864,24 +864,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-26 17:38:02</t>
+          <t>2026-09-28 10:10:05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@samstrendingdeals</t>
+          <t>https://www.tiktok.com/@azlanzaynahzayrahuk</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>beauty_shine07</t>
+          <t>brookesbaddestfinds</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -906,29 +906,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-04 18:25:03</t>
+          <t>2026-10-06 11:15:02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beauty_shine07</t>
+          <t>https://www.tiktok.com/@brookesbaddestfinds</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mersoo712</t>
+          <t>samstrendingdeals</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -948,29 +948,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-24 12:56:04</t>
+          <t>2026-09-26 17:38:02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mersoo712</t>
+          <t>https://www.tiktok.com/@samstrendingdeals</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>shelleybelle26</t>
+          <t>beauty_shine07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -985,29 +985,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-30 14:56:03</t>
+          <t>2026-10-04 18:25:03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shelleybelle26</t>
+          <t>https://www.tiktok.com/@beauty_shine07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fairyfaryal11</t>
+          <t>mersoo712</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1032,24 +1032,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-24 20:07:02</t>
+          <t>2026-09-24 12:56:04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fairyfaryal11</t>
+          <t>https://www.tiktok.com/@mersoo712</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mummyzaraa</t>
+          <t>shelleybelle26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1059,39 +1059,39 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5K-10K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Free sample from TikTok Shop (FBT)</t>
+          <t>Free sample from seller</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-23 08:16:05</t>
+          <t>2026-09-30 14:56:03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mummyzaraa</t>
+          <t>https://www.tiktok.com/@shelleybelle26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>georgiaxx___</t>
+          <t>fairyfaryal11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>50K-100K</t>
+          <t>1K-5K</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1116,24 +1116,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-26 17:37:02</t>
+          <t>2026-09-24 20:07:02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@georgiaxx___</t>
+          <t>https://www.tiktok.com/@fairyfaryal11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>lisamercyjones</t>
+          <t>mummyzaraa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1148,34 +1148,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Free sample from seller</t>
+          <t>Free sample from TikTok Shop (FBT)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15:02</t>
+          <t>2026-09-23 08:16:05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lisamercyjones</t>
+          <t>https://www.tiktok.com/@mummyzaraa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tosinreviews</t>
+          <t>georgiaxx___</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1K-5K</t>
+          <t>50K-100K</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1200,24 +1200,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15:04</t>
+          <t>2026-09-26 17:37:02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tosinreviews</t>
+          <t>https://www.tiktok.com/@georgiaxx___</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>shannyt30</t>
+          <t>lisamercyjones</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ceremonial Matcha Powder</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1242,24 +1242,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-06 11:05:02</t>
+          <t>2026-10-06 11:15:02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@shannyt30</t>
+          <t>https://www.tiktok.com/@lisamercyjones</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jasminehagen3</t>
+          <t>tosinreviews</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1274,34 +1274,34 @@
 